--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2_final.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2_final.xlsx
@@ -21,8 +21,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Var_A_Agregovany_Dum'!$A$1:$G$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Var_A_Agregovany_Sklad'!$A$1:$G$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$118</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$188</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$189</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Var_F_URS_Verification_Trail'!$A$1:$H$14</definedName>
   </definedNames>
@@ -1009,11 +1009,11 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>HSV položkově (105 ks) + PSV/TZB/VRN agregovaně (12 skupin) = 117 řádků.</t>
+          <t>HSV položkově (106 ks) + PSV/TZB/VRN agregovaně (12 skupin) = 118 řádků.</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D24" s="10" t="n"/>
       <c r="E24" s="10" t="n"/>
@@ -1027,11 +1027,11 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Plný detail (187 dum + 28 sklad = 215 položek). Cílový rozsah pro produkční pricing.</t>
+          <t>Plný detail (188 dum + 28 sklad = 216 položek). Cílový rozsah pro produkční pricing.</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D25" s="10" t="n"/>
       <c r="E25" s="10" t="n"/>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>215 (187 dum + 28 sklad)</t>
+          <t>216 (188 dum + 28 sklad)</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>HSV 105 | PSV 54 | TZB 34 | VRN 22</t>
+          <t>HSV 106 | PSV 54 | TZB 34 | VRN 22</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>0.99: 17 | 0.95: 32 | 0.90: 35 | 0.85: 41 | 0.80: 19 | 0.75: 69 | 0.70: 1 | 0.60: 1</t>
+          <t>0.99: 17 | 0.95: 32 | 0.90: 35 | 0.85: 41 | 0.80: 19 | 0.75: 69 | 0.70: 1 | 0.60: 2</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>8 WebSearch verified (3.7 %) ✓ | 5 wrong leaf flagged (2.3 %) ⚠ | 140 needs_production_lookup (65.1 %)</t>
+          <t>8 WebSearch verified (3.7 %) ✓ | 5 wrong leaf flagged (2.3 %) ⚠ | 140 needs_production_lookup (64.8 %)</t>
         </is>
       </c>
     </row>
@@ -1182,8 +1182,8 @@
       <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Rozpočet generován STAVAGENT pipelinem z DSP dokumentace s DPS-grade DXF metadaty.
-215 položek celkem (187 dum + 28 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
-Confidence distribution: 17×0.99 · 32×0.95 · 35×0.90 · 41×0.85 · 19×0.80 · 69×0.75 · 1×0.70 · 1×0.60.
+216 položek celkem (188 dum + 28 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
+Confidence distribution: 17×0.99 · 32×0.95 · 35×0.90 · 41×0.85 · 19×0.80 · 69×0.75 · 1×0.70 · 2×0.60.
 25 položek vzniklo per-room expansion ze 9 aggregate parents (každá expanded položka tagged _expansion_origin).
 10 položek recalculated s exact external perimeter 38.70 m (DXF km_R_návrh_tlustá 2 closed polygon) vs prior fallback 41.0 m.
 Skladby vrstev (Sheet 8 Var_E) pochází POUZE z TZ explicit text + DXF cross-validation HATCH patterns. ŽÁDNÉ generic 'standardní RD' assumption — kde TZ silent, explicit fallback flag s ČSN default.
@@ -1255,7 +1255,7 @@
     <row r="55">
       <c r="A55" s="45" t="inlineStr">
         <is>
-          <t>• Total items: 215 (187 dům + 28 sklad) — vč. CEV +3 (komín/zídky/drenáž), anchor-gap +2 (přesun hmot/lešení), terasa-area fix + venkovní schody na terénu. 56 items s realizuje_skladbu.</t>
+          <t>• Total items: 216 (188 dům + 28 sklad) — vč. CEV +3 (komín/zídky/drenáž), anchor-gap +2 (přesun hmot/lešení), terasa-area fix + venkovní schody na terénu. 57 items s realizuje_skladbu.</t>
         </is>
       </c>
     </row>
@@ -2620,11 +2620,11 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Krokve 100/180 á 800 mm; Kleštiny 2×60/180; Pozednice 140/160; Námětky pro přesah; … (+12 dalších)</t>
+          <t>Krokve 100/180 á 800 mm; Kleštiny 2×60/180; Pozednice 140/160; Námětky pro přesah; … (+13 dalších)</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" s="10" t="n"/>
       <c r="F6" s="10" t="n"/>
@@ -3182,7 +3182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J118"/>
+  <dimension ref="A1:J119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7455,37 +7455,37 @@
       </c>
       <c r="B107" s="20" t="inlineStr">
         <is>
-          <t>260217_sklad</t>
-        </is>
-      </c>
-      <c r="C107" s="21" t="inlineStr">
-        <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Bezpečnostní dveře RC3 sklad</t>
+          <t>Spojovací prostředky krovu — svorníky tesařských spojů — Montáž svorníků / šroubů tesařských spojů krovu délky přes 150 do 300 mm — spojení kleštin 2×60/180 mm s krokvemi (svorník cca 250 mm, M12), vč. tyče závitové + matic + podložek</t>
         </is>
       </c>
       <c r="E107" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F107" s="9" t="n">
-        <v>1</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="F107" s="23" t="n">
+        <v>50</v>
       </c>
       <c r="G107" s="10" t="n"/>
       <c r="H107" s="10" t="n"/>
       <c r="I107" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>tesar</t>
         </is>
       </c>
       <c r="J107" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop 762085112</t>
         </is>
       </c>
     </row>
@@ -7500,12 +7500,12 @@
       </c>
       <c r="C108" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
+          <t>[agregát] 1 položek: Bezpečnostní dveře RC3 sklad</t>
         </is>
       </c>
       <c r="E108" s="20" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="C109" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 4 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+1 dalších)</t>
+          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
         </is>
       </c>
       <c r="E109" s="20" t="inlineStr">
@@ -7575,17 +7575,17 @@
       </c>
       <c r="B110" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C110" s="21" t="inlineStr">
         <is>
-          <t>M-21 — Elektroinstalace silnoproudá</t>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
         </is>
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 7 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+4 dalších)</t>
+          <t>[agregát] 4 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+1 dalších)</t>
         </is>
       </c>
       <c r="E110" s="20" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="C111" s="21" t="inlineStr">
         <is>
-          <t>PSV-71 — Izolace HI + TI</t>
+          <t>M-21 — Elektroinstalace silnoproudá</t>
         </is>
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
+          <t>[agregát] 7 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+4 dalších)</t>
         </is>
       </c>
       <c r="E111" s="20" t="inlineStr">
@@ -7660,12 +7660,12 @@
       </c>
       <c r="C112" s="21" t="inlineStr">
         <is>
-          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
+          <t>PSV-71 — Izolace HI + TI</t>
         </is>
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
+          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E112" s="20" t="inlineStr">
@@ -7700,12 +7700,12 @@
       </c>
       <c r="C113" s="21" t="inlineStr">
         <is>
-          <t>PSV-73 — Vytápění + komín</t>
+          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
         </is>
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
+          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
         </is>
       </c>
       <c r="E113" s="20" t="inlineStr">
@@ -7740,12 +7740,12 @@
       </c>
       <c r="C114" s="21" t="inlineStr">
         <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>PSV-73 — Vytápění + komín</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
+          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E114" s="20" t="inlineStr">
@@ -7780,12 +7780,12 @@
       </c>
       <c r="C115" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
+          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
         </is>
       </c>
       <c r="E115" s="20" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="C116" s="21" t="inlineStr">
         <is>
-          <t>PSV-78 — Povrchové úpravy</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
+          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
         </is>
       </c>
       <c r="E116" s="20" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="C117" s="21" t="inlineStr">
         <is>
-          <t>PSV-95 — Detekce požární</t>
+          <t>PSV-78 — Povrchové úpravy</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 2 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A</t>
+          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
         </is>
       </c>
       <c r="E117" s="20" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="C118" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>PSV-95 — Detekce požární</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
+          <t>[agregát] 2 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A</t>
         </is>
       </c>
       <c r="E118" s="20" t="inlineStr">
@@ -7929,8 +7929,48 @@
         </is>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" s="20" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C119" s="21" t="inlineStr">
+        <is>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
+        </is>
+      </c>
+      <c r="D119" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
+        </is>
+      </c>
+      <c r="E119" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F119" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" s="10" t="n"/>
+      <c r="H119" s="10" t="n"/>
+      <c r="I119" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J119" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J118"/>
+  <autoFilter ref="A1:J119"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7941,7 +7981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R188"/>
+  <dimension ref="A1:R189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12249,55 +12289,55 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Bourání kompletního stávajícího krovu</t>
+          <t>Spojovací prostředky krovu — svorníky tesařských spojů</t>
         </is>
       </c>
       <c r="D62" s="20" t="inlineStr">
         <is>
-          <t>962041141</t>
+          <t>762085112</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>Bourání kompletního stávajícího krovu vč. vikýřů — vaznicový s ležatou stolicí — manuálně, odvoz</t>
+          <t>Montáž svorníků / šroubů tesařských spojů krovu délky přes 150 do 300 mm — spojení kleštin 2×60/180 mm s krokvemi (svorník cca 250 mm, M12), vč. tyče závitové + matic + podložek</t>
         </is>
       </c>
       <c r="F62" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="G62" s="22" t="n">
-        <v>12</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G62" s="23" t="n">
+        <v>50</v>
       </c>
       <c r="H62" s="10" t="n"/>
       <c r="I62" s="10" t="n"/>
       <c r="J62" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>tesar</t>
         </is>
       </c>
       <c r="K62" s="24" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="L62" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>matched_catalog</t>
         </is>
       </c>
       <c r="M62" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e — 9 t dřeva celkem; krov hlavní zdroj</t>
+          <t>KROS/ÚRS catalog (762085112 montáž svorníků tesařských spojů) + STAVAGENT MCP; TZ statika §4 krov ocelové spojky</t>
         </is>
       </c>
       <c r="N62" s="20" t="inlineStr">
         <is>
-          <t>#9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O62" s="26" t="inlineStr">
@@ -12305,10 +12345,14 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P62" s="41" t="n"/>
+      <c r="P62" s="41" t="inlineStr">
+        <is>
+          <t>Krov — spojovací prostředky</t>
+        </is>
+      </c>
       <c r="Q62" s="41" t="inlineStr">
         <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+          <t>KROV_SVORNIKY_ADD_2026-05-31</t>
         </is>
       </c>
     </row>
@@ -12323,26 +12367,26 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>Bourání plechové střešní krytiny</t>
-        </is>
-      </c>
-      <c r="D63" s="27" t="inlineStr">
-        <is>
-          <t>762??? ?</t>
+          <t>Bourání kompletního stávajícího krovu</t>
+        </is>
+      </c>
+      <c r="D63" s="20" t="inlineStr">
+        <is>
+          <t>962041141</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>Bourání stávající plechové krytiny (manuálně, recyklace plechu)</t>
+          <t>Bourání kompletního stávajícího krovu vč. vikýřů — vaznicový s ležatou stolicí — manuálně, odvoz</t>
         </is>
       </c>
       <c r="F63" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="G63" s="22" t="n">
-        <v>140.9</v>
+        <v>12</v>
       </c>
       <c r="H63" s="10" t="n"/>
       <c r="I63" s="10" t="n"/>
@@ -12356,12 +12400,12 @@
       </c>
       <c r="L63" s="20" t="inlineStr">
         <is>
-          <t>wrong_leaf_disambiguation_needed</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M63" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e — 0.1 t kovů; stávající plech krytina</t>
+          <t>TZ B m.10.e — 9 t dřeva celkem; krov hlavní zdroj</t>
         </is>
       </c>
       <c r="N63" s="20" t="inlineStr">
@@ -12369,13 +12413,17 @@
           <t>#9</t>
         </is>
       </c>
-      <c r="O63" s="28" t="inlineStr">
-        <is>
-          <t>LEAF CHYBNÝ — viz alternatives</t>
+      <c r="O63" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
         </is>
       </c>
       <c r="P63" s="41" t="n"/>
-      <c r="Q63" s="41" t="n"/>
+      <c r="Q63" s="41" t="inlineStr">
+        <is>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="20" t="n">
@@ -12388,26 +12436,26 @@
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Bourání nadezdívek nad stropem 2.NP</t>
-        </is>
-      </c>
-      <c r="D64" s="20" t="inlineStr">
-        <is>
-          <t>962031132</t>
+          <t>Bourání plechové střešní krytiny</t>
+        </is>
+      </c>
+      <c r="D64" s="27" t="inlineStr">
+        <is>
+          <t>762??? ?</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>Bourání zděných nadezdívek nad stropem 2.NP (mimo štítových stěn) — cihla pálená</t>
+          <t>Bourání stávající plechové krytiny (manuálně, recyklace plechu)</t>
         </is>
       </c>
       <c r="F64" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G64" s="22" t="n">
-        <v>6</v>
+        <v>140.9</v>
       </c>
       <c r="H64" s="10" t="n"/>
       <c r="I64" s="10" t="n"/>
@@ -12421,12 +12469,12 @@
       </c>
       <c r="L64" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>wrong_leaf_disambiguation_needed</t>
         </is>
       </c>
       <c r="M64" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3 — bourání nadezdívek mimo štítů</t>
+          <t>TZ B m.10.e — 0.1 t kovů; stávající plech krytina</t>
         </is>
       </c>
       <c r="N64" s="20" t="inlineStr">
@@ -12434,9 +12482,9 @@
           <t>#9</t>
         </is>
       </c>
-      <c r="O64" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
+      <c r="O64" s="28" t="inlineStr">
+        <is>
+          <t>LEAF CHYBNÝ — viz alternatives</t>
         </is>
       </c>
       <c r="P64" s="41" t="n"/>
@@ -12453,26 +12501,26 @@
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>Bourání trámového stropu 2.NP/podkroví</t>
+          <t>Bourání nadezdívek nad stropem 2.NP</t>
         </is>
       </c>
       <c r="D65" s="20" t="inlineStr">
         <is>
-          <t>962041141</t>
+          <t>962031132</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>Bourání trámového stropu 2.NP/podkroví — kompletně (vč. zajištění schodiště)</t>
+          <t>Bourání zděných nadezdívek nad stropem 2.NP (mimo štítových stěn) — cihla pálená</t>
         </is>
       </c>
       <c r="F65" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="G65" s="22" t="n">
-        <v>104.4</v>
+        <v>6</v>
       </c>
       <c r="H65" s="10" t="n"/>
       <c r="I65" s="10" t="n"/>
@@ -12491,7 +12539,7 @@
       </c>
       <c r="M65" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3 — strop 2.NP/3.NP KOMPLETNĚ bourán</t>
+          <t>TZ ARS dům §3 — bourání nadezdívek mimo štítů</t>
         </is>
       </c>
       <c r="N65" s="20" t="inlineStr">
@@ -12518,17 +12566,17 @@
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Bourání lehkých příček</t>
+          <t>Bourání trámového stropu 2.NP/podkroví</t>
         </is>
       </c>
       <c r="D66" s="20" t="inlineStr">
         <is>
-          <t>962031132</t>
+          <t>962041141</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>Bourání stávajících lehkých příček (cihla, sádrokarton, dřevo)</t>
+          <t>Bourání trámového stropu 2.NP/podkroví — kompletně (vč. zajištění schodiště)</t>
         </is>
       </c>
       <c r="F66" s="20" t="inlineStr">
@@ -12537,7 +12585,7 @@
         </is>
       </c>
       <c r="G66" s="22" t="n">
-        <v>80</v>
+        <v>104.4</v>
       </c>
       <c r="H66" s="10" t="n"/>
       <c r="I66" s="10" t="n"/>
@@ -12556,7 +12604,7 @@
       </c>
       <c r="M66" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3 — lehké příčky bourány</t>
+          <t>TZ ARS dům §3 — strop 2.NP/3.NP KOMPLETNĚ bourán</t>
         </is>
       </c>
       <c r="N66" s="20" t="inlineStr">
@@ -12583,7 +12631,7 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>Bourání otvorů pro nové dveře/okna</t>
+          <t>Bourání lehkých příček</t>
         </is>
       </c>
       <c r="D67" s="20" t="inlineStr">
@@ -12593,16 +12641,16 @@
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>Bourání 8 nových otvorů v nosných cihelných zdech pro dveře/okna (~1.0 × 2.1 m)</t>
+          <t>Bourání stávajících lehkých příček (cihla, sádrokarton, dřevo)</t>
         </is>
       </c>
       <c r="F67" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G67" s="23" t="n">
-        <v>8</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G67" s="22" t="n">
+        <v>80</v>
       </c>
       <c r="H67" s="10" t="n"/>
       <c r="I67" s="10" t="n"/>
@@ -12621,12 +12669,12 @@
       </c>
       <c r="M67" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + statika — nové otvory s IPN160 překlady</t>
+          <t>TZ ARS dům §3 — lehké příčky bourány</t>
         </is>
       </c>
       <c r="N67" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#9</t>
         </is>
       </c>
       <c r="O67" s="26" t="inlineStr">
@@ -12648,26 +12696,26 @@
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Bourání obkladů v koupelnách</t>
+          <t>Bourání otvorů pro nové dveře/okna</t>
         </is>
       </c>
       <c r="D68" s="20" t="inlineStr">
         <is>
-          <t>781473810</t>
+          <t>962031132</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>Bourání keramických obkladů a zařizovacích předmětů v koupelnách 1.NP + 2.NP</t>
+          <t>Bourání 8 nových otvorů v nosných cihelných zdech pro dveře/okna (~1.0 × 2.1 m)</t>
         </is>
       </c>
       <c r="F68" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G68" s="22" t="n">
-        <v>60</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G68" s="23" t="n">
+        <v>8</v>
       </c>
       <c r="H68" s="10" t="n"/>
       <c r="I68" s="10" t="n"/>
@@ -12681,17 +12729,17 @@
       </c>
       <c r="L68" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M68" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3 — koupelny kompletně bourány</t>
+          <t>TZ ARS + statika — nové otvory s IPN160 překlady</t>
         </is>
       </c>
       <c r="N68" s="20" t="inlineStr">
         <is>
-          <t>#9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O68" s="26" t="inlineStr">
@@ -12700,11 +12748,7 @@
         </is>
       </c>
       <c r="P68" s="41" t="n"/>
-      <c r="Q68" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+      <c r="Q68" s="41" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="20" t="n">
@@ -12717,17 +12761,17 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>Bourání podlah 1.NP + 2.NP</t>
+          <t>Bourání obkladů v koupelnách</t>
         </is>
       </c>
       <c r="D69" s="20" t="inlineStr">
         <is>
-          <t>974031132</t>
+          <t>781473810</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>Sejmutí podlah 1.NP a 2.NP — vč. nášlapů, podkladních vrstev</t>
+          <t>Bourání keramických obkladů a zařizovacích předmětů v koupelnách 1.NP + 2.NP</t>
         </is>
       </c>
       <c r="F69" s="20" t="inlineStr">
@@ -12736,7 +12780,7 @@
         </is>
       </c>
       <c r="G69" s="22" t="n">
-        <v>153.51</v>
+        <v>60</v>
       </c>
       <c r="H69" s="10" t="n"/>
       <c r="I69" s="10" t="n"/>
@@ -12750,12 +12794,12 @@
       </c>
       <c r="L69" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M69" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3 — podlahy 1.NP+2.NP sejmuty</t>
+          <t>TZ ARS dům §3 — koupelny kompletně bourány</t>
         </is>
       </c>
       <c r="N69" s="20" t="inlineStr">
@@ -12769,7 +12813,11 @@
         </is>
       </c>
       <c r="P69" s="41" t="n"/>
-      <c r="Q69" s="41" t="n"/>
+      <c r="Q69" s="41" t="inlineStr">
+        <is>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="20" t="n">
@@ -12782,26 +12830,26 @@
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Záklop + zásyp — demontáž</t>
+          <t>Bourání podlah 1.NP + 2.NP</t>
         </is>
       </c>
       <c r="D70" s="20" t="inlineStr">
         <is>
-          <t>974041151</t>
+          <t>974031132</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>Demontáž záklopu a zásypů stropu 1.NP (prkenný záklop na trámech zachován)</t>
+          <t>Sejmutí podlah 1.NP a 2.NP — vč. nášlapů, podkladních vrstev</t>
         </is>
       </c>
       <c r="F70" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G70" s="22" t="n">
-        <v>5</v>
+        <v>153.51</v>
       </c>
       <c r="H70" s="10" t="n"/>
       <c r="I70" s="10" t="n"/>
@@ -12820,7 +12868,7 @@
       </c>
       <c r="M70" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3 — záklop+zásyp demontován; trámy zachovány</t>
+          <t>TZ ARS dům §3 — podlahy 1.NP+2.NP sejmuty</t>
         </is>
       </c>
       <c r="N70" s="20" t="inlineStr">
@@ -12847,26 +12895,26 @@
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>Demontáž oken a dveří</t>
+          <t>Záklop + zásyp — demontáž</t>
         </is>
       </c>
       <c r="D71" s="20" t="inlineStr">
         <is>
-          <t>968071120</t>
+          <t>974041151</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>Demontáž všech oken a dveří stávajících (recyklace)</t>
+          <t>Demontáž záklopu a zásypů stropu 1.NP (prkenný záklop na trámech zachován)</t>
         </is>
       </c>
       <c r="F71" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G71" s="23" t="n">
-        <v>25</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="G71" s="22" t="n">
+        <v>5</v>
       </c>
       <c r="H71" s="10" t="n"/>
       <c r="I71" s="10" t="n"/>
@@ -12885,12 +12933,12 @@
       </c>
       <c r="M71" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3 — VŠECHNY okna a dveře demontovány</t>
+          <t>TZ ARS dům §3 — záklop+zásyp demontován; trámy zachovány</t>
         </is>
       </c>
       <c r="N71" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>#9</t>
         </is>
       </c>
       <c r="O71" s="26" t="inlineStr">
@@ -12912,17 +12960,17 @@
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Demontáž zařizovacích předmětů</t>
+          <t>Demontáž oken a dveří</t>
         </is>
       </c>
       <c r="D72" s="20" t="inlineStr">
         <is>
-          <t>725900001</t>
+          <t>968071120</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
+          <t>Demontáž všech oken a dveří stávajících (recyklace)</t>
         </is>
       </c>
       <c r="F72" s="20" t="inlineStr">
@@ -12931,7 +12979,7 @@
         </is>
       </c>
       <c r="G72" s="23" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H72" s="10" t="n"/>
       <c r="I72" s="10" t="n"/>
@@ -12950,12 +12998,12 @@
       </c>
       <c r="M72" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3 — zařizovací předměty kompletně demontovány</t>
+          <t>TZ ARS dům §3 — VŠECHNY okna a dveře demontovány</t>
         </is>
       </c>
       <c r="N72" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O72" s="26" t="inlineStr">
@@ -12977,26 +13025,26 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>Odvoz suti a likvidace</t>
+          <t>Demontáž zařizovacích předmětů</t>
         </is>
       </c>
       <c r="D73" s="20" t="inlineStr">
         <is>
-          <t>997013501</t>
+          <t>725900001</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
+          <t>Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
         </is>
       </c>
       <c r="F73" s="20" t="inlineStr">
         <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G73" s="22" t="n">
-        <v>56.5</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G73" s="23" t="n">
+        <v>12</v>
       </c>
       <c r="H73" s="10" t="n"/>
       <c r="I73" s="10" t="n"/>
@@ -13006,7 +13054,7 @@
         </is>
       </c>
       <c r="K73" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L73" s="20" t="inlineStr">
         <is>
@@ -13015,12 +13063,12 @@
       </c>
       <c r="M73" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e bilance odpadů</t>
+          <t>TZ ARS dům §3 — zařizovací předměty kompletně demontovány</t>
         </is>
       </c>
       <c r="N73" s="20" t="inlineStr">
         <is>
-          <t>#9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O73" s="26" t="inlineStr">
@@ -13042,26 +13090,26 @@
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Demontáž oken</t>
+          <t>Odvoz suti a likvidace</t>
         </is>
       </c>
       <c r="D74" s="20" t="inlineStr">
         <is>
-          <t>978013181</t>
+          <t>997013501</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
+          <t>Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
         </is>
       </c>
       <c r="F74" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G74" s="23" t="n">
-        <v>16</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G74" s="22" t="n">
+        <v>56.5</v>
       </c>
       <c r="H74" s="10" t="n"/>
       <c r="I74" s="10" t="n"/>
@@ -13071,34 +13119,30 @@
         </is>
       </c>
       <c r="K74" s="24" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="L74" s="20" t="inlineStr">
         <is>
-          <t>matched_websearch_verified</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M74" s="8" t="inlineStr">
         <is>
-          <t>DXF blocks okno* (Path C Tier 4) + TZ ARS — všechna okna nová</t>
+          <t>TZ B m.10.e bilance odpadů</t>
         </is>
       </c>
       <c r="N74" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
-        </is>
-      </c>
-      <c r="O74" s="25" t="inlineStr">
-        <is>
-          <t>OVĚŘENO ✓</t>
+          <t>#9</t>
+        </is>
+      </c>
+      <c r="O74" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
         </is>
       </c>
       <c r="P74" s="41" t="n"/>
-      <c r="Q74" s="41" t="inlineStr">
-        <is>
-          <t>GAP_002</t>
-        </is>
-      </c>
+      <c r="Q74" s="41" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="20" t="n">
@@ -13111,7 +13155,7 @@
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>Demontáž vstupních dveří venkovních</t>
+          <t>Demontáž oken</t>
         </is>
       </c>
       <c r="D75" s="20" t="inlineStr">
@@ -13121,7 +13165,7 @@
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
+          <t>Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
         </is>
       </c>
       <c r="F75" s="20" t="inlineStr">
@@ -13130,7 +13174,7 @@
         </is>
       </c>
       <c r="G75" s="23" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H75" s="10" t="n"/>
       <c r="I75" s="10" t="n"/>
@@ -13149,7 +13193,7 @@
       </c>
       <c r="M75" s="8" t="inlineStr">
         <is>
-          <t>DXF blocks dveře (vstupní 2) + TZ ARS — 'plastové vstupní dveře' x 2</t>
+          <t>DXF blocks okno* (Path C Tier 4) + TZ ARS — všechna okna nová</t>
         </is>
       </c>
       <c r="N75" s="20" t="inlineStr">
@@ -13180,17 +13224,17 @@
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>Demontáž vnitřních dveří vč. zárubní</t>
+          <t>Demontáž vstupních dveří venkovních</t>
         </is>
       </c>
       <c r="D76" s="20" t="inlineStr">
         <is>
-          <t>968072456</t>
+          <t>978013181</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
+          <t>Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
         </is>
       </c>
       <c r="F76" s="20" t="inlineStr">
@@ -13199,7 +13243,7 @@
         </is>
       </c>
       <c r="G76" s="23" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H76" s="10" t="n"/>
       <c r="I76" s="10" t="n"/>
@@ -13209,16 +13253,16 @@
         </is>
       </c>
       <c r="K76" s="24" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="L76" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>matched_websearch_verified</t>
         </is>
       </c>
       <c r="M76" s="8" t="inlineStr">
         <is>
-          <t>DXF SM__dveře polyline count → estimate (Path C Tier 4)</t>
+          <t>DXF blocks dveře (vstupní 2) + TZ ARS — 'plastové vstupní dveře' x 2</t>
         </is>
       </c>
       <c r="N76" s="20" t="inlineStr">
@@ -13226,9 +13270,9 @@
           <t>#3</t>
         </is>
       </c>
-      <c r="O76" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
+      <c r="O76" s="25" t="inlineStr">
+        <is>
+          <t>OVĚŘENO ✓</t>
         </is>
       </c>
       <c r="P76" s="41" t="n"/>
@@ -13249,26 +13293,26 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>Bourání zdiva komínu</t>
+          <t>Demontáž vnitřních dveří vč. zárubní</t>
         </is>
       </c>
       <c r="D77" s="20" t="inlineStr">
         <is>
-          <t>962024141</t>
+          <t>968072456</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
+          <t>Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
         </is>
       </c>
       <c r="F77" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="G77" s="22" t="n">
-        <v>0.6</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G77" s="23" t="n">
+        <v>15</v>
       </c>
       <c r="H77" s="10" t="n"/>
       <c r="I77" s="10" t="n"/>
@@ -13278,21 +13322,21 @@
         </is>
       </c>
       <c r="K77" s="24" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="L77" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M77" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ řez A-A bourání + POZN.1.02 z půdorysů bourání</t>
+          <t>DXF SM__dveře polyline count → estimate (Path C Tier 4)</t>
         </is>
       </c>
       <c r="N77" s="20" t="inlineStr">
         <is>
-          <t>#9</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O77" s="26" t="inlineStr">
@@ -13303,7 +13347,7 @@
       <c r="P77" s="41" t="n"/>
       <c r="Q77" s="41" t="inlineStr">
         <is>
-          <t>PER_DRAWING_GAP_POZN_1_02; URS_PHASE5B_FAMILY_VERIFIED; CHATGPT_KOMIN_QTY_FIX_2026-05-29</t>
+          <t>GAP_002</t>
         </is>
       </c>
     </row>
@@ -13318,17 +13362,17 @@
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>Bourání venkovních konstrukcí</t>
+          <t>Bourání zdiva komínu</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
         <is>
-          <t>961044111</t>
+          <t>962024141</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
+          <t>Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
         </is>
       </c>
       <c r="F78" s="20" t="inlineStr">
@@ -13337,7 +13381,7 @@
         </is>
       </c>
       <c r="G78" s="22" t="n">
-        <v>8</v>
+        <v>0.6</v>
       </c>
       <c r="H78" s="10" t="n"/>
       <c r="I78" s="10" t="n"/>
@@ -13347,7 +13391,7 @@
         </is>
       </c>
       <c r="K78" s="24" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="L78" s="20" t="inlineStr">
         <is>
@@ -13356,7 +13400,7 @@
       </c>
       <c r="M78" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ řez A-A bourání + POZN.1.03 + půdorys bourání</t>
+          <t>DXF dum_DPZ řez A-A bourání + POZN.1.02 z půdorysů bourání</t>
         </is>
       </c>
       <c r="N78" s="20" t="inlineStr">
@@ -13372,7 +13416,7 @@
       <c r="P78" s="41" t="n"/>
       <c r="Q78" s="41" t="inlineStr">
         <is>
-          <t>PER_DRAWING_GAP_POZN_1_03; URS_PHASE5B_FAMILY_VERIFIED</t>
+          <t>PER_DRAWING_GAP_POZN_1_02; URS_PHASE5B_FAMILY_VERIFIED; CHATGPT_KOMIN_QTY_FIX_2026-05-29</t>
         </is>
       </c>
     </row>
@@ -13382,55 +13426,55 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda ETICS</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>Příprava podkladu</t>
+          <t>Bourání venkovních konstrukcí</t>
         </is>
       </c>
       <c r="D79" s="20" t="inlineStr">
         <is>
-          <t>622401110</t>
+          <t>961044111</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>Příprava fasádního podkladu — očištění tlakovou vodou, vyspravení omítek, fungicidní nátěr</t>
+          <t>Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
         </is>
       </c>
       <c r="F79" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="G79" s="22" t="n">
-        <v>276.7</v>
+        <v>8</v>
       </c>
       <c r="H79" s="10" t="n"/>
       <c r="I79" s="10" t="n"/>
       <c r="J79" s="8" t="inlineStr">
         <is>
-          <t>fasadnik_etics</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K79" s="24" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="L79" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M79" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — ETICS kontaktní, podklad existující omítka + DXF perimeter</t>
+          <t>DXF dum_DPZ řez A-A bourání + POZN.1.03 + půdorys bourání</t>
         </is>
       </c>
       <c r="N79" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>#9</t>
         </is>
       </c>
       <c r="O79" s="26" t="inlineStr">
@@ -13438,12 +13482,12 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P79" s="41" t="inlineStr">
-        <is>
-          <t>S01</t>
-        </is>
-      </c>
-      <c r="Q79" s="41" t="n"/>
+      <c r="P79" s="41" t="n"/>
+      <c r="Q79" s="41" t="inlineStr">
+        <is>
+          <t>PER_DRAWING_GAP_POZN_1_03; URS_PHASE5B_FAMILY_VERIFIED</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="20" t="n">
@@ -13456,17 +13500,17 @@
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>ETICS EPS 70F grey 160 mm</t>
+          <t>Příprava podkladu</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
         <is>
-          <t>622221121</t>
+          <t>622401110</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>ETICS kontaktní zateplení — EPS 70F grey λ=0.032 tl. 160 mm + síťka + lepidlo + zatírací stěrka (řez S01+S12a explicit, ne 200 mm fallback)</t>
+          <t>Příprava fasádního podkladu — očištění tlakovou vodou, vyspravení omítek, fungicidní nátěr</t>
         </is>
       </c>
       <c r="F80" s="20" t="inlineStr">
@@ -13489,12 +13533,12 @@
       </c>
       <c r="L80" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M80" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 EXPLICIT 'fasádní EPS 70f grey (λ=0,032 W/mK)' + PBŘ EXPLICIT 'EPS tl. max. 200 mm' + DXF perimeter</t>
+          <t>TZ ARS dům §3.2 — ETICS kontaktní, podklad existující omítka + DXF perimeter</t>
         </is>
       </c>
       <c r="N80" s="20" t="inlineStr">
@@ -13509,14 +13553,10 @@
       </c>
       <c r="P80" s="41" t="inlineStr">
         <is>
-          <t>S01, S12a</t>
-        </is>
-      </c>
-      <c r="Q80" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="Q80" s="41" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="20" t="n">
@@ -13529,17 +13569,17 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>ETICS sokl XPS</t>
+          <t>ETICS EPS 70F grey 160 mm</t>
         </is>
       </c>
       <c r="D81" s="20" t="inlineStr">
         <is>
-          <t>622223111</t>
+          <t>622221121</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>ETICS sokl — XPS λ=0.034 tl. 120 mm + soklový profil + cihelný obklad spárovaný</t>
+          <t>ETICS kontaktní zateplení — EPS 70F grey λ=0.032 tl. 160 mm + síťka + lepidlo + zatírací stěrka (řez S01+S12a explicit, ne 200 mm fallback)</t>
         </is>
       </c>
       <c r="F81" s="20" t="inlineStr">
@@ -13548,7 +13588,7 @@
         </is>
       </c>
       <c r="G81" s="22" t="n">
-        <v>13.5</v>
+        <v>276.7</v>
       </c>
       <c r="H81" s="10" t="n"/>
       <c r="I81" s="10" t="n"/>
@@ -13567,12 +13607,12 @@
       </c>
       <c r="M81" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — sokl XPS + cihelný obklad + DXF perimeter</t>
+          <t>TZ ARS dům §3.2 EXPLICIT 'fasádní EPS 70f grey (λ=0,032 W/mK)' + PBŘ EXPLICIT 'EPS tl. max. 200 mm' + DXF perimeter</t>
         </is>
       </c>
       <c r="N81" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O81" s="26" t="inlineStr">
@@ -13582,7 +13622,7 @@
       </c>
       <c r="P81" s="41" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S01, S12a</t>
         </is>
       </c>
       <c r="Q81" s="41" t="inlineStr">
@@ -13602,26 +13642,26 @@
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>Špalety EPS</t>
+          <t>ETICS sokl XPS</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
         <is>
-          <t>622221221</t>
+          <t>622223111</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
+          <t>ETICS sokl — XPS λ=0.034 tl. 120 mm + soklový profil + cihelný obklad spárovaný</t>
         </is>
       </c>
       <c r="F82" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G82" s="22" t="n">
-        <v>82.2</v>
+        <v>13.5</v>
       </c>
       <c r="H82" s="10" t="n"/>
       <c r="I82" s="10" t="n"/>
@@ -13631,21 +13671,21 @@
         </is>
       </c>
       <c r="K82" s="24" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
       <c r="L82" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M82" s="8" t="inlineStr">
         <is>
-          <t>DXF okna per typ bbox + TZ ARS §3.2 EPS přesah na špaletách 35-40 mm</t>
+          <t>TZ ARS dům §3.2 — sokl XPS + cihelný obklad + DXF perimeter</t>
         </is>
       </c>
       <c r="N82" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O82" s="26" t="inlineStr">
@@ -13655,10 +13695,14 @@
       </c>
       <c r="P82" s="41" t="inlineStr">
         <is>
-          <t>S01, S12a</t>
-        </is>
-      </c>
-      <c r="Q82" s="41" t="n"/>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="Q82" s="41" t="inlineStr">
+        <is>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="20" t="n">
@@ -13671,7 +13715,7 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>Profilace fasády</t>
+          <t>Špalety EPS</t>
         </is>
       </c>
       <c r="D83" s="20" t="inlineStr">
@@ -13681,16 +13725,16 @@
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
+          <t>Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
         </is>
       </c>
       <c r="F83" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="G83" s="23" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G83" s="22" t="n">
+        <v>82.2</v>
       </c>
       <c r="H83" s="10" t="n"/>
       <c r="I83" s="10" t="n"/>
@@ -13709,12 +13753,12 @@
       </c>
       <c r="M83" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — profilace různými tl. EPS</t>
+          <t>DXF okna per typ bbox + TZ ARS §3.2 EPS přesah na špaletách 35-40 mm</t>
         </is>
       </c>
       <c r="N83" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O83" s="26" t="inlineStr">
@@ -13740,26 +13784,26 @@
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>Tenkovrstvá omítka pastovitá</t>
+          <t>Profilace fasády</t>
         </is>
       </c>
       <c r="D84" s="20" t="inlineStr">
         <is>
-          <t>622521111</t>
+          <t>622221221</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
+          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
         </is>
       </c>
       <c r="F84" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G84" s="22" t="n">
-        <v>290.2</v>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="G84" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H84" s="10" t="n"/>
       <c r="I84" s="10" t="n"/>
@@ -13769,16 +13813,16 @@
         </is>
       </c>
       <c r="K84" s="24" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
       <c r="L84" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M84" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — pastovitá probarvená lomená bílá + DXF perimeter</t>
+          <t>TZ ARS dům §3.2 — profilace různými tl. EPS</t>
         </is>
       </c>
       <c r="N84" s="20" t="inlineStr">
@@ -13793,14 +13837,10 @@
       </c>
       <c r="P84" s="41" t="inlineStr">
         <is>
-          <t>S01, S12a, S12b</t>
-        </is>
-      </c>
-      <c r="Q84" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+          <t>S01, S12a</t>
+        </is>
+      </c>
+      <c r="Q84" s="41" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="20" t="n">
@@ -13808,22 +13848,22 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace HI</t>
+          <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>HI pod ŽB deskou 1.NP</t>
+          <t>Tenkovrstvá omítka pastovitá</t>
         </is>
       </c>
       <c r="D85" s="20" t="inlineStr">
         <is>
-          <t>712311101</t>
+          <t>622521111</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolace pod ŽB deskou 1.NP — modifikované asfaltové pásy SBS 2× (zároveň protiradonová bariéra)</t>
+          <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
         </is>
       </c>
       <c r="F85" s="20" t="inlineStr">
@@ -13832,17 +13872,17 @@
         </is>
       </c>
       <c r="G85" s="22" t="n">
-        <v>80.40000000000001</v>
+        <v>290.2</v>
       </c>
       <c r="H85" s="10" t="n"/>
       <c r="I85" s="10" t="n"/>
       <c r="J85" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>fasadnik_etics</t>
         </is>
       </c>
       <c r="K85" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L85" s="20" t="inlineStr">
         <is>
@@ -13851,12 +13891,12 @@
       </c>
       <c r="M85" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + statika §5.5 — asfaltové pásy mod. proti radonu</t>
+          <t>TZ ARS dům §3.2 — pastovitá probarvená lomená bílá + DXF perimeter</t>
         </is>
       </c>
       <c r="N85" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O85" s="26" t="inlineStr">
@@ -13864,10 +13904,14 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P85" s="41" t="n"/>
+      <c r="P85" s="41" t="inlineStr">
+        <is>
+          <t>S01, S12a, S12b</t>
+        </is>
+      </c>
       <c r="Q85" s="41" t="inlineStr">
         <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED; URS_PHASE5B_FAMILY_VERIFIED</t>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
         </is>
       </c>
     </row>
@@ -13882,26 +13926,26 @@
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>Odvětrání radonu z podloží</t>
+          <t>HI pod ŽB deskou 1.NP</t>
         </is>
       </c>
       <c r="D86" s="20" t="inlineStr">
         <is>
-          <t>712381111</t>
+          <t>712311101</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>Odvětrání radonu z podloží — perforované DN50 trubky v štěrkovém loži + výdech nad střechu</t>
+          <t>Hydroizolace pod ŽB deskou 1.NP — modifikované asfaltové pásy SBS 2× (zároveň protiradonová bariéra)</t>
         </is>
       </c>
       <c r="F86" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G86" s="22" t="n">
-        <v>12</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="H86" s="10" t="n"/>
       <c r="I86" s="10" t="n"/>
@@ -13920,12 +13964,12 @@
       </c>
       <c r="M86" s="8" t="inlineStr">
         <is>
-          <t>TZ statika §5.5 'ochrana proti radonu — modifikované asf. pásy + odvětrání'</t>
+          <t>TZ ARS dům §4 + statika §5.5 — asfaltové pásy mod. proti radonu</t>
         </is>
       </c>
       <c r="N86" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O86" s="26" t="inlineStr">
@@ -13936,7 +13980,7 @@
       <c r="P86" s="41" t="n"/>
       <c r="Q86" s="41" t="inlineStr">
         <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+          <t>URS_PHASE5B_FAMILY_VERIFIED; URS_PHASE5B_FAMILY_VERIFIED</t>
         </is>
       </c>
     </row>
@@ -13951,26 +13995,26 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>HI koupelny 1.NP + 2.NP + 3.NP</t>
-        </is>
-      </c>
-      <c r="D87" s="27" t="inlineStr">
-        <is>
-          <t>711??? ?</t>
+          <t>Odvětrání radonu z podloží</t>
+        </is>
+      </c>
+      <c r="D87" s="20" t="inlineStr">
+        <is>
+          <t>712381111</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolační stěrka koupelen 3 ks — podlaha + sokl 200 mm + sprchový kout výška 2.0 m</t>
+          <t>Odvětrání radonu z podloží — perforované DN50 trubky v štěrkovém loži + výdech nad střechu</t>
         </is>
       </c>
       <c r="F87" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G87" s="22" t="n">
-        <v>40.5</v>
+        <v>12</v>
       </c>
       <c r="H87" s="10" t="n"/>
       <c r="I87" s="10" t="n"/>
@@ -13980,7 +14024,7 @@
         </is>
       </c>
       <c r="K87" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L87" s="20" t="inlineStr">
         <is>
@@ -13989,12 +14033,12 @@
       </c>
       <c r="M87" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT labels: 3× koupelna; TZ ARS — HI vana koupelny</t>
+          <t>TZ statika §5.5 'ochrana proti radonu — modifikované asf. pásy + odvětrání'</t>
         </is>
       </c>
       <c r="N87" s="20" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O87" s="26" t="inlineStr">
@@ -14015,22 +14059,22 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace TI</t>
+          <t>PSV-71 Izolace HI</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>Podlahový EPS 150</t>
+          <t>HI koupelny 1.NP + 2.NP + 3.NP</t>
         </is>
       </c>
       <c r="D88" s="27" t="inlineStr">
         <is>
-          <t>713121??? ?</t>
+          <t>711??? ?</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>Podlahový EPS 150 λ=0.035 tl. 120 mm — pod betonový potěr 1.NP a 3.NP</t>
+          <t>Hydroizolační stěrka koupelen 3 ks — podlaha + sokl 200 mm + sprchový kout výška 2.0 m</t>
         </is>
       </c>
       <c r="F88" s="20" t="inlineStr">
@@ -14039,17 +14083,17 @@
         </is>
       </c>
       <c r="G88" s="22" t="n">
-        <v>177.5</v>
+        <v>40.5</v>
       </c>
       <c r="H88" s="10" t="n"/>
       <c r="I88" s="10" t="n"/>
       <c r="J88" s="8" t="inlineStr">
         <is>
-          <t>izolater_TI</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K88" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L88" s="20" t="inlineStr">
         <is>
@@ -14058,7 +14102,7 @@
       </c>
       <c r="M88" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — EPS 150 λ=0.035 tl. 120 mm</t>
+          <t>DXF dum_DPZ MTEXT labels: 3× koupelna; TZ ARS — HI vana koupelny</t>
         </is>
       </c>
       <c r="N88" s="20" t="inlineStr">
@@ -14089,7 +14133,7 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>Kročejová EPS nad ocelobeton</t>
+          <t>Podlahový EPS 150</t>
         </is>
       </c>
       <c r="D89" s="27" t="inlineStr">
@@ -14099,7 +14143,7 @@
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>Kročejová EPS 150 / 30 dB tl. 30 mm nad ocelobetonovým stropem 2.NP/3.NP</t>
+          <t>Podlahový EPS 150 λ=0.035 tl. 120 mm — pod betonový potěr 1.NP a 3.NP</t>
         </is>
       </c>
       <c r="F89" s="20" t="inlineStr">
@@ -14108,7 +14152,7 @@
         </is>
       </c>
       <c r="G89" s="22" t="n">
-        <v>104.4</v>
+        <v>177.5</v>
       </c>
       <c r="H89" s="10" t="n"/>
       <c r="I89" s="10" t="n"/>
@@ -14118,7 +14162,7 @@
         </is>
       </c>
       <c r="K89" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L89" s="20" t="inlineStr">
         <is>
@@ -14127,12 +14171,12 @@
       </c>
       <c r="M89" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kročejová EPS shora ocelobeton</t>
+          <t>TZ ARS dům §4 — EPS 150 λ=0.035 tl. 120 mm</t>
         </is>
       </c>
       <c r="N89" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#4</t>
         </is>
       </c>
       <c r="O89" s="26" t="inlineStr">
@@ -14153,41 +14197,41 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Klempíř</t>
+          <t>PSV-71 Izolace TI</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>Oplechování krytiny</t>
-        </is>
-      </c>
-      <c r="D90" s="20" t="inlineStr">
-        <is>
-          <t>764312235</t>
+          <t>Kročejová EPS nad ocelobeton</t>
+        </is>
+      </c>
+      <c r="D90" s="27" t="inlineStr">
+        <is>
+          <t>713121??? ?</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>Klempířské oplechování krytiny — úžlabí, hřeben, štítové lemy (Al / Pzn lakovaný 0.55 mm)</t>
+          <t>Kročejová EPS 150 / 30 dB tl. 30 mm nad ocelobetonovým stropem 2.NP/3.NP</t>
         </is>
       </c>
       <c r="F90" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G90" s="22" t="n">
-        <v>69.5</v>
+        <v>104.4</v>
       </c>
       <c r="H90" s="10" t="n"/>
       <c r="I90" s="10" t="n"/>
       <c r="J90" s="8" t="inlineStr">
         <is>
-          <t>klempir</t>
+          <t>izolater_TI</t>
         </is>
       </c>
       <c r="K90" s="24" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="L90" s="20" t="inlineStr">
         <is>
@@ -14196,12 +14240,12 @@
       </c>
       <c r="M90" s="8" t="inlineStr">
         <is>
-          <t>DXF MA_klempíř (75.4 m) + SM__ klempířina (98.4 m) total = 173.8 m × 0.40 split heuristic — Path C Tier 3</t>
+          <t>TZ ARS dům §4 — kročejová EPS shora ocelobeton</t>
         </is>
       </c>
       <c r="N90" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O90" s="26" t="inlineStr">
@@ -14212,12 +14256,7 @@
       <c r="P90" s="41" t="n"/>
       <c r="Q90" s="41" t="inlineStr">
         <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED_CHAPTER_MATCH</t>
-        </is>
-      </c>
-      <c r="R90" s="41" t="inlineStr">
-        <is>
-          <t>PSV-76 Klempíř items sum 159.9 m vs DXF MA_klempíř + SM__ klempířina total 173.8 m, Δ -8.0 % (-13.9 m). Within ±15 % tolerance per CEV Matrix D.4 verdict (gate-3). FLAG for Karel site walkthrough — possible missing klempíř segment (small). Source: outputs/cev_matrix_d_cross_doc_consistency.json D.4.</t>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
         </is>
       </c>
     </row>
@@ -14232,17 +14271,17 @@
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>Venkovní parapety oken</t>
+          <t>Oplechování krytiny</t>
         </is>
       </c>
       <c r="D91" s="20" t="inlineStr">
         <is>
-          <t>764218201</t>
+          <t>764312235</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>Venkovní parapety oken — Pzn plech lakovaný 250 mm × tl. 0.55 mm × 16 ks oken</t>
+          <t>Klempířské oplechování krytiny — úžlabí, hřeben, štítové lemy (Al / Pzn lakovaný 0.55 mm)</t>
         </is>
       </c>
       <c r="F91" s="20" t="inlineStr">
@@ -14251,7 +14290,7 @@
         </is>
       </c>
       <c r="G91" s="22" t="n">
-        <v>20.8</v>
+        <v>69.5</v>
       </c>
       <c r="H91" s="10" t="n"/>
       <c r="I91" s="10" t="n"/>
@@ -14261,7 +14300,7 @@
         </is>
       </c>
       <c r="K91" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L91" s="20" t="inlineStr">
         <is>
@@ -14270,12 +14309,12 @@
       </c>
       <c r="M91" s="8" t="inlineStr">
         <is>
-          <t>DXF okna 16 ks INSERT blocks + standard parapet width</t>
+          <t>DXF MA_klempíř (75.4 m) + SM__ klempířina (98.4 m) total = 173.8 m × 0.40 split heuristic — Path C Tier 3</t>
         </is>
       </c>
       <c r="N91" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O91" s="26" t="inlineStr">
@@ -14306,17 +14345,17 @@
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>Dešťové svody + žlaby</t>
+          <t>Venkovní parapety oken</t>
         </is>
       </c>
       <c r="D92" s="20" t="inlineStr">
         <is>
-          <t>764454802</t>
+          <t>764218201</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>Dešťové svody Pzn 100 mm + žlaby — 4 svody × ~14 m + žlaby per obvod střechy</t>
+          <t>Venkovní parapety oken — Pzn plech lakovaný 250 mm × tl. 0.55 mm × 16 ks oken</t>
         </is>
       </c>
       <c r="F92" s="20" t="inlineStr">
@@ -14325,7 +14364,7 @@
         </is>
       </c>
       <c r="G92" s="22" t="n">
-        <v>43.5</v>
+        <v>20.8</v>
       </c>
       <c r="H92" s="10" t="n"/>
       <c r="I92" s="10" t="n"/>
@@ -14335,7 +14374,7 @@
         </is>
       </c>
       <c r="K92" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L92" s="20" t="inlineStr">
         <is>
@@ -14344,7 +14383,7 @@
       </c>
       <c r="M92" s="8" t="inlineStr">
         <is>
-          <t>DXF klempířina lengths split + TZ ARS dešťové svody</t>
+          <t>DXF okna 16 ks INSERT blocks + standard parapet width</t>
         </is>
       </c>
       <c r="N92" s="20" t="inlineStr">
@@ -14380,17 +14419,17 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>Vikýře + atika + závětrné lemy</t>
+          <t>Dešťové svody + žlaby</t>
         </is>
       </c>
       <c r="D93" s="20" t="inlineStr">
         <is>
-          <t>764315235</t>
+          <t>764454802</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>Klempířské doplňky vikýřů + atika + závětrné lemy (4 vikýře komplexní detail)</t>
+          <t>Dešťové svody Pzn 100 mm + žlaby — 4 svody × ~14 m + žlaby per obvod střechy</t>
         </is>
       </c>
       <c r="F93" s="20" t="inlineStr">
@@ -14399,7 +14438,7 @@
         </is>
       </c>
       <c r="G93" s="22" t="n">
-        <v>26.1</v>
+        <v>43.5</v>
       </c>
       <c r="H93" s="10" t="n"/>
       <c r="I93" s="10" t="n"/>
@@ -14418,7 +14457,7 @@
       </c>
       <c r="M93" s="8" t="inlineStr">
         <is>
-          <t>DXF klempířina geometry split + TZ ARS 4 vikýře</t>
+          <t>DXF klempířina lengths split + TZ ARS dešťové svody</t>
         </is>
       </c>
       <c r="N93" s="20" t="inlineStr">
@@ -14449,50 +14488,50 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Truhlář</t>
+          <t>PSV-76 Klempíř</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stupně schodišť</t>
+          <t>Vikýře + atika + závětrné lemy</t>
         </is>
       </c>
       <c r="D94" s="20" t="inlineStr">
         <is>
-          <t>766811111</t>
+          <t>764315235</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stupně ocelových schodišť (truhlářské, dub masiv tl. 40 mm)</t>
+          <t>Klempířské doplňky vikýřů + atika + závětrné lemy (4 vikýře komplexní detail)</t>
         </is>
       </c>
       <c r="F94" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G94" s="23" t="n">
-        <v>16</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G94" s="22" t="n">
+        <v>26.1</v>
       </c>
       <c r="H94" s="10" t="n"/>
       <c r="I94" s="10" t="n"/>
       <c r="J94" s="8" t="inlineStr">
         <is>
-          <t>truhlar</t>
+          <t>klempir</t>
         </is>
       </c>
       <c r="K94" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L94" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni truhlářské</t>
+          <t>DXF klempířina geometry split + TZ ARS 4 vikýře</t>
         </is>
       </c>
       <c r="N94" s="20" t="inlineStr">
@@ -14506,7 +14545,16 @@
         </is>
       </c>
       <c r="P94" s="41" t="n"/>
-      <c r="Q94" s="41" t="n"/>
+      <c r="Q94" s="41" t="inlineStr">
+        <is>
+          <t>URS_PHASE5B_FAMILY_VERIFIED_CHAPTER_MATCH</t>
+        </is>
+      </c>
+      <c r="R94" s="41" t="inlineStr">
+        <is>
+          <t>PSV-76 Klempíř items sum 159.9 m vs DXF MA_klempíř + SM__ klempířina total 173.8 m, Δ -8.0 % (-13.9 m). Within ±15 % tolerance per CEV Matrix D.4 verdict (gate-3). FLAG for Karel site walkthrough — possible missing klempíř segment (small). Source: outputs/cev_matrix_d_cross_doc_consistency.json D.4.</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="20" t="n">
@@ -14519,26 +14567,26 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>Terasa garapa za opěrnou stěnou — dřevěná pochozí vrstva</t>
-        </is>
-      </c>
-      <c r="D95" s="27" t="inlineStr">
-        <is>
-          <t>762??? ?</t>
+          <t>Dřevěné stupně schodišť</t>
+        </is>
+      </c>
+      <c r="D95" s="20" t="inlineStr">
+        <is>
+          <t>766811111</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném roštu z hranolů 50 mm na rektifikovatelných terčích (terče + podkladní skladba viz HSV1.005)</t>
+          <t>Dřevěné stupně ocelových schodišť (truhlářské, dub masiv tl. 40 mm)</t>
         </is>
       </c>
       <c r="F95" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G95" s="22" t="n">
-        <v>9.23</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G95" s="23" t="n">
+        <v>16</v>
       </c>
       <c r="H95" s="10" t="n"/>
       <c r="I95" s="10" t="n"/>
@@ -14548,16 +14596,16 @@
         </is>
       </c>
       <c r="K95" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L95" s="20" t="inlineStr">
         <is>
-          <t>family_762_leaf_lookup_required</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M95" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + DXF dum_situace PLOT_DREVENY_04 (terasa, ne 3.NP); ŘEZ C-C potvrzuje dřevěný rošt z hranolů (NE hliníkový) + dřevěnou pochozí vrstvu</t>
+          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni truhlářské</t>
         </is>
       </c>
       <c r="N95" s="20" t="inlineStr">
@@ -14571,11 +14619,7 @@
         </is>
       </c>
       <c r="P95" s="41" t="n"/>
-      <c r="Q95" s="41" t="inlineStr">
-        <is>
-          <t>REZ_CC_TERASA_FIX_2026-05-29; SITUACE_AREA_FIX_2026-05-29</t>
-        </is>
-      </c>
+      <c r="Q95" s="41" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="20" t="n">
@@ -14583,55 +14627,55 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>PSV-76 Truhlář</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 1.NP' (ulice)</t>
-        </is>
-      </c>
-      <c r="D96" s="20" t="inlineStr">
-        <is>
-          <t>766621011</t>
+          <t>Terasa garapa za opěrnou stěnou — dřevěná pochozí vrstva</t>
+        </is>
+      </c>
+      <c r="D96" s="27" t="inlineStr">
+        <is>
+          <t>762??? ?</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP' velikost 1185×1600 mm × 2 ks (fasáda ulice)</t>
+          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném roštu z hranolů 50 mm na rektifikovatelných terčích (terče + podkladní skladba viz HSV1.005)</t>
         </is>
       </c>
       <c r="F96" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G96" s="23" t="n">
-        <v>2</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G96" s="22" t="n">
+        <v>9.23</v>
       </c>
       <c r="H96" s="10" t="n"/>
       <c r="I96" s="10" t="n"/>
       <c r="J96" s="8" t="inlineStr">
         <is>
-          <t>okennar</t>
+          <t>truhlar</t>
         </is>
       </c>
       <c r="K96" s="24" t="n">
-        <v>0.99</v>
+        <v>0.95</v>
       </c>
       <c r="L96" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>family_762_leaf_lookup_required</t>
         </is>
       </c>
       <c r="M96" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 1.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>TZ ARS dům §4 + DXF dum_situace PLOT_DREVENY_04 (terasa, ne 3.NP); ŘEZ C-C potvrzuje dřevěný rošt z hranolů (NE hliníkový) + dřevěnou pochozí vrstvu</t>
         </is>
       </c>
       <c r="N96" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O96" s="26" t="inlineStr">
@@ -14640,7 +14684,11 @@
         </is>
       </c>
       <c r="P96" s="41" t="n"/>
-      <c r="Q96" s="41" t="n"/>
+      <c r="Q96" s="41" t="inlineStr">
+        <is>
+          <t>REZ_CC_TERASA_FIX_2026-05-29; SITUACE_AREA_FIX_2026-05-29</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="20" t="n">
@@ -14653,7 +14701,7 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada)</t>
+          <t>Plastové okno trojsklo — 'okno 1.NP' (ulice)</t>
         </is>
       </c>
       <c r="D97" s="20" t="inlineStr">
@@ -14663,7 +14711,7 @@
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP vzadu' velikost 920×1600 mm × 3 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP' velikost 1185×1600 mm × 2 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="F97" s="20" t="inlineStr">
@@ -14672,7 +14720,7 @@
         </is>
       </c>
       <c r="G97" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H97" s="10" t="n"/>
       <c r="I97" s="10" t="n"/>
@@ -14686,12 +14734,12 @@
       </c>
       <c r="L97" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M97" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 1.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 1.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N97" s="20" t="inlineStr">
@@ -14718,7 +14766,7 @@
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 2.NP' (ulice)</t>
+          <t>Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D98" s="20" t="inlineStr">
@@ -14728,7 +14776,7 @@
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 2.NP' velikost 1160×1480 mm × 4 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP vzadu' velikost 920×1600 mm × 3 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F98" s="20" t="inlineStr">
@@ -14737,7 +14785,7 @@
         </is>
       </c>
       <c r="G98" s="23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H98" s="10" t="n"/>
       <c r="I98" s="10" t="n"/>
@@ -14756,7 +14804,7 @@
       </c>
       <c r="M98" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 2.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 1.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N98" s="20" t="inlineStr">
@@ -14783,7 +14831,7 @@
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 3.NP' (ulice)</t>
+          <t>Plastové okno trojsklo — 'okno 2.NP' (ulice)</t>
         </is>
       </c>
       <c r="D99" s="20" t="inlineStr">
@@ -14793,7 +14841,7 @@
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP' velikost 1785×1241 mm × 3 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 2.NP' velikost 1160×1480 mm × 4 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="F99" s="20" t="inlineStr">
@@ -14802,7 +14850,7 @@
         </is>
       </c>
       <c r="G99" s="23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H99" s="10" t="n"/>
       <c r="I99" s="10" t="n"/>
@@ -14821,7 +14869,7 @@
       </c>
       <c r="M99" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 3.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 2.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N99" s="20" t="inlineStr">
@@ -14848,7 +14896,7 @@
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 3.NP vzadu' (zahrada)</t>
+          <t>Plastové okno trojsklo — 'okno 3.NP' (ulice)</t>
         </is>
       </c>
       <c r="D100" s="20" t="inlineStr">
@@ -14858,7 +14906,7 @@
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP vzadu' velikost 2075×1241 mm × 1 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP' velikost 1785×1241 mm × 3 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="F100" s="20" t="inlineStr">
@@ -14867,7 +14915,7 @@
         </is>
       </c>
       <c r="G100" s="23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H100" s="10" t="n"/>
       <c r="I100" s="10" t="n"/>
@@ -14886,7 +14934,7 @@
       </c>
       <c r="M100" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 3.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N100" s="20" t="inlineStr">
@@ -14913,7 +14961,7 @@
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno male 3.NP vzadu' (zahrada)</t>
+          <t>Plastové okno trojsklo — 'okno 3.NP vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D101" s="20" t="inlineStr">
@@ -14923,7 +14971,7 @@
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno male 3.NP vzadu' velikost 800×1241 mm × 1 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP vzadu' velikost 2075×1241 mm × 1 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F101" s="20" t="inlineStr">
@@ -14951,7 +14999,7 @@
       </c>
       <c r="M101" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno male 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N101" s="20" t="inlineStr">
@@ -14978,7 +15026,7 @@
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno malé vzadu' (zahrada)</t>
+          <t>Plastové okno trojsklo — 'okno male 3.NP vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D102" s="20" t="inlineStr">
@@ -14988,7 +15036,7 @@
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno malé vzadu' velikost 700×800 mm × 2 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno male 3.NP vzadu' velikost 800×1241 mm × 1 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F102" s="20" t="inlineStr">
@@ -14997,7 +15045,7 @@
         </is>
       </c>
       <c r="G102" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H102" s="10" t="n"/>
       <c r="I102" s="10" t="n"/>
@@ -15016,7 +15064,7 @@
       </c>
       <c r="M102" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno malé vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno male 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N102" s="20" t="inlineStr">
@@ -15043,17 +15091,17 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>Žaluzie kastlík purenit</t>
+          <t>Plastové okno trojsklo — 'okno malé vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D103" s="20" t="inlineStr">
         <is>
-          <t>766631211</t>
+          <t>766621011</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>Integrované stínící venkovní žaluzie v kastlíku pod omítkou s purenitovou izolací — uliční fasáda Fibichova (9 ks)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno malé vzadu' velikost 700×800 mm × 2 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F103" s="20" t="inlineStr">
@@ -15062,17 +15110,17 @@
         </is>
       </c>
       <c r="G103" s="23" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H103" s="10" t="n"/>
       <c r="I103" s="10" t="n"/>
       <c r="J103" s="8" t="inlineStr">
         <is>
-          <t>okenni_zaluzie_kastlik_purenit</t>
+          <t>okennar</t>
         </is>
       </c>
       <c r="K103" s="24" t="n">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="L103" s="20" t="inlineStr">
         <is>
@@ -15081,7 +15129,7 @@
       </c>
       <c r="M103" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — 'do ulice Fibichova s integrovanými stínícími žaluziemi v kastlíku pod omítkou s purenitovou izolací'</t>
+          <t>DXF dum_DPZ INSERT block 'okno malé vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N103" s="20" t="inlineStr">
@@ -15108,17 +15156,17 @@
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>Vstupní plastové dveře</t>
+          <t>Žaluzie kastlík purenit</t>
         </is>
       </c>
       <c r="D104" s="20" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>766631211</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>Plastové vstupní dveře (ulice + zahrada) — 2 ks</t>
+          <t>Integrované stínící venkovní žaluzie v kastlíku pod omítkou s purenitovou izolací — uliční fasáda Fibichova (9 ks)</t>
         </is>
       </c>
       <c r="F104" s="20" t="inlineStr">
@@ -15127,17 +15175,17 @@
         </is>
       </c>
       <c r="G104" s="23" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H104" s="10" t="n"/>
       <c r="I104" s="10" t="n"/>
       <c r="J104" s="8" t="inlineStr">
         <is>
-          <t>okennar</t>
+          <t>okenni_zaluzie_kastlik_purenit</t>
         </is>
       </c>
       <c r="K104" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L104" s="20" t="inlineStr">
         <is>
@@ -15146,12 +15194,12 @@
       </c>
       <c r="M104" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — plastové vstupní dveře</t>
+          <t>TZ ARS dům §3.2 — 'do ulice Fibichova s integrovanými stínícími žaluziemi v kastlíku pod omítkou s purenitovou izolací'</t>
         </is>
       </c>
       <c r="N104" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O104" s="26" t="inlineStr">
@@ -15173,17 +15221,17 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>Vnitřní dveře DTD laminované</t>
+          <t>Vstupní plastové dveře</t>
         </is>
       </c>
       <c r="D105" s="20" t="inlineStr">
         <is>
-          <t>766660035</t>
+          <t>766682111</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>Vnitřní dveře DTD laminované s obložkovou zárubní — odhad 15 ks</t>
+          <t>Plastové vstupní dveře (ulice + zahrada) — 2 ks</t>
         </is>
       </c>
       <c r="F105" s="20" t="inlineStr">
@@ -15192,13 +15240,13 @@
         </is>
       </c>
       <c r="G105" s="23" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H105" s="10" t="n"/>
       <c r="I105" s="10" t="n"/>
       <c r="J105" s="8" t="inlineStr">
         <is>
-          <t>truhlar</t>
+          <t>okennar</t>
         </is>
       </c>
       <c r="K105" s="24" t="n">
@@ -15211,12 +15259,12 @@
       </c>
       <c r="M105" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + DXF MTEXT room labels</t>
+          <t>TZ ARS dům §4 — plastové vstupní dveře</t>
         </is>
       </c>
       <c r="N105" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O105" s="26" t="inlineStr">
@@ -15238,17 +15286,17 @@
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>Požárně odolné dveře EI 30 DP3</t>
+          <t>Vnitřní dveře DTD laminované</t>
         </is>
       </c>
       <c r="D106" s="20" t="inlineStr">
         <is>
-          <t>766694112</t>
+          <t>766660035</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>Požárně odolné jednokřídlové dveře EI 30 DP3 na vrcholu schodiště mezi 1.PP a 1.NP — uzavírá otvor v REI 90 stropu klenby sklepa (per PBŘ TUSPO § 'Požární uzávěry otvorů v požárních stěnách a požárních stropech: podzemní 30 DP1')</t>
+          <t>Vnitřní dveře DTD laminované s obložkovou zárubní — odhad 15 ks</t>
         </is>
       </c>
       <c r="F106" s="20" t="inlineStr">
@@ -15257,17 +15305,17 @@
         </is>
       </c>
       <c r="G106" s="23" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H106" s="10" t="n"/>
       <c r="I106" s="10" t="n"/>
       <c r="J106" s="8" t="inlineStr">
         <is>
-          <t>specialista_RC3_dvere</t>
+          <t>truhlar</t>
         </is>
       </c>
       <c r="K106" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L106" s="20" t="inlineStr">
         <is>
@@ -15276,12 +15324,12 @@
       </c>
       <c r="M106" s="8" t="inlineStr">
         <is>
-          <t>PBŘ TUSPO § Požární uzávěry otvorů 'podzemní 30DP1'; DXF schodiště 1.PP→1.NP</t>
+          <t>TZ ARS dům §4 + DXF MTEXT room labels</t>
         </is>
       </c>
       <c r="N106" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O106" s="26" t="inlineStr">
@@ -15290,11 +15338,7 @@
         </is>
       </c>
       <c r="P106" s="41" t="n"/>
-      <c r="Q106" s="41" t="inlineStr">
-        <is>
-          <t>GAP_008</t>
-        </is>
-      </c>
+      <c r="Q106" s="41" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="20" t="n">
@@ -15307,17 +15351,17 @@
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>Oplechování venkovních parapetů Pzn — 16 ks</t>
+          <t>Požárně odolné dveře EI 30 DP3</t>
         </is>
       </c>
       <c r="D107" s="20" t="inlineStr">
         <is>
-          <t>764811112</t>
+          <t>766694112</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>Oplechování venkovních parapetů Pzn plech lakovaný 250 mm × tl. 0.55 mm, vč. okapnice + boční zakončení — 16 ks (per DXF INSERT okno × 16)</t>
+          <t>Požárně odolné jednokřídlové dveře EI 30 DP3 na vrcholu schodiště mezi 1.PP a 1.NP — uzavírá otvor v REI 90 stropu klenby sklepa (per PBŘ TUSPO § 'Požární uzávěry otvorů v požárních stěnách a požárních stropech: podzemní 30 DP1')</t>
         </is>
       </c>
       <c r="F107" s="20" t="inlineStr">
@@ -15326,17 +15370,17 @@
         </is>
       </c>
       <c r="G107" s="23" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H107" s="10" t="n"/>
       <c r="I107" s="10" t="n"/>
       <c r="J107" s="8" t="inlineStr">
         <is>
-          <t>klempir</t>
+          <t>specialista_RC3_dvere</t>
         </is>
       </c>
       <c r="K107" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L107" s="20" t="inlineStr">
         <is>
@@ -15345,7 +15389,7 @@
       </c>
       <c r="M107" s="8" t="inlineStr">
         <is>
-          <t>DXF blocks okno* 16 ks + DXF klempir_parapet 16 ks (Path C Tier 4 INSERT discovery)</t>
+          <t>PBŘ TUSPO § Požární uzávěry otvorů 'podzemní 30DP1'; DXF schodiště 1.PP→1.NP</t>
         </is>
       </c>
       <c r="N107" s="20" t="inlineStr">
@@ -15361,7 +15405,7 @@
       <c r="P107" s="41" t="n"/>
       <c r="Q107" s="41" t="inlineStr">
         <is>
-          <t>GAP_004</t>
+          <t>GAP_008</t>
         </is>
       </c>
     </row>
@@ -15371,55 +15415,55 @@
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>Ocelové schodiště UPE200 ze zahrady</t>
+          <t>Oplechování venkovních parapetů Pzn — 16 ks</t>
         </is>
       </c>
       <c r="D108" s="20" t="inlineStr">
         <is>
-          <t>767531111</t>
+          <t>764811112</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>Ocelové schodiště ze zahrady na mezipodestu — UPE200 schodnice + dřevěné nášlapy, kotvené do koruny opěrné stěny a zdiva (TZ statika §4)</t>
+          <t>Oplechování venkovních parapetů Pzn plech lakovaný 250 mm × tl. 0.55 mm, vč. okapnice + boční zakončení — 16 ks (per DXF INSERT okno × 16)</t>
         </is>
       </c>
       <c r="F108" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G108" s="23" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H108" s="10" t="n"/>
       <c r="I108" s="10" t="n"/>
       <c r="J108" s="8" t="inlineStr">
         <is>
-          <t>zamecnik_PSV</t>
+          <t>klempir</t>
         </is>
       </c>
       <c r="K108" s="24" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="L108" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M108" s="8" t="inlineStr">
         <is>
-          <t>TZ statika dům §4 — schodiště UPE200 + UPE100 podružné prvky</t>
+          <t>DXF blocks okno* 16 ks + DXF klempir_parapet 16 ks (Path C Tier 4 INSERT discovery)</t>
         </is>
       </c>
       <c r="N108" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O108" s="26" t="inlineStr">
@@ -15430,7 +15474,7 @@
       <c r="P108" s="41" t="n"/>
       <c r="Q108" s="41" t="inlineStr">
         <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+          <t>GAP_004</t>
         </is>
       </c>
     </row>
@@ -15445,7 +15489,7 @@
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>Ocelové schodiště do spacího patra 3.NP</t>
+          <t>Ocelové schodiště UPE200 ze zahrady</t>
         </is>
       </c>
       <c r="D109" s="20" t="inlineStr">
@@ -15455,7 +15499,7 @@
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>Interní ocelové schodiště do spacího patra v 3.NP s dřevěnými stupni (truhlářské)</t>
+          <t>Ocelové schodiště ze zahrady na mezipodestu — UPE200 schodnice + dřevěné nášlapy, kotvené do koruny opěrné stěny a zdiva (TZ statika §4)</t>
         </is>
       </c>
       <c r="F109" s="20" t="inlineStr">
@@ -15483,12 +15527,12 @@
       </c>
       <c r="M109" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni</t>
+          <t>TZ statika dům §4 — schodiště UPE200 + UPE100 podružné prvky</t>
         </is>
       </c>
       <c r="N109" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O109" s="26" t="inlineStr">
@@ -15514,26 +15558,26 @@
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>Stříšky nad vstupy</t>
+          <t>Ocelové schodiště do spacího patra 3.NP</t>
         </is>
       </c>
       <c r="D110" s="20" t="inlineStr">
         <is>
-          <t>767532111</t>
+          <t>767531111</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>Stříšky nad vstupy z ocelové konstrukce + Cetris desky + falcovaná krytina — 2 ks (ulice + zahrada)</t>
+          <t>Interní ocelové schodiště do spacího patra v 3.NP s dřevěnými stupni (truhlářské)</t>
         </is>
       </c>
       <c r="F110" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G110" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H110" s="10" t="n"/>
       <c r="I110" s="10" t="n"/>
@@ -15543,16 +15587,16 @@
         </is>
       </c>
       <c r="K110" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L110" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M110" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — stříšky nad vstupy ocel+Cetris+plech</t>
+          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni</t>
         </is>
       </c>
       <c r="N110" s="20" t="inlineStr">
@@ -15566,7 +15610,11 @@
         </is>
       </c>
       <c r="P110" s="41" t="n"/>
-      <c r="Q110" s="41" t="n"/>
+      <c r="Q110" s="41" t="inlineStr">
+        <is>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="20" t="n">
@@ -15579,26 +15627,26 @@
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>Zábradlí z jeklů + nerez výplň</t>
+          <t>Stříšky nad vstupy</t>
         </is>
       </c>
       <c r="D111" s="20" t="inlineStr">
         <is>
-          <t>767163115</t>
+          <t>767532111</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>Ocelové zábradlí svařované z jeklů + nerez výplň pZn antracit — schodiště interier + venkovní terasa</t>
+          <t>Stříšky nad vstupy z ocelové konstrukce + Cetris desky + falcovaná krytina — 2 ks (ulice + zahrada)</t>
         </is>
       </c>
       <c r="F111" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G111" s="22" t="n">
-        <v>18</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G111" s="23" t="n">
+        <v>2</v>
       </c>
       <c r="H111" s="10" t="n"/>
       <c r="I111" s="10" t="n"/>
@@ -15617,7 +15665,7 @@
       </c>
       <c r="M111" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — zábradlí svařované z jeklů + nerez výplň</t>
+          <t>TZ ARS dům §4 — stříšky nad vstupy ocel+Cetris+plech</t>
         </is>
       </c>
       <c r="N111" s="20" t="inlineStr">
@@ -15639,55 +15687,55 @@
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>Nášlap vinyl obytné místnosti</t>
+          <t>Zábradlí z jeklů + nerez výplň</t>
         </is>
       </c>
       <c r="D112" s="20" t="inlineStr">
         <is>
-          <t>776511820</t>
+          <t>767163115</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva vinyl tl. 4 mm na suchou skladbu — obytné místnosti (ložnice, obývák, kuchyně, chodby)</t>
+          <t>Ocelové zábradlí svařované z jeklů + nerez výplň pZn antracit — schodiště interier + venkovní terasa</t>
         </is>
       </c>
       <c r="F112" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G112" s="22" t="n">
-        <v>171.5</v>
+        <v>18</v>
       </c>
       <c r="H112" s="10" t="n"/>
       <c r="I112" s="10" t="n"/>
       <c r="J112" s="8" t="inlineStr">
         <is>
-          <t>podlahar</t>
+          <t>zamecnik_PSV</t>
         </is>
       </c>
       <c r="K112" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L112" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M112" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (kuchyně/obytná/chodba = vinyl) + TZ ARS §3.2.4 nášlapná vrstva</t>
+          <t>TZ ARS dům §4 — zábradlí svařované z jeklů + nerez výplň</t>
         </is>
       </c>
       <c r="N112" s="20" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O112" s="26" t="inlineStr">
@@ -15696,11 +15744,7 @@
         </is>
       </c>
       <c r="P112" s="41" t="n"/>
-      <c r="Q112" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+      <c r="Q112" s="41" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="20" t="n">
@@ -15713,17 +15757,17 @@
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>Nášlap keramická dlažba — mokré zóny</t>
+          <t>Nášlap vinyl obytné místnosti</t>
         </is>
       </c>
       <c r="D113" s="20" t="inlineStr">
         <is>
-          <t>771274102</t>
+          <t>776511820</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva keramická dlažba lepená — koupelny + WC + spíž + komora (NÁDRŽ NP)</t>
+          <t>Nášlapná vrstva vinyl tl. 4 mm na suchou skladbu — obytné místnosti (ložnice, obývák, kuchyně, chodby)</t>
         </is>
       </c>
       <c r="F113" s="20" t="inlineStr">
@@ -15732,13 +15776,13 @@
         </is>
       </c>
       <c r="G113" s="22" t="n">
-        <v>13.5</v>
+        <v>171.5</v>
       </c>
       <c r="H113" s="10" t="n"/>
       <c r="I113" s="10" t="n"/>
       <c r="J113" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>podlahar</t>
         </is>
       </c>
       <c r="K113" s="24" t="n">
@@ -15746,12 +15790,12 @@
       </c>
       <c r="L113" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M113" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (koupelna/WC/spíž = dlažba mokré) + TZ ARS skladba mokrá</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (kuchyně/obytná/chodba = vinyl) + TZ ARS §3.2.4 nášlapná vrstva</t>
         </is>
       </c>
       <c r="N113" s="20" t="inlineStr">
@@ -15765,7 +15809,11 @@
         </is>
       </c>
       <c r="P113" s="41" t="n"/>
-      <c r="Q113" s="41" t="n"/>
+      <c r="Q113" s="41" t="inlineStr">
+        <is>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="20" t="n">
@@ -15778,7 +15826,7 @@
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>Nášlap keramická dlažba — 1.PP sklep</t>
+          <t>Nášlap keramická dlažba — mokré zóny</t>
         </is>
       </c>
       <c r="D114" s="20" t="inlineStr">
@@ -15788,7 +15836,7 @@
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva keramická dlažba — 1.PP technické místnosti (sušárna + sklepy + schodiště + chodba)</t>
+          <t>Nášlapná vrstva keramická dlažba lepená — koupelny + WC + spíž + komora (NÁDRŽ NP)</t>
         </is>
       </c>
       <c r="F114" s="20" t="inlineStr">
@@ -15797,7 +15845,7 @@
         </is>
       </c>
       <c r="G114" s="22" t="n">
-        <v>32.4</v>
+        <v>13.5</v>
       </c>
       <c r="H114" s="10" t="n"/>
       <c r="I114" s="10" t="n"/>
@@ -15816,7 +15864,7 @@
       </c>
       <c r="M114" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — 1.PP all rooms = dlažba sklep zone</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (koupelna/WC/spíž = dlažba mokré) + TZ ARS skladba mokrá</t>
         </is>
       </c>
       <c r="N114" s="20" t="inlineStr">
@@ -15843,17 +15891,17 @@
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>Nášlap biodeska 3.NP spací patro</t>
+          <t>Nášlap keramická dlažba — 1.PP sklep</t>
         </is>
       </c>
       <c r="D115" s="20" t="inlineStr">
         <is>
-          <t>766411111</t>
+          <t>771274102</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva biodeska (smrk masiv) nebo OSB v 3.NP spací části nad krovem</t>
+          <t>Nášlapná vrstva keramická dlažba — 1.PP technické místnosti (sušárna + sklepy + schodiště + chodba)</t>
         </is>
       </c>
       <c r="F115" s="20" t="inlineStr">
@@ -15862,17 +15910,17 @@
         </is>
       </c>
       <c r="G115" s="22" t="n">
-        <v>25</v>
+        <v>32.4</v>
       </c>
       <c r="H115" s="10" t="n"/>
       <c r="I115" s="10" t="n"/>
       <c r="J115" s="8" t="inlineStr">
         <is>
-          <t>biodeska_konstrukcni</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K115" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L115" s="20" t="inlineStr">
         <is>
@@ -15881,12 +15929,12 @@
       </c>
       <c r="M115" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.3 — biodeska patro pro přespání</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — 1.PP all rooms = dlažba sklep zone</t>
         </is>
       </c>
       <c r="N115" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>#4</t>
         </is>
       </c>
       <c r="O115" s="26" t="inlineStr">
@@ -15908,17 +15956,17 @@
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>Betonový potěr s kari nad EPS</t>
+          <t>Nášlap biodeska 3.NP spací patro</t>
         </is>
       </c>
       <c r="D116" s="20" t="inlineStr">
         <is>
-          <t>631321311</t>
+          <t>766411111</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>Mokrá podlahová skladba — betonový potěr s kari síťkou 4/100/100 tl. 50 mm + samonivelační stěrka</t>
+          <t>Nášlapná vrstva biodeska (smrk masiv) nebo OSB v 3.NP spací části nad krovem</t>
         </is>
       </c>
       <c r="F116" s="20" t="inlineStr">
@@ -15927,17 +15975,17 @@
         </is>
       </c>
       <c r="G116" s="22" t="n">
-        <v>126.4</v>
+        <v>25</v>
       </c>
       <c r="H116" s="10" t="n"/>
       <c r="I116" s="10" t="n"/>
       <c r="J116" s="8" t="inlineStr">
         <is>
-          <t>podlahar</t>
+          <t>biodeska_konstrukcni</t>
         </is>
       </c>
       <c r="K116" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L116" s="20" t="inlineStr">
         <is>
@@ -15946,12 +15994,12 @@
       </c>
       <c r="M116" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.4 + §3.2.x — 'kročejová izolace + betonový potěr s kari sítí'; DXF rooms areas</t>
+          <t>TZ ARS dům §3.2.3 — biodeska patro pro přespání</t>
         </is>
       </c>
       <c r="N116" s="20" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O116" s="26" t="inlineStr">
@@ -15973,26 +16021,26 @@
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>Soklíky vinyl</t>
+          <t>Betonový potěr s kari nad EPS</t>
         </is>
       </c>
       <c r="D117" s="20" t="inlineStr">
         <is>
-          <t>776511831</t>
+          <t>631321311</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>Soklíky podlahové laminátové (dub) v obytných místnostech s vinyl podlahou</t>
+          <t>Mokrá podlahová skladba — betonový potěr s kari síťkou 4/100/100 tl. 50 mm + samonivelační stěrka</t>
         </is>
       </c>
       <c r="F117" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G117" s="22" t="n">
-        <v>72.03</v>
+        <v>126.4</v>
       </c>
       <c r="H117" s="10" t="n"/>
       <c r="I117" s="10" t="n"/>
@@ -16011,12 +16059,12 @@
       </c>
       <c r="M117" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms vinyl + standard ratio per RD geometry</t>
+          <t>TZ ARS dům §3.2.4 + §3.2.x — 'kročejová izolace + betonový potěr s kari sítí'; DXF rooms areas</t>
         </is>
       </c>
       <c r="N117" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#4</t>
         </is>
       </c>
       <c r="O117" s="26" t="inlineStr">
@@ -16038,17 +16086,17 @@
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>Soklíky keramické</t>
+          <t>Soklíky vinyl</t>
         </is>
       </c>
       <c r="D118" s="20" t="inlineStr">
         <is>
-          <t>771274107</t>
+          <t>776511831</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>Soklíky keramické v místnostech s dlažbou (koupelny + WC + spíž + 1.PP)</t>
+          <t>Soklíky podlahové laminátové (dub) v obytných místnostech s vinyl podlahou</t>
         </is>
       </c>
       <c r="F118" s="20" t="inlineStr">
@@ -16057,13 +16105,13 @@
         </is>
       </c>
       <c r="G118" s="22" t="n">
-        <v>19.28</v>
+        <v>72.03</v>
       </c>
       <c r="H118" s="10" t="n"/>
       <c r="I118" s="10" t="n"/>
       <c r="J118" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>podlahar</t>
         </is>
       </c>
       <c r="K118" s="24" t="n">
@@ -16076,7 +16124,7 @@
       </c>
       <c r="M118" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms dlažba + standard ratio per RD geometry</t>
+          <t>DXF rooms vinyl + standard ratio per RD geometry</t>
         </is>
       </c>
       <c r="N118" s="20" t="inlineStr">
@@ -16098,41 +16146,41 @@
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 1.PP</t>
+          <t>Soklíky keramické</t>
         </is>
       </c>
       <c r="D119" s="20" t="inlineStr">
         <is>
-          <t>612311311</t>
+          <t>771274107</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.PP (stávající vyspravené + nové zděné)</t>
+          <t>Soklíky keramické v místnostech s dlažbou (koupelny + WC + spíž + 1.PP)</t>
         </is>
       </c>
       <c r="F119" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G119" s="22" t="n">
-        <v>78.2</v>
+        <v>19.28</v>
       </c>
       <c r="H119" s="10" t="n"/>
       <c r="I119" s="10" t="n"/>
       <c r="J119" s="8" t="inlineStr">
         <is>
-          <t>zednik</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K119" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L119" s="20" t="inlineStr">
         <is>
@@ -16141,12 +16189,12 @@
       </c>
       <c r="M119" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 1.PP obvod + výška podlaží 2.1 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms dlažba + standard ratio per RD geometry</t>
         </is>
       </c>
       <c r="N119" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O119" s="26" t="inlineStr">
@@ -16168,7 +16216,7 @@
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 1.NP</t>
+          <t>Omítka jádrová + štuk 1.PP</t>
         </is>
       </c>
       <c r="D120" s="20" t="inlineStr">
@@ -16178,7 +16226,7 @@
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.NP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.PP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F120" s="20" t="inlineStr">
@@ -16187,7 +16235,7 @@
         </is>
       </c>
       <c r="G120" s="22" t="n">
-        <v>208.4</v>
+        <v>78.2</v>
       </c>
       <c r="H120" s="10" t="n"/>
       <c r="I120" s="10" t="n"/>
@@ -16206,7 +16254,7 @@
       </c>
       <c r="M120" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 1.NP obvod + výška podlaží 2.795 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 1.PP obvod + výška podlaží 2.1 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N120" s="20" t="inlineStr">
@@ -16233,7 +16281,7 @@
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 2.NP</t>
+          <t>Omítka jádrová + štuk 1.NP</t>
         </is>
       </c>
       <c r="D121" s="20" t="inlineStr">
@@ -16243,7 +16291,7 @@
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 2.NP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F121" s="20" t="inlineStr">
@@ -16252,7 +16300,7 @@
         </is>
       </c>
       <c r="G121" s="22" t="n">
-        <v>201.6</v>
+        <v>208.4</v>
       </c>
       <c r="H121" s="10" t="n"/>
       <c r="I121" s="10" t="n"/>
@@ -16271,7 +16319,7 @@
       </c>
       <c r="M121" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 2.NP obvod + výška podlaží 2.865 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 1.NP obvod + výška podlaží 2.795 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N121" s="20" t="inlineStr">
@@ -16298,7 +16346,7 @@
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 3.NP</t>
+          <t>Omítka jádrová + štuk 2.NP</t>
         </is>
       </c>
       <c r="D122" s="20" t="inlineStr">
@@ -16308,7 +16356,7 @@
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 3.NP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 2.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F122" s="20" t="inlineStr">
@@ -16317,7 +16365,7 @@
         </is>
       </c>
       <c r="G122" s="22" t="n">
-        <v>179.1</v>
+        <v>201.6</v>
       </c>
       <c r="H122" s="10" t="n"/>
       <c r="I122" s="10" t="n"/>
@@ -16336,7 +16384,7 @@
       </c>
       <c r="M122" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 3.NP obvod + výška podlaží 2.63 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 2.NP obvod + výška podlaží 2.865 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N122" s="20" t="inlineStr">
@@ -16363,17 +16411,17 @@
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled — tmelení + úprava 1.NP</t>
+          <t>Omítka jádrová + štuk 3.NP</t>
         </is>
       </c>
       <c r="D123" s="20" t="inlineStr">
         <is>
-          <t>612471141</t>
+          <t>612311311</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (1.NP)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 3.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F123" s="20" t="inlineStr">
@@ -16382,17 +16430,17 @@
         </is>
       </c>
       <c r="G123" s="22" t="n">
-        <v>59.5</v>
+        <v>179.1</v>
       </c>
       <c r="H123" s="10" t="n"/>
       <c r="I123" s="10" t="n"/>
       <c r="J123" s="8" t="inlineStr">
         <is>
-          <t>sadrokartonar</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K123" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L123" s="20" t="inlineStr">
         <is>
@@ -16401,12 +16449,12 @@
       </c>
       <c r="M123" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 1.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF rooms 3.NP obvod + výška podlaží 2.63 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N123" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O123" s="26" t="inlineStr">
@@ -16428,7 +16476,7 @@
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled — tmelení + úprava 2.NP</t>
+          <t>SDK podhled — tmelení + úprava 1.NP</t>
         </is>
       </c>
       <c r="D124" s="20" t="inlineStr">
@@ -16438,7 +16486,7 @@
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (2.NP)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (1.NP)</t>
         </is>
       </c>
       <c r="F124" s="20" t="inlineStr">
@@ -16447,7 +16495,7 @@
         </is>
       </c>
       <c r="G124" s="22" t="n">
-        <v>61.1</v>
+        <v>59.5</v>
       </c>
       <c r="H124" s="10" t="n"/>
       <c r="I124" s="10" t="n"/>
@@ -16466,7 +16514,7 @@
       </c>
       <c r="M124" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 2.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 1.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="N124" s="20" t="inlineStr">
@@ -16493,7 +16541,7 @@
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled — tmelení + úprava 3.NP</t>
+          <t>SDK podhled — tmelení + úprava 2.NP</t>
         </is>
       </c>
       <c r="D125" s="20" t="inlineStr">
@@ -16503,7 +16551,7 @@
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (3.NP)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (2.NP)</t>
         </is>
       </c>
       <c r="F125" s="20" t="inlineStr">
@@ -16512,7 +16560,7 @@
         </is>
       </c>
       <c r="G125" s="22" t="n">
-        <v>64.5</v>
+        <v>61.1</v>
       </c>
       <c r="H125" s="10" t="n"/>
       <c r="I125" s="10" t="n"/>
@@ -16531,7 +16579,7 @@
       </c>
       <c r="M125" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 3.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 2.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="N125" s="20" t="inlineStr">
@@ -16558,17 +16606,17 @@
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad koupelna 1.05 (1.NP)</t>
+          <t>SDK podhled — tmelení + úprava 3.NP</t>
         </is>
       </c>
       <c r="D126" s="20" t="inlineStr">
         <is>
-          <t>781447001</t>
+          <t>612471141</t>
         </is>
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 1.05 1.NP — výška obkladu 1.6 m (z DXF km Obklady layer)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (3.NP)</t>
         </is>
       </c>
       <c r="F126" s="20" t="inlineStr">
@@ -16577,17 +16625,17 @@
         </is>
       </c>
       <c r="G126" s="22" t="n">
-        <v>13.4</v>
+        <v>64.5</v>
       </c>
       <c r="H126" s="10" t="n"/>
       <c r="I126" s="10" t="n"/>
       <c r="J126" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>sadrokartonar</t>
         </is>
       </c>
       <c r="K126" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L126" s="20" t="inlineStr">
         <is>
@@ -16596,7 +16644,7 @@
       </c>
       <c r="M126" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 1.05 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 3.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="N126" s="20" t="inlineStr">
@@ -16623,7 +16671,7 @@
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad koupelna 2.03 (2.NP)</t>
+          <t>Keramický obklad koupelna 1.05 (1.NP)</t>
         </is>
       </c>
       <c r="D127" s="20" t="inlineStr">
@@ -16633,7 +16681,7 @@
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 2.03 2.NP — výška obkladu 2.45 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad stěn koupelny 1.05 1.NP — výška obkladu 1.6 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="F127" s="20" t="inlineStr">
@@ -16642,7 +16690,7 @@
         </is>
       </c>
       <c r="G127" s="22" t="n">
-        <v>15.2</v>
+        <v>13.4</v>
       </c>
       <c r="H127" s="10" t="n"/>
       <c r="I127" s="10" t="n"/>
@@ -16661,7 +16709,7 @@
       </c>
       <c r="M127" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 2.03 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF rooms PIP perimeter 1.05 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="N127" s="20" t="inlineStr">
@@ -16688,7 +16736,7 @@
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad koupelna 3.04 (3.NP)</t>
+          <t>Keramický obklad koupelna 2.03 (2.NP)</t>
         </is>
       </c>
       <c r="D128" s="20" t="inlineStr">
@@ -16698,7 +16746,7 @@
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 3.04 3.NP — výška obkladu 2.7 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad stěn koupelny 2.03 2.NP — výška obkladu 2.45 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="F128" s="20" t="inlineStr">
@@ -16707,7 +16755,7 @@
         </is>
       </c>
       <c r="G128" s="22" t="n">
-        <v>24.3</v>
+        <v>15.2</v>
       </c>
       <c r="H128" s="10" t="n"/>
       <c r="I128" s="10" t="n"/>
@@ -16726,7 +16774,7 @@
       </c>
       <c r="M128" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 3.04 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF rooms PIP perimeter 2.03 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="N128" s="20" t="inlineStr">
@@ -16753,7 +16801,7 @@
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t>Obklad za kuchyňskou linkou</t>
+          <t>Keramický obklad koupelna 3.04 (3.NP)</t>
         </is>
       </c>
       <c r="D129" s="20" t="inlineStr">
@@ -16763,7 +16811,7 @@
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad za kuchyňskou linkou nad pracovní deskou — 2 kuchyně × ~5 m² (1.06 byt rodičů + 3.05 byt 3.NP)</t>
+          <t>Keramický obklad stěn koupelny 3.04 3.NP — výška obkladu 2.7 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="F129" s="20" t="inlineStr">
@@ -16772,7 +16820,7 @@
         </is>
       </c>
       <c r="G129" s="22" t="n">
-        <v>10</v>
+        <v>24.3</v>
       </c>
       <c r="H129" s="10" t="n"/>
       <c r="I129" s="10" t="n"/>
@@ -16782,7 +16830,7 @@
         </is>
       </c>
       <c r="K129" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L129" s="20" t="inlineStr">
         <is>
@@ -16791,7 +16839,7 @@
       </c>
       <c r="M129" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ 2× kuchyně MTEXT + TZ ARS</t>
+          <t>DXF rooms PIP perimeter 3.04 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="N129" s="20" t="inlineStr">
@@ -16818,17 +16866,17 @@
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba</t>
+          <t>Obklad za kuchyňskou linkou</t>
         </is>
       </c>
       <c r="D130" s="20" t="inlineStr">
         <is>
-          <t>784121011</t>
+          <t>781447001</t>
         </is>
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba akrylátová bílá 2× — všechny stěny + podhledy mimo obklad</t>
+          <t>Keramický obklad za kuchyňskou linkou nad pracovní deskou — 2 kuchyně × ~5 m² (1.06 byt rodičů + 3.05 byt 3.NP)</t>
         </is>
       </c>
       <c r="F130" s="20" t="inlineStr">
@@ -16837,17 +16885,17 @@
         </is>
       </c>
       <c r="G130" s="22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H130" s="10" t="n"/>
       <c r="I130" s="10" t="n"/>
       <c r="J130" s="8" t="inlineStr">
         <is>
-          <t>malir</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K130" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L130" s="20" t="inlineStr">
         <is>
@@ -16856,7 +16904,7 @@
       </c>
       <c r="M130" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS — interiérová výmalba (aggregate, no TZ per-room directive)</t>
+          <t>DXF dum_DPZ 2× kuchyně MTEXT + TZ ARS</t>
         </is>
       </c>
       <c r="N130" s="20" t="inlineStr">
@@ -16870,11 +16918,7 @@
         </is>
       </c>
       <c r="P130" s="41" t="n"/>
-      <c r="Q130" s="41" t="inlineStr">
-        <is>
-          <t>GAP_007_deprecated</t>
-        </is>
-      </c>
+      <c r="Q130" s="41" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="20" t="n">
@@ -16887,7 +16931,7 @@
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.NP</t>
+          <t>Interiérová výmalba</t>
         </is>
       </c>
       <c r="D131" s="20" t="inlineStr">
@@ -16897,7 +16941,7 @@
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.NP — stěny + SDK podhled − obklad koupelny 1.05 (1.6 m výška)</t>
+          <t>Interiérová výmalba akrylátová bílá 2× — všechny stěny + podhledy mimo obklad</t>
         </is>
       </c>
       <c r="F131" s="20" t="inlineStr">
@@ -16906,7 +16950,7 @@
         </is>
       </c>
       <c r="G131" s="22" t="n">
-        <v>254.5</v>
+        <v>0</v>
       </c>
       <c r="H131" s="10" t="n"/>
       <c r="I131" s="10" t="n"/>
@@ -16916,7 +16960,7 @@
         </is>
       </c>
       <c r="K131" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L131" s="20" t="inlineStr">
         <is>
@@ -16925,7 +16969,7 @@
       </c>
       <c r="M131" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.002 + SDK podhled PSV78.005</t>
+          <t>TZ ARS — interiérová výmalba (aggregate, no TZ per-room directive)</t>
         </is>
       </c>
       <c r="N131" s="20" t="inlineStr">
@@ -16941,7 +16985,7 @@
       <c r="P131" s="41" t="n"/>
       <c r="Q131" s="41" t="inlineStr">
         <is>
-          <t>GAP_007</t>
+          <t>GAP_007_deprecated</t>
         </is>
       </c>
     </row>
@@ -16956,7 +17000,7 @@
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.PP</t>
+          <t>Interiérová výmalba 1.NP</t>
         </is>
       </c>
       <c r="D132" s="20" t="inlineStr">
@@ -16966,7 +17010,7 @@
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.PP — sklep stěny + klenba bílá vápenná 2×</t>
+          <t>Interiérová výmalba 1.NP — stěny + SDK podhled − obklad koupelny 1.05 (1.6 m výška)</t>
         </is>
       </c>
       <c r="F132" s="20" t="inlineStr">
@@ -16975,7 +17019,7 @@
         </is>
       </c>
       <c r="G132" s="22" t="n">
-        <v>78.2</v>
+        <v>254.5</v>
       </c>
       <c r="H132" s="10" t="n"/>
       <c r="I132" s="10" t="n"/>
@@ -16994,7 +17038,7 @@
       </c>
       <c r="M132" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.001 + SDK podhled PSV78.—</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.002 + SDK podhled PSV78.005</t>
         </is>
       </c>
       <c r="N132" s="20" t="inlineStr">
@@ -17025,7 +17069,7 @@
       </c>
       <c r="C133" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 2.NP</t>
+          <t>Interiérová výmalba 1.PP</t>
         </is>
       </c>
       <c r="D133" s="20" t="inlineStr">
@@ -17035,7 +17079,7 @@
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 2.NP — stěny + SDK podhled − obklad koupelny 2.03 (2.45 m výška)</t>
+          <t>Interiérová výmalba 1.PP — sklep stěny + klenba bílá vápenná 2×</t>
         </is>
       </c>
       <c r="F133" s="20" t="inlineStr">
@@ -17044,7 +17088,7 @@
         </is>
       </c>
       <c r="G133" s="22" t="n">
-        <v>247.5</v>
+        <v>78.2</v>
       </c>
       <c r="H133" s="10" t="n"/>
       <c r="I133" s="10" t="n"/>
@@ -17063,7 +17107,7 @@
       </c>
       <c r="M133" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.003 + SDK podhled PSV78.006</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.001 + SDK podhled PSV78.—</t>
         </is>
       </c>
       <c r="N133" s="20" t="inlineStr">
@@ -17094,7 +17138,7 @@
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 3.NP</t>
+          <t>Interiérová výmalba 2.NP</t>
         </is>
       </c>
       <c r="D134" s="20" t="inlineStr">
@@ -17104,7 +17148,7 @@
       </c>
       <c r="E134" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 3.NP — stěny + SDK podhled − obklad koupelny 3.04 (2.7 m výška)</t>
+          <t>Interiérová výmalba 2.NP — stěny + SDK podhled − obklad koupelny 2.03 (2.45 m výška)</t>
         </is>
       </c>
       <c r="F134" s="20" t="inlineStr">
@@ -17113,7 +17157,7 @@
         </is>
       </c>
       <c r="G134" s="22" t="n">
-        <v>219.3</v>
+        <v>247.5</v>
       </c>
       <c r="H134" s="10" t="n"/>
       <c r="I134" s="10" t="n"/>
@@ -17132,7 +17176,7 @@
       </c>
       <c r="M134" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.004 + SDK podhled PSV78.007</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.003 + SDK podhled PSV78.006</t>
         </is>
       </c>
       <c r="N134" s="20" t="inlineStr">
@@ -17158,37 +17202,37 @@
       </c>
       <c r="B135" s="8" t="inlineStr">
         <is>
-          <t>PSV-95 Detekce požární</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="C135" s="8" t="inlineStr">
         <is>
-          <t>Autonomní hlásič kouře</t>
+          <t>Interiérová výmalba 3.NP</t>
         </is>
       </c>
       <c r="D135" s="20" t="inlineStr">
         <is>
-          <t>375211101</t>
+          <t>784121011</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>Autonomní hlásič kouře dle ČSN EN 14604 — 4 ks v místnostech 1.01, 1.02, 2.04, 3.03 dle PBŘ</t>
+          <t>Interiérová výmalba 3.NP — stěny + SDK podhled − obklad koupelny 3.04 (2.7 m výška)</t>
         </is>
       </c>
       <c r="F135" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G135" s="23" t="n">
-        <v>4</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G135" s="22" t="n">
+        <v>219.3</v>
       </c>
       <c r="H135" s="10" t="n"/>
       <c r="I135" s="10" t="n"/>
       <c r="J135" s="8" t="inlineStr">
         <is>
-          <t>elektroinstalater</t>
+          <t>malir</t>
         </is>
       </c>
       <c r="K135" s="24" t="n">
@@ -17196,12 +17240,12 @@
       </c>
       <c r="L135" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M135" s="8" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — ČSN EN 14604 autonomní hlásič kouře 4 ks</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.004 + SDK podhled PSV78.007</t>
         </is>
       </c>
       <c r="N135" s="20" t="inlineStr">
@@ -17217,7 +17261,7 @@
       <c r="P135" s="41" t="n"/>
       <c r="Q135" s="41" t="inlineStr">
         <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+          <t>GAP_007</t>
         </is>
       </c>
     </row>
@@ -17232,17 +17276,17 @@
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>Přenosný hasicí přístroj 34A</t>
+          <t>Autonomní hlásič kouře</t>
         </is>
       </c>
       <c r="D136" s="20" t="inlineStr">
         <is>
-          <t>966067121</t>
+          <t>375211101</t>
         </is>
       </c>
       <c r="E136" s="8" t="inlineStr">
         <is>
-          <t>Přenosný hasicí přístroj 34A dle PBŘ — min. 1 ks na společné chodbě</t>
+          <t>Autonomní hlásič kouře dle ČSN EN 14604 — 4 ks v místnostech 1.01, 1.02, 2.04, 3.03 dle PBŘ</t>
         </is>
       </c>
       <c r="F136" s="20" t="inlineStr">
@@ -17251,13 +17295,13 @@
         </is>
       </c>
       <c r="G136" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H136" s="10" t="n"/>
       <c r="I136" s="10" t="n"/>
       <c r="J136" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>elektroinstalater</t>
         </is>
       </c>
       <c r="K136" s="24" t="n">
@@ -17265,12 +17309,12 @@
       </c>
       <c r="L136" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M136" s="8" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — PHP 34A 1 ks minimum</t>
+          <t>TZ PBŘ dům — ČSN EN 14604 autonomní hlásič kouře 4 ks</t>
         </is>
       </c>
       <c r="N136" s="20" t="inlineStr">
@@ -17284,7 +17328,11 @@
         </is>
       </c>
       <c r="P136" s="41" t="n"/>
-      <c r="Q136" s="41" t="n"/>
+      <c r="Q136" s="41" t="inlineStr">
+        <is>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="20" t="n">
@@ -17292,27 +17340,27 @@
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>PSV-95 Detekce požární</t>
         </is>
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávající ELI</t>
+          <t>Přenosný hasicí přístroj 34A</t>
         </is>
       </c>
       <c r="D137" s="20" t="inlineStr">
         <is>
-          <t>210010011</t>
+          <t>966067121</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
+          <t>Přenosný hasicí přístroj 34A dle PBŘ — min. 1 ks na společné chodbě</t>
         </is>
       </c>
       <c r="F137" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G137" s="23" t="n">
@@ -17322,7 +17370,7 @@
       <c r="I137" s="10" t="n"/>
       <c r="J137" s="8" t="inlineStr">
         <is>
-          <t>elektroinstalater</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K137" s="24" t="n">
@@ -17335,12 +17383,12 @@
       </c>
       <c r="M137" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kompletně nová ELI</t>
+          <t>TZ PBŘ dům — PHP 34A 1 ks minimum</t>
         </is>
       </c>
       <c r="N137" s="20" t="inlineStr">
         <is>
-          <t>#7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O137" s="26" t="inlineStr">
@@ -17362,26 +17410,26 @@
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>Pojistková skříň + 3× podružný rozvaděč</t>
+          <t>Demontáž stávající ELI</t>
         </is>
       </c>
       <c r="D138" s="20" t="inlineStr">
         <is>
-          <t>210110023</t>
+          <t>210010011</t>
         </is>
       </c>
       <c r="E138" s="8" t="inlineStr">
         <is>
-          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
+          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
         </is>
       </c>
       <c r="F138" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G138" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H138" s="10" t="n"/>
       <c r="I138" s="10" t="n"/>
@@ -17400,7 +17448,7 @@
       </c>
       <c r="M138" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — 'nová pojistková skříň s podružným měřením pro každé patro'</t>
+          <t>TZ ARS dům §4 — kompletně nová ELI</t>
         </is>
       </c>
       <c r="N138" s="20" t="inlineStr">
@@ -17427,26 +17475,26 @@
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t>Rozvody silnoproud</t>
+          <t>Pojistková skříň + 3× podružný rozvaděč</t>
         </is>
       </c>
       <c r="D139" s="20" t="inlineStr">
         <is>
-          <t>210800012</t>
+          <t>210110023</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
+          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
         </is>
       </c>
       <c r="F139" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G139" s="22" t="n">
-        <v>700</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G139" s="23" t="n">
+        <v>4</v>
       </c>
       <c r="H139" s="10" t="n"/>
       <c r="I139" s="10" t="n"/>
@@ -17456,7 +17504,7 @@
         </is>
       </c>
       <c r="K139" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L139" s="20" t="inlineStr">
         <is>
@@ -17465,7 +17513,7 @@
       </c>
       <c r="M139" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD 3-byt. dispozice</t>
+          <t>TZ ARS dům §4 — 'nová pojistková skříň s podružným měřením pro každé patro'</t>
         </is>
       </c>
       <c r="N139" s="20" t="inlineStr">
@@ -17492,26 +17540,26 @@
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>Zásuvky a vypínače</t>
+          <t>Rozvody silnoproud</t>
         </is>
       </c>
       <c r="D140" s="20" t="inlineStr">
         <is>
-          <t>210810050</t>
+          <t>210800012</t>
         </is>
       </c>
       <c r="E140" s="8" t="inlineStr">
         <is>
-          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
+          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
         </is>
       </c>
       <c r="F140" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G140" s="23" t="n">
-        <v>70</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G140" s="22" t="n">
+        <v>700</v>
       </c>
       <c r="H140" s="10" t="n"/>
       <c r="I140" s="10" t="n"/>
@@ -17530,7 +17578,7 @@
       </c>
       <c r="M140" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD 220 m² 3-byt.</t>
+          <t>TZ ARS + B4_productivity standard RD 3-byt. dispozice</t>
         </is>
       </c>
       <c r="N140" s="20" t="inlineStr">
@@ -17557,17 +17605,17 @@
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t>Svítidla</t>
+          <t>Zásuvky a vypínače</t>
         </is>
       </c>
       <c r="D141" s="20" t="inlineStr">
         <is>
-          <t>210820002</t>
+          <t>210810050</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
+          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
         </is>
       </c>
       <c r="F141" s="20" t="inlineStr">
@@ -17576,7 +17624,7 @@
         </is>
       </c>
       <c r="G141" s="23" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="H141" s="10" t="n"/>
       <c r="I141" s="10" t="n"/>
@@ -17595,7 +17643,7 @@
       </c>
       <c r="M141" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD</t>
+          <t>TZ ARS + B4_productivity standard RD 220 m² 3-byt.</t>
         </is>
       </c>
       <c r="N141" s="20" t="inlineStr">
@@ -17622,26 +17670,26 @@
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>Příprava FVE</t>
+          <t>Svítidla</t>
         </is>
       </c>
       <c r="D142" s="20" t="inlineStr">
         <is>
-          <t>210800099</t>
+          <t>210820002</t>
         </is>
       </c>
       <c r="E142" s="8" t="inlineStr">
         <is>
-          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
+          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
         </is>
       </c>
       <c r="F142" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G142" s="23" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="H142" s="10" t="n"/>
       <c r="I142" s="10" t="n"/>
@@ -17651,7 +17699,7 @@
         </is>
       </c>
       <c r="K142" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L142" s="20" t="inlineStr">
         <is>
@@ -17660,7 +17708,7 @@
       </c>
       <c r="M142" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — FVE příprava (bez panelů samotných)</t>
+          <t>TZ ARS + B4_productivity standard RD</t>
         </is>
       </c>
       <c r="N142" s="20" t="inlineStr">
@@ -17687,17 +17735,17 @@
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t>Revize ELI při kolaudaci</t>
+          <t>Příprava FVE</t>
         </is>
       </c>
       <c r="D143" s="20" t="inlineStr">
         <is>
-          <t>996019011</t>
+          <t>210800099</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
+          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
         </is>
       </c>
       <c r="F143" s="20" t="inlineStr">
@@ -17712,11 +17760,11 @@
       <c r="I143" s="10" t="n"/>
       <c r="J143" s="8" t="inlineStr">
         <is>
-          <t>revize_specialista</t>
+          <t>elektroinstalater</t>
         </is>
       </c>
       <c r="K143" s="24" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="L143" s="20" t="inlineStr">
         <is>
@@ -17725,12 +17773,12 @@
       </c>
       <c r="M143" s="8" t="inlineStr">
         <is>
-          <t>Povinná revize ELI dle ČSN 33 2000-6 + kolaudace</t>
+          <t>TZ ARS dům §4 — FVE příprava (bez panelů samotných)</t>
         </is>
       </c>
       <c r="N143" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#7</t>
         </is>
       </c>
       <c r="O143" s="26" t="inlineStr">
@@ -17747,22 +17795,22 @@
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajících přípojek</t>
+          <t>Revize ELI při kolaudaci</t>
         </is>
       </c>
       <c r="D144" s="20" t="inlineStr">
         <is>
-          <t>722290515</t>
+          <t>996019011</t>
         </is>
       </c>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajícího napojení vodovodu + kanalizace na pozemku — kontrola stavu, čištění, tlaková zkouška</t>
+          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
         </is>
       </c>
       <c r="F144" s="20" t="inlineStr">
@@ -17777,25 +17825,25 @@
       <c r="I144" s="10" t="n"/>
       <c r="J144" s="8" t="inlineStr">
         <is>
-          <t>vodar</t>
+          <t>revize_specialista</t>
         </is>
       </c>
       <c r="K144" s="24" t="n">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
       <c r="L144" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M144" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — vodovod + kanalizace stávající, bez změny</t>
+          <t>Povinná revize ELI dle ČSN 33 2000-6 + kolaudace</t>
         </is>
       </c>
       <c r="N144" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O144" s="26" t="inlineStr">
@@ -17804,11 +17852,7 @@
         </is>
       </c>
       <c r="P144" s="41" t="n"/>
-      <c r="Q144" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+      <c r="Q144" s="41" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="20" t="n">
@@ -17821,26 +17865,26 @@
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t>Nové rozvody vody do 3.NP</t>
+          <t>Revize stávajících přípojek</t>
         </is>
       </c>
       <c r="D145" s="20" t="inlineStr">
         <is>
-          <t>722172011</t>
+          <t>722290515</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>Nové rozvody studené + teplé vody do koupelen 1.NP + 2.NP + 3.NP a kuchyní (PEX/Cu, dimenze DN15-25)</t>
+          <t>Revize stávajícího napojení vodovodu + kanalizace na pozemku — kontrola stavu, čištění, tlaková zkouška</t>
         </is>
       </c>
       <c r="F145" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G145" s="22" t="n">
-        <v>80</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G145" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H145" s="10" t="n"/>
       <c r="I145" s="10" t="n"/>
@@ -17850,7 +17894,7 @@
         </is>
       </c>
       <c r="K145" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L145" s="20" t="inlineStr">
         <is>
@@ -17859,7 +17903,7 @@
       </c>
       <c r="M145" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — nové koupelny + kuchyně, vyjasnění #6 working assumption</t>
+          <t>TZ ARS dům §4 — vodovod + kanalizace stávající, bez změny</t>
         </is>
       </c>
       <c r="N145" s="20" t="inlineStr">
@@ -17890,17 +17934,17 @@
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>Nové odpadní rozvody</t>
+          <t>Nové rozvody vody do 3.NP</t>
         </is>
       </c>
       <c r="D146" s="20" t="inlineStr">
         <is>
-          <t>721174021</t>
+          <t>722172011</t>
         </is>
       </c>
       <c r="E146" s="8" t="inlineStr">
         <is>
-          <t>Nové odpadní rozvody PVC-HT DN40-DN110 ke koupelnám 1.NP, 2.NP, 3.NP a kuchyním + napojení na stávající</t>
+          <t>Nové rozvody studené + teplé vody do koupelen 1.NP + 2.NP + 3.NP a kuchyní (PEX/Cu, dimenze DN15-25)</t>
         </is>
       </c>
       <c r="F146" s="20" t="inlineStr">
@@ -17909,7 +17953,7 @@
         </is>
       </c>
       <c r="G146" s="22" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H146" s="10" t="n"/>
       <c r="I146" s="10" t="n"/>
@@ -17923,12 +17967,12 @@
       </c>
       <c r="L146" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M146" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — nové koupelny + kuchyně, odpad do stávající kanalizace</t>
+          <t>TZ ARS dům §4 — nové koupelny + kuchyně, vyjasnění #6 working assumption</t>
         </is>
       </c>
       <c r="N146" s="20" t="inlineStr">
@@ -17942,7 +17986,11 @@
         </is>
       </c>
       <c r="P146" s="41" t="n"/>
-      <c r="Q146" s="41" t="n"/>
+      <c r="Q146" s="41" t="inlineStr">
+        <is>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="20" t="n">
@@ -17955,26 +18003,26 @@
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP)</t>
+          <t>Nové odpadní rozvody</t>
         </is>
       </c>
       <c r="D147" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>721174021</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
+          <t>Nové odpadní rozvody PVC-HT DN40-DN110 ke koupelnám 1.NP, 2.NP, 3.NP a kuchyním + napojení na stávající</t>
         </is>
       </c>
       <c r="F147" s="20" t="inlineStr">
         <is>
-          <t>set</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G147" s="22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H147" s="10" t="n"/>
       <c r="I147" s="10" t="n"/>
@@ -17993,7 +18041,7 @@
       </c>
       <c r="M147" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 1.05 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>TZ ARS dům §4 — nové koupelny + kuchyně, odpad do stávající kanalizace</t>
         </is>
       </c>
       <c r="N147" s="20" t="inlineStr">
@@ -18007,11 +18055,7 @@
         </is>
       </c>
       <c r="P147" s="41" t="n"/>
-      <c r="Q147" s="41" t="inlineStr">
-        <is>
-          <t>GAP_005_deprecated</t>
-        </is>
-      </c>
+      <c r="Q147" s="41" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="20" t="n">
@@ -18024,26 +18068,26 @@
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP)</t>
         </is>
       </c>
       <c r="D148" s="20" t="inlineStr">
         <is>
-          <t>725211101</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E148" s="8" t="inlineStr">
         <is>
-          <t>Vana koupelnová obdélníková 170×70 cm — koupelna 1.05 1.NP</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
         </is>
       </c>
       <c r="F148" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G148" s="23" t="n">
-        <v>1</v>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G148" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H148" s="10" t="n"/>
       <c r="I148" s="10" t="n"/>
@@ -18053,7 +18097,7 @@
         </is>
       </c>
       <c r="K148" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L148" s="20" t="inlineStr">
         <is>
@@ -18062,12 +18106,12 @@
       </c>
       <c r="M148" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 1.05 1.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 1.05 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N148" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O148" s="26" t="inlineStr">
@@ -18078,7 +18122,7 @@
       <c r="P148" s="41" t="n"/>
       <c r="Q148" s="41" t="inlineStr">
         <is>
-          <t>GAP_005</t>
+          <t>GAP_005_deprecated</t>
         </is>
       </c>
     </row>
@@ -18093,17 +18137,17 @@
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture A</t>
         </is>
       </c>
       <c r="D149" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725211101</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 1.05 1.NP</t>
+          <t>Vana koupelnová obdélníková 170×70 cm — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F149" s="20" t="inlineStr">
@@ -18162,17 +18206,17 @@
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture C</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture B</t>
         </is>
       </c>
       <c r="D150" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 1.05 1.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F150" s="20" t="inlineStr">
@@ -18231,26 +18275,26 @@
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP)</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture C</t>
         </is>
       </c>
       <c r="D151" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standard)</t>
+          <t>WC kombi keramické bílé — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F151" s="20" t="inlineStr">
         <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="G151" s="22" t="n">
-        <v>0</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G151" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H151" s="10" t="n"/>
       <c r="I151" s="10" t="n"/>
@@ -18260,7 +18304,7 @@
         </is>
       </c>
       <c r="K151" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L151" s="20" t="inlineStr">
         <is>
@@ -18269,12 +18313,12 @@
       </c>
       <c r="M151" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 2.03 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ MTEXT room 1.05 1.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N151" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O151" s="26" t="inlineStr">
@@ -18285,7 +18329,7 @@
       <c r="P151" s="41" t="n"/>
       <c r="Q151" s="41" t="inlineStr">
         <is>
-          <t>GAP_005_deprecated</t>
+          <t>GAP_005</t>
         </is>
       </c>
     </row>
@@ -18300,26 +18344,26 @@
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP)</t>
         </is>
       </c>
       <c r="D152" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E152" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 2.03 2.NP</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standard)</t>
         </is>
       </c>
       <c r="F152" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G152" s="23" t="n">
-        <v>1</v>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G152" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H152" s="10" t="n"/>
       <c r="I152" s="10" t="n"/>
@@ -18329,7 +18373,7 @@
         </is>
       </c>
       <c r="K152" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L152" s="20" t="inlineStr">
         <is>
@@ -18338,12 +18382,12 @@
       </c>
       <c r="M152" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 2.03 2.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 2.03 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N152" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O152" s="26" t="inlineStr">
@@ -18354,7 +18398,7 @@
       <c r="P152" s="41" t="n"/>
       <c r="Q152" s="41" t="inlineStr">
         <is>
-          <t>GAP_005</t>
+          <t>GAP_005_deprecated</t>
         </is>
       </c>
     </row>
@@ -18369,17 +18413,17 @@
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture A</t>
         </is>
       </c>
       <c r="D153" s="20" t="inlineStr">
         <is>
-          <t>725221201</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 2.03 2.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F153" s="20" t="inlineStr">
@@ -18438,17 +18482,17 @@
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture C</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture B</t>
         </is>
       </c>
       <c r="D154" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725221201</t>
         </is>
       </c>
       <c r="E154" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 2.03 2.NP</t>
+          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F154" s="20" t="inlineStr">
@@ -18507,26 +18551,26 @@
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP)</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture C</t>
         </is>
       </c>
       <c r="D155" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standard)</t>
+          <t>WC kombi keramické bílé — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F155" s="20" t="inlineStr">
         <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="G155" s="22" t="n">
-        <v>0</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G155" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H155" s="10" t="n"/>
       <c r="I155" s="10" t="n"/>
@@ -18536,7 +18580,7 @@
         </is>
       </c>
       <c r="K155" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L155" s="20" t="inlineStr">
         <is>
@@ -18545,12 +18589,12 @@
       </c>
       <c r="M155" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 3.04 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ MTEXT room 2.03 2.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N155" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O155" s="26" t="inlineStr">
@@ -18561,7 +18605,7 @@
       <c r="P155" s="41" t="n"/>
       <c r="Q155" s="41" t="inlineStr">
         <is>
-          <t>GAP_005_deprecated</t>
+          <t>GAP_005</t>
         </is>
       </c>
     </row>
@@ -18576,26 +18620,26 @@
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP)</t>
         </is>
       </c>
       <c r="D156" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E156" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 3.04 3.NP</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standard)</t>
         </is>
       </c>
       <c r="F156" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G156" s="23" t="n">
-        <v>1</v>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G156" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H156" s="10" t="n"/>
       <c r="I156" s="10" t="n"/>
@@ -18605,7 +18649,7 @@
         </is>
       </c>
       <c r="K156" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L156" s="20" t="inlineStr">
         <is>
@@ -18614,12 +18658,12 @@
       </c>
       <c r="M156" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 3.04 3.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 3.04 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N156" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O156" s="26" t="inlineStr">
@@ -18630,7 +18674,7 @@
       <c r="P156" s="41" t="n"/>
       <c r="Q156" s="41" t="inlineStr">
         <is>
-          <t>GAP_005</t>
+          <t>GAP_005_deprecated</t>
         </is>
       </c>
     </row>
@@ -18645,17 +18689,17 @@
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture A</t>
         </is>
       </c>
       <c r="D157" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 3.04 3.NP</t>
+          <t>WC kombi keramické bílé — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F157" s="20" t="inlineStr">
@@ -18714,17 +18758,17 @@
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture C</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture B</t>
         </is>
       </c>
       <c r="D158" s="20" t="inlineStr">
         <is>
-          <t>725221201</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E158" s="8" t="inlineStr">
         <is>
-          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 3.04 3.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F158" s="20" t="inlineStr">
@@ -18783,17 +18827,17 @@
       </c>
       <c r="C159" s="8" t="inlineStr">
         <is>
-          <t>Kuchyňský dřez 2 ks (1.06 + 3.05)</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture C</t>
         </is>
       </c>
       <c r="D159" s="20" t="inlineStr">
         <is>
-          <t>725840111</t>
+          <t>725221201</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>Kuchyňský dřez nerez + montáž — 2 ks (kuchyně 1.06 byt rodičů + kuchyně 3.05 byt 3.NP)</t>
+          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F159" s="20" t="inlineStr">
@@ -18802,7 +18846,7 @@
         </is>
       </c>
       <c r="G159" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H159" s="10" t="n"/>
       <c r="I159" s="10" t="n"/>
@@ -18812,7 +18856,7 @@
         </is>
       </c>
       <c r="K159" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L159" s="20" t="inlineStr">
         <is>
@@ -18821,12 +18865,12 @@
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>DXF kuchyně MTEXT 2× + TZ ARS — dispozice byty</t>
+          <t>DXF dum_DPZ MTEXT room 3.04 3.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N159" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O159" s="26" t="inlineStr">
@@ -18835,7 +18879,11 @@
         </is>
       </c>
       <c r="P159" s="41" t="n"/>
-      <c r="Q159" s="41" t="n"/>
+      <c r="Q159" s="41" t="inlineStr">
+        <is>
+          <t>GAP_005</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="20" t="n">
@@ -18848,17 +18896,17 @@
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>Vodovodní baterie + drobnosti</t>
+          <t>Kuchyňský dřez 2 ks (1.06 + 3.05)</t>
         </is>
       </c>
       <c r="D160" s="20" t="inlineStr">
         <is>
-          <t>725822611</t>
+          <t>725840111</t>
         </is>
       </c>
       <c r="E160" s="8" t="inlineStr">
         <is>
-          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační materiály</t>
+          <t>Kuchyňský dřez nerez + montáž — 2 ks (kuchyně 1.06 byt rodičů + kuchyně 3.05 byt 3.NP)</t>
         </is>
       </c>
       <c r="F160" s="20" t="inlineStr">
@@ -18867,7 +18915,7 @@
         </is>
       </c>
       <c r="G160" s="23" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H160" s="10" t="n"/>
       <c r="I160" s="10" t="n"/>
@@ -18877,7 +18925,7 @@
         </is>
       </c>
       <c r="K160" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L160" s="20" t="inlineStr">
         <is>
@@ -18886,7 +18934,7 @@
       </c>
       <c r="M160" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS — kompletní baterie nové</t>
+          <t>DXF kuchyně MTEXT 2× + TZ ARS — dispozice byty</t>
         </is>
       </c>
       <c r="N160" s="20" t="inlineStr">
@@ -18913,17 +18961,17 @@
       </c>
       <c r="C161" s="8" t="inlineStr">
         <is>
-          <t>Akumulační zásobník TUV v suterénu</t>
+          <t>Vodovodní baterie + drobnosti</t>
         </is>
       </c>
       <c r="D161" s="20" t="inlineStr">
         <is>
-          <t>732419411</t>
+          <t>725822611</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t>Akumulační zásobník TUV ~300 l v 1.PP napojený na topný systém (sporáková kamna + krb + elektrokotel) — nepřímotop</t>
+          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační materiály</t>
         </is>
       </c>
       <c r="F161" s="20" t="inlineStr">
@@ -18932,17 +18980,17 @@
         </is>
       </c>
       <c r="G161" s="23" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H161" s="10" t="n"/>
       <c r="I161" s="10" t="n"/>
       <c r="J161" s="8" t="inlineStr">
         <is>
-          <t>instalater_TUV_akumulacni_zasobnik</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K161" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L161" s="20" t="inlineStr">
         <is>
@@ -18951,7 +18999,7 @@
       </c>
       <c r="M161" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kombi akumulační zásobník napojený na multivariantní topný systém</t>
+          <t>TZ ARS — kompletní baterie nové</t>
         </is>
       </c>
       <c r="N161" s="20" t="inlineStr">
@@ -18978,17 +19026,17 @@
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>Elektrický bojler 3.NP</t>
+          <t>Akumulační zásobník TUV v suterénu</t>
         </is>
       </c>
       <c r="D162" s="20" t="inlineStr">
         <is>
-          <t>732429211</t>
+          <t>732419411</t>
         </is>
       </c>
       <c r="E162" s="8" t="inlineStr">
         <is>
-          <t>Elektrický bojler ~80 l v koupelně 3.NP (nezávislý zdroj pro samostatný byt)</t>
+          <t>Akumulační zásobník TUV ~300 l v 1.PP napojený na topný systém (sporáková kamna + krb + elektrokotel) — nepřímotop</t>
         </is>
       </c>
       <c r="F162" s="20" t="inlineStr">
@@ -19003,7 +19051,7 @@
       <c r="I162" s="10" t="n"/>
       <c r="J162" s="8" t="inlineStr">
         <is>
-          <t>vodar</t>
+          <t>instalater_TUV_akumulacni_zasobnik</t>
         </is>
       </c>
       <c r="K162" s="24" t="n">
@@ -19016,7 +19064,7 @@
       </c>
       <c r="M162" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — elektrický bojler v 3.NP koupelně, vyjasnění #6 odhad 80 l</t>
+          <t>TZ ARS dům §4 — kombi akumulační zásobník napojený na multivariantní topný systém</t>
         </is>
       </c>
       <c r="N162" s="20" t="inlineStr">
@@ -19038,22 +19086,22 @@
       </c>
       <c r="B163" s="8" t="inlineStr">
         <is>
-          <t>PSV-73 Vytápění</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="C163" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna na tuhá paliva</t>
+          <t>Elektrický bojler 3.NP</t>
         </is>
       </c>
       <c r="D163" s="20" t="inlineStr">
         <is>
-          <t>733241011</t>
+          <t>732429211</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna na tuhá paliva ~10 kW s akumulačním zásobníkem TUV — dodávka</t>
+          <t>Elektrický bojler ~80 l v koupelně 3.NP (nezávislý zdroj pro samostatný byt)</t>
         </is>
       </c>
       <c r="F163" s="20" t="inlineStr">
@@ -19068,7 +19116,7 @@
       <c r="I163" s="10" t="n"/>
       <c r="J163" s="8" t="inlineStr">
         <is>
-          <t>topenar</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K163" s="24" t="n">
@@ -19081,7 +19129,7 @@
       </c>
       <c r="M163" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — primární zdroj 1.NP/2.NP, ~10 kW odhad standard RD</t>
+          <t>TZ ARS dům §4 — elektrický bojler v 3.NP koupelně, vyjasnění #6 odhad 80 l</t>
         </is>
       </c>
       <c r="N163" s="20" t="inlineStr">
@@ -19108,22 +19156,22 @@
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna — montáž</t>
+          <t>Sporáková kamna na tuhá paliva</t>
         </is>
       </c>
       <c r="D164" s="20" t="inlineStr">
         <is>
-          <t>733281011</t>
+          <t>733241011</t>
         </is>
       </c>
       <c r="E164" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna — montáž vč. napojení na komín + akumulační zásobník (cca 8 Nh)</t>
+          <t>Sporáková kamna na tuhá paliva ~10 kW s akumulačním zásobníkem TUV — dodávka</t>
         </is>
       </c>
       <c r="F164" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G164" s="23" t="n">
@@ -19137,7 +19185,7 @@
         </is>
       </c>
       <c r="K164" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L164" s="20" t="inlineStr">
         <is>
@@ -19146,12 +19194,12 @@
       </c>
       <c r="M164" s="8" t="inlineStr">
         <is>
-          <t>Standard montáž kamen s napojením na zásobník</t>
+          <t>TZ ARS dům §4 — primární zdroj 1.NP/2.NP, ~10 kW odhad standard RD</t>
         </is>
       </c>
       <c r="N164" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O164" s="26" t="inlineStr">
@@ -19173,22 +19221,22 @@
       </c>
       <c r="C165" s="8" t="inlineStr">
         <is>
-          <t>Elektrokotel 3.NP</t>
+          <t>Sporáková kamna — montáž</t>
         </is>
       </c>
       <c r="D165" s="20" t="inlineStr">
         <is>
-          <t>733131221</t>
+          <t>733281011</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
         <is>
-          <t>Elektrokotel ~8 kW pro 3.NP samostatný byt — dodávka + montáž + napojení</t>
+          <t>Sporáková kamna — montáž vč. napojení na komín + akumulační zásobník (cca 8 Nh)</t>
         </is>
       </c>
       <c r="F165" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G165" s="23" t="n">
@@ -19202,7 +19250,7 @@
         </is>
       </c>
       <c r="K165" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L165" s="20" t="inlineStr">
         <is>
@@ -19211,12 +19259,12 @@
       </c>
       <c r="M165" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — 'Nově navržené 3.NP bude vytápěno elektrokotlem'; ~8 kW odhad</t>
+          <t>Standard montáž kamen s napojením na zásobník</t>
         </is>
       </c>
       <c r="N165" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O165" s="26" t="inlineStr">
@@ -19238,17 +19286,17 @@
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>Krb na tuhá paliva 3.NP</t>
+          <t>Elektrokotel 3.NP</t>
         </is>
       </c>
       <c r="D166" s="20" t="inlineStr">
         <is>
-          <t>733241011</t>
+          <t>733131221</t>
         </is>
       </c>
       <c r="E166" s="8" t="inlineStr">
         <is>
-          <t>Krb na tuhá paliva v 3.NP ~6 kW — dodávka + montáž s napojením na samostatný komín</t>
+          <t>Elektrokotel ~8 kW pro 3.NP samostatný byt — dodávka + montáž + napojení</t>
         </is>
       </c>
       <c r="F166" s="20" t="inlineStr">
@@ -19276,7 +19324,7 @@
       </c>
       <c r="M166" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — krb v 3.NP, ~6 kW odhad</t>
+          <t>TZ ARS dům §4 — 'Nově navržené 3.NP bude vytápěno elektrokotlem'; ~8 kW odhad</t>
         </is>
       </c>
       <c r="N166" s="20" t="inlineStr">
@@ -19303,17 +19351,17 @@
       </c>
       <c r="C167" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — venkovní jednotka</t>
+          <t>Krb na tuhá paliva 3.NP</t>
         </is>
       </c>
       <c r="D167" s="20" t="inlineStr">
         <is>
-          <t>733425211</t>
+          <t>733241011</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
         <is>
-          <t>Multisplit tepelné čerpadlo vzduch-vzduch — 1× venkovní jednotka ~10 kW (silent mode hl. tlaku ≤49 dBA)</t>
+          <t>Krb na tuhá paliva v 3.NP ~6 kW — dodávka + montáž s napojením na samostatný komín</t>
         </is>
       </c>
       <c r="F167" s="20" t="inlineStr">
@@ -19328,7 +19376,7 @@
       <c r="I167" s="10" t="n"/>
       <c r="J167" s="8" t="inlineStr">
         <is>
-          <t>specialista_TC_multisplit</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K167" s="24" t="n">
@@ -19341,7 +19389,7 @@
       </c>
       <c r="M167" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — multisplit TČ s akustikou hl. tlaku ≤49 dBA, NV 272/2011</t>
+          <t>TZ ARS dům §4 — krb v 3.NP, ~6 kW odhad</t>
         </is>
       </c>
       <c r="N167" s="20" t="inlineStr">
@@ -19368,17 +19416,17 @@
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — vnitřní jednotky</t>
+          <t>Multisplit TČ — venkovní jednotka</t>
         </is>
       </c>
       <c r="D168" s="20" t="inlineStr">
         <is>
-          <t>733425221</t>
+          <t>733425211</t>
         </is>
       </c>
       <c r="E168" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — 5× vnitřní jednotka v obytných místnostech (1.NP, 2.NP, 3.NP — chlazení + vytápění)</t>
+          <t>Multisplit tepelné čerpadlo vzduch-vzduch — 1× venkovní jednotka ~10 kW (silent mode hl. tlaku ≤49 dBA)</t>
         </is>
       </c>
       <c r="F168" s="20" t="inlineStr">
@@ -19387,7 +19435,7 @@
         </is>
       </c>
       <c r="G168" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H168" s="10" t="n"/>
       <c r="I168" s="10" t="n"/>
@@ -19397,7 +19445,7 @@
         </is>
       </c>
       <c r="K168" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L168" s="20" t="inlineStr">
         <is>
@@ -19406,7 +19454,7 @@
       </c>
       <c r="M168" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — vnitřní jednotky multisplit, vyjasnění #6 odhad 5 ks</t>
+          <t>TZ ARS dům §4 — multisplit TČ s akustikou hl. tlaku ≤49 dBA, NV 272/2011</t>
         </is>
       </c>
       <c r="N168" s="20" t="inlineStr">
@@ -19433,36 +19481,36 @@
       </c>
       <c r="C169" s="8" t="inlineStr">
         <is>
-          <t>Revize komínu</t>
+          <t>Multisplit TČ — vnitřní jednotky</t>
         </is>
       </c>
       <c r="D169" s="20" t="inlineStr">
         <is>
-          <t>734262122</t>
+          <t>733425221</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajícího komínu — kontrola, čištění, vystrojení vložkou nerez DN160 pro kamna + krb 3.NP</t>
+          <t>Multisplit TČ — 5× vnitřní jednotka v obytných místnostech (1.NP, 2.NP, 3.NP — chlazení + vytápění)</t>
         </is>
       </c>
       <c r="F169" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G169" s="23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H169" s="10" t="n"/>
       <c r="I169" s="10" t="n"/>
       <c r="J169" s="8" t="inlineStr">
         <is>
-          <t>kominik</t>
+          <t>specialista_TC_multisplit</t>
         </is>
       </c>
       <c r="K169" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L169" s="20" t="inlineStr">
         <is>
@@ -19471,7 +19519,7 @@
       </c>
       <c r="M169" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — komín stávající, vystrojení vložkou pro kamna + krb</t>
+          <t>TZ ARS dům §4 — vnitřní jednotky multisplit, vyjasnění #6 odhad 5 ks</t>
         </is>
       </c>
       <c r="N169" s="20" t="inlineStr">
@@ -19498,36 +19546,36 @@
       </c>
       <c r="C170" s="8" t="inlineStr">
         <is>
-          <t>Rozvody otopné soustavy</t>
+          <t>Revize komínu</t>
         </is>
       </c>
       <c r="D170" s="20" t="inlineStr">
         <is>
-          <t>733111021</t>
+          <t>734262122</t>
         </is>
       </c>
       <c r="E170" s="8" t="inlineStr">
         <is>
-          <t>Rozvody otopné soustavy Cu/PEX k vnitřním jednotkám TČ + radiátorům pro doplňkové (cca 100 bm odhad)</t>
+          <t>Revize stávajícího komínu — kontrola, čištění, vystrojení vložkou nerez DN160 pro kamna + krb 3.NP</t>
         </is>
       </c>
       <c r="F170" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G170" s="22" t="n">
-        <v>100</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G170" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H170" s="10" t="n"/>
       <c r="I170" s="10" t="n"/>
       <c r="J170" s="8" t="inlineStr">
         <is>
-          <t>topenar</t>
+          <t>kominik</t>
         </is>
       </c>
       <c r="K170" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L170" s="20" t="inlineStr">
         <is>
@@ -19536,7 +19584,7 @@
       </c>
       <c r="M170" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — rozvody otopné soustavy</t>
+          <t>TZ ARS dům §4 — komín stávající, vystrojení vložkou pro kamna + krb</t>
         </is>
       </c>
       <c r="N170" s="20" t="inlineStr">
@@ -19558,41 +19606,41 @@
       </c>
       <c r="B171" s="8" t="inlineStr">
         <is>
-          <t>VRN — BOZP</t>
+          <t>PSV-73 Vytápění</t>
         </is>
       </c>
       <c r="C171" s="8" t="inlineStr">
         <is>
-          <t>Koordinace BOZP</t>
+          <t>Rozvody otopné soustavy</t>
         </is>
       </c>
       <c r="D171" s="20" t="inlineStr">
         <is>
-          <t>030091000</t>
+          <t>733111021</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
         <is>
-          <t>Koordinátor BOZP na staveništi dle zákona 309/2006 Sb. — pro stavbu s více než jedním zhotovitelem</t>
+          <t>Rozvody otopné soustavy Cu/PEX k vnitřním jednotkám TČ + radiátorům pro doplňkové (cca 100 bm odhad)</t>
         </is>
       </c>
       <c r="F171" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G171" s="23" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G171" s="22" t="n">
+        <v>100</v>
       </c>
       <c r="H171" s="10" t="n"/>
       <c r="I171" s="10" t="n"/>
       <c r="J171" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K171" s="24" t="n">
-        <v>0.99</v>
+        <v>0.75</v>
       </c>
       <c r="L171" s="20" t="inlineStr">
         <is>
@@ -19601,12 +19649,12 @@
       </c>
       <c r="M171" s="8" t="inlineStr">
         <is>
-          <t>Zákon 309/2006 Sb. — povinný BOZP koordinátor pro vícezhotovitelskou stavbu</t>
+          <t>TZ ARS dům §4 — rozvody otopné soustavy</t>
         </is>
       </c>
       <c r="N171" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O171" s="26" t="inlineStr">
@@ -19623,22 +19671,22 @@
       </c>
       <c r="B172" s="8" t="inlineStr">
         <is>
-          <t>VRN — Dokumentace</t>
+          <t>VRN — BOZP</t>
         </is>
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokoly + DSP</t>
+          <t>Koordinace BOZP</t>
         </is>
       </c>
       <c r="D172" s="20" t="inlineStr">
         <is>
-          <t>030151000</t>
+          <t>030091000</t>
         </is>
       </c>
       <c r="E172" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokoly + Dokumentace skutečného provedení (DSP) — sestavení, vázání, dodávka 2× tiskem + elektronická verze</t>
+          <t>Koordinátor BOZP na staveništi dle zákona 309/2006 Sb. — pro stavbu s více než jedním zhotovitelem</t>
         </is>
       </c>
       <c r="F172" s="20" t="inlineStr">
@@ -19666,12 +19714,12 @@
       </c>
       <c r="M172" s="8" t="inlineStr">
         <is>
-          <t>Vyhláška 499/2006 Sb. + ČKAIT — DSP povinná pro kolaudaci</t>
+          <t>Zákon 309/2006 Sb. — povinný BOZP koordinátor pro vícezhotovitelskou stavbu</t>
         </is>
       </c>
       <c r="N172" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O172" s="26" t="inlineStr">
@@ -19688,41 +19736,41 @@
       </c>
       <c r="B173" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>VRN — Dokumentace</t>
         </is>
       </c>
       <c r="C173" s="8" t="inlineStr">
         <is>
-          <t>Kontejnery suti tříděné</t>
+          <t>Předávací protokoly + DSP</t>
         </is>
       </c>
       <c r="D173" s="20" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>030151000</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
         <is>
-          <t>Kontejnery na suť tříděnou velkoobjemové (beton/cihly, dřevo, kovy, EPS, sádra, směs) — pronájem + svozy</t>
+          <t>Předávací protokoly + Dokumentace skutečného provedení (DSP) — sestavení, vázání, dodávka 2× tiskem + elektronická verze</t>
         </is>
       </c>
       <c r="F173" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G173" s="23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H173" s="10" t="n"/>
       <c r="I173" s="10" t="n"/>
       <c r="J173" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K173" s="24" t="n">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
       <c r="L173" s="20" t="inlineStr">
         <is>
@@ -19731,12 +19779,12 @@
       </c>
       <c r="M173" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e: beton/cihly 46 t + dřevo 9 t + kovy 0.1 + EPS 0.1 + sádra 0.2 + směs 1.0</t>
+          <t>Vyhláška 499/2006 Sb. + ČKAIT — DSP povinná pro kolaudaci</t>
         </is>
       </c>
       <c r="N173" s="20" t="inlineStr">
         <is>
-          <t>#9, #10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O173" s="26" t="inlineStr">
@@ -19758,36 +19806,36 @@
       </c>
       <c r="C174" s="8" t="inlineStr">
         <is>
-          <t>Doprava materiálu</t>
+          <t>Kontejnery suti tříděné</t>
         </is>
       </c>
       <c r="D174" s="20" t="inlineStr">
         <is>
-          <t>031031000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="E174" s="8" t="inlineStr">
         <is>
-          <t>Doprava materiálu na stavbu (centrální koordinace) — paušál ~2-3 % z PN materiál</t>
+          <t>Kontejnery na suť tříděnou velkoobjemové (beton/cihly, dřevo, kovy, EPS, sádra, směs) — pronájem + svozy</t>
         </is>
       </c>
       <c r="F174" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G174" s="23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H174" s="10" t="n"/>
       <c r="I174" s="10" t="n"/>
       <c r="J174" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K174" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L174" s="20" t="inlineStr">
         <is>
@@ -19796,12 +19844,12 @@
       </c>
       <c r="M174" s="8" t="inlineStr">
         <is>
-          <t>B4_productivity — standard doprava RD městská zástavba</t>
+          <t>TZ B m.10.e: beton/cihly 46 t + dřevo 9 t + kovy 0.1 + EPS 0.1 + sádra 0.2 + směs 1.0</t>
         </is>
       </c>
       <c r="N174" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>#9, #10</t>
         </is>
       </c>
       <c r="O174" s="26" t="inlineStr">
@@ -19823,36 +19871,36 @@
       </c>
       <c r="C175" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadů 56.9 t</t>
+          <t>Doprava materiálu</t>
         </is>
       </c>
       <c r="D175" s="20" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>031031000</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
         <is>
-          <t>Likvidace stavební suti dle vyhl. 8/2021 Sb. — skládkovné + recyklace + třídění (56.9 t celkem per TZ B m.10.e)</t>
+          <t>Doprava materiálu na stavbu (centrální koordinace) — paušál ~2-3 % z PN materiál</t>
         </is>
       </c>
       <c r="F175" s="20" t="inlineStr">
         <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G175" s="22" t="n">
-        <v>56.9</v>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G175" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H175" s="10" t="n"/>
       <c r="I175" s="10" t="n"/>
       <c r="J175" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K175" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L175" s="20" t="inlineStr">
         <is>
@@ -19861,12 +19909,12 @@
       </c>
       <c r="M175" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e bilance odpadů celkem dům</t>
+          <t>B4_productivity — standard doprava RD městská zástavba</t>
         </is>
       </c>
       <c r="N175" s="20" t="inlineStr">
         <is>
-          <t>#9, #10</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O175" s="26" t="inlineStr">
@@ -19883,41 +19931,41 @@
       </c>
       <c r="B176" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C176" s="8" t="inlineStr">
         <is>
-          <t>Geodetické zaměření před + po realizaci</t>
+          <t>Likvidace odpadů 56.9 t</t>
         </is>
       </c>
       <c r="D176" s="20" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="E176" s="8" t="inlineStr">
         <is>
-          <t>Geodetické zaměření před realizací (verifikace polohopis + výškopis) + po dokončení (zaměření skutečného provedení pro kolaudaci)</t>
+          <t>Likvidace stavební suti dle vyhl. 8/2021 Sb. — skládkovné + recyklace + třídění (56.9 t celkem per TZ B m.10.e)</t>
         </is>
       </c>
       <c r="F176" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G176" s="23" t="n">
-        <v>2</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G176" s="22" t="n">
+        <v>56.9</v>
       </c>
       <c r="H176" s="10" t="n"/>
       <c r="I176" s="10" t="n"/>
       <c r="J176" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K176" s="24" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="L176" s="20" t="inlineStr">
         <is>
@@ -19926,12 +19974,12 @@
       </c>
       <c r="M176" s="8" t="inlineStr">
         <is>
-          <t>Standard — geodet před+po pro každou stavbu</t>
+          <t>TZ B m.10.e bilance odpadů celkem dům</t>
         </is>
       </c>
       <c r="N176" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#9, #10</t>
         </is>
       </c>
       <c r="O176" s="26" t="inlineStr">
@@ -19948,37 +19996,37 @@
       </c>
       <c r="B177" s="8" t="inlineStr">
         <is>
-          <t>VRN — Kolaudace</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="C177" s="8" t="inlineStr">
         <is>
-          <t>Kolaudační řízení</t>
+          <t>Geodetické zaměření před + po realizaci</t>
         </is>
       </c>
       <c r="D177" s="20" t="inlineStr">
         <is>
-          <t>030171000</t>
+          <t>030141000</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
         <is>
-          <t>Kolaudační řízení — paušál (správní poplatky + součinnost) dle zákona 183/2006 Sb.</t>
+          <t>Geodetické zaměření před realizací (verifikace polohopis + výškopis) + po dokončení (zaměření skutečného provedení pro kolaudaci)</t>
         </is>
       </c>
       <c r="F177" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G177" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H177" s="10" t="n"/>
       <c r="I177" s="10" t="n"/>
       <c r="J177" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>geodet</t>
         </is>
       </c>
       <c r="K177" s="24" t="n">
@@ -19991,7 +20039,7 @@
       </c>
       <c r="M177" s="8" t="inlineStr">
         <is>
-          <t>Zákon 183/2006 Sb. + vyhl. 499/2006 Sb.</t>
+          <t>Standard — geodet před+po pro každou stavbu</t>
         </is>
       </c>
       <c r="N177" s="20" t="inlineStr">
@@ -20013,31 +20061,31 @@
       </c>
       <c r="B178" s="8" t="inlineStr">
         <is>
-          <t>VRN — Lešení</t>
+          <t>VRN — Kolaudace</t>
         </is>
       </c>
       <c r="C178" s="8" t="inlineStr">
         <is>
-          <t>Fasádní lešení (ETICS + krov + klempířina)</t>
+          <t>Kolaudační řízení</t>
         </is>
       </c>
       <c r="D178" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>030171000</t>
         </is>
       </c>
       <c r="E178" s="8" t="inlineStr">
         <is>
-          <t>Fasádní lešení trubkové/rámové vč. montáže + pronájmu + demontáže — pro provedení ETICS fasády, krovu a klempířiny po obvodu domu (výška 13 m)</t>
+          <t>Kolaudační řízení — paušál (správní poplatky + součinnost) dle zákona 183/2006 Sb.</t>
         </is>
       </c>
       <c r="F178" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G178" s="22" t="n">
-        <v>503.1</v>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G178" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H178" s="10" t="n"/>
       <c r="I178" s="10" t="n"/>
@@ -20047,7 +20095,7 @@
         </is>
       </c>
       <c r="K178" s="24" t="n">
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="L178" s="20" t="inlineStr">
         <is>
@@ -20056,7 +20104,7 @@
       </c>
       <c r="M178" s="8" t="inlineStr">
         <is>
-          <t>anchor checklist PM02 — technical necessity (ETICS 276.7 m² nelze provést bez lešení, 941xxx URS família) + DXF obvod 38.7 m + řez výška 13 m</t>
+          <t>Zákon 183/2006 Sb. + vyhl. 499/2006 Sb.</t>
         </is>
       </c>
       <c r="N178" s="20" t="inlineStr">
@@ -20070,11 +20118,7 @@
         </is>
       </c>
       <c r="P178" s="41" t="n"/>
-      <c r="Q178" s="41" t="inlineStr">
-        <is>
-          <t>ANCHOR_CHECKLIST_PM02</t>
-        </is>
-      </c>
+      <c r="Q178" s="41" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="20" t="n">
@@ -20082,31 +20126,31 @@
       </c>
       <c r="B179" s="8" t="inlineStr">
         <is>
-          <t>VRN — Pojištění + zábory</t>
+          <t>VRN — Lešení</t>
         </is>
       </c>
       <c r="C179" s="8" t="inlineStr">
         <is>
-          <t>Pojištění stavby (montážní + odpovědnostní)</t>
+          <t>Fasádní lešení (ETICS + krov + klempířina)</t>
         </is>
       </c>
       <c r="D179" s="20" t="inlineStr">
         <is>
-          <t>030081000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
         <is>
-          <t>Montážní pojištění stavby (CAR) + pojištění odpovědnosti za škodu (zhotovitel) — paušál cca 0.3-0.5 % z PN</t>
+          <t>Fasádní lešení trubkové/rámové vč. montáže + pronájmu + demontáže — pro provedení ETICS fasády, krovu a klempířiny po obvodu domu (výška 13 m)</t>
         </is>
       </c>
       <c r="F179" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="G179" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G179" s="22" t="n">
+        <v>503.1</v>
       </c>
       <c r="H179" s="10" t="n"/>
       <c r="I179" s="10" t="n"/>
@@ -20116,7 +20160,7 @@
         </is>
       </c>
       <c r="K179" s="24" t="n">
-        <v>0.99</v>
+        <v>0.8</v>
       </c>
       <c r="L179" s="20" t="inlineStr">
         <is>
@@ -20125,12 +20169,12 @@
       </c>
       <c r="M179" s="8" t="inlineStr">
         <is>
-          <t>Standard zhotovitel — pojistná povinnost</t>
+          <t>anchor checklist PM02 — technical necessity (ETICS 276.7 m² nelze provést bez lešení, 941xxx URS família) + DXF obvod 38.7 m + řez výška 13 m</t>
         </is>
       </c>
       <c r="N179" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O179" s="26" t="inlineStr">
@@ -20139,7 +20183,11 @@
         </is>
       </c>
       <c r="P179" s="41" t="n"/>
-      <c r="Q179" s="41" t="n"/>
+      <c r="Q179" s="41" t="inlineStr">
+        <is>
+          <t>ANCHOR_CHECKLIST_PM02</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="20" t="n">
@@ -20152,22 +20200,22 @@
       </c>
       <c r="C180" s="8" t="inlineStr">
         <is>
-          <t>Krátkodobé zábory ul. Fibichova</t>
+          <t>Pojištění stavby (montážní + odpovědnostní)</t>
         </is>
       </c>
       <c r="D180" s="20" t="inlineStr">
         <is>
-          <t>030083000</t>
+          <t>030081000</t>
         </is>
       </c>
       <c r="E180" s="8" t="inlineStr">
         <is>
-          <t>Krátkodobé zábory ulice Fibichova pro materiál a kontejnery (povolení MU Jáchymov + DI) — odhad 30 dnů kumulativně</t>
+          <t>Montážní pojištění stavby (CAR) + pojištění odpovědnosti za škodu (zhotovitel) — paušál cca 0.3-0.5 % z PN</t>
         </is>
       </c>
       <c r="F180" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>paušál</t>
         </is>
       </c>
       <c r="G180" s="23" t="n">
@@ -20181,7 +20229,7 @@
         </is>
       </c>
       <c r="K180" s="24" t="n">
-        <v>0.75</v>
+        <v>0.99</v>
       </c>
       <c r="L180" s="20" t="inlineStr">
         <is>
@@ -20190,7 +20238,7 @@
       </c>
       <c r="M180" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10 + situace — řadovka ul. Fibichova</t>
+          <t>Standard zhotovitel — pojistná povinnost</t>
         </is>
       </c>
       <c r="N180" s="20" t="inlineStr">
@@ -20212,22 +20260,22 @@
       </c>
       <c r="B181" s="8" t="inlineStr">
         <is>
-          <t>VRN — Průzkumy</t>
+          <t>VRN — Pojištění + zábory</t>
         </is>
       </c>
       <c r="C181" s="8" t="inlineStr">
         <is>
-          <t>Mykologický průzkum dřeva při bourání</t>
+          <t>Krátkodobé zábory ul. Fibichova</t>
         </is>
       </c>
       <c r="D181" s="20" t="inlineStr">
         <is>
-          <t>030131000</t>
+          <t>030083000</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
         <is>
-          <t>Mykologický průzkum + průzkum výskytu dřevokazného hmyzu stávajícího krovu a dřevěných trámů zhlaví — pro vyloučení narušení dřevěných konstrukcí; provádí autorizovaný mykolog při bourání</t>
+          <t>Krátkodobé zábory ulice Fibichova pro materiál a kontejnery (povolení MU Jáchymov + DI) — odhad 30 dnů kumulativně</t>
         </is>
       </c>
       <c r="F181" s="20" t="inlineStr">
@@ -20242,11 +20290,11 @@
       <c r="I181" s="10" t="n"/>
       <c r="J181" s="8" t="inlineStr">
         <is>
-          <t>mykolog</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K181" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L181" s="20" t="inlineStr">
         <is>
@@ -20255,7 +20303,7 @@
       </c>
       <c r="M181" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.3 + POZN.2.05 z půdorysů návrh + řez A-A návrh (explicit dřevokazný hmyz scope per drawing wording)</t>
+          <t>TZ B m.10 + situace — řadovka ul. Fibichova</t>
         </is>
       </c>
       <c r="N181" s="20" t="inlineStr">
@@ -20269,11 +20317,7 @@
         </is>
       </c>
       <c r="P181" s="41" t="n"/>
-      <c r="Q181" s="41" t="inlineStr">
-        <is>
-          <t>PER_DRAWING_ENRICHMENT_POZN_2_05</t>
-        </is>
-      </c>
+      <c r="Q181" s="41" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="20" t="n">
@@ -20286,17 +20330,17 @@
       </c>
       <c r="C182" s="8" t="inlineStr">
         <is>
-          <t>Azbestový průzkum podrobný před demolicí</t>
+          <t>Mykologický průzkum dřeva při bourání</t>
         </is>
       </c>
       <c r="D182" s="20" t="inlineStr">
         <is>
-          <t>030133000</t>
+          <t>030131000</t>
         </is>
       </c>
       <c r="E182" s="8" t="inlineStr">
         <is>
-          <t>Azbestový průzkum podrobný před demolicí — laboratorní vzorky a posudek (B kap. m.7.a předběžně negativní, ale podrobný před bouráním povinný)</t>
+          <t>Mykologický průzkum + průzkum výskytu dřevokazného hmyzu stávajícího krovu a dřevěných trámů zhlaví — pro vyloučení narušení dřevěných konstrukcí; provádí autorizovaný mykolog při bourání</t>
         </is>
       </c>
       <c r="F182" s="20" t="inlineStr">
@@ -20311,7 +20355,7 @@
       <c r="I182" s="10" t="n"/>
       <c r="J182" s="8" t="inlineStr">
         <is>
-          <t>azbestovy_specialista</t>
+          <t>mykolog</t>
         </is>
       </c>
       <c r="K182" s="24" t="n">
@@ -20324,7 +20368,7 @@
       </c>
       <c r="M182" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.7.a + ARS §3.2 — azbestový průzkum povinný před demolicí</t>
+          <t>TZ ARS dům §3.2.3 + POZN.2.05 z půdorysů návrh + řez A-A návrh (explicit dřevokazný hmyz scope per drawing wording)</t>
         </is>
       </c>
       <c r="N182" s="20" t="inlineStr">
@@ -20338,7 +20382,11 @@
         </is>
       </c>
       <c r="P182" s="41" t="n"/>
-      <c r="Q182" s="41" t="n"/>
+      <c r="Q182" s="41" t="inlineStr">
+        <is>
+          <t>PER_DRAWING_ENRICHMENT_POZN_2_05</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="20" t="n">
@@ -20346,41 +20394,41 @@
       </c>
       <c r="B183" s="8" t="inlineStr">
         <is>
-          <t>VRN — Přesun hmot</t>
+          <t>VRN — Průzkumy</t>
         </is>
       </c>
       <c r="C183" s="8" t="inlineStr">
         <is>
-          <t>Přesun hmot pro budovu</t>
+          <t>Azbestový průzkum podrobný před demolicí</t>
         </is>
       </c>
       <c r="D183" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>030133000</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
         <is>
-          <t>Přesun hmot pro budovu — vnitrostaveništní vertikální + horizontální doprava materiálu a hmot (rekonstrukce vícepodlažní RD + nástavba 3.NP)</t>
+          <t>Azbestový průzkum podrobný před demolicí — laboratorní vzorky a posudek (B kap. m.7.a předběžně negativní, ale podrobný před bouráním povinný)</t>
         </is>
       </c>
       <c r="F183" s="20" t="inlineStr">
         <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G183" s="22" t="n">
-        <v>0</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G183" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H183" s="10" t="n"/>
       <c r="I183" s="10" t="n"/>
       <c r="J183" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>azbestovy_specialista</t>
         </is>
       </c>
       <c r="K183" s="24" t="n">
-        <v>0.6</v>
+        <v>0.85</v>
       </c>
       <c r="L183" s="20" t="inlineStr">
         <is>
@@ -20389,12 +20437,12 @@
       </c>
       <c r="M183" s="8" t="inlineStr">
         <is>
-          <t>anchor checklist PM01 — technical necessity (povinná položka každého rozpočtu, 998xxx URS família)</t>
+          <t>TZ B m.7.a + ARS §3.2 — azbestový průzkum povinný před demolicí</t>
         </is>
       </c>
       <c r="N183" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O183" s="26" t="inlineStr">
@@ -20403,11 +20451,7 @@
         </is>
       </c>
       <c r="P183" s="41" t="n"/>
-      <c r="Q183" s="41" t="inlineStr">
-        <is>
-          <t>ANCHOR_CHECKLIST_PM01</t>
-        </is>
-      </c>
+      <c r="Q183" s="41" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="20" t="n">
@@ -20415,41 +20459,41 @@
       </c>
       <c r="B184" s="8" t="inlineStr">
         <is>
-          <t>VRN — Revize</t>
+          <t>VRN — Přesun hmot</t>
         </is>
       </c>
       <c r="C184" s="8" t="inlineStr">
         <is>
-          <t>Revize hydrantu vnějšího</t>
+          <t>Přesun hmot pro budovu</t>
         </is>
       </c>
       <c r="D184" s="20" t="inlineStr">
         <is>
-          <t>030161000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E184" s="8" t="inlineStr">
         <is>
-          <t>Revize vnějšího hydrantu pro požární zabezpečení (DN min. 80, vzdálenost 100 m dle TZ PBŘ) — periodická kontrola</t>
+          <t>Přesun hmot pro budovu — vnitrostaveništní vertikální + horizontální doprava materiálu a hmot (rekonstrukce vícepodlažní RD + nástavba 3.NP)</t>
         </is>
       </c>
       <c r="F184" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G184" s="23" t="n">
-        <v>1</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G184" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H184" s="10" t="n"/>
       <c r="I184" s="10" t="n"/>
       <c r="J184" s="8" t="inlineStr">
         <is>
-          <t>revize_specialista</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K184" s="24" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="L184" s="20" t="inlineStr">
         <is>
@@ -20458,7 +20502,7 @@
       </c>
       <c r="M184" s="8" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — vnější odběrné místo požární vody, revize před kolaudací</t>
+          <t>anchor checklist PM01 — technical necessity (povinná položka každého rozpočtu, 998xxx URS família)</t>
         </is>
       </c>
       <c r="N184" s="20" t="inlineStr">
@@ -20472,7 +20516,11 @@
         </is>
       </c>
       <c r="P184" s="41" t="n"/>
-      <c r="Q184" s="41" t="n"/>
+      <c r="Q184" s="41" t="inlineStr">
+        <is>
+          <t>ANCHOR_CHECKLIST_PM01</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="20" t="n">
@@ -20480,41 +20528,41 @@
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
-          <t>VRN — Zařízení staveniště</t>
+          <t>VRN — Revize</t>
         </is>
       </c>
       <c r="C185" s="8" t="inlineStr">
         <is>
-          <t>Buňky kancelář + sociální</t>
+          <t>Revize hydrantu vnějšího</t>
         </is>
       </c>
       <c r="D185" s="20" t="inlineStr">
         <is>
-          <t>030011000</t>
+          <t>030161000</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
         <is>
-          <t>Zařízení staveniště — buňka kancelář + sociální buňka (WC + šatna), pronájem ~8 měsíců</t>
+          <t>Revize vnějšího hydrantu pro požární zabezpečení (DN min. 80, vzdálenost 100 m dle TZ PBŘ) — periodická kontrola</t>
         </is>
       </c>
       <c r="F185" s="20" t="inlineStr">
         <is>
-          <t>kpl-měs</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G185" s="23" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H185" s="10" t="n"/>
       <c r="I185" s="10" t="n"/>
       <c r="J185" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>revize_specialista</t>
         </is>
       </c>
       <c r="K185" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L185" s="20" t="inlineStr">
         <is>
@@ -20523,12 +20571,12 @@
       </c>
       <c r="M185" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.1.m realizace 2026-2027 + standard staveniště RD městská zástavba</t>
+          <t>TZ PBŘ dům — vnější odběrné místo požární vody, revize před kolaudací</t>
         </is>
       </c>
       <c r="N185" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O185" s="26" t="inlineStr">
@@ -20550,22 +20598,22 @@
       </c>
       <c r="C186" s="8" t="inlineStr">
         <is>
-          <t>Mobilní WC</t>
+          <t>Buňky kancelář + sociální</t>
         </is>
       </c>
       <c r="D186" s="20" t="inlineStr">
         <is>
-          <t>030013000</t>
+          <t>030011000</t>
         </is>
       </c>
       <c r="E186" s="8" t="inlineStr">
         <is>
-          <t>Mobilní chemické WC TOI TOI pro pracovníky — pronájem ~8 měsíců</t>
+          <t>Zařízení staveniště — buňka kancelář + sociální buňka (WC + šatna), pronájem ~8 měsíců</t>
         </is>
       </c>
       <c r="F186" s="20" t="inlineStr">
         <is>
-          <t>ks-měs</t>
+          <t>kpl-měs</t>
         </is>
       </c>
       <c r="G186" s="23" t="n">
@@ -20588,7 +20636,7 @@
       </c>
       <c r="M186" s="8" t="inlineStr">
         <is>
-          <t>BOZP — mobilní WC povinné pro stavbu RD</t>
+          <t>TZ B m.1.m realizace 2026-2027 + standard staveniště RD městská zástavba</t>
         </is>
       </c>
       <c r="N186" s="20" t="inlineStr">
@@ -20615,26 +20663,26 @@
       </c>
       <c r="C187" s="8" t="inlineStr">
         <is>
-          <t>El. odběr + vodovodní odběr stavby</t>
+          <t>Mobilní WC</t>
         </is>
       </c>
       <c r="D187" s="20" t="inlineStr">
         <is>
-          <t>031011000</t>
+          <t>030013000</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
         <is>
-          <t>El. odběr stavby (zřízení staveništního rozvaděče + měřič) + vodovodní odběr (zřízení staveništní přípojky + vodoměr) — ~8 měsíců</t>
+          <t>Mobilní chemické WC TOI TOI pro pracovníky — pronájem ~8 měsíců</t>
         </is>
       </c>
       <c r="F187" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks-měs</t>
         </is>
       </c>
       <c r="G187" s="23" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H187" s="10" t="n"/>
       <c r="I187" s="10" t="n"/>
@@ -20653,7 +20701,7 @@
       </c>
       <c r="M187" s="8" t="inlineStr">
         <is>
-          <t>Standard staveniště — el. + voda zřízení a odběr po dobu stavby</t>
+          <t>BOZP — mobilní WC povinné pro stavbu RD</t>
         </is>
       </c>
       <c r="N187" s="20" t="inlineStr">
@@ -20680,17 +20728,17 @@
       </c>
       <c r="C188" s="8" t="inlineStr">
         <is>
-          <t>Voda staveniště</t>
+          <t>El. odběr + vodovodní odběr stavby</t>
         </is>
       </c>
       <c r="D188" s="20" t="inlineStr">
         <is>
-          <t>012103101</t>
+          <t>031011000</t>
         </is>
       </c>
       <c r="E188" s="8" t="inlineStr">
         <is>
-          <t>Voda staveniště — napojení na stávající vodovodní přípojku, dočasné rozvody na staveništi (mísení malt, čištění, soc. zázemí), paušál pro dobu výstavby ~18 měs.</t>
+          <t>El. odběr stavby (zřízení staveništního rozvaděče + měřič) + vodovodní odběr (zřízení staveništní přípojky + vodoměr) — ~8 měsíců</t>
         </is>
       </c>
       <c r="F188" s="20" t="inlineStr">
@@ -20709,38 +20757,103 @@
         </is>
       </c>
       <c r="K188" s="24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L188" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M188" s="8" t="inlineStr">
+        <is>
+          <t>Standard staveniště — el. + voda zřízení a odběr po dobu stavby</t>
+        </is>
+      </c>
+      <c r="N188" s="20" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
+      <c r="O188" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P188" s="41" t="n"/>
+      <c r="Q188" s="41" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="20" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Zařízení staveniště</t>
+        </is>
+      </c>
+      <c r="C189" s="8" t="inlineStr">
+        <is>
+          <t>Voda staveniště</t>
+        </is>
+      </c>
+      <c r="D189" s="20" t="inlineStr">
+        <is>
+          <t>012103101</t>
+        </is>
+      </c>
+      <c r="E189" s="8" t="inlineStr">
+        <is>
+          <t>Voda staveniště — napojení na stávající vodovodní přípojku, dočasné rozvody na staveništi (mísení malt, čištění, soc. zázemí), paušál pro dobu výstavby ~18 měs.</t>
+        </is>
+      </c>
+      <c r="F189" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G189" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H189" s="10" t="n"/>
+      <c r="I189" s="10" t="n"/>
+      <c r="J189" s="8" t="inlineStr">
+        <is>
+          <t>VRN_management</t>
+        </is>
+      </c>
+      <c r="K189" s="24" t="n">
         <v>0.9</v>
       </c>
-      <c r="L188" s="20" t="inlineStr">
+      <c r="L189" s="20" t="inlineStr">
         <is>
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M188" s="8" t="inlineStr">
+      <c r="M189" s="8" t="inlineStr">
         <is>
           <t>TZ B Souhrnná m.5 — 'Stávající vodovodní přípojka z veřejného vodovodu'</t>
         </is>
       </c>
-      <c r="N188" s="20" t="inlineStr">
+      <c r="N189" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O188" s="26" t="inlineStr">
+      <c r="O189" s="26" t="inlineStr">
         <is>
           <t>ANO</t>
         </is>
       </c>
-      <c r="P188" s="41" t="n"/>
-      <c r="Q188" s="41" t="inlineStr">
+      <c r="P189" s="41" t="n"/>
+      <c r="Q189" s="41" t="inlineStr">
         <is>
           <t>GAP_003</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O188"/>
-  <conditionalFormatting sqref="K2:K188">
+  <autoFilter ref="A1:O189"/>
+  <conditionalFormatting sqref="K2:K189">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0" stopIfTrue="1">
       <formula>0.70</formula>
     </cfRule>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2_final.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2_final.xlsx
@@ -27004,7 +27004,7 @@
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>Podlahový EPS 150 λ=0.035 tl. 120 mm — pod betonový potěr 1.NP a 3.NP…</t>
+          <t>Hydroizolace pod ŽB deskou 1.NP — modifikované asfaltové pásy SBS 2× (zároveň pr…</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2_final.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2_final.xlsx
@@ -19,11 +19,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_verification" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Var_A_Agregovany_Dum'!$A$1:$G$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Var_A_Agregovany_Dum'!$A$1:$G$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Var_A_Agregovany_Sklad'!$A$1:$G$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$131</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$201</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Var_F_URS_Verification_Trail'!$A$1:$H$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -991,11 +991,11 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>GROUP BY kapitola per objekt (24 souhrnných řádků). Pro orientační cenovku.</t>
+          <t>GROUP BY kapitola per objekt (25 souhrnných řádků). Pro orientační cenovku.</t>
         </is>
       </c>
       <c r="C23" s="9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D23" s="10" t="n"/>
       <c r="E23" s="10" t="n"/>
@@ -1009,11 +1009,11 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>HSV položkově (118 ks) + PSV/TZB/VRN agregovaně (12 skupin) = 130 řádků.</t>
+          <t>HSV položkově (119 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 132 řádků.</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D24" s="10" t="n"/>
       <c r="E24" s="10" t="n"/>
@@ -1027,11 +1027,11 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Plný detail (200 dum + 28 sklad = 228 položek). Cílový rozsah pro produkční pricing.</t>
+          <t>Plný detail (203 dum + 31 sklad = 234 položek). Cílový rozsah pro produkční pricing.</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="D25" s="10" t="n"/>
       <c r="E25" s="10" t="n"/>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>228 (200 dum + 28 sklad)</t>
+          <t>234 (203 dum + 31 sklad)</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>HSV 118 | PSV 54 | TZB 34 | VRN 22</t>
+          <t>HSV 119 | M 2 | PSV 56 | TZB 34 | VRN 23</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>0.99: 17 | 0.95: 32 | 0.90: 35 | 0.85: 41 | 0.80: 19 | 0.75: 72 | 0.70: 2 | 0.60: 2 | 0.50: 4 | 0.00: 4</t>
+          <t>0.99: 17 | 0.95: 32 | 0.90: 35 | 0.85: 41 | 0.80: 21 | 0.75: 72 | 0.70: 4 | 0.60: 3 | 0.50: 4 | 0.00: 5</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>8 WebSearch verified (3.5 %) ✓ | 5 wrong leaf flagged (2.2 %) ⚠ | 150 needs_production_lookup (65.8 %)</t>
+          <t>8 WebSearch verified (3.4 %) ✓ | 5 wrong leaf flagged (2.1 %) ⚠ | 156 needs_production_lookup (66.7 %)</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>28 items (viz Otazky_pro_Karla docx)</t>
+          <t>29 items (viz Otazky_pro_Karla docx)</t>
         </is>
       </c>
     </row>
@@ -1182,8 +1182,8 @@
       <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Rozpočet generován STAVAGENT pipelinem z DSP dokumentace s DPS-grade DXF metadaty.
-228 položek celkem (200 dum + 28 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
-Confidence distribution: 17×0.99 · 32×0.95 · 35×0.90 · 41×0.85 · 19×0.80 · 72×0.75 · 2×0.70 · 2×0.60 · 4×0.50 · 4×0.00.
+234 položek celkem (203 dum + 31 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
+Confidence distribution: 17×0.99 · 32×0.95 · 35×0.90 · 41×0.85 · 21×0.80 · 72×0.75 · 4×0.70 · 3×0.60 · 4×0.50 · 5×0.00.
 25 položek vzniklo per-room expansion ze 9 aggregate parents (každá expanded položka tagged _expansion_origin).
 10 položek recalculated s exact external perimeter 38.70 m (DXF km_R_návrh_tlustá 2 closed polygon) vs prior fallback 41.0 m.
 Skladby vrstev (Sheet 8 Var_E) pochází POUZE z TZ explicit text + DXF cross-validation HATCH patterns. ŽÁDNÉ generic 'standardní RD' assumption — kde TZ silent, explicit fallback flag s ČSN default.
@@ -1255,7 +1255,7 @@
     <row r="55">
       <c r="A55" s="45" t="inlineStr">
         <is>
-          <t>• Total items: 228 (200 dům + 28 sklad) — vč. CEV +3 (komín/zídky/drenáž), anchor-gap +2 (přesun hmot/lešení), terasa-area fix + venkovní schody na terénu. 70 items s realizuje_skladbu.</t>
+          <t>• Total items: 234 (203 dům + 31 sklad) — vč. CEV +3 (komín/zídky/drenáž), anchor-gap +2 (přesun hmot/lešení), terasa-area fix + venkovní schody na terénu. 70 items s realizuje_skladbu.</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2695,11 +2695,11 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; Zásuvky a vypínače; … (+3 dalších)</t>
+          <t>Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; Zásuvky a vypínače; … (+4 dalších)</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" s="10" t="n"/>
       <c r="F9" s="10" t="n"/>
@@ -2715,16 +2715,16 @@
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>PSV-71 — Izolace HI + TI</t>
+          <t>M-24</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; Podlahový EPS 150; … (+1 dalších)</t>
+          <t>Lokální odtah digestoří kuchyní</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E10" s="10" t="n"/>
       <c r="F10" s="10" t="n"/>
@@ -2740,16 +2740,16 @@
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
+          <t>PSV-71 — Izolace HI + TI</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; Sanitární keramika koupelna 1.05 (1.NP); … (+15 dalších)</t>
+          <t>HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; Podlahový EPS 150; … (+1 dalších)</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E11" s="10" t="n"/>
       <c r="F11" s="10" t="n"/>
@@ -2765,16 +2765,16 @@
       </c>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t>PSV-73 — Vytápění + komín</t>
+          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; Krb na tuhá paliva 3.NP; … (+4 dalších)</t>
+          <t>Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; Sanitární keramika koupelna 1.05 (1.NP); … (+15 dalších)</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E12" s="10" t="n"/>
       <c r="F12" s="10" t="n"/>
@@ -2790,16 +2790,16 @@
       </c>
       <c r="B13" s="21" t="inlineStr">
         <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>PSV-73 — Vytápění + komín</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); Plastové okno trojsklo — 'okno 3.NP' (ulice); … (+18 dalších)</t>
+          <t>Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; Krb na tuhá paliva 3.NP; … (+4 dalších)</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E13" s="10" t="n"/>
       <c r="F13" s="10" t="n"/>
@@ -2815,16 +2815,16 @@
       </c>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; Nášlap biodeska 3.NP spací patro; … (+3 dalších)</t>
+          <t>Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); Plastové okno trojsklo — 'okno 3.NP' (ulice); … (+18 dalších)</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E14" s="10" t="n"/>
       <c r="F14" s="10" t="n"/>
@@ -2840,16 +2840,16 @@
       </c>
       <c r="B15" s="21" t="inlineStr">
         <is>
-          <t>PSV-78 — Povrchové úpravy</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; Omítka jádrová + štuk 3.NP; … (+12 dalších)</t>
+          <t>Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; Nášlap biodeska 3.NP spací patro; … (+3 dalších)</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E15" s="10" t="n"/>
       <c r="F15" s="10" t="n"/>
@@ -2865,16 +2865,16 @@
       </c>
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t>PSV-95 — Detekce požární</t>
+          <t>PSV-78 — Povrchové úpravy</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Autonomní hlásič kouře; Přenosný hasicí přístroj 34A</t>
+          <t>Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; Omítka jádrová + štuk 3.NP; … (+12 dalších)</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E16" s="10" t="n"/>
       <c r="F16" s="10" t="n"/>
@@ -2890,16 +2890,16 @@
       </c>
       <c r="B17" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>PSV-95 — Detekce požární</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; Kontejnery suti tříděné; … (+14 dalších)</t>
+          <t>Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E17" s="10" t="n"/>
       <c r="F17" s="10" t="n"/>
@@ -2909,8 +2909,33 @@
         </is>
       </c>
     </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="20" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; Kontejnery suti tříděné; … (+14 dalších)</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>agregát — detail viz List B</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G17"/>
+  <autoFilter ref="A1:G18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3081,11 +3106,11 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Sklad mezipodesta schodiště prefa</t>
+          <t>Sklad mezipodesta schodiště prefa; Vjezd Dvořákova — napojení na komunikaci</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="10" t="n"/>
       <c r="F6" s="10" t="n"/>
@@ -3106,11 +3131,11 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 sklad</t>
+          <t>Bezpečnostní dveře RC3 sklad; Vjezdová brána</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="10" t="n"/>
       <c r="F7" s="10" t="n"/>
@@ -3156,11 +3181,11 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; Podíl na obecných VRN dům</t>
+          <t>Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; Podíl na obecných VRN dům; … (+1 dalších)</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" s="10" t="n"/>
       <c r="F9" s="10" t="n"/>
@@ -3182,7 +3207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J131"/>
+  <dimension ref="A1:J133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7970,34 +7995,32 @@
           <t>260217_sklad</t>
         </is>
       </c>
-      <c r="C120" s="21" t="inlineStr">
-        <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+      <c r="C120" s="8" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + vjezd</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Bezpečnostní dveře RC3 sklad</t>
+          <t>Vjezd Dvořákova — napojení na komunikaci — Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťové vody na pozemek (ne na komunikaci)</t>
         </is>
       </c>
       <c r="E120" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F120" s="9" t="n">
-        <v>1</v>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F120" s="22" t="n"/>
       <c r="G120" s="10" t="n"/>
       <c r="H120" s="10" t="n"/>
       <c r="I120" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>komunikace</t>
         </is>
       </c>
       <c r="J120" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8035,12 @@
       </c>
       <c r="C121" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
+          <t>[agregát] 2 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána</t>
         </is>
       </c>
       <c r="E121" s="20" t="inlineStr">
@@ -8052,12 +8075,12 @@
       </c>
       <c r="C122" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 4 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+1 dalších)</t>
+          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
         </is>
       </c>
       <c r="E122" s="20" t="inlineStr">
@@ -8087,17 +8110,17 @@
       </c>
       <c r="B123" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C123" s="21" t="inlineStr">
         <is>
-          <t>M-21 — Elektroinstalace silnoproudá</t>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 7 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+4 dalších)</t>
+          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E123" s="20" t="inlineStr">
@@ -8132,12 +8155,12 @@
       </c>
       <c r="C124" s="21" t="inlineStr">
         <is>
-          <t>PSV-71 — Izolace HI + TI</t>
+          <t>M-21 — Elektroinstalace silnoproudá</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
+          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E124" s="20" t="inlineStr">
@@ -8172,12 +8195,12 @@
       </c>
       <c r="C125" s="21" t="inlineStr">
         <is>
-          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
+          <t>M-24</t>
         </is>
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
+          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
         </is>
       </c>
       <c r="E125" s="20" t="inlineStr">
@@ -8212,12 +8235,12 @@
       </c>
       <c r="C126" s="21" t="inlineStr">
         <is>
-          <t>PSV-73 — Vytápění + komín</t>
+          <t>PSV-71 — Izolace HI + TI</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
+          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E126" s="20" t="inlineStr">
@@ -8252,12 +8275,12 @@
       </c>
       <c r="C127" s="21" t="inlineStr">
         <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
         </is>
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
+          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
         </is>
       </c>
       <c r="E127" s="20" t="inlineStr">
@@ -8292,12 +8315,12 @@
       </c>
       <c r="C128" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>PSV-73 — Vytápění + komín</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
+          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E128" s="20" t="inlineStr">
@@ -8332,12 +8355,12 @@
       </c>
       <c r="C129" s="21" t="inlineStr">
         <is>
-          <t>PSV-78 — Povrchové úpravy</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
+          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
         </is>
       </c>
       <c r="E129" s="20" t="inlineStr">
@@ -8372,12 +8395,12 @@
       </c>
       <c r="C130" s="21" t="inlineStr">
         <is>
-          <t>PSV-95 — Detekce požární</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 2 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A</t>
+          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
         </is>
       </c>
       <c r="E130" s="20" t="inlineStr">
@@ -8412,12 +8435,12 @@
       </c>
       <c r="C131" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>PSV-78 — Povrchové úpravy</t>
         </is>
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
+          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
         </is>
       </c>
       <c r="E131" s="20" t="inlineStr">
@@ -8441,8 +8464,88 @@
         </is>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" s="20" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C132" s="21" t="inlineStr">
+        <is>
+          <t>PSV-95 — Detekce požární</t>
+        </is>
+      </c>
+      <c r="D132" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+        </is>
+      </c>
+      <c r="E132" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F132" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" s="10" t="n"/>
+      <c r="H132" s="10" t="n"/>
+      <c r="I132" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J132" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="20" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C133" s="21" t="inlineStr">
+        <is>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
+        </is>
+      </c>
+      <c r="D133" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
+        </is>
+      </c>
+      <c r="E133" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F133" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" s="10" t="n"/>
+      <c r="H133" s="10" t="n"/>
+      <c r="I133" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J133" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J131"/>
+  <autoFilter ref="A1:J133"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8453,7 +8556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R201"/>
+  <dimension ref="A1:R204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -18749,27 +18852,27 @@
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>PSV-95 Detekce požární</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávající ELI</t>
+          <t>Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
         </is>
       </c>
       <c r="D150" s="20" t="inlineStr">
         <is>
-          <t>210010011</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
+          <t>Předávací protokol krbu na tuhá paliva + kontrola bezpečných vzdáleností (800 mm směr sálání / 400 mm strany, nehořlavá zóna podlahy) dle PBŘ</t>
         </is>
       </c>
       <c r="F150" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>soubor</t>
         </is>
       </c>
       <c r="G150" s="23" t="n">
@@ -18779,11 +18882,11 @@
       <c r="I150" s="10" t="n"/>
       <c r="J150" s="8" t="inlineStr">
         <is>
-          <t>elektroinstalater</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K150" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L150" s="20" t="inlineStr">
         <is>
@@ -18792,12 +18895,12 @@
       </c>
       <c r="M150" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kompletně nová ELI</t>
+          <t>PBŘ D.3</t>
         </is>
       </c>
       <c r="N150" s="20" t="inlineStr">
         <is>
-          <t>#7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O150" s="26" t="inlineStr">
@@ -18805,8 +18908,12 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P150" s="41" t="n"/>
-      <c r="Q150" s="41" t="n"/>
+      <c r="P150" s="41" t="inlineStr"/>
+      <c r="Q150" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="20" t="n">
@@ -18819,26 +18926,26 @@
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t>Pojistková skříň + 3× podružný rozvaděč</t>
+          <t>Demontáž stávající ELI</t>
         </is>
       </c>
       <c r="D151" s="20" t="inlineStr">
         <is>
-          <t>210110023</t>
+          <t>210010011</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
+          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
         </is>
       </c>
       <c r="F151" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G151" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H151" s="10" t="n"/>
       <c r="I151" s="10" t="n"/>
@@ -18857,7 +18964,7 @@
       </c>
       <c r="M151" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — 'nová pojistková skříň s podružným měřením pro každé patro'</t>
+          <t>TZ ARS dům §4 — kompletně nová ELI</t>
         </is>
       </c>
       <c r="N151" s="20" t="inlineStr">
@@ -18884,26 +18991,26 @@
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>Rozvody silnoproud</t>
+          <t>Pojistková skříň + 3× podružný rozvaděč</t>
         </is>
       </c>
       <c r="D152" s="20" t="inlineStr">
         <is>
-          <t>210800012</t>
+          <t>210110023</t>
         </is>
       </c>
       <c r="E152" s="8" t="inlineStr">
         <is>
-          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
+          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
         </is>
       </c>
       <c r="F152" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G152" s="22" t="n">
-        <v>700</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G152" s="23" t="n">
+        <v>4</v>
       </c>
       <c r="H152" s="10" t="n"/>
       <c r="I152" s="10" t="n"/>
@@ -18913,7 +19020,7 @@
         </is>
       </c>
       <c r="K152" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L152" s="20" t="inlineStr">
         <is>
@@ -18922,7 +19029,7 @@
       </c>
       <c r="M152" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD 3-byt. dispozice</t>
+          <t>TZ ARS dům §4 — 'nová pojistková skříň s podružným měřením pro každé patro'</t>
         </is>
       </c>
       <c r="N152" s="20" t="inlineStr">
@@ -18949,26 +19056,26 @@
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t>Zásuvky a vypínače</t>
+          <t>Rozvody silnoproud</t>
         </is>
       </c>
       <c r="D153" s="20" t="inlineStr">
         <is>
-          <t>210810050</t>
+          <t>210800012</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
+          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
         </is>
       </c>
       <c r="F153" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G153" s="23" t="n">
-        <v>70</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G153" s="22" t="n">
+        <v>700</v>
       </c>
       <c r="H153" s="10" t="n"/>
       <c r="I153" s="10" t="n"/>
@@ -18987,7 +19094,7 @@
       </c>
       <c r="M153" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD 220 m² 3-byt.</t>
+          <t>TZ ARS + B4_productivity standard RD 3-byt. dispozice</t>
         </is>
       </c>
       <c r="N153" s="20" t="inlineStr">
@@ -19014,17 +19121,17 @@
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>Svítidla</t>
+          <t>Zásuvky a vypínače</t>
         </is>
       </c>
       <c r="D154" s="20" t="inlineStr">
         <is>
-          <t>210820002</t>
+          <t>210810050</t>
         </is>
       </c>
       <c r="E154" s="8" t="inlineStr">
         <is>
-          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
+          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
         </is>
       </c>
       <c r="F154" s="20" t="inlineStr">
@@ -19033,7 +19140,7 @@
         </is>
       </c>
       <c r="G154" s="23" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="H154" s="10" t="n"/>
       <c r="I154" s="10" t="n"/>
@@ -19052,7 +19159,7 @@
       </c>
       <c r="M154" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD</t>
+          <t>TZ ARS + B4_productivity standard RD 220 m² 3-byt.</t>
         </is>
       </c>
       <c r="N154" s="20" t="inlineStr">
@@ -19079,26 +19186,26 @@
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t>Příprava FVE</t>
+          <t>Svítidla</t>
         </is>
       </c>
       <c r="D155" s="20" t="inlineStr">
         <is>
-          <t>210800099</t>
+          <t>210820002</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
+          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
         </is>
       </c>
       <c r="F155" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G155" s="23" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="H155" s="10" t="n"/>
       <c r="I155" s="10" t="n"/>
@@ -19108,7 +19215,7 @@
         </is>
       </c>
       <c r="K155" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L155" s="20" t="inlineStr">
         <is>
@@ -19117,7 +19224,7 @@
       </c>
       <c r="M155" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — FVE příprava (bez panelů samotných)</t>
+          <t>TZ ARS + B4_productivity standard RD</t>
         </is>
       </c>
       <c r="N155" s="20" t="inlineStr">
@@ -19144,17 +19251,17 @@
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>Revize ELI při kolaudaci</t>
+          <t>Příprava FVE</t>
         </is>
       </c>
       <c r="D156" s="20" t="inlineStr">
         <is>
-          <t>996019011</t>
+          <t>210800099</t>
         </is>
       </c>
       <c r="E156" s="8" t="inlineStr">
         <is>
-          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
+          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
         </is>
       </c>
       <c r="F156" s="20" t="inlineStr">
@@ -19169,11 +19276,11 @@
       <c r="I156" s="10" t="n"/>
       <c r="J156" s="8" t="inlineStr">
         <is>
-          <t>revize_specialista</t>
+          <t>elektroinstalater</t>
         </is>
       </c>
       <c r="K156" s="24" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="L156" s="20" t="inlineStr">
         <is>
@@ -19182,12 +19289,12 @@
       </c>
       <c r="M156" s="8" t="inlineStr">
         <is>
-          <t>Povinná revize ELI dle ČSN 33 2000-6 + kolaudace</t>
+          <t>TZ ARS dům §4 — FVE příprava (bez panelů samotných)</t>
         </is>
       </c>
       <c r="N156" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#7</t>
         </is>
       </c>
       <c r="O156" s="26" t="inlineStr">
@@ -19204,22 +19311,22 @@
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajících přípojek</t>
+          <t>Revize ELI při kolaudaci</t>
         </is>
       </c>
       <c r="D157" s="20" t="inlineStr">
         <is>
-          <t>722290515</t>
+          <t>996019011</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajícího napojení vodovodu + kanalizace na pozemku — kontrola stavu, čištění, tlaková zkouška</t>
+          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
         </is>
       </c>
       <c r="F157" s="20" t="inlineStr">
@@ -19234,25 +19341,25 @@
       <c r="I157" s="10" t="n"/>
       <c r="J157" s="8" t="inlineStr">
         <is>
-          <t>vodar</t>
+          <t>revize_specialista</t>
         </is>
       </c>
       <c r="K157" s="24" t="n">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
       <c r="L157" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M157" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — vodovod + kanalizace stávající, bez změny</t>
+          <t>Povinná revize ELI dle ČSN 33 2000-6 + kolaudace</t>
         </is>
       </c>
       <c r="N157" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O157" s="26" t="inlineStr">
@@ -19261,11 +19368,7 @@
         </is>
       </c>
       <c r="P157" s="41" t="n"/>
-      <c r="Q157" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+      <c r="Q157" s="41" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="20" t="n">
@@ -19278,26 +19381,26 @@
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>Nové rozvody vody do 3.NP</t>
+          <t>Revize stávajících přípojek</t>
         </is>
       </c>
       <c r="D158" s="20" t="inlineStr">
         <is>
-          <t>722172011</t>
+          <t>722290515</t>
         </is>
       </c>
       <c r="E158" s="8" t="inlineStr">
         <is>
-          <t>Nové rozvody studené + teplé vody do koupelen 1.NP + 2.NP + 3.NP a kuchyní (PEX/Cu, dimenze DN15-25)</t>
+          <t>Revize stávajícího napojení vodovodu + kanalizace na pozemku — kontrola stavu, čištění, tlaková zkouška</t>
         </is>
       </c>
       <c r="F158" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G158" s="22" t="n">
-        <v>80</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G158" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H158" s="10" t="n"/>
       <c r="I158" s="10" t="n"/>
@@ -19307,7 +19410,7 @@
         </is>
       </c>
       <c r="K158" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L158" s="20" t="inlineStr">
         <is>
@@ -19316,7 +19419,7 @@
       </c>
       <c r="M158" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — nové koupelny + kuchyně, vyjasnění #6 working assumption</t>
+          <t>TZ ARS dům §4 — vodovod + kanalizace stávající, bez změny</t>
         </is>
       </c>
       <c r="N158" s="20" t="inlineStr">
@@ -19347,17 +19450,17 @@
       </c>
       <c r="C159" s="8" t="inlineStr">
         <is>
-          <t>Nové odpadní rozvody</t>
+          <t>Nové rozvody vody do 3.NP</t>
         </is>
       </c>
       <c r="D159" s="20" t="inlineStr">
         <is>
-          <t>721174021</t>
+          <t>722172011</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>Nové odpadní rozvody PVC-HT DN40-DN110 ke koupelnám 1.NP, 2.NP, 3.NP a kuchyním + napojení na stávající</t>
+          <t>Nové rozvody studené + teplé vody do koupelen 1.NP + 2.NP + 3.NP a kuchyní (PEX/Cu, dimenze DN15-25)</t>
         </is>
       </c>
       <c r="F159" s="20" t="inlineStr">
@@ -19366,7 +19469,7 @@
         </is>
       </c>
       <c r="G159" s="22" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H159" s="10" t="n"/>
       <c r="I159" s="10" t="n"/>
@@ -19380,12 +19483,12 @@
       </c>
       <c r="L159" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — nové koupelny + kuchyně, odpad do stávající kanalizace</t>
+          <t>TZ ARS dům §4 — nové koupelny + kuchyně, vyjasnění #6 working assumption</t>
         </is>
       </c>
       <c r="N159" s="20" t="inlineStr">
@@ -19399,7 +19502,11 @@
         </is>
       </c>
       <c r="P159" s="41" t="n"/>
-      <c r="Q159" s="41" t="n"/>
+      <c r="Q159" s="41" t="inlineStr">
+        <is>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="20" t="n">
@@ -19412,26 +19519,26 @@
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP)</t>
+          <t>Nové odpadní rozvody</t>
         </is>
       </c>
       <c r="D160" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>721174021</t>
         </is>
       </c>
       <c r="E160" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
+          <t>Nové odpadní rozvody PVC-HT DN40-DN110 ke koupelnám 1.NP, 2.NP, 3.NP a kuchyním + napojení na stávající</t>
         </is>
       </c>
       <c r="F160" s="20" t="inlineStr">
         <is>
-          <t>set</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G160" s="22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H160" s="10" t="n"/>
       <c r="I160" s="10" t="n"/>
@@ -19450,7 +19557,7 @@
       </c>
       <c r="M160" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 1.05 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>TZ ARS dům §4 — nové koupelny + kuchyně, odpad do stávající kanalizace</t>
         </is>
       </c>
       <c r="N160" s="20" t="inlineStr">
@@ -19464,11 +19571,7 @@
         </is>
       </c>
       <c r="P160" s="41" t="n"/>
-      <c r="Q160" s="41" t="inlineStr">
-        <is>
-          <t>GAP_005_deprecated</t>
-        </is>
-      </c>
+      <c r="Q160" s="41" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="20" t="n">
@@ -19481,26 +19584,26 @@
       </c>
       <c r="C161" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP)</t>
         </is>
       </c>
       <c r="D161" s="20" t="inlineStr">
         <is>
-          <t>725211101</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t>Vana koupelnová obdélníková 170×70 cm — koupelna 1.05 1.NP</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
         </is>
       </c>
       <c r="F161" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G161" s="23" t="n">
-        <v>1</v>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G161" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H161" s="10" t="n"/>
       <c r="I161" s="10" t="n"/>
@@ -19510,7 +19613,7 @@
         </is>
       </c>
       <c r="K161" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L161" s="20" t="inlineStr">
         <is>
@@ -19519,12 +19622,12 @@
       </c>
       <c r="M161" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 1.05 1.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 1.05 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N161" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O161" s="26" t="inlineStr">
@@ -19535,7 +19638,7 @@
       <c r="P161" s="41" t="n"/>
       <c r="Q161" s="41" t="inlineStr">
         <is>
-          <t>GAP_005</t>
+          <t>GAP_005_deprecated</t>
         </is>
       </c>
     </row>
@@ -19550,17 +19653,17 @@
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture A</t>
         </is>
       </c>
       <c r="D162" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725211101</t>
         </is>
       </c>
       <c r="E162" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 1.05 1.NP</t>
+          <t>Vana koupelnová obdélníková 170×70 cm — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F162" s="20" t="inlineStr">
@@ -19619,17 +19722,17 @@
       </c>
       <c r="C163" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture C</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture B</t>
         </is>
       </c>
       <c r="D163" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 1.05 1.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F163" s="20" t="inlineStr">
@@ -19688,26 +19791,26 @@
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP)</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture C</t>
         </is>
       </c>
       <c r="D164" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E164" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standard)</t>
+          <t>WC kombi keramické bílé — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F164" s="20" t="inlineStr">
         <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="G164" s="22" t="n">
-        <v>0</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G164" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H164" s="10" t="n"/>
       <c r="I164" s="10" t="n"/>
@@ -19717,7 +19820,7 @@
         </is>
       </c>
       <c r="K164" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L164" s="20" t="inlineStr">
         <is>
@@ -19726,12 +19829,12 @@
       </c>
       <c r="M164" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 2.03 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ MTEXT room 1.05 1.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N164" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O164" s="26" t="inlineStr">
@@ -19742,7 +19845,7 @@
       <c r="P164" s="41" t="n"/>
       <c r="Q164" s="41" t="inlineStr">
         <is>
-          <t>GAP_005_deprecated</t>
+          <t>GAP_005</t>
         </is>
       </c>
     </row>
@@ -19757,26 +19860,26 @@
       </c>
       <c r="C165" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP)</t>
         </is>
       </c>
       <c r="D165" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 2.03 2.NP</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standard)</t>
         </is>
       </c>
       <c r="F165" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G165" s="23" t="n">
-        <v>1</v>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G165" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H165" s="10" t="n"/>
       <c r="I165" s="10" t="n"/>
@@ -19786,7 +19889,7 @@
         </is>
       </c>
       <c r="K165" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L165" s="20" t="inlineStr">
         <is>
@@ -19795,12 +19898,12 @@
       </c>
       <c r="M165" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 2.03 2.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 2.03 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N165" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O165" s="26" t="inlineStr">
@@ -19811,7 +19914,7 @@
       <c r="P165" s="41" t="n"/>
       <c r="Q165" s="41" t="inlineStr">
         <is>
-          <t>GAP_005</t>
+          <t>GAP_005_deprecated</t>
         </is>
       </c>
     </row>
@@ -19826,17 +19929,17 @@
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture A</t>
         </is>
       </c>
       <c r="D166" s="20" t="inlineStr">
         <is>
-          <t>725221201</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E166" s="8" t="inlineStr">
         <is>
-          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 2.03 2.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F166" s="20" t="inlineStr">
@@ -19895,17 +19998,17 @@
       </c>
       <c r="C167" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture C</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture B</t>
         </is>
       </c>
       <c r="D167" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725221201</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 2.03 2.NP</t>
+          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F167" s="20" t="inlineStr">
@@ -19964,26 +20067,26 @@
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP)</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture C</t>
         </is>
       </c>
       <c r="D168" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E168" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standard)</t>
+          <t>WC kombi keramické bílé — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F168" s="20" t="inlineStr">
         <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="G168" s="22" t="n">
-        <v>0</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G168" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H168" s="10" t="n"/>
       <c r="I168" s="10" t="n"/>
@@ -19993,7 +20096,7 @@
         </is>
       </c>
       <c r="K168" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L168" s="20" t="inlineStr">
         <is>
@@ -20002,12 +20105,12 @@
       </c>
       <c r="M168" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 3.04 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ MTEXT room 2.03 2.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N168" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O168" s="26" t="inlineStr">
@@ -20018,7 +20121,7 @@
       <c r="P168" s="41" t="n"/>
       <c r="Q168" s="41" t="inlineStr">
         <is>
-          <t>GAP_005_deprecated</t>
+          <t>GAP_005</t>
         </is>
       </c>
     </row>
@@ -20033,26 +20136,26 @@
       </c>
       <c r="C169" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP)</t>
         </is>
       </c>
       <c r="D169" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 3.04 3.NP</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standard)</t>
         </is>
       </c>
       <c r="F169" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G169" s="23" t="n">
-        <v>1</v>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G169" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H169" s="10" t="n"/>
       <c r="I169" s="10" t="n"/>
@@ -20062,7 +20165,7 @@
         </is>
       </c>
       <c r="K169" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L169" s="20" t="inlineStr">
         <is>
@@ -20071,12 +20174,12 @@
       </c>
       <c r="M169" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 3.04 3.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 3.04 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N169" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O169" s="26" t="inlineStr">
@@ -20087,7 +20190,7 @@
       <c r="P169" s="41" t="n"/>
       <c r="Q169" s="41" t="inlineStr">
         <is>
-          <t>GAP_005</t>
+          <t>GAP_005_deprecated</t>
         </is>
       </c>
     </row>
@@ -20102,17 +20205,17 @@
       </c>
       <c r="C170" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture A</t>
         </is>
       </c>
       <c r="D170" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E170" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 3.04 3.NP</t>
+          <t>WC kombi keramické bílé — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F170" s="20" t="inlineStr">
@@ -20171,17 +20274,17 @@
       </c>
       <c r="C171" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture C</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture B</t>
         </is>
       </c>
       <c r="D171" s="20" t="inlineStr">
         <is>
-          <t>725221201</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
         <is>
-          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 3.04 3.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F171" s="20" t="inlineStr">
@@ -20240,17 +20343,17 @@
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t>Kuchyňský dřez 2 ks (1.06 + 3.05)</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture C</t>
         </is>
       </c>
       <c r="D172" s="20" t="inlineStr">
         <is>
-          <t>725840111</t>
+          <t>725221201</t>
         </is>
       </c>
       <c r="E172" s="8" t="inlineStr">
         <is>
-          <t>Kuchyňský dřez nerez + montáž — 2 ks (kuchyně 1.06 byt rodičů + kuchyně 3.05 byt 3.NP)</t>
+          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F172" s="20" t="inlineStr">
@@ -20259,7 +20362,7 @@
         </is>
       </c>
       <c r="G172" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H172" s="10" t="n"/>
       <c r="I172" s="10" t="n"/>
@@ -20269,7 +20372,7 @@
         </is>
       </c>
       <c r="K172" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L172" s="20" t="inlineStr">
         <is>
@@ -20278,12 +20381,12 @@
       </c>
       <c r="M172" s="8" t="inlineStr">
         <is>
-          <t>DXF kuchyně MTEXT 2× + TZ ARS — dispozice byty</t>
+          <t>DXF dum_DPZ MTEXT room 3.04 3.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N172" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O172" s="26" t="inlineStr">
@@ -20292,7 +20395,11 @@
         </is>
       </c>
       <c r="P172" s="41" t="n"/>
-      <c r="Q172" s="41" t="n"/>
+      <c r="Q172" s="41" t="inlineStr">
+        <is>
+          <t>GAP_005</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="20" t="n">
@@ -20305,17 +20412,17 @@
       </c>
       <c r="C173" s="8" t="inlineStr">
         <is>
-          <t>Vodovodní baterie + drobnosti</t>
+          <t>Kuchyňský dřez 2 ks (1.06 + 3.05)</t>
         </is>
       </c>
       <c r="D173" s="20" t="inlineStr">
         <is>
-          <t>725822611</t>
+          <t>725840111</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
         <is>
-          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační materiály</t>
+          <t>Kuchyňský dřez nerez + montáž — 2 ks (kuchyně 1.06 byt rodičů + kuchyně 3.05 byt 3.NP)</t>
         </is>
       </c>
       <c r="F173" s="20" t="inlineStr">
@@ -20324,7 +20431,7 @@
         </is>
       </c>
       <c r="G173" s="23" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H173" s="10" t="n"/>
       <c r="I173" s="10" t="n"/>
@@ -20334,7 +20441,7 @@
         </is>
       </c>
       <c r="K173" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L173" s="20" t="inlineStr">
         <is>
@@ -20343,7 +20450,7 @@
       </c>
       <c r="M173" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS — kompletní baterie nové</t>
+          <t>DXF kuchyně MTEXT 2× + TZ ARS — dispozice byty</t>
         </is>
       </c>
       <c r="N173" s="20" t="inlineStr">
@@ -20370,17 +20477,17 @@
       </c>
       <c r="C174" s="8" t="inlineStr">
         <is>
-          <t>Akumulační zásobník TUV v suterénu</t>
+          <t>Vodovodní baterie + drobnosti</t>
         </is>
       </c>
       <c r="D174" s="20" t="inlineStr">
         <is>
-          <t>732419411</t>
+          <t>725822611</t>
         </is>
       </c>
       <c r="E174" s="8" t="inlineStr">
         <is>
-          <t>Akumulační zásobník TUV ~300 l v 1.PP napojený na topný systém (sporáková kamna + krb + elektrokotel) — nepřímotop</t>
+          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační materiály</t>
         </is>
       </c>
       <c r="F174" s="20" t="inlineStr">
@@ -20389,17 +20496,17 @@
         </is>
       </c>
       <c r="G174" s="23" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H174" s="10" t="n"/>
       <c r="I174" s="10" t="n"/>
       <c r="J174" s="8" t="inlineStr">
         <is>
-          <t>instalater_TUV_akumulacni_zasobnik</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K174" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L174" s="20" t="inlineStr">
         <is>
@@ -20408,7 +20515,7 @@
       </c>
       <c r="M174" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kombi akumulační zásobník napojený na multivariantní topný systém</t>
+          <t>TZ ARS — kompletní baterie nové</t>
         </is>
       </c>
       <c r="N174" s="20" t="inlineStr">
@@ -20435,17 +20542,17 @@
       </c>
       <c r="C175" s="8" t="inlineStr">
         <is>
-          <t>Elektrický bojler 3.NP</t>
+          <t>Akumulační zásobník TUV v suterénu</t>
         </is>
       </c>
       <c r="D175" s="20" t="inlineStr">
         <is>
-          <t>732429211</t>
+          <t>732419411</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
         <is>
-          <t>Elektrický bojler ~80 l v koupelně 3.NP (nezávislý zdroj pro samostatný byt)</t>
+          <t>Akumulační zásobník TUV ~300 l v 1.PP napojený na topný systém (sporáková kamna + krb + elektrokotel) — nepřímotop</t>
         </is>
       </c>
       <c r="F175" s="20" t="inlineStr">
@@ -20460,7 +20567,7 @@
       <c r="I175" s="10" t="n"/>
       <c r="J175" s="8" t="inlineStr">
         <is>
-          <t>vodar</t>
+          <t>instalater_TUV_akumulacni_zasobnik</t>
         </is>
       </c>
       <c r="K175" s="24" t="n">
@@ -20473,7 +20580,7 @@
       </c>
       <c r="M175" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — elektrický bojler v 3.NP koupelně, vyjasnění #6 odhad 80 l</t>
+          <t>TZ ARS dům §4 — kombi akumulační zásobník napojený na multivariantní topný systém</t>
         </is>
       </c>
       <c r="N175" s="20" t="inlineStr">
@@ -20495,22 +20602,22 @@
       </c>
       <c r="B176" s="8" t="inlineStr">
         <is>
-          <t>PSV-73 Vytápění</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="C176" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna na tuhá paliva</t>
+          <t>Elektrický bojler 3.NP</t>
         </is>
       </c>
       <c r="D176" s="20" t="inlineStr">
         <is>
-          <t>733241011</t>
+          <t>732429211</t>
         </is>
       </c>
       <c r="E176" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna na tuhá paliva ~10 kW s akumulačním zásobníkem TUV — dodávka</t>
+          <t>Elektrický bojler ~80 l v koupelně 3.NP (nezávislý zdroj pro samostatný byt)</t>
         </is>
       </c>
       <c r="F176" s="20" t="inlineStr">
@@ -20525,7 +20632,7 @@
       <c r="I176" s="10" t="n"/>
       <c r="J176" s="8" t="inlineStr">
         <is>
-          <t>topenar</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K176" s="24" t="n">
@@ -20538,7 +20645,7 @@
       </c>
       <c r="M176" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — primární zdroj 1.NP/2.NP, ~10 kW odhad standard RD</t>
+          <t>TZ ARS dům §4 — elektrický bojler v 3.NP koupelně, vyjasnění #6 odhad 80 l</t>
         </is>
       </c>
       <c r="N176" s="20" t="inlineStr">
@@ -20565,22 +20672,22 @@
       </c>
       <c r="C177" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna — montáž</t>
+          <t>Sporáková kamna na tuhá paliva</t>
         </is>
       </c>
       <c r="D177" s="20" t="inlineStr">
         <is>
-          <t>733281011</t>
+          <t>733241011</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna — montáž vč. napojení na komín + akumulační zásobník (cca 8 Nh)</t>
+          <t>Sporáková kamna na tuhá paliva ~10 kW s akumulačním zásobníkem TUV — dodávka</t>
         </is>
       </c>
       <c r="F177" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G177" s="23" t="n">
@@ -20594,7 +20701,7 @@
         </is>
       </c>
       <c r="K177" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L177" s="20" t="inlineStr">
         <is>
@@ -20603,12 +20710,12 @@
       </c>
       <c r="M177" s="8" t="inlineStr">
         <is>
-          <t>Standard montáž kamen s napojením na zásobník</t>
+          <t>TZ ARS dům §4 — primární zdroj 1.NP/2.NP, ~10 kW odhad standard RD</t>
         </is>
       </c>
       <c r="N177" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O177" s="26" t="inlineStr">
@@ -20630,22 +20737,22 @@
       </c>
       <c r="C178" s="8" t="inlineStr">
         <is>
-          <t>Elektrokotel 3.NP</t>
+          <t>Sporáková kamna — montáž</t>
         </is>
       </c>
       <c r="D178" s="20" t="inlineStr">
         <is>
-          <t>733131221</t>
+          <t>733281011</t>
         </is>
       </c>
       <c r="E178" s="8" t="inlineStr">
         <is>
-          <t>Elektrokotel ~8 kW pro 3.NP samostatný byt — dodávka + montáž + napojení</t>
+          <t>Sporáková kamna — montáž vč. napojení na komín + akumulační zásobník (cca 8 Nh)</t>
         </is>
       </c>
       <c r="F178" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G178" s="23" t="n">
@@ -20659,7 +20766,7 @@
         </is>
       </c>
       <c r="K178" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L178" s="20" t="inlineStr">
         <is>
@@ -20668,12 +20775,12 @@
       </c>
       <c r="M178" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — 'Nově navržené 3.NP bude vytápěno elektrokotlem'; ~8 kW odhad</t>
+          <t>Standard montáž kamen s napojením na zásobník</t>
         </is>
       </c>
       <c r="N178" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O178" s="26" t="inlineStr">
@@ -20695,17 +20802,17 @@
       </c>
       <c r="C179" s="8" t="inlineStr">
         <is>
-          <t>Krb na tuhá paliva 3.NP</t>
+          <t>Elektrokotel 3.NP</t>
         </is>
       </c>
       <c r="D179" s="20" t="inlineStr">
         <is>
-          <t>733241011</t>
+          <t>733131221</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
         <is>
-          <t>Krb na tuhá paliva v 3.NP ~6 kW — dodávka + montáž s napojením na samostatný komín</t>
+          <t>Elektrokotel ~8 kW pro 3.NP samostatný byt — dodávka + montáž + napojení</t>
         </is>
       </c>
       <c r="F179" s="20" t="inlineStr">
@@ -20733,7 +20840,7 @@
       </c>
       <c r="M179" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — krb v 3.NP, ~6 kW odhad</t>
+          <t>TZ ARS dům §4 — 'Nově navržené 3.NP bude vytápěno elektrokotlem'; ~8 kW odhad</t>
         </is>
       </c>
       <c r="N179" s="20" t="inlineStr">
@@ -20760,17 +20867,17 @@
       </c>
       <c r="C180" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — venkovní jednotka</t>
+          <t>Krb na tuhá paliva 3.NP</t>
         </is>
       </c>
       <c r="D180" s="20" t="inlineStr">
         <is>
-          <t>733425211</t>
+          <t>733241011</t>
         </is>
       </c>
       <c r="E180" s="8" t="inlineStr">
         <is>
-          <t>Multisplit tepelné čerpadlo vzduch-vzduch — 1× venkovní jednotka ~10 kW (silent mode hl. tlaku ≤49 dBA)</t>
+          <t>Krb na tuhá paliva v 3.NP ~6 kW — dodávka + montáž s napojením na samostatný komín</t>
         </is>
       </c>
       <c r="F180" s="20" t="inlineStr">
@@ -20785,7 +20892,7 @@
       <c r="I180" s="10" t="n"/>
       <c r="J180" s="8" t="inlineStr">
         <is>
-          <t>specialista_TC_multisplit</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K180" s="24" t="n">
@@ -20798,7 +20905,7 @@
       </c>
       <c r="M180" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — multisplit TČ s akustikou hl. tlaku ≤49 dBA, NV 272/2011</t>
+          <t>TZ ARS dům §4 — krb v 3.NP, ~6 kW odhad</t>
         </is>
       </c>
       <c r="N180" s="20" t="inlineStr">
@@ -20825,17 +20932,17 @@
       </c>
       <c r="C181" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — vnitřní jednotky</t>
+          <t>Multisplit TČ — venkovní jednotka</t>
         </is>
       </c>
       <c r="D181" s="20" t="inlineStr">
         <is>
-          <t>733425221</t>
+          <t>733425211</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — 5× vnitřní jednotka v obytných místnostech (1.NP, 2.NP, 3.NP — chlazení + vytápění)</t>
+          <t>Multisplit tepelné čerpadlo vzduch-vzduch — 1× venkovní jednotka ~10 kW (silent mode hl. tlaku ≤49 dBA)</t>
         </is>
       </c>
       <c r="F181" s="20" t="inlineStr">
@@ -20844,7 +20951,7 @@
         </is>
       </c>
       <c r="G181" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H181" s="10" t="n"/>
       <c r="I181" s="10" t="n"/>
@@ -20854,7 +20961,7 @@
         </is>
       </c>
       <c r="K181" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L181" s="20" t="inlineStr">
         <is>
@@ -20863,7 +20970,7 @@
       </c>
       <c r="M181" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — vnitřní jednotky multisplit, vyjasnění #6 odhad 5 ks</t>
+          <t>TZ ARS dům §4 — multisplit TČ s akustikou hl. tlaku ≤49 dBA, NV 272/2011</t>
         </is>
       </c>
       <c r="N181" s="20" t="inlineStr">
@@ -20890,36 +20997,36 @@
       </c>
       <c r="C182" s="8" t="inlineStr">
         <is>
-          <t>Revize komínu</t>
+          <t>Multisplit TČ — vnitřní jednotky</t>
         </is>
       </c>
       <c r="D182" s="20" t="inlineStr">
         <is>
-          <t>734262122</t>
+          <t>733425221</t>
         </is>
       </c>
       <c r="E182" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajícího komínu — kontrola, čištění, vystrojení vložkou nerez DN160 pro kamna + krb 3.NP</t>
+          <t>Multisplit TČ — 5× vnitřní jednotka v obytných místnostech (1.NP, 2.NP, 3.NP — chlazení + vytápění)</t>
         </is>
       </c>
       <c r="F182" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G182" s="23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H182" s="10" t="n"/>
       <c r="I182" s="10" t="n"/>
       <c r="J182" s="8" t="inlineStr">
         <is>
-          <t>kominik</t>
+          <t>specialista_TC_multisplit</t>
         </is>
       </c>
       <c r="K182" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L182" s="20" t="inlineStr">
         <is>
@@ -20928,7 +21035,7 @@
       </c>
       <c r="M182" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — komín stávající, vystrojení vložkou pro kamna + krb</t>
+          <t>TZ ARS dům §4 — vnitřní jednotky multisplit, vyjasnění #6 odhad 5 ks</t>
         </is>
       </c>
       <c r="N182" s="20" t="inlineStr">
@@ -20955,36 +21062,36 @@
       </c>
       <c r="C183" s="8" t="inlineStr">
         <is>
-          <t>Rozvody otopné soustavy</t>
+          <t>Revize komínu</t>
         </is>
       </c>
       <c r="D183" s="20" t="inlineStr">
         <is>
-          <t>733111021</t>
+          <t>734262122</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
         <is>
-          <t>Rozvody otopné soustavy Cu/PEX k vnitřním jednotkám TČ + radiátorům pro doplňkové (cca 100 bm odhad)</t>
+          <t>Revize stávajícího komínu — kontrola, čištění, vystrojení vložkou nerez DN160 pro kamna + krb 3.NP</t>
         </is>
       </c>
       <c r="F183" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G183" s="22" t="n">
-        <v>100</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G183" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H183" s="10" t="n"/>
       <c r="I183" s="10" t="n"/>
       <c r="J183" s="8" t="inlineStr">
         <is>
-          <t>topenar</t>
+          <t>kominik</t>
         </is>
       </c>
       <c r="K183" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L183" s="20" t="inlineStr">
         <is>
@@ -20993,7 +21100,7 @@
       </c>
       <c r="M183" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — rozvody otopné soustavy</t>
+          <t>TZ ARS dům §4 — komín stávající, vystrojení vložkou pro kamna + krb</t>
         </is>
       </c>
       <c r="N183" s="20" t="inlineStr">
@@ -21015,41 +21122,41 @@
       </c>
       <c r="B184" s="8" t="inlineStr">
         <is>
-          <t>VRN — BOZP</t>
+          <t>PSV-73 Vytápění</t>
         </is>
       </c>
       <c r="C184" s="8" t="inlineStr">
         <is>
-          <t>Koordinace BOZP</t>
+          <t>Rozvody otopné soustavy</t>
         </is>
       </c>
       <c r="D184" s="20" t="inlineStr">
         <is>
-          <t>030091000</t>
+          <t>733111021</t>
         </is>
       </c>
       <c r="E184" s="8" t="inlineStr">
         <is>
-          <t>Koordinátor BOZP na staveništi dle zákona 309/2006 Sb. — pro stavbu s více než jedním zhotovitelem</t>
+          <t>Rozvody otopné soustavy Cu/PEX k vnitřním jednotkám TČ + radiátorům pro doplňkové (cca 100 bm odhad)</t>
         </is>
       </c>
       <c r="F184" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G184" s="23" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G184" s="22" t="n">
+        <v>100</v>
       </c>
       <c r="H184" s="10" t="n"/>
       <c r="I184" s="10" t="n"/>
       <c r="J184" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K184" s="24" t="n">
-        <v>0.99</v>
+        <v>0.75</v>
       </c>
       <c r="L184" s="20" t="inlineStr">
         <is>
@@ -21058,12 +21165,12 @@
       </c>
       <c r="M184" s="8" t="inlineStr">
         <is>
-          <t>Zákon 309/2006 Sb. — povinný BOZP koordinátor pro vícezhotovitelskou stavbu</t>
+          <t>TZ ARS dům §4 — rozvody otopné soustavy</t>
         </is>
       </c>
       <c r="N184" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O184" s="26" t="inlineStr">
@@ -21080,22 +21187,22 @@
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
-          <t>VRN — Dokumentace</t>
+          <t>VRN — BOZP</t>
         </is>
       </c>
       <c r="C185" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokoly + DSP</t>
+          <t>Koordinace BOZP</t>
         </is>
       </c>
       <c r="D185" s="20" t="inlineStr">
         <is>
-          <t>030151000</t>
+          <t>030091000</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokoly + Dokumentace skutečného provedení (DSP) — sestavení, vázání, dodávka 2× tiskem + elektronická verze</t>
+          <t>Koordinátor BOZP na staveništi dle zákona 309/2006 Sb. — pro stavbu s více než jedním zhotovitelem</t>
         </is>
       </c>
       <c r="F185" s="20" t="inlineStr">
@@ -21123,12 +21230,12 @@
       </c>
       <c r="M185" s="8" t="inlineStr">
         <is>
-          <t>Vyhláška 499/2006 Sb. + ČKAIT — DSP povinná pro kolaudaci</t>
+          <t>Zákon 309/2006 Sb. — povinný BOZP koordinátor pro vícezhotovitelskou stavbu</t>
         </is>
       </c>
       <c r="N185" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O185" s="26" t="inlineStr">
@@ -21145,41 +21252,41 @@
       </c>
       <c r="B186" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>VRN — Dokumentace</t>
         </is>
       </c>
       <c r="C186" s="8" t="inlineStr">
         <is>
-          <t>Kontejnery suti tříděné</t>
+          <t>Předávací protokoly + DSP</t>
         </is>
       </c>
       <c r="D186" s="20" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>030151000</t>
         </is>
       </c>
       <c r="E186" s="8" t="inlineStr">
         <is>
-          <t>Kontejnery na suť tříděnou velkoobjemové (beton/cihly, dřevo, kovy, EPS, sádra, směs) — pronájem + svozy</t>
+          <t>Předávací protokoly + Dokumentace skutečného provedení (DSP) — sestavení, vázání, dodávka 2× tiskem + elektronická verze</t>
         </is>
       </c>
       <c r="F186" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G186" s="23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H186" s="10" t="n"/>
       <c r="I186" s="10" t="n"/>
       <c r="J186" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K186" s="24" t="n">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
       <c r="L186" s="20" t="inlineStr">
         <is>
@@ -21188,12 +21295,12 @@
       </c>
       <c r="M186" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e: beton/cihly 46 t + dřevo 9 t + kovy 0.1 + EPS 0.1 + sádra 0.2 + směs 1.0</t>
+          <t>Vyhláška 499/2006 Sb. + ČKAIT — DSP povinná pro kolaudaci</t>
         </is>
       </c>
       <c r="N186" s="20" t="inlineStr">
         <is>
-          <t>#9, #10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O186" s="26" t="inlineStr">
@@ -21215,36 +21322,36 @@
       </c>
       <c r="C187" s="8" t="inlineStr">
         <is>
-          <t>Doprava materiálu</t>
+          <t>Kontejnery suti tříděné</t>
         </is>
       </c>
       <c r="D187" s="20" t="inlineStr">
         <is>
-          <t>031031000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
         <is>
-          <t>Doprava materiálu na stavbu (centrální koordinace) — paušál ~2-3 % z PN materiál</t>
+          <t>Kontejnery na suť tříděnou velkoobjemové (beton/cihly, dřevo, kovy, EPS, sádra, směs) — pronájem + svozy</t>
         </is>
       </c>
       <c r="F187" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G187" s="23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H187" s="10" t="n"/>
       <c r="I187" s="10" t="n"/>
       <c r="J187" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K187" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L187" s="20" t="inlineStr">
         <is>
@@ -21253,12 +21360,12 @@
       </c>
       <c r="M187" s="8" t="inlineStr">
         <is>
-          <t>B4_productivity — standard doprava RD městská zástavba</t>
+          <t>TZ B m.10.e: beton/cihly 46 t + dřevo 9 t + kovy 0.1 + EPS 0.1 + sádra 0.2 + směs 1.0</t>
         </is>
       </c>
       <c r="N187" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>#9, #10</t>
         </is>
       </c>
       <c r="O187" s="26" t="inlineStr">
@@ -21280,36 +21387,36 @@
       </c>
       <c r="C188" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadů 56.9 t</t>
+          <t>Doprava materiálu</t>
         </is>
       </c>
       <c r="D188" s="20" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>031031000</t>
         </is>
       </c>
       <c r="E188" s="8" t="inlineStr">
         <is>
-          <t>Likvidace stavební suti dle vyhl. 8/2021 Sb. — skládkovné + recyklace + třídění (56.9 t celkem per TZ B m.10.e)</t>
+          <t>Doprava materiálu na stavbu (centrální koordinace) — paušál ~2-3 % z PN materiál</t>
         </is>
       </c>
       <c r="F188" s="20" t="inlineStr">
         <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G188" s="22" t="n">
-        <v>56.9</v>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G188" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H188" s="10" t="n"/>
       <c r="I188" s="10" t="n"/>
       <c r="J188" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K188" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L188" s="20" t="inlineStr">
         <is>
@@ -21318,12 +21425,12 @@
       </c>
       <c r="M188" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e bilance odpadů celkem dům</t>
+          <t>B4_productivity — standard doprava RD městská zástavba</t>
         </is>
       </c>
       <c r="N188" s="20" t="inlineStr">
         <is>
-          <t>#9, #10</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O188" s="26" t="inlineStr">
@@ -21340,41 +21447,41 @@
       </c>
       <c r="B189" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C189" s="8" t="inlineStr">
         <is>
-          <t>Geodetické zaměření před + po realizaci</t>
+          <t>Likvidace odpadů 56.9 t</t>
         </is>
       </c>
       <c r="D189" s="20" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
         <is>
-          <t>Geodetické zaměření před realizací (verifikace polohopis + výškopis) + po dokončení (zaměření skutečného provedení pro kolaudaci)</t>
+          <t>Likvidace stavební suti dle vyhl. 8/2021 Sb. — skládkovné + recyklace + třídění (56.9 t celkem per TZ B m.10.e)</t>
         </is>
       </c>
       <c r="F189" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G189" s="23" t="n">
-        <v>2</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G189" s="22" t="n">
+        <v>56.9</v>
       </c>
       <c r="H189" s="10" t="n"/>
       <c r="I189" s="10" t="n"/>
       <c r="J189" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K189" s="24" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="L189" s="20" t="inlineStr">
         <is>
@@ -21383,12 +21490,12 @@
       </c>
       <c r="M189" s="8" t="inlineStr">
         <is>
-          <t>Standard — geodet před+po pro každou stavbu</t>
+          <t>TZ B m.10.e bilance odpadů celkem dům</t>
         </is>
       </c>
       <c r="N189" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#9, #10</t>
         </is>
       </c>
       <c r="O189" s="26" t="inlineStr">
@@ -21405,37 +21512,37 @@
       </c>
       <c r="B190" s="8" t="inlineStr">
         <is>
-          <t>VRN — Kolaudace</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="C190" s="8" t="inlineStr">
         <is>
-          <t>Kolaudační řízení</t>
+          <t>Geodetické zaměření před + po realizaci</t>
         </is>
       </c>
       <c r="D190" s="20" t="inlineStr">
         <is>
-          <t>030171000</t>
+          <t>030141000</t>
         </is>
       </c>
       <c r="E190" s="8" t="inlineStr">
         <is>
-          <t>Kolaudační řízení — paušál (správní poplatky + součinnost) dle zákona 183/2006 Sb.</t>
+          <t>Geodetické zaměření před realizací (verifikace polohopis + výškopis) + po dokončení (zaměření skutečného provedení pro kolaudaci)</t>
         </is>
       </c>
       <c r="F190" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G190" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H190" s="10" t="n"/>
       <c r="I190" s="10" t="n"/>
       <c r="J190" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>geodet</t>
         </is>
       </c>
       <c r="K190" s="24" t="n">
@@ -21448,7 +21555,7 @@
       </c>
       <c r="M190" s="8" t="inlineStr">
         <is>
-          <t>Zákon 183/2006 Sb. + vyhl. 499/2006 Sb.</t>
+          <t>Standard — geodet před+po pro každou stavbu</t>
         </is>
       </c>
       <c r="N190" s="20" t="inlineStr">
@@ -21470,31 +21577,31 @@
       </c>
       <c r="B191" s="8" t="inlineStr">
         <is>
-          <t>VRN — Lešení</t>
+          <t>VRN — Kolaudace</t>
         </is>
       </c>
       <c r="C191" s="8" t="inlineStr">
         <is>
-          <t>Fasádní lešení (ETICS + krov + klempířina)</t>
+          <t>Kolaudační řízení</t>
         </is>
       </c>
       <c r="D191" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>030171000</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
         <is>
-          <t>Fasádní lešení trubkové/rámové vč. montáže + pronájmu + demontáže — pro provedení ETICS fasády, krovu a klempířiny po obvodu domu (výška 13 m)</t>
+          <t>Kolaudační řízení — paušál (správní poplatky + součinnost) dle zákona 183/2006 Sb.</t>
         </is>
       </c>
       <c r="F191" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G191" s="22" t="n">
-        <v>503.1</v>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G191" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H191" s="10" t="n"/>
       <c r="I191" s="10" t="n"/>
@@ -21504,7 +21611,7 @@
         </is>
       </c>
       <c r="K191" s="24" t="n">
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="L191" s="20" t="inlineStr">
         <is>
@@ -21513,7 +21620,7 @@
       </c>
       <c r="M191" s="8" t="inlineStr">
         <is>
-          <t>anchor checklist PM02 — technical necessity (ETICS 276.7 m² nelze provést bez lešení, 941xxx URS família) + DXF obvod 38.7 m + řez výška 13 m</t>
+          <t>Zákon 183/2006 Sb. + vyhl. 499/2006 Sb.</t>
         </is>
       </c>
       <c r="N191" s="20" t="inlineStr">
@@ -21527,11 +21634,7 @@
         </is>
       </c>
       <c r="P191" s="41" t="n"/>
-      <c r="Q191" s="41" t="inlineStr">
-        <is>
-          <t>ANCHOR_CHECKLIST_PM02</t>
-        </is>
-      </c>
+      <c r="Q191" s="41" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="20" t="n">
@@ -21539,31 +21642,31 @@
       </c>
       <c r="B192" s="8" t="inlineStr">
         <is>
-          <t>VRN — Pojištění + zábory</t>
+          <t>VRN — Lešení</t>
         </is>
       </c>
       <c r="C192" s="8" t="inlineStr">
         <is>
-          <t>Pojištění stavby (montážní + odpovědnostní)</t>
+          <t>Fasádní lešení (ETICS + krov + klempířina)</t>
         </is>
       </c>
       <c r="D192" s="20" t="inlineStr">
         <is>
-          <t>030081000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E192" s="8" t="inlineStr">
         <is>
-          <t>Montážní pojištění stavby (CAR) + pojištění odpovědnosti za škodu (zhotovitel) — paušál cca 0.3-0.5 % z PN</t>
+          <t>Fasádní lešení trubkové/rámové vč. montáže + pronájmu + demontáže — pro provedení ETICS fasády, krovu a klempířiny po obvodu domu (výška 13 m)</t>
         </is>
       </c>
       <c r="F192" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="G192" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G192" s="22" t="n">
+        <v>503.1</v>
       </c>
       <c r="H192" s="10" t="n"/>
       <c r="I192" s="10" t="n"/>
@@ -21573,7 +21676,7 @@
         </is>
       </c>
       <c r="K192" s="24" t="n">
-        <v>0.99</v>
+        <v>0.8</v>
       </c>
       <c r="L192" s="20" t="inlineStr">
         <is>
@@ -21582,12 +21685,12 @@
       </c>
       <c r="M192" s="8" t="inlineStr">
         <is>
-          <t>Standard zhotovitel — pojistná povinnost</t>
+          <t>anchor checklist PM02 — technical necessity (ETICS 276.7 m² nelze provést bez lešení, 941xxx URS família) + DXF obvod 38.7 m + řez výška 13 m</t>
         </is>
       </c>
       <c r="N192" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O192" s="26" t="inlineStr">
@@ -21596,7 +21699,11 @@
         </is>
       </c>
       <c r="P192" s="41" t="n"/>
-      <c r="Q192" s="41" t="n"/>
+      <c r="Q192" s="41" t="inlineStr">
+        <is>
+          <t>ANCHOR_CHECKLIST_PM02</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="20" t="n">
@@ -21609,22 +21716,22 @@
       </c>
       <c r="C193" s="8" t="inlineStr">
         <is>
-          <t>Krátkodobé zábory ul. Fibichova</t>
+          <t>Pojištění stavby (montážní + odpovědnostní)</t>
         </is>
       </c>
       <c r="D193" s="20" t="inlineStr">
         <is>
-          <t>030083000</t>
+          <t>030081000</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
         <is>
-          <t>Krátkodobé zábory ulice Fibichova pro materiál a kontejnery (povolení MU Jáchymov + DI) — odhad 30 dnů kumulativně</t>
+          <t>Montážní pojištění stavby (CAR) + pojištění odpovědnosti za škodu (zhotovitel) — paušál cca 0.3-0.5 % z PN</t>
         </is>
       </c>
       <c r="F193" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>paušál</t>
         </is>
       </c>
       <c r="G193" s="23" t="n">
@@ -21638,7 +21745,7 @@
         </is>
       </c>
       <c r="K193" s="24" t="n">
-        <v>0.75</v>
+        <v>0.99</v>
       </c>
       <c r="L193" s="20" t="inlineStr">
         <is>
@@ -21647,7 +21754,7 @@
       </c>
       <c r="M193" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10 + situace — řadovka ul. Fibichova</t>
+          <t>Standard zhotovitel — pojistná povinnost</t>
         </is>
       </c>
       <c r="N193" s="20" t="inlineStr">
@@ -21669,22 +21776,22 @@
       </c>
       <c r="B194" s="8" t="inlineStr">
         <is>
-          <t>VRN — Průzkumy</t>
+          <t>VRN — Pojištění + zábory</t>
         </is>
       </c>
       <c r="C194" s="8" t="inlineStr">
         <is>
-          <t>Mykologický průzkum dřeva při bourání</t>
+          <t>Krátkodobé zábory ul. Fibichova</t>
         </is>
       </c>
       <c r="D194" s="20" t="inlineStr">
         <is>
-          <t>030131000</t>
+          <t>030083000</t>
         </is>
       </c>
       <c r="E194" s="8" t="inlineStr">
         <is>
-          <t>Mykologický průzkum + průzkum výskytu dřevokazného hmyzu stávajícího krovu a dřevěných trámů zhlaví — pro vyloučení narušení dřevěných konstrukcí; provádí autorizovaný mykolog při bourání</t>
+          <t>Krátkodobé zábory ulice Fibichova pro materiál a kontejnery (povolení MU Jáchymov + DI) — odhad 30 dnů kumulativně</t>
         </is>
       </c>
       <c r="F194" s="20" t="inlineStr">
@@ -21699,11 +21806,11 @@
       <c r="I194" s="10" t="n"/>
       <c r="J194" s="8" t="inlineStr">
         <is>
-          <t>mykolog</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K194" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L194" s="20" t="inlineStr">
         <is>
@@ -21712,7 +21819,7 @@
       </c>
       <c r="M194" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.3 + POZN.2.05 z půdorysů návrh + řez A-A návrh (explicit dřevokazný hmyz scope per drawing wording)</t>
+          <t>TZ B m.10 + situace — řadovka ul. Fibichova</t>
         </is>
       </c>
       <c r="N194" s="20" t="inlineStr">
@@ -21726,11 +21833,7 @@
         </is>
       </c>
       <c r="P194" s="41" t="n"/>
-      <c r="Q194" s="41" t="inlineStr">
-        <is>
-          <t>PER_DRAWING_ENRICHMENT_POZN_2_05</t>
-        </is>
-      </c>
+      <c r="Q194" s="41" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="20" t="n">
@@ -21743,17 +21846,17 @@
       </c>
       <c r="C195" s="8" t="inlineStr">
         <is>
-          <t>Azbestový průzkum podrobný před demolicí</t>
+          <t>Mykologický průzkum dřeva při bourání</t>
         </is>
       </c>
       <c r="D195" s="20" t="inlineStr">
         <is>
-          <t>030133000</t>
+          <t>030131000</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
         <is>
-          <t>Azbestový průzkum podrobný před demolicí — laboratorní vzorky a posudek (B kap. m.7.a předběžně negativní, ale podrobný před bouráním povinný)</t>
+          <t>Mykologický průzkum + průzkum výskytu dřevokazného hmyzu stávajícího krovu a dřevěných trámů zhlaví — pro vyloučení narušení dřevěných konstrukcí; provádí autorizovaný mykolog při bourání</t>
         </is>
       </c>
       <c r="F195" s="20" t="inlineStr">
@@ -21768,7 +21871,7 @@
       <c r="I195" s="10" t="n"/>
       <c r="J195" s="8" t="inlineStr">
         <is>
-          <t>azbestovy_specialista</t>
+          <t>mykolog</t>
         </is>
       </c>
       <c r="K195" s="24" t="n">
@@ -21781,7 +21884,7 @@
       </c>
       <c r="M195" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.7.a + ARS §3.2 — azbestový průzkum povinný před demolicí</t>
+          <t>TZ ARS dům §3.2.3 + POZN.2.05 z půdorysů návrh + řez A-A návrh (explicit dřevokazný hmyz scope per drawing wording)</t>
         </is>
       </c>
       <c r="N195" s="20" t="inlineStr">
@@ -21795,7 +21898,11 @@
         </is>
       </c>
       <c r="P195" s="41" t="n"/>
-      <c r="Q195" s="41" t="n"/>
+      <c r="Q195" s="41" t="inlineStr">
+        <is>
+          <t>PER_DRAWING_ENRICHMENT_POZN_2_05</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="20" t="n">
@@ -21803,41 +21910,41 @@
       </c>
       <c r="B196" s="8" t="inlineStr">
         <is>
-          <t>VRN — Přesun hmot</t>
+          <t>VRN — Průzkumy</t>
         </is>
       </c>
       <c r="C196" s="8" t="inlineStr">
         <is>
-          <t>Přesun hmot pro budovu</t>
+          <t>Azbestový průzkum podrobný před demolicí</t>
         </is>
       </c>
       <c r="D196" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>030133000</t>
         </is>
       </c>
       <c r="E196" s="8" t="inlineStr">
         <is>
-          <t>Přesun hmot pro budovu — vnitrostaveništní vertikální + horizontální doprava materiálu a hmot (rekonstrukce vícepodlažní RD + nástavba 3.NP)</t>
+          <t>Azbestový průzkum podrobný před demolicí — laboratorní vzorky a posudek (B kap. m.7.a předběžně negativní, ale podrobný před bouráním povinný)</t>
         </is>
       </c>
       <c r="F196" s="20" t="inlineStr">
         <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G196" s="22" t="n">
-        <v>0</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G196" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H196" s="10" t="n"/>
       <c r="I196" s="10" t="n"/>
       <c r="J196" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>azbestovy_specialista</t>
         </is>
       </c>
       <c r="K196" s="24" t="n">
-        <v>0.6</v>
+        <v>0.85</v>
       </c>
       <c r="L196" s="20" t="inlineStr">
         <is>
@@ -21846,12 +21953,12 @@
       </c>
       <c r="M196" s="8" t="inlineStr">
         <is>
-          <t>anchor checklist PM01 — technical necessity (povinná položka každého rozpočtu, 998xxx URS família)</t>
+          <t>TZ B m.7.a + ARS §3.2 — azbestový průzkum povinný před demolicí</t>
         </is>
       </c>
       <c r="N196" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O196" s="26" t="inlineStr">
@@ -21860,11 +21967,7 @@
         </is>
       </c>
       <c r="P196" s="41" t="n"/>
-      <c r="Q196" s="41" t="inlineStr">
-        <is>
-          <t>ANCHOR_CHECKLIST_PM01</t>
-        </is>
-      </c>
+      <c r="Q196" s="41" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="20" t="n">
@@ -21872,41 +21975,41 @@
       </c>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t>VRN — Revize</t>
+          <t>VRN — Přesun hmot</t>
         </is>
       </c>
       <c r="C197" s="8" t="inlineStr">
         <is>
-          <t>Revize hydrantu vnějšího</t>
+          <t>Přesun hmot pro budovu</t>
         </is>
       </c>
       <c r="D197" s="20" t="inlineStr">
         <is>
-          <t>030161000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
         <is>
-          <t>Revize vnějšího hydrantu pro požární zabezpečení (DN min. 80, vzdálenost 100 m dle TZ PBŘ) — periodická kontrola</t>
+          <t>Přesun hmot pro budovu — vnitrostaveništní vertikální + horizontální doprava materiálu a hmot (rekonstrukce vícepodlažní RD + nástavba 3.NP)</t>
         </is>
       </c>
       <c r="F197" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G197" s="23" t="n">
-        <v>1</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G197" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H197" s="10" t="n"/>
       <c r="I197" s="10" t="n"/>
       <c r="J197" s="8" t="inlineStr">
         <is>
-          <t>revize_specialista</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K197" s="24" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="L197" s="20" t="inlineStr">
         <is>
@@ -21915,7 +22018,7 @@
       </c>
       <c r="M197" s="8" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — vnější odběrné místo požární vody, revize před kolaudací</t>
+          <t>anchor checklist PM01 — technical necessity (povinná položka každého rozpočtu, 998xxx URS família)</t>
         </is>
       </c>
       <c r="N197" s="20" t="inlineStr">
@@ -21929,7 +22032,11 @@
         </is>
       </c>
       <c r="P197" s="41" t="n"/>
-      <c r="Q197" s="41" t="n"/>
+      <c r="Q197" s="41" t="inlineStr">
+        <is>
+          <t>ANCHOR_CHECKLIST_PM01</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="20" t="n">
@@ -21937,41 +22044,41 @@
       </c>
       <c r="B198" s="8" t="inlineStr">
         <is>
-          <t>VRN — Zařízení staveniště</t>
+          <t>VRN — Revize</t>
         </is>
       </c>
       <c r="C198" s="8" t="inlineStr">
         <is>
-          <t>Buňky kancelář + sociální</t>
+          <t>Revize hydrantu vnějšího</t>
         </is>
       </c>
       <c r="D198" s="20" t="inlineStr">
         <is>
-          <t>030011000</t>
+          <t>030161000</t>
         </is>
       </c>
       <c r="E198" s="8" t="inlineStr">
         <is>
-          <t>Zařízení staveniště — buňka kancelář + sociální buňka (WC + šatna), pronájem ~8 měsíců</t>
+          <t>Revize vnějšího hydrantu pro požární zabezpečení (DN min. 80, vzdálenost 100 m dle TZ PBŘ) — periodická kontrola</t>
         </is>
       </c>
       <c r="F198" s="20" t="inlineStr">
         <is>
-          <t>kpl-měs</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G198" s="23" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H198" s="10" t="n"/>
       <c r="I198" s="10" t="n"/>
       <c r="J198" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>revize_specialista</t>
         </is>
       </c>
       <c r="K198" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L198" s="20" t="inlineStr">
         <is>
@@ -21980,12 +22087,12 @@
       </c>
       <c r="M198" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.1.m realizace 2026-2027 + standard staveniště RD městská zástavba</t>
+          <t>TZ PBŘ dům — vnější odběrné místo požární vody, revize před kolaudací</t>
         </is>
       </c>
       <c r="N198" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O198" s="26" t="inlineStr">
@@ -22007,22 +22114,22 @@
       </c>
       <c r="C199" s="8" t="inlineStr">
         <is>
-          <t>Mobilní WC</t>
+          <t>Buňky kancelář + sociální</t>
         </is>
       </c>
       <c r="D199" s="20" t="inlineStr">
         <is>
-          <t>030013000</t>
+          <t>030011000</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
         <is>
-          <t>Mobilní chemické WC TOI TOI pro pracovníky — pronájem ~8 měsíců</t>
+          <t>Zařízení staveniště — buňka kancelář + sociální buňka (WC + šatna), pronájem ~8 měsíců</t>
         </is>
       </c>
       <c r="F199" s="20" t="inlineStr">
         <is>
-          <t>ks-měs</t>
+          <t>kpl-měs</t>
         </is>
       </c>
       <c r="G199" s="23" t="n">
@@ -22045,7 +22152,7 @@
       </c>
       <c r="M199" s="8" t="inlineStr">
         <is>
-          <t>BOZP — mobilní WC povinné pro stavbu RD</t>
+          <t>TZ B m.1.m realizace 2026-2027 + standard staveniště RD městská zástavba</t>
         </is>
       </c>
       <c r="N199" s="20" t="inlineStr">
@@ -22072,26 +22179,26 @@
       </c>
       <c r="C200" s="8" t="inlineStr">
         <is>
-          <t>El. odběr + vodovodní odběr stavby</t>
+          <t>Mobilní WC</t>
         </is>
       </c>
       <c r="D200" s="20" t="inlineStr">
         <is>
-          <t>031011000</t>
+          <t>030013000</t>
         </is>
       </c>
       <c r="E200" s="8" t="inlineStr">
         <is>
-          <t>El. odběr stavby (zřízení staveništního rozvaděče + měřič) + vodovodní odběr (zřízení staveništní přípojky + vodoměr) — ~8 měsíců</t>
+          <t>Mobilní chemické WC TOI TOI pro pracovníky — pronájem ~8 měsíců</t>
         </is>
       </c>
       <c r="F200" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks-měs</t>
         </is>
       </c>
       <c r="G200" s="23" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H200" s="10" t="n"/>
       <c r="I200" s="10" t="n"/>
@@ -22110,7 +22217,7 @@
       </c>
       <c r="M200" s="8" t="inlineStr">
         <is>
-          <t>Standard staveniště — el. + voda zřízení a odběr po dobu stavby</t>
+          <t>BOZP — mobilní WC povinné pro stavbu RD</t>
         </is>
       </c>
       <c r="N200" s="20" t="inlineStr">
@@ -22137,17 +22244,17 @@
       </c>
       <c r="C201" s="8" t="inlineStr">
         <is>
-          <t>Voda staveniště</t>
+          <t>El. odběr + vodovodní odběr stavby</t>
         </is>
       </c>
       <c r="D201" s="20" t="inlineStr">
         <is>
-          <t>012103101</t>
+          <t>031011000</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
         <is>
-          <t>Voda staveniště — napojení na stávající vodovodní přípojku, dočasné rozvody na staveništi (mísení malt, čištění, soc. zázemí), paušál pro dobu výstavby ~18 měs.</t>
+          <t>El. odběr stavby (zřízení staveništního rozvaděče + měřič) + vodovodní odběr (zřízení staveništní přípojky + vodoměr) — ~8 měsíců</t>
         </is>
       </c>
       <c r="F201" s="20" t="inlineStr">
@@ -22166,38 +22273,241 @@
         </is>
       </c>
       <c r="K201" s="24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L201" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M201" s="8" t="inlineStr">
+        <is>
+          <t>Standard staveniště — el. + voda zřízení a odběr po dobu stavby</t>
+        </is>
+      </c>
+      <c r="N201" s="20" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
+      <c r="O201" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P201" s="41" t="n"/>
+      <c r="Q201" s="41" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="20" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Zařízení staveniště</t>
+        </is>
+      </c>
+      <c r="C202" s="8" t="inlineStr">
+        <is>
+          <t>Voda staveniště</t>
+        </is>
+      </c>
+      <c r="D202" s="20" t="inlineStr">
+        <is>
+          <t>012103101</t>
+        </is>
+      </c>
+      <c r="E202" s="8" t="inlineStr">
+        <is>
+          <t>Voda staveniště — napojení na stávající vodovodní přípojku, dočasné rozvody na staveništi (mísení malt, čištění, soc. zázemí), paušál pro dobu výstavby ~18 měs.</t>
+        </is>
+      </c>
+      <c r="F202" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G202" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H202" s="10" t="n"/>
+      <c r="I202" s="10" t="n"/>
+      <c r="J202" s="8" t="inlineStr">
+        <is>
+          <t>VRN_management</t>
+        </is>
+      </c>
+      <c r="K202" s="24" t="n">
         <v>0.9</v>
       </c>
-      <c r="L201" s="20" t="inlineStr">
+      <c r="L202" s="20" t="inlineStr">
         <is>
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M201" s="8" t="inlineStr">
+      <c r="M202" s="8" t="inlineStr">
         <is>
           <t>TZ B Souhrnná m.5 — 'Stávající vodovodní přípojka z veřejného vodovodu'</t>
         </is>
       </c>
-      <c r="N201" s="20" t="inlineStr">
+      <c r="N202" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O201" s="26" t="inlineStr">
+      <c r="O202" s="26" t="inlineStr">
         <is>
           <t>ANO</t>
         </is>
       </c>
-      <c r="P201" s="41" t="n"/>
-      <c r="Q201" s="41" t="inlineStr">
+      <c r="P202" s="41" t="n"/>
+      <c r="Q202" s="41" t="inlineStr">
         <is>
           <t>GAP_003</t>
         </is>
       </c>
     </row>
+    <row r="203">
+      <c r="A203" s="20" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" s="8" t="inlineStr">
+        <is>
+          <t>M-21 ELI silnoproud</t>
+        </is>
+      </c>
+      <c r="C203" s="8" t="inlineStr">
+        <is>
+          <t>Hlavní vypínač TOTAL STOP + požární značení</t>
+        </is>
+      </c>
+      <c r="D203" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E203" s="8" t="inlineStr">
+        <is>
+          <t>Hlavní vypínač elektrické energie TOTAL STOP + požární značení rozvodného zařízení a uzávěrů (voda/elektro)</t>
+        </is>
+      </c>
+      <c r="F203" s="20" t="inlineStr">
+        <is>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="G203" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H203" s="10" t="n"/>
+      <c r="I203" s="10" t="n"/>
+      <c r="J203" s="8" t="inlineStr">
+        <is>
+          <t>elektrikar</t>
+        </is>
+      </c>
+      <c r="K203" s="24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L203" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M203" s="8" t="inlineStr">
+        <is>
+          <t>PBŘ D.3 §16.05/16.06</t>
+        </is>
+      </c>
+      <c r="N203" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O203" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P203" s="41" t="inlineStr"/>
+      <c r="Q203" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="20" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" s="8" t="inlineStr">
+        <is>
+          <t>M-24 VZT</t>
+        </is>
+      </c>
+      <c r="C204" s="8" t="inlineStr">
+        <is>
+          <t>Lokální odtah digestoří kuchyní</t>
+        </is>
+      </c>
+      <c r="D204" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E204" s="8" t="inlineStr">
+        <is>
+          <t>Lokální odtah digestoří kuchyní (1.NP + 3.NP) — dodávka + montáž digestoře + prostup fasádou/střechou + zpětná klapka</t>
+        </is>
+      </c>
+      <c r="F204" s="20" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G204" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H204" s="10" t="n"/>
+      <c r="I204" s="10" t="n"/>
+      <c r="J204" s="8" t="inlineStr">
+        <is>
+          <t>vzduchotechnik</t>
+        </is>
+      </c>
+      <c r="K204" s="24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L204" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M204" s="8" t="inlineStr">
+        <is>
+          <t>B zpráva — VZT: obytné místnosti větrání okny, kuchyně lokální odtah digestoří</t>
+        </is>
+      </c>
+      <c r="N204" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O204" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P204" s="41" t="inlineStr"/>
+      <c r="Q204" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O201"/>
-  <conditionalFormatting sqref="K2:K201">
+  <autoFilter ref="A1:O204"/>
+  <conditionalFormatting sqref="K2:K204">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0" stopIfTrue="1">
       <formula>0.70</formula>
     </cfRule>
@@ -22215,12 +22525,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R29"/>
+  <dimension ref="A1:R32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="47" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
@@ -23845,41 +24155,39 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>HSV-5 Komunikace + vjezd</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 sklad</t>
+          <t>Vjezd Dvořákova — napojení na komunikaci</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
+          <t>Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťové vody na pozemek (ne na komunikaci)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G24" s="23" t="n">
-        <v>1</v>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="n"/>
       <c r="H24" s="10" t="n"/>
       <c r="I24" s="10" t="n"/>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>specialista_RC3_dvere</t>
+          <t>komunikace</t>
         </is>
       </c>
       <c r="K24" s="24" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="L24" s="20" t="inlineStr">
         <is>
@@ -23888,7 +24196,7 @@
       </c>
       <c r="M24" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §1.4 — RC3 bezpečnostní dveře v ocelové zárubni</t>
+          <t>Dodatek PD č.1 (E.01) / DI PČR požadavek</t>
         </is>
       </c>
       <c r="N24" s="20" t="inlineStr">
@@ -23901,8 +24209,12 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P24" s="41" t="n"/>
-      <c r="Q24" s="41" t="n"/>
+      <c r="P24" s="41" t="inlineStr"/>
+      <c r="Q24" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="20" t="n">
@@ -23910,50 +24222,50 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Betonová dlažba sklad</t>
-        </is>
-      </c>
-      <c r="D25" s="27" t="inlineStr">
-        <is>
-          <t>596??? ?</t>
+          <t>Bezpečnostní dveře RC3 sklad</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>766682111</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Betonová dlažba do pískového lože — povrch podlahy skladu (~21 m²)</t>
+          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G25" s="22" t="n">
-        <v>17.6</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G25" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H25" s="10" t="n"/>
       <c r="I25" s="10" t="n"/>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>podlahar</t>
+          <t>specialista_RC3_dvere</t>
         </is>
       </c>
       <c r="K25" s="24" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="L25" s="20" t="inlineStr">
         <is>
-          <t>wrong_leaf_disambiguation_needed</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
+          <t>TZ statika sklad §1.4 — RC3 bezpečnostní dveře v ocelové zárubni</t>
         </is>
       </c>
       <c r="N25" s="20" t="inlineStr">
@@ -23961,21 +24273,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O25" s="28" t="inlineStr">
-        <is>
-          <t>LEAF CHYBNÝ — viz alternatives</t>
-        </is>
-      </c>
-      <c r="P25" s="41" t="inlineStr">
-        <is>
-          <t>S01_sklad</t>
-        </is>
-      </c>
-      <c r="Q25" s="41" t="inlineStr">
-        <is>
-          <t>PHASE_3_5_SKLAD_QTY_DXF_VERIFY</t>
-        </is>
-      </c>
+      <c r="O25" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P25" s="41" t="n"/>
+      <c r="Q25" s="41" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="20" t="n">
@@ -23983,27 +24287,27 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Doprava prefa H-BLOK auto s hyd. rukou</t>
+          <t>Vjezdová brána</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>031032000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
+          <t>Vjezdová brána na pozemku investora (ocelová) — dodávka + montáž</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G26" s="23" t="n">
@@ -24013,11 +24317,11 @@
       <c r="I26" s="10" t="n"/>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>prefa_bloky_specialista</t>
+          <t>zamecnik</t>
         </is>
       </c>
       <c r="K26" s="24" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="L26" s="20" t="inlineStr">
         <is>
@@ -24026,7 +24330,7 @@
       </c>
       <c r="M26" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + ARS — auto s hyd. rukou pro osazení H-BLOK</t>
+          <t>Dodatek PD č.1 (E.01)</t>
         </is>
       </c>
       <c r="N26" s="20" t="inlineStr">
@@ -24039,8 +24343,12 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P26" s="41" t="n"/>
-      <c r="Q26" s="41" t="n"/>
+      <c r="P26" s="41" t="inlineStr"/>
+      <c r="Q26" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="20" t="n">
@@ -24048,50 +24356,50 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadu sklad</t>
-        </is>
-      </c>
-      <c r="D27" s="20" t="inlineStr">
-        <is>
-          <t>997013211</t>
+          <t>Betonová dlažba sklad</t>
+        </is>
+      </c>
+      <c r="D27" s="27" t="inlineStr">
+        <is>
+          <t>596??? ?</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
+          <t>Betonová dlažba do pískového lože — povrch podlahy skladu (~21 m²)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G27" s="22" t="n">
-        <v>8</v>
+        <v>17.6</v>
       </c>
       <c r="H27" s="10" t="n"/>
       <c r="I27" s="10" t="n"/>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>podlahar</t>
         </is>
       </c>
       <c r="K27" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L27" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>wrong_leaf_disambiguation_needed</t>
         </is>
       </c>
       <c r="M27" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS sklad §3 — kamenné zídky + schodiště odstraneny</t>
+          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
         </is>
       </c>
       <c r="N27" s="20" t="inlineStr">
@@ -24099,13 +24407,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O27" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
-        </is>
-      </c>
-      <c r="P27" s="41" t="n"/>
-      <c r="Q27" s="41" t="n"/>
+      <c r="O27" s="28" t="inlineStr">
+        <is>
+          <t>LEAF CHYBNÝ — viz alternatives</t>
+        </is>
+      </c>
+      <c r="P27" s="41" t="inlineStr">
+        <is>
+          <t>S01_sklad</t>
+        </is>
+      </c>
+      <c r="Q27" s="41" t="inlineStr">
+        <is>
+          <t>PHASE_3_5_SKLAD_QTY_DXF_VERIFY</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="20" t="n">
@@ -24113,22 +24429,22 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Geodetické vytýčení sklad</t>
+          <t>Doprava prefa H-BLOK auto s hyd. rukou</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>031032000</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
+          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -24143,11 +24459,11 @@
       <c r="I28" s="10" t="n"/>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>prefa_bloky_specialista</t>
         </is>
       </c>
       <c r="K28" s="24" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="L28" s="20" t="inlineStr">
         <is>
@@ -24156,7 +24472,7 @@
       </c>
       <c r="M28" s="8" t="inlineStr">
         <is>
-          <t>Standard — geodet vytýčení pro každý nový objekt</t>
+          <t>TZ statika sklad §4 + ARS — auto s hyd. rukou pro osazení H-BLOK</t>
         </is>
       </c>
       <c r="N28" s="20" t="inlineStr">
@@ -24178,41 +24494,41 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN dům</t>
+          <t>Likvidace odpadu sklad</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
         <is>
-          <t>030001000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="G29" s="23" t="n">
-        <v>1</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G29" s="22" t="n">
+        <v>8</v>
       </c>
       <c r="H29" s="10" t="n"/>
       <c r="I29" s="10" t="n"/>
       <c r="J29" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K29" s="24" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="L29" s="20" t="inlineStr">
         <is>
@@ -24221,7 +24537,7 @@
       </c>
       <c r="M29" s="8" t="inlineStr">
         <is>
-          <t>Standard zhotovitel — alokace VRN pro paralelně realizovaný sklad</t>
+          <t>TZ ARS sklad §3 — kamenné zídky + schodiště odstraneny</t>
         </is>
       </c>
       <c r="N29" s="20" t="inlineStr">
@@ -24237,9 +24553,208 @@
       <c r="P29" s="41" t="n"/>
       <c r="Q29" s="41" t="n"/>
     </row>
+    <row r="30">
+      <c r="A30" s="20" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Geodet</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Geodetické vytýčení sklad</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>030141000</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="10" t="n"/>
+      <c r="I30" s="10" t="n"/>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>geodet</t>
+        </is>
+      </c>
+      <c r="K30" s="24" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L30" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M30" s="8" t="inlineStr">
+        <is>
+          <t>Standard — geodet vytýčení pro každý nový objekt</t>
+        </is>
+      </c>
+      <c r="N30" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O30" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P30" s="41" t="n"/>
+      <c r="Q30" s="41" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Geodet / PČR</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Rozhledové trojúhelníky — vytyčení + kontrola</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40 km/h, Dz=25 m) dle požadavku DI PČR</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="G31" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="10" t="n"/>
+      <c r="I31" s="10" t="n"/>
+      <c r="J31" s="8" t="inlineStr">
+        <is>
+          <t>geodet</t>
+        </is>
+      </c>
+      <c r="K31" s="24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L31" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M31" s="8" t="inlineStr">
+        <is>
+          <t>Dodatek PD č.1 (E.01) / DI PČR</t>
+        </is>
+      </c>
+      <c r="N31" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O31" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P31" s="41" t="inlineStr"/>
+      <c r="Q31" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="20" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Společné</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN dům</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>030001000</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+        </is>
+      </c>
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G32" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="10" t="n"/>
+      <c r="I32" s="10" t="n"/>
+      <c r="J32" s="8" t="inlineStr">
+        <is>
+          <t>VRN_management</t>
+        </is>
+      </c>
+      <c r="K32" s="24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L32" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M32" s="8" t="inlineStr">
+        <is>
+          <t>Standard zhotovitel — alokace VRN pro paralelně realizovaný sklad</t>
+        </is>
+      </c>
+      <c r="N32" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O32" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P32" s="41" t="n"/>
+      <c r="Q32" s="41" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O29"/>
-  <conditionalFormatting sqref="K2:K29">
+  <autoFilter ref="A1:O32"/>
+  <conditionalFormatting sqref="K2:K32">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0" stopIfTrue="1">
       <formula>0.70</formula>
     </cfRule>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2_final.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2_final.xlsx
@@ -21,8 +21,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Var_A_Agregovany_Dum'!$A$1:$G$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Var_A_Agregovany_Sklad'!$A$1:$G$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$133</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$203</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Var_F_URS_Verification_Trail'!$A$1:$H$14</definedName>
   </definedNames>
@@ -1009,11 +1009,11 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>HSV položkově (119 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 132 řádků.</t>
+          <t>HSV položkově (118 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 131 řádků.</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D24" s="10" t="n"/>
       <c r="E24" s="10" t="n"/>
@@ -1027,11 +1027,11 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Plný detail (203 dum + 31 sklad = 234 položek). Cílový rozsah pro produkční pricing.</t>
+          <t>Plný detail (202 dum + 31 sklad = 233 položek). Cílový rozsah pro produkční pricing.</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D25" s="10" t="n"/>
       <c r="E25" s="10" t="n"/>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>234 (203 dum + 31 sklad)</t>
+          <t>233 (202 dum + 31 sklad)</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>HSV 119 | M 2 | PSV 56 | TZB 34 | VRN 23</t>
+          <t>HSV 118 | M 2 | PSV 56 | TZB 34 | VRN 23</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>0.99: 17 | 0.95: 32 | 0.90: 35 | 0.85: 41 | 0.80: 21 | 0.75: 72 | 0.70: 4 | 0.60: 3 | 0.50: 4 | 0.00: 5</t>
+          <t>0.99: 17 | 0.95: 32 | 0.90: 35 | 0.85: 41 | 0.80: 21 | 0.75: 71 | 0.70: 4 | 0.60: 3 | 0.50: 4 | 0.00: 5</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>8 WebSearch verified (3.4 %) ✓ | 5 wrong leaf flagged (2.1 %) ⚠ | 156 needs_production_lookup (66.7 %)</t>
+          <t>8 WebSearch verified (3.4 %) ✓ | 5 wrong leaf flagged (2.1 %) ⚠ | 155 needs_production_lookup (66.5 %)</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>29 items (viz Otazky_pro_Karla docx)</t>
+          <t>30 items (viz Otazky_pro_Karla docx)</t>
         </is>
       </c>
     </row>
@@ -1182,8 +1182,8 @@
       <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Rozpočet generován STAVAGENT pipelinem z DSP dokumentace s DPS-grade DXF metadaty.
-234 položek celkem (203 dum + 31 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
-Confidence distribution: 17×0.99 · 32×0.95 · 35×0.90 · 41×0.85 · 21×0.80 · 72×0.75 · 4×0.70 · 3×0.60 · 4×0.50 · 5×0.00.
+233 položek celkem (202 dum + 31 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
+Confidence distribution: 17×0.99 · 32×0.95 · 35×0.90 · 41×0.85 · 21×0.80 · 71×0.75 · 4×0.70 · 3×0.60 · 4×0.50 · 5×0.00.
 25 položek vzniklo per-room expansion ze 9 aggregate parents (každá expanded položka tagged _expansion_origin).
 10 položek recalculated s exact external perimeter 38.70 m (DXF km_R_návrh_tlustá 2 closed polygon) vs prior fallback 41.0 m.
 Skladby vrstev (Sheet 8 Var_E) pochází POUZE z TZ explicit text + DXF cross-validation HATCH patterns. ŽÁDNÉ generic 'standardní RD' assumption — kde TZ silent, explicit fallback flag s ČSN default.
@@ -1255,7 +1255,7 @@
     <row r="55">
       <c r="A55" s="45" t="inlineStr">
         <is>
-          <t>• Total items: 234 (203 dům + 31 sklad) — vč. CEV +3 (komín/zídky/drenáž), anchor-gap +2 (přesun hmot/lešení), terasa-area fix + venkovní schody na terénu. 70 items s realizuje_skladbu.</t>
+          <t>• Total items: 233 (202 dům + 31 sklad) — vč. CEV +3 (komín/zídky/drenáž), anchor-gap +2 (přesun hmot/lešení), terasa-area fix + venkovní schody na terénu. 70 items s realizuje_skladbu.</t>
         </is>
       </c>
     </row>
@@ -2645,11 +2645,11 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Bourání kompletního stávajícího krovu; Bourání plechové střešní krytiny; Bourání nadezdívek nad stropem 2.NP; Bourání trámového stropu 2.NP/podkroví; … (+14 dalších)</t>
+          <t>Bourání kompletního stávajícího krovu; Bourání plechové střešní krytiny; Bourání nadezdívek nad stropem 2.NP; Bourání trámového stropu 2.NP/podkroví; … (+13 dalších)</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E7" s="10" t="n"/>
       <c r="F7" s="10" t="n"/>
@@ -3207,7 +3207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J133"/>
+  <dimension ref="A1:J132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>Demontáž oken a dveří — Demontáž všech oken a dveří stávajících (recyklace)</t>
+          <t>Demontáž zařizovacích předmětů — Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
         </is>
       </c>
       <c r="E90" s="20" t="inlineStr">
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="F90" s="23" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G90" s="10" t="n"/>
       <c r="H90" s="10" t="n"/>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="J90" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 968071120</t>
+          <t>URS-prop 725900001</t>
         </is>
       </c>
     </row>
@@ -6850,16 +6850,16 @@
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>Demontáž zařizovacích předmětů — Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
+          <t>Odvoz suti a likvidace — Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
         </is>
       </c>
       <c r="E91" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="F91" s="23" t="n">
-        <v>12</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="F91" s="22" t="n">
+        <v>56.5</v>
       </c>
       <c r="G91" s="10" t="n"/>
       <c r="H91" s="10" t="n"/>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="J91" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 725900001</t>
+          <t>URS-prop 997013501</t>
         </is>
       </c>
     </row>
@@ -6885,32 +6885,32 @@
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>Odvoz suti a likvidace — Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
+          <t>Příprava podkladu — Příprava fasádního podkladu — očištění tlakovou vodou, vyspravení omítek, fungicidní nátěr</t>
         </is>
       </c>
       <c r="E92" s="20" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F92" s="22" t="n">
-        <v>56.5</v>
+        <v>276.7</v>
       </c>
       <c r="G92" s="10" t="n"/>
       <c r="H92" s="10" t="n"/>
       <c r="I92" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>fasadnik_etics</t>
         </is>
       </c>
       <c r="J92" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 997013501</t>
+          <t>URS-prop 622401110</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>Příprava podkladu — Příprava fasádního podkladu — očištění tlakovou vodou, vyspravení omítek, fungicidní nátěr</t>
+          <t>ETICS EPS 70F grey 160 mm — ETICS kontaktní zateplení — EPS 70F grey λ=0.032 tl. 160 mm + síťka + lepidlo + zatírací stěrka (řez S01+S12a explicit, ne 200 mm fallback)</t>
         </is>
       </c>
       <c r="E93" s="20" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="J93" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 622401110</t>
+          <t>URS-prop 622221121</t>
         </is>
       </c>
     </row>
@@ -6970,7 +6970,7 @@
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>ETICS EPS 70F grey 160 mm — ETICS kontaktní zateplení — EPS 70F grey λ=0.032 tl. 160 mm + síťka + lepidlo + zatírací stěrka (řez S01+S12a explicit, ne 200 mm fallback)</t>
+          <t>ETICS sokl XPS — ETICS sokl — XPS λ=0.034 tl. 120 mm + soklový profil + cihelný obklad spárovaný</t>
         </is>
       </c>
       <c r="E94" s="20" t="inlineStr">
@@ -6979,7 +6979,7 @@
         </is>
       </c>
       <c r="F94" s="22" t="n">
-        <v>276.7</v>
+        <v>13.5</v>
       </c>
       <c r="G94" s="10" t="n"/>
       <c r="H94" s="10" t="n"/>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="J94" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 622221121</t>
+          <t>URS-prop 622223111</t>
         </is>
       </c>
     </row>
@@ -7010,16 +7010,16 @@
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>ETICS sokl XPS — ETICS sokl — XPS λ=0.034 tl. 120 mm + soklový profil + cihelný obklad spárovaný</t>
+          <t>Špalety EPS — Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
         </is>
       </c>
       <c r="E95" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="F95" s="22" t="n">
-        <v>13.5</v>
+        <v>82.2</v>
       </c>
       <c r="G95" s="10" t="n"/>
       <c r="H95" s="10" t="n"/>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="J95" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 622223111</t>
+          <t>URS-prop 622221221</t>
         </is>
       </c>
     </row>
@@ -7050,16 +7050,16 @@
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Špalety EPS — Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
+          <t>Profilace fasády — Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
         </is>
       </c>
       <c r="E96" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="F96" s="22" t="n">
-        <v>82.2</v>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="F96" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="G96" s="10" t="n"/>
       <c r="H96" s="10" t="n"/>
@@ -7090,16 +7090,16 @@
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>Profilace fasády — Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
+          <t>Tenkovrstvá omítka pastovitá — Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
         </is>
       </c>
       <c r="E97" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="F97" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F97" s="22" t="n">
+        <v>290.2</v>
       </c>
       <c r="G97" s="10" t="n"/>
       <c r="H97" s="10" t="n"/>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="J97" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 622221221</t>
+          <t>URS-prop 622521111</t>
         </is>
       </c>
     </row>
@@ -7125,32 +7125,32 @@
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda ETICS</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>Tenkovrstvá omítka pastovitá — Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
+          <t>Demontáž oken — Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
         </is>
       </c>
       <c r="E98" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F98" s="22" t="n">
-        <v>290.2</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="F98" s="23" t="n">
+        <v>16</v>
       </c>
       <c r="G98" s="10" t="n"/>
       <c r="H98" s="10" t="n"/>
       <c r="I98" s="8" t="inlineStr">
         <is>
-          <t>fasadnik_etics</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="J98" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 622521111</t>
+          <t>URS-prop 978013181</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>Demontáž oken — Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
+          <t>Demontáž vstupních dveří venkovních — Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
         </is>
       </c>
       <c r="E99" s="20" t="inlineStr">
@@ -7179,7 +7179,7 @@
         </is>
       </c>
       <c r="F99" s="23" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G99" s="10" t="n"/>
       <c r="H99" s="10" t="n"/>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>Demontáž vstupních dveří venkovních — Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
+          <t>Demontáž vnitřních dveří vč. zárubní — Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
         </is>
       </c>
       <c r="E100" s="20" t="inlineStr">
@@ -7219,7 +7219,7 @@
         </is>
       </c>
       <c r="F100" s="23" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G100" s="10" t="n"/>
       <c r="H100" s="10" t="n"/>
@@ -7230,7 +7230,7 @@
       </c>
       <c r="J100" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 978013181</t>
+          <t>URS-prop 968072456</t>
         </is>
       </c>
     </row>
@@ -7250,16 +7250,16 @@
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>Demontáž vnitřních dveří vč. zárubní — Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
+          <t>Bourání zdiva komínu — Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
         </is>
       </c>
       <c r="E101" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="F101" s="23" t="n">
-        <v>15</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F101" s="22" t="n">
+        <v>0.6</v>
       </c>
       <c r="G101" s="10" t="n"/>
       <c r="H101" s="10" t="n"/>
@@ -7270,7 +7270,7 @@
       </c>
       <c r="J101" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 968072456</t>
+          <t>URS-prop 962024141</t>
         </is>
       </c>
     </row>
@@ -7290,7 +7290,7 @@
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>Bourání zdiva komínu — Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
+          <t>Bourání venkovních konstrukcí — Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
         </is>
       </c>
       <c r="E102" s="20" t="inlineStr">
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="F102" s="22" t="n">
-        <v>0.6</v>
+        <v>8</v>
       </c>
       <c r="G102" s="10" t="n"/>
       <c r="H102" s="10" t="n"/>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="J102" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 962024141</t>
+          <t>URS-prop 961044111</t>
         </is>
       </c>
     </row>
@@ -7325,32 +7325,32 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>Bourání venkovních konstrukcí — Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
+          <t>Drenáž za bílou vanou — Drenáž za opěrnou stěnou (bílou vanou) — drenážní trubka DN100 vlnitá perforovaná + štěrkový obsyp 16/32 + geotextilie + napojení do dešťové kanalizace, L po obvodu BV</t>
         </is>
       </c>
       <c r="E103" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F103" s="22" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G103" s="10" t="n"/>
       <c r="H103" s="10" t="n"/>
       <c r="I103" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="J103" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 961044111</t>
+          <t>URS-prop 877315111</t>
         </is>
       </c>
     </row>
@@ -7360,37 +7360,37 @@
       </c>
       <c r="B104" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>HSV-1 Zemní práce</t>
+          <t>HSV-5 Komunikace + schodiště</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>Drenáž za bílou vanou — Drenáž za opěrnou stěnou (bílou vanou) — drenážní trubka DN100 vlnitá perforovaná + štěrkový obsyp 16/32 + geotextilie + napojení do dešťové kanalizace, L po obvodu BV</t>
+          <t>Sklad mezipodesta schodiště prefa — Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
         </is>
       </c>
       <c r="E104" s="20" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F104" s="22" t="n">
-        <v>12</v>
+        <v>5.5</v>
       </c>
       <c r="G104" s="10" t="n"/>
       <c r="H104" s="10" t="n"/>
       <c r="I104" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>betonar</t>
         </is>
       </c>
       <c r="J104" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 877315111</t>
+          <t>URS-prop 121301101</t>
         </is>
       </c>
     </row>
@@ -7400,37 +7400,37 @@
       </c>
       <c r="B105" s="20" t="inlineStr">
         <is>
-          <t>260217_sklad</t>
+          <t>260219_dum</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + schodiště</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>Sklad mezipodesta schodiště prefa — Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
+          <t>Venkovní schody na terénu (zahrada za opěrnou stěnou) — Venkovní schody na terénu z betonových dílců do betonového lože — rameno 1: 8×175×280 mm + rameno 2: 5×175×280 mm (13 stupňů), zahrada za opěrnou stěnou</t>
         </is>
       </c>
       <c r="E105" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F105" s="22" t="n">
-        <v>5.5</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="F105" s="23" t="n">
+        <v>13</v>
       </c>
       <c r="G105" s="10" t="n"/>
       <c r="H105" s="10" t="n"/>
       <c r="I105" s="8" t="inlineStr">
         <is>
-          <t>betonar</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="J105" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 121301101</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>HSV-1 Zemní práce</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>Venkovní schody na terénu (zahrada za opěrnou stěnou) — Venkovní schody na terénu z betonových dílců do betonového lože — rameno 1: 8×175×280 mm + rameno 2: 5×175×280 mm (13 stupňů), zahrada za opěrnou stěnou</t>
+          <t>Spojovací prostředky krovu — svorníky tesařských spojů — Montáž svorníků / šroubů tesařských spojů krovu délky přes 150 do 300 mm — spojení kleštin 2×60/180 mm s krokvemi (svorník cca 250 mm, M12), vč. tyče závitové + matic + podložek</t>
         </is>
       </c>
       <c r="E106" s="20" t="inlineStr">
@@ -7459,18 +7459,18 @@
         </is>
       </c>
       <c r="F106" s="23" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="G106" s="10" t="n"/>
       <c r="H106" s="10" t="n"/>
       <c r="I106" s="8" t="inlineStr">
         <is>
-          <t>zednik</t>
+          <t>tesar</t>
         </is>
       </c>
       <c r="J106" s="8" t="inlineStr">
         <is>
-          <t>URS-prop —</t>
+          <t>URS-prop 762085112</t>
         </is>
       </c>
     </row>
@@ -7485,32 +7485,32 @@
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Krov + střecha</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>Spojovací prostředky krovu — svorníky tesařských spojů — Montáž svorníků / šroubů tesařských spojů krovu délky přes 150 do 300 mm — spojení kleštin 2×60/180 mm s krokvemi (svorník cca 250 mm, M12), vč. tyče závitové + matic + podložek</t>
+          <t>Strop 1.NP/2.NP — kročejová izolace (S07) — Desky kročejové izolace (Isover T-P) tl. 30 mm — trámový strop 1.NP/2.NP</t>
         </is>
       </c>
       <c r="E107" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="F107" s="23" t="n">
-        <v>50</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F107" s="22" t="n">
+        <v>59.5</v>
       </c>
       <c r="G107" s="10" t="n"/>
       <c r="H107" s="10" t="n"/>
       <c r="I107" s="8" t="inlineStr">
         <is>
-          <t>tesar</t>
+          <t>izolater_TI</t>
         </is>
       </c>
       <c r="J107" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 762085112</t>
+          <t>URS-prop 713191</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>Strop 1.NP/2.NP — kročejová izolace (S07) — Desky kročejové izolace (Isover T-P) tl. 30 mm — trámový strop 1.NP/2.NP</t>
+          <t>Strop 1.NP/2.NP — separační geotextilie (S07) — Separační geotextilie pod suchý podsyp — trámový strop 1.NP/2.NP</t>
         </is>
       </c>
       <c r="E108" s="20" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="J108" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 713191</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>Strop 1.NP/2.NP — separační geotextilie (S07) — Separační geotextilie pod suchý podsyp — trámový strop 1.NP/2.NP</t>
+          <t>Strop 2.NP/3.NP — min. vata výplň mezi nosníky (S09) — Tepelná/akustická izolace minerální vata výplň mezi ocelové nosníky stropu 2.NP/3.NP, tl. 180/200 mm</t>
         </is>
       </c>
       <c r="E109" s="20" t="inlineStr">
@@ -7579,7 +7579,7 @@
         </is>
       </c>
       <c r="F109" s="22" t="n">
-        <v>59.5</v>
+        <v>104.4</v>
       </c>
       <c r="G109" s="10" t="n"/>
       <c r="H109" s="10" t="n"/>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="J109" s="8" t="inlineStr">
         <is>
-          <t>URS-prop —</t>
+          <t>URS-prop 713121</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>Strop 2.NP/3.NP — min. vata výplň mezi nosníky (S09) — Tepelná/akustická izolace minerální vata výplň mezi ocelové nosníky stropu 2.NP/3.NP, tl. 180/200 mm</t>
+          <t>Strop klemba mezi patry — Fermacell (S08) — Roznášecí sádrovláknité dílce Fermacell 2E22 tl. 25 mm — suchá skladba nad cihelnou klembou S08</t>
         </is>
       </c>
       <c r="E110" s="20" t="inlineStr">
@@ -7618,19 +7618,17 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="F110" s="22" t="n">
-        <v>104.4</v>
-      </c>
+      <c r="F110" s="22" t="n"/>
       <c r="G110" s="10" t="n"/>
       <c r="H110" s="10" t="n"/>
       <c r="I110" s="8" t="inlineStr">
         <is>
-          <t>izolater_TI</t>
+          <t>suchá_vystavba</t>
         </is>
       </c>
       <c r="J110" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 713121</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7648,7 @@
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>Strop klemba mezi patry — Fermacell (S08) — Roznášecí sádrovláknité dílce Fermacell 2E22 tl. 25 mm — suchá skladba nad cihelnou klembou S08</t>
+          <t>Strop klemba mezi patry — kročejová izolace (S08) — Desky kročejové izolace (Isover T-P) tl. 30 mm — suchá skladba nad klembou S08</t>
         </is>
       </c>
       <c r="E111" s="20" t="inlineStr">
@@ -7663,12 +7661,12 @@
       <c r="H111" s="10" t="n"/>
       <c r="I111" s="8" t="inlineStr">
         <is>
-          <t>suchá_vystavba</t>
+          <t>izolater_TI</t>
         </is>
       </c>
       <c r="J111" s="8" t="inlineStr">
         <is>
-          <t>URS-prop —</t>
+          <t>URS-prop 713191</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7686,7 @@
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>Strop klemba mezi patry — kročejová izolace (S08) — Desky kročejové izolace (Isover T-P) tl. 30 mm — suchá skladba nad klembou S08</t>
+          <t>Strop klemba mezi patry — suchý podsyp + dřevěný rošt (S08) — Vyrovnávací suchý podsyp keramzit/liapor + dřevěný rošt tl. 50 mm — nad klembou S08</t>
         </is>
       </c>
       <c r="E112" s="20" t="inlineStr">
@@ -7701,12 +7699,12 @@
       <c r="H112" s="10" t="n"/>
       <c r="I112" s="8" t="inlineStr">
         <is>
-          <t>izolater_TI</t>
+          <t>suchá_vystavba</t>
         </is>
       </c>
       <c r="J112" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 713191</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7724,7 @@
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>Strop klemba mezi patry — suchý podsyp + dřevěný rošt (S08) — Vyrovnávací suchý podsyp keramzit/liapor + dřevěný rošt tl. 50 mm — nad klembou S08</t>
+          <t>Strop klemba mezi patry — separační vrstva (S08) — Separační vrstva pod suchý podsyp — nad cihelnou klembou S08</t>
         </is>
       </c>
       <c r="E113" s="20" t="inlineStr">
@@ -7759,12 +7757,12 @@
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-7 Fasáda + zateplení</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>Strop klemba mezi patry — separační vrstva (S08) — Separační vrstva pod suchý podsyp — nad cihelnou klembou S08</t>
+          <t>Sokl suterénu — sanační zateplení (S03) — Sanační zateplení soklu — sanační izolační deska Styrcon 200 + lepící tmel (Lepstyr plus) + armovací vrstva s tkaninou + penetrace</t>
         </is>
       </c>
       <c r="E114" s="20" t="inlineStr">
@@ -7772,12 +7770,14 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="F114" s="22" t="n"/>
+      <c r="F114" s="22" t="n">
+        <v>23</v>
+      </c>
       <c r="G114" s="10" t="n"/>
       <c r="H114" s="10" t="n"/>
       <c r="I114" s="8" t="inlineStr">
         <is>
-          <t>suchá_vystavba</t>
+          <t>fasader</t>
         </is>
       </c>
       <c r="J114" s="8" t="inlineStr">
@@ -7802,7 +7802,7 @@
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>Sokl suterénu — sanační zateplení (S03) — Sanační zateplení soklu — sanační izolační deska Styrcon 200 + lepící tmel (Lepstyr plus) + armovací vrstva s tkaninou + penetrace</t>
+          <t>Sokl pod terénem — drenážní nopová folie (S03a) — Drenážní vrstva — nopová folie tl. 20 mm na suterénní stěnu pod úrovní terénu</t>
         </is>
       </c>
       <c r="E115" s="20" t="inlineStr">
@@ -7817,7 +7817,7 @@
       <c r="H115" s="10" t="n"/>
       <c r="I115" s="8" t="inlineStr">
         <is>
-          <t>fasader</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="J115" s="8" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>Sokl pod terénem — drenážní nopová folie (S03a) — Drenážní vrstva — nopová folie tl. 20 mm na suterénní stěnu pod úrovní terénu</t>
+          <t>Sokl nad terénem — provětraný obklad (S03b) — Provětrávaná mezera s kotevním roštem 40 mm + keramický obklad 20 mm — sokl nad úrovní terénu</t>
         </is>
       </c>
       <c r="E116" s="20" t="inlineStr">
@@ -7857,7 +7857,7 @@
       <c r="H116" s="10" t="n"/>
       <c r="I116" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="J116" s="8" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda + zateplení</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>Sokl nad terénem — provětraný obklad (S03b) — Provětrávaná mezera s kotevním roštem 40 mm + keramický obklad 20 mm — sokl nad úrovní terénu</t>
+          <t>Střecha — pojistná HI folie pod Al krytinu (S10) — Pojistná hydroizolační folie pod hliníkovou falcovanou krytinu (nad celoplošným bedněním)</t>
         </is>
       </c>
       <c r="E117" s="20" t="inlineStr">
@@ -7891,13 +7891,13 @@
         </is>
       </c>
       <c r="F117" s="22" t="n">
-        <v>23</v>
+        <v>140.94</v>
       </c>
       <c r="G117" s="10" t="n"/>
       <c r="H117" s="10" t="n"/>
       <c r="I117" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>pokryvac</t>
         </is>
       </c>
       <c r="J117" s="8" t="inlineStr">
@@ -7917,12 +7917,12 @@
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Krov + střecha</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>Střecha — pojistná HI folie pod Al krytinu (S10) — Pojistná hydroizolační folie pod hliníkovou falcovanou krytinu (nad celoplošným bedněním)</t>
+          <t>Demontáž vnějšího keram. obkladu suterénu (S03 stávající) — Demontáž stávajícího vnějšího keramického obkladu suterénní stěny (sokl) tl. 20 mm</t>
         </is>
       </c>
       <c r="E118" s="20" t="inlineStr">
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="F118" s="22" t="n">
-        <v>140.94</v>
+        <v>23</v>
       </c>
       <c r="G118" s="10" t="n"/>
       <c r="H118" s="10" t="n"/>
       <c r="I118" s="8" t="inlineStr">
         <is>
-          <t>pokryvac</t>
+          <t>bourac</t>
         </is>
       </c>
       <c r="J118" s="8" t="inlineStr">
@@ -7952,17 +7952,17 @@
       </c>
       <c r="B119" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-5 Komunikace + vjezd</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr">
         <is>
-          <t>Demontáž vnějšího keram. obkladu suterénu (S03 stávající) — Demontáž stávajícího vnějšího keramického obkladu suterénní stěny (sokl) tl. 20 mm</t>
+          <t>Vjezd Dvořákova — napojení na komunikaci — Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťové vody na pozemek (ne na komunikaci)</t>
         </is>
       </c>
       <c r="E119" s="20" t="inlineStr">
@@ -7970,14 +7970,12 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="F119" s="22" t="n">
-        <v>23</v>
-      </c>
+      <c r="F119" s="22" t="n"/>
       <c r="G119" s="10" t="n"/>
       <c r="H119" s="10" t="n"/>
       <c r="I119" s="8" t="inlineStr">
         <is>
-          <t>bourac</t>
+          <t>komunikace</t>
         </is>
       </c>
       <c r="J119" s="8" t="inlineStr">
@@ -7995,32 +7993,34 @@
           <t>260217_sklad</t>
         </is>
       </c>
-      <c r="C120" s="8" t="inlineStr">
-        <is>
-          <t>HSV-5 Komunikace + vjezd</t>
+      <c r="C120" s="21" t="inlineStr">
+        <is>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>Vjezd Dvořákova — napojení na komunikaci — Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťové vody na pozemek (ne na komunikaci)</t>
+          <t>[agregát] 2 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána</t>
         </is>
       </c>
       <c r="E120" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F120" s="22" t="n"/>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F120" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="G120" s="10" t="n"/>
       <c r="H120" s="10" t="n"/>
       <c r="I120" s="8" t="inlineStr">
         <is>
-          <t>komunikace</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J120" s="8" t="inlineStr">
         <is>
-          <t>URS-prop —</t>
+          <t>agregát</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="C121" s="21" t="inlineStr">
         <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 2 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána</t>
+          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
         </is>
       </c>
       <c r="E121" s="20" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="C122" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
+          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E122" s="20" t="inlineStr">
@@ -8110,17 +8110,17 @@
       </c>
       <c r="B123" s="20" t="inlineStr">
         <is>
-          <t>260217_sklad</t>
+          <t>260219_dum</t>
         </is>
       </c>
       <c r="C123" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>M-21 — Elektroinstalace silnoproudá</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
+          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E123" s="20" t="inlineStr">
@@ -8155,12 +8155,12 @@
       </c>
       <c r="C124" s="21" t="inlineStr">
         <is>
-          <t>M-21 — Elektroinstalace silnoproudá</t>
+          <t>M-24</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
+          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
         </is>
       </c>
       <c r="E124" s="20" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="C125" s="21" t="inlineStr">
         <is>
-          <t>M-24</t>
+          <t>PSV-71 — Izolace HI + TI</t>
         </is>
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
+          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E125" s="20" t="inlineStr">
@@ -8235,12 +8235,12 @@
       </c>
       <c r="C126" s="21" t="inlineStr">
         <is>
-          <t>PSV-71 — Izolace HI + TI</t>
+          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
+          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
         </is>
       </c>
       <c r="E126" s="20" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="C127" s="21" t="inlineStr">
         <is>
-          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
+          <t>PSV-73 — Vytápění + komín</t>
         </is>
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
+          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E127" s="20" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="C128" s="21" t="inlineStr">
         <is>
-          <t>PSV-73 — Vytápění + komín</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
+          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
         </is>
       </c>
       <c r="E128" s="20" t="inlineStr">
@@ -8355,12 +8355,12 @@
       </c>
       <c r="C129" s="21" t="inlineStr">
         <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
+          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
         </is>
       </c>
       <c r="E129" s="20" t="inlineStr">
@@ -8395,12 +8395,12 @@
       </c>
       <c r="C130" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>PSV-78 — Povrchové úpravy</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
+          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
         </is>
       </c>
       <c r="E130" s="20" t="inlineStr">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="C131" s="21" t="inlineStr">
         <is>
-          <t>PSV-78 — Povrchové úpravy</t>
+          <t>PSV-95 — Detekce požární</t>
         </is>
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
+          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
         </is>
       </c>
       <c r="E131" s="20" t="inlineStr">
@@ -8475,12 +8475,12 @@
       </c>
       <c r="C132" s="21" t="inlineStr">
         <is>
-          <t>PSV-95 — Detekce požární</t>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
         </is>
       </c>
       <c r="E132" s="20" t="inlineStr">
@@ -8504,48 +8504,8 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="20" t="n">
-        <v>132</v>
-      </c>
-      <c r="B133" s="20" t="inlineStr">
-        <is>
-          <t>260219_dum</t>
-        </is>
-      </c>
-      <c r="C133" s="21" t="inlineStr">
-        <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
-        </is>
-      </c>
-      <c r="D133" s="8" t="inlineStr">
-        <is>
-          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
-        </is>
-      </c>
-      <c r="E133" s="20" t="inlineStr">
-        <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F133" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G133" s="10" t="n"/>
-      <c r="H133" s="10" t="n"/>
-      <c r="I133" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J133" s="8" t="inlineStr">
-        <is>
-          <t>agregát</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J133"/>
+  <autoFilter ref="A1:J132"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8556,7 +8516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R204"/>
+  <dimension ref="A1:R203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -14111,17 +14071,17 @@
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>Demontáž oken a dveří</t>
+          <t>Demontáž zařizovacích předmětů</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
         <is>
-          <t>968071120</t>
+          <t>725900001</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>Demontáž všech oken a dveří stávajících (recyklace)</t>
+          <t>Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
         </is>
       </c>
       <c r="F80" s="20" t="inlineStr">
@@ -14130,7 +14090,7 @@
         </is>
       </c>
       <c r="G80" s="23" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="H80" s="10" t="n"/>
       <c r="I80" s="10" t="n"/>
@@ -14149,12 +14109,12 @@
       </c>
       <c r="M80" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3 — VŠECHNY okna a dveře demontovány</t>
+          <t>TZ ARS dům §3 — zařizovací předměty kompletně demontovány</t>
         </is>
       </c>
       <c r="N80" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O80" s="26" t="inlineStr">
@@ -14176,26 +14136,26 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>Demontáž zařizovacích předmětů</t>
+          <t>Odvoz suti a likvidace</t>
         </is>
       </c>
       <c r="D81" s="20" t="inlineStr">
         <is>
-          <t>725900001</t>
+          <t>997013501</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
+          <t>Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
         </is>
       </c>
       <c r="F81" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G81" s="23" t="n">
-        <v>12</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G81" s="22" t="n">
+        <v>56.5</v>
       </c>
       <c r="H81" s="10" t="n"/>
       <c r="I81" s="10" t="n"/>
@@ -14205,7 +14165,7 @@
         </is>
       </c>
       <c r="K81" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L81" s="20" t="inlineStr">
         <is>
@@ -14214,12 +14174,12 @@
       </c>
       <c r="M81" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3 — zařizovací předměty kompletně demontovány</t>
+          <t>TZ B m.10.e bilance odpadů</t>
         </is>
       </c>
       <c r="N81" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#9</t>
         </is>
       </c>
       <c r="O81" s="26" t="inlineStr">
@@ -14241,26 +14201,26 @@
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>Odvoz suti a likvidace</t>
+          <t>Demontáž oken</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
         <is>
-          <t>997013501</t>
+          <t>978013181</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
+          <t>Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
         </is>
       </c>
       <c r="F82" s="20" t="inlineStr">
         <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G82" s="22" t="n">
-        <v>56.5</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G82" s="23" t="n">
+        <v>16</v>
       </c>
       <c r="H82" s="10" t="n"/>
       <c r="I82" s="10" t="n"/>
@@ -14270,30 +14230,34 @@
         </is>
       </c>
       <c r="K82" s="24" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="L82" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>matched_websearch_verified</t>
         </is>
       </c>
       <c r="M82" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e bilance odpadů</t>
+          <t>DXF blocks okno* (Path C Tier 4) + TZ ARS — všechna okna nová</t>
         </is>
       </c>
       <c r="N82" s="20" t="inlineStr">
         <is>
-          <t>#9</t>
-        </is>
-      </c>
-      <c r="O82" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="O82" s="25" t="inlineStr">
+        <is>
+          <t>OVĚŘENO ✓</t>
         </is>
       </c>
       <c r="P82" s="41" t="n"/>
-      <c r="Q82" s="41" t="n"/>
+      <c r="Q82" s="41" t="inlineStr">
+        <is>
+          <t>F2_DEDUP_DEMONTAZ_OKEN_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="20" t="n">
@@ -14306,7 +14270,7 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>Demontáž oken</t>
+          <t>Demontáž vstupních dveří venkovních</t>
         </is>
       </c>
       <c r="D83" s="20" t="inlineStr">
@@ -14316,7 +14280,7 @@
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
+          <t>Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
         </is>
       </c>
       <c r="F83" s="20" t="inlineStr">
@@ -14325,7 +14289,7 @@
         </is>
       </c>
       <c r="G83" s="23" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="H83" s="10" t="n"/>
       <c r="I83" s="10" t="n"/>
@@ -14344,7 +14308,7 @@
       </c>
       <c r="M83" s="8" t="inlineStr">
         <is>
-          <t>DXF blocks okno* (Path C Tier 4) + TZ ARS — všechna okna nová</t>
+          <t>DXF blocks dveře (vstupní 2) + TZ ARS — 'plastové vstupní dveře' x 2</t>
         </is>
       </c>
       <c r="N83" s="20" t="inlineStr">
@@ -14375,17 +14339,17 @@
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>Demontáž vstupních dveří venkovních</t>
+          <t>Demontáž vnitřních dveří vč. zárubní</t>
         </is>
       </c>
       <c r="D84" s="20" t="inlineStr">
         <is>
-          <t>978013181</t>
+          <t>968072456</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
+          <t>Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
         </is>
       </c>
       <c r="F84" s="20" t="inlineStr">
@@ -14394,7 +14358,7 @@
         </is>
       </c>
       <c r="G84" s="23" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H84" s="10" t="n"/>
       <c r="I84" s="10" t="n"/>
@@ -14404,16 +14368,16 @@
         </is>
       </c>
       <c r="K84" s="24" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="L84" s="20" t="inlineStr">
         <is>
-          <t>matched_websearch_verified</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M84" s="8" t="inlineStr">
         <is>
-          <t>DXF blocks dveře (vstupní 2) + TZ ARS — 'plastové vstupní dveře' x 2</t>
+          <t>DXF SM__dveře polyline count → estimate (Path C Tier 4)</t>
         </is>
       </c>
       <c r="N84" s="20" t="inlineStr">
@@ -14421,9 +14385,9 @@
           <t>#3</t>
         </is>
       </c>
-      <c r="O84" s="25" t="inlineStr">
-        <is>
-          <t>OVĚŘENO ✓</t>
+      <c r="O84" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
         </is>
       </c>
       <c r="P84" s="41" t="n"/>
@@ -14444,26 +14408,26 @@
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>Demontáž vnitřních dveří vč. zárubní</t>
+          <t>Bourání zdiva komínu</t>
         </is>
       </c>
       <c r="D85" s="20" t="inlineStr">
         <is>
-          <t>968072456</t>
+          <t>962024141</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
+          <t>Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
         </is>
       </c>
       <c r="F85" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G85" s="23" t="n">
-        <v>15</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="G85" s="22" t="n">
+        <v>0.6</v>
       </c>
       <c r="H85" s="10" t="n"/>
       <c r="I85" s="10" t="n"/>
@@ -14473,21 +14437,21 @@
         </is>
       </c>
       <c r="K85" s="24" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="L85" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M85" s="8" t="inlineStr">
         <is>
-          <t>DXF SM__dveře polyline count → estimate (Path C Tier 4)</t>
+          <t>DXF dum_DPZ řez A-A bourání + POZN.1.02 z půdorysů bourání</t>
         </is>
       </c>
       <c r="N85" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>#9</t>
         </is>
       </c>
       <c r="O85" s="26" t="inlineStr">
@@ -14498,7 +14462,7 @@
       <c r="P85" s="41" t="n"/>
       <c r="Q85" s="41" t="inlineStr">
         <is>
-          <t>GAP_002</t>
+          <t>PER_DRAWING_GAP_POZN_1_02; URS_PHASE5B_FAMILY_VERIFIED; CHATGPT_KOMIN_QTY_FIX_2026-05-29</t>
         </is>
       </c>
     </row>
@@ -14513,17 +14477,17 @@
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>Bourání zdiva komínu</t>
+          <t>Bourání venkovních konstrukcí</t>
         </is>
       </c>
       <c r="D86" s="20" t="inlineStr">
         <is>
-          <t>962024141</t>
+          <t>961044111</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
+          <t>Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
         </is>
       </c>
       <c r="F86" s="20" t="inlineStr">
@@ -14532,7 +14496,7 @@
         </is>
       </c>
       <c r="G86" s="22" t="n">
-        <v>0.6</v>
+        <v>8</v>
       </c>
       <c r="H86" s="10" t="n"/>
       <c r="I86" s="10" t="n"/>
@@ -14542,7 +14506,7 @@
         </is>
       </c>
       <c r="K86" s="24" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="L86" s="20" t="inlineStr">
         <is>
@@ -14551,7 +14515,7 @@
       </c>
       <c r="M86" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ řez A-A bourání + POZN.1.02 z půdorysů bourání</t>
+          <t>DXF dum_DPZ řez A-A bourání + POZN.1.03 + půdorys bourání</t>
         </is>
       </c>
       <c r="N86" s="20" t="inlineStr">
@@ -14567,7 +14531,7 @@
       <c r="P86" s="41" t="n"/>
       <c r="Q86" s="41" t="inlineStr">
         <is>
-          <t>PER_DRAWING_GAP_POZN_1_02; URS_PHASE5B_FAMILY_VERIFIED; CHATGPT_KOMIN_QTY_FIX_2026-05-29</t>
+          <t>PER_DRAWING_GAP_POZN_1_03; URS_PHASE5B_FAMILY_VERIFIED</t>
         </is>
       </c>
     </row>
@@ -14582,50 +14546,50 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>Bourání venkovních konstrukcí</t>
+          <t>Demontáž vnějšího keram. obkladu suterénu (S03 stávající)</t>
         </is>
       </c>
       <c r="D87" s="20" t="inlineStr">
         <is>
-          <t>961044111</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
+          <t>Demontáž stávajícího vnějšího keramického obkladu suterénní stěny (sokl) tl. 20 mm</t>
         </is>
       </c>
       <c r="F87" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G87" s="22" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H87" s="10" t="n"/>
       <c r="I87" s="10" t="n"/>
       <c r="J87" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>bourac</t>
         </is>
       </c>
       <c r="K87" s="24" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="L87" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M87" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ řez A-A bourání + POZN.1.03 + půdorys bourání</t>
+          <t>skladba S03 stávající (vnější keram. obklad) + Řez A-A sokl</t>
         </is>
       </c>
       <c r="N87" s="20" t="inlineStr">
         <is>
-          <t>#9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O87" s="26" t="inlineStr">
@@ -14633,10 +14597,14 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P87" s="41" t="n"/>
+      <c r="P87" s="41" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
       <c r="Q87" s="41" t="inlineStr">
         <is>
-          <t>PER_DRAWING_GAP_POZN_1_03; URS_PHASE5B_FAMILY_VERIFIED</t>
+          <t>SKLADBY_GAPS_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -14646,12 +14614,12 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-7 Fasáda + zateplení</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>Demontáž vnějšího keram. obkladu suterénu (S03 stávající)</t>
+          <t>Sokl suterénu — sanační zateplení (S03)</t>
         </is>
       </c>
       <c r="D88" s="20" t="inlineStr">
@@ -14661,7 +14629,7 @@
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávajícího vnějšího keramického obkladu suterénní stěny (sokl) tl. 20 mm</t>
+          <t>Sanační zateplení soklu — sanační izolační deska Styrcon 200 + lepící tmel (Lepstyr plus) + armovací vrstva s tkaninou + penetrace</t>
         </is>
       </c>
       <c r="F88" s="20" t="inlineStr">
@@ -14676,7 +14644,7 @@
       <c r="I88" s="10" t="n"/>
       <c r="J88" s="8" t="inlineStr">
         <is>
-          <t>bourac</t>
+          <t>fasader</t>
         </is>
       </c>
       <c r="K88" s="24" t="n">
@@ -14689,7 +14657,7 @@
       </c>
       <c r="M88" s="8" t="inlineStr">
         <is>
-          <t>skladba S03 stávající (vnější keram. obklad) + Řez A-A sokl</t>
+          <t>Řez A-A sokl tags (S03b -0.200/-0.975) + obvod ETICS</t>
         </is>
       </c>
       <c r="N88" s="20" t="inlineStr">
@@ -14724,7 +14692,7 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>Sokl suterénu — sanační zateplení (S03)</t>
+          <t>Sokl pod terénem — drenážní nopová folie (S03a)</t>
         </is>
       </c>
       <c r="D89" s="20" t="inlineStr">
@@ -14734,7 +14702,7 @@
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>Sanační zateplení soklu — sanační izolační deska Styrcon 200 + lepící tmel (Lepstyr plus) + armovací vrstva s tkaninou + penetrace</t>
+          <t>Drenážní vrstva — nopová folie tl. 20 mm na suterénní stěnu pod úrovní terénu</t>
         </is>
       </c>
       <c r="F89" s="20" t="inlineStr">
@@ -14749,7 +14717,7 @@
       <c r="I89" s="10" t="n"/>
       <c r="J89" s="8" t="inlineStr">
         <is>
-          <t>fasader</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K89" s="24" t="n">
@@ -14762,7 +14730,7 @@
       </c>
       <c r="M89" s="8" t="inlineStr">
         <is>
-          <t>Řez A-A sokl tags (S03b -0.200/-0.975) + obvod ETICS</t>
+          <t>Řez A-A/C-C sokl + obvod ETICS</t>
         </is>
       </c>
       <c r="N89" s="20" t="inlineStr">
@@ -14797,7 +14765,7 @@
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>Sokl pod terénem — drenážní nopová folie (S03a)</t>
+          <t>Sokl nad terénem — provětraný obklad (S03b)</t>
         </is>
       </c>
       <c r="D90" s="20" t="inlineStr">
@@ -14807,7 +14775,7 @@
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>Drenážní vrstva — nopová folie tl. 20 mm na suterénní stěnu pod úrovní terénu</t>
+          <t>Provětrávaná mezera s kotevním roštem 40 mm + keramický obklad 20 mm — sokl nad úrovní terénu</t>
         </is>
       </c>
       <c r="F90" s="20" t="inlineStr">
@@ -14822,7 +14790,7 @@
       <c r="I90" s="10" t="n"/>
       <c r="J90" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K90" s="24" t="n">
@@ -14835,7 +14803,7 @@
       </c>
       <c r="M90" s="8" t="inlineStr">
         <is>
-          <t>Řez A-A/C-C sokl + obvod ETICS</t>
+          <t>Řez A-A sokl tags S03b + obvod ETICS</t>
         </is>
       </c>
       <c r="N90" s="20" t="inlineStr">
@@ -14865,22 +14833,22 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda + zateplení</t>
+          <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>Sokl nad terénem — provětraný obklad (S03b)</t>
+          <t>Příprava podkladu</t>
         </is>
       </c>
       <c r="D91" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>622401110</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>Provětrávaná mezera s kotevním roštem 40 mm + keramický obklad 20 mm — sokl nad úrovní terénu</t>
+          <t>Příprava fasádního podkladu — očištění tlakovou vodou, vyspravení omítek, fungicidní nátěr</t>
         </is>
       </c>
       <c r="F91" s="20" t="inlineStr">
@@ -14889,17 +14857,17 @@
         </is>
       </c>
       <c r="G91" s="22" t="n">
-        <v>23</v>
+        <v>276.7</v>
       </c>
       <c r="H91" s="10" t="n"/>
       <c r="I91" s="10" t="n"/>
       <c r="J91" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>fasadnik_etics</t>
         </is>
       </c>
       <c r="K91" s="24" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="L91" s="20" t="inlineStr">
         <is>
@@ -14908,12 +14876,12 @@
       </c>
       <c r="M91" s="8" t="inlineStr">
         <is>
-          <t>Řez A-A sokl tags S03b + obvod ETICS</t>
+          <t>TZ ARS dům §3.2 — ETICS kontaktní, podklad existující omítka + DXF perimeter</t>
         </is>
       </c>
       <c r="N91" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O91" s="26" t="inlineStr">
@@ -14923,14 +14891,10 @@
       </c>
       <c r="P91" s="41" t="inlineStr">
         <is>
-          <t>S03</t>
-        </is>
-      </c>
-      <c r="Q91" s="41" t="inlineStr">
-        <is>
-          <t>SKLADBY_GAPS_2026-06-01</t>
-        </is>
-      </c>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="Q91" s="41" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="20" t="n">
@@ -14943,17 +14907,17 @@
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>Příprava podkladu</t>
+          <t>ETICS EPS 70F grey 160 mm</t>
         </is>
       </c>
       <c r="D92" s="20" t="inlineStr">
         <is>
-          <t>622401110</t>
+          <t>622221121</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>Příprava fasádního podkladu — očištění tlakovou vodou, vyspravení omítek, fungicidní nátěr</t>
+          <t>ETICS kontaktní zateplení — EPS 70F grey λ=0.032 tl. 160 mm + síťka + lepidlo + zatírací stěrka (řez S01+S12a explicit, ne 200 mm fallback)</t>
         </is>
       </c>
       <c r="F92" s="20" t="inlineStr">
@@ -14976,12 +14940,12 @@
       </c>
       <c r="L92" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M92" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — ETICS kontaktní, podklad existující omítka + DXF perimeter</t>
+          <t>TZ ARS dům §3.2 EXPLICIT 'fasádní EPS 70f grey (λ=0,032 W/mK)' + PBŘ EXPLICIT 'EPS tl. max. 200 mm' + DXF perimeter</t>
         </is>
       </c>
       <c r="N92" s="20" t="inlineStr">
@@ -14996,10 +14960,14 @@
       </c>
       <c r="P92" s="41" t="inlineStr">
         <is>
-          <t>S01</t>
-        </is>
-      </c>
-      <c r="Q92" s="41" t="n"/>
+          <t>S01, S12a</t>
+        </is>
+      </c>
+      <c r="Q92" s="41" t="inlineStr">
+        <is>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="20" t="n">
@@ -15012,17 +14980,17 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>ETICS EPS 70F grey 160 mm</t>
+          <t>ETICS sokl XPS</t>
         </is>
       </c>
       <c r="D93" s="20" t="inlineStr">
         <is>
-          <t>622221121</t>
+          <t>622223111</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>ETICS kontaktní zateplení — EPS 70F grey λ=0.032 tl. 160 mm + síťka + lepidlo + zatírací stěrka (řez S01+S12a explicit, ne 200 mm fallback)</t>
+          <t>ETICS sokl — XPS λ=0.034 tl. 120 mm + soklový profil + cihelný obklad spárovaný</t>
         </is>
       </c>
       <c r="F93" s="20" t="inlineStr">
@@ -15031,7 +14999,7 @@
         </is>
       </c>
       <c r="G93" s="22" t="n">
-        <v>276.7</v>
+        <v>13.5</v>
       </c>
       <c r="H93" s="10" t="n"/>
       <c r="I93" s="10" t="n"/>
@@ -15050,12 +15018,12 @@
       </c>
       <c r="M93" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 EXPLICIT 'fasádní EPS 70f grey (λ=0,032 W/mK)' + PBŘ EXPLICIT 'EPS tl. max. 200 mm' + DXF perimeter</t>
+          <t>TZ ARS dům §3.2 — sokl XPS + cihelný obklad + DXF perimeter</t>
         </is>
       </c>
       <c r="N93" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O93" s="26" t="inlineStr">
@@ -15065,7 +15033,7 @@
       </c>
       <c r="P93" s="41" t="inlineStr">
         <is>
-          <t>S01, S12a</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="Q93" s="41" t="inlineStr">
@@ -15085,26 +15053,26 @@
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>ETICS sokl XPS</t>
+          <t>Špalety EPS</t>
         </is>
       </c>
       <c r="D94" s="20" t="inlineStr">
         <is>
-          <t>622223111</t>
+          <t>622221221</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>ETICS sokl — XPS λ=0.034 tl. 120 mm + soklový profil + cihelný obklad spárovaný</t>
+          <t>Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
         </is>
       </c>
       <c r="F94" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G94" s="22" t="n">
-        <v>13.5</v>
+        <v>82.2</v>
       </c>
       <c r="H94" s="10" t="n"/>
       <c r="I94" s="10" t="n"/>
@@ -15114,21 +15082,21 @@
         </is>
       </c>
       <c r="K94" s="24" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
       <c r="L94" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — sokl XPS + cihelný obklad + DXF perimeter</t>
+          <t>DXF okna per typ bbox + TZ ARS §3.2 EPS přesah na špaletách 35-40 mm</t>
         </is>
       </c>
       <c r="N94" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O94" s="26" t="inlineStr">
@@ -15138,14 +15106,10 @@
       </c>
       <c r="P94" s="41" t="inlineStr">
         <is>
-          <t>S01</t>
-        </is>
-      </c>
-      <c r="Q94" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+          <t>S01, S12a</t>
+        </is>
+      </c>
+      <c r="Q94" s="41" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="20" t="n">
@@ -15158,7 +15122,7 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>Špalety EPS</t>
+          <t>Profilace fasády</t>
         </is>
       </c>
       <c r="D95" s="20" t="inlineStr">
@@ -15168,16 +15132,16 @@
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
+          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
         </is>
       </c>
       <c r="F95" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G95" s="22" t="n">
-        <v>82.2</v>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="G95" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H95" s="10" t="n"/>
       <c r="I95" s="10" t="n"/>
@@ -15196,12 +15160,12 @@
       </c>
       <c r="M95" s="8" t="inlineStr">
         <is>
-          <t>DXF okna per typ bbox + TZ ARS §3.2 EPS přesah na špaletách 35-40 mm</t>
+          <t>TZ ARS dům §3.2 — profilace různými tl. EPS</t>
         </is>
       </c>
       <c r="N95" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O95" s="26" t="inlineStr">
@@ -15227,26 +15191,26 @@
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>Profilace fasády</t>
+          <t>Tenkovrstvá omítka pastovitá</t>
         </is>
       </c>
       <c r="D96" s="20" t="inlineStr">
         <is>
-          <t>622221221</t>
+          <t>622521111</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
+          <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
         </is>
       </c>
       <c r="F96" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="G96" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G96" s="22" t="n">
+        <v>290.2</v>
       </c>
       <c r="H96" s="10" t="n"/>
       <c r="I96" s="10" t="n"/>
@@ -15256,16 +15220,16 @@
         </is>
       </c>
       <c r="K96" s="24" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
       <c r="L96" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M96" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — profilace různými tl. EPS</t>
+          <t>TZ ARS dům §3.2 — pastovitá probarvená lomená bílá + DXF perimeter</t>
         </is>
       </c>
       <c r="N96" s="20" t="inlineStr">
@@ -15280,10 +15244,14 @@
       </c>
       <c r="P96" s="41" t="inlineStr">
         <is>
-          <t>S01, S12a</t>
-        </is>
-      </c>
-      <c r="Q96" s="41" t="n"/>
+          <t>S01, S12a, S12b</t>
+        </is>
+      </c>
+      <c r="Q96" s="41" t="inlineStr">
+        <is>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="20" t="n">
@@ -15291,22 +15259,22 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda ETICS</t>
+          <t>PSV-71 Izolace HI</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>Tenkovrstvá omítka pastovitá</t>
+          <t>HI pod ŽB deskou 1.NP</t>
         </is>
       </c>
       <c r="D97" s="20" t="inlineStr">
         <is>
-          <t>622521111</t>
+          <t>712311101</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
+          <t>Hydroizolace pod ŽB deskou 1.NP — modifikované asfaltové pásy SBS 2× (zároveň protiradonová bariéra)</t>
         </is>
       </c>
       <c r="F97" s="20" t="inlineStr">
@@ -15315,17 +15283,17 @@
         </is>
       </c>
       <c r="G97" s="22" t="n">
-        <v>290.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="H97" s="10" t="n"/>
       <c r="I97" s="10" t="n"/>
       <c r="J97" s="8" t="inlineStr">
         <is>
-          <t>fasadnik_etics</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K97" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L97" s="20" t="inlineStr">
         <is>
@@ -15334,12 +15302,12 @@
       </c>
       <c r="M97" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — pastovitá probarvená lomená bílá + DXF perimeter</t>
+          <t>TZ ARS dům §4 + statika §5.5 — asfaltové pásy mod. proti radonu</t>
         </is>
       </c>
       <c r="N97" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O97" s="26" t="inlineStr">
@@ -15347,14 +15315,10 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P97" s="41" t="inlineStr">
-        <is>
-          <t>S01, S12a, S12b</t>
-        </is>
-      </c>
+      <c r="P97" s="41" t="n"/>
       <c r="Q97" s="41" t="inlineStr">
         <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+          <t>URS_PHASE5B_FAMILY_VERIFIED; URS_PHASE5B_FAMILY_VERIFIED</t>
         </is>
       </c>
     </row>
@@ -15369,26 +15333,26 @@
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>HI pod ŽB deskou 1.NP</t>
+          <t>Odvětrání radonu z podloží</t>
         </is>
       </c>
       <c r="D98" s="20" t="inlineStr">
         <is>
-          <t>712311101</t>
+          <t>712381111</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolace pod ŽB deskou 1.NP — modifikované asfaltové pásy SBS 2× (zároveň protiradonová bariéra)</t>
+          <t>Odvětrání radonu z podloží — perforované DN50 trubky v štěrkovém loži + výdech nad střechu</t>
         </is>
       </c>
       <c r="F98" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G98" s="22" t="n">
-        <v>80.40000000000001</v>
+        <v>12</v>
       </c>
       <c r="H98" s="10" t="n"/>
       <c r="I98" s="10" t="n"/>
@@ -15407,12 +15371,12 @@
       </c>
       <c r="M98" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + statika §5.5 — asfaltové pásy mod. proti radonu</t>
+          <t>TZ statika §5.5 'ochrana proti radonu — modifikované asf. pásy + odvětrání'</t>
         </is>
       </c>
       <c r="N98" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O98" s="26" t="inlineStr">
@@ -15423,7 +15387,7 @@
       <c r="P98" s="41" t="n"/>
       <c r="Q98" s="41" t="inlineStr">
         <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED; URS_PHASE5B_FAMILY_VERIFIED</t>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
         </is>
       </c>
     </row>
@@ -15438,26 +15402,26 @@
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>Odvětrání radonu z podloží</t>
-        </is>
-      </c>
-      <c r="D99" s="20" t="inlineStr">
-        <is>
-          <t>712381111</t>
+          <t>HI koupelny 1.NP + 2.NP + 3.NP</t>
+        </is>
+      </c>
+      <c r="D99" s="27" t="inlineStr">
+        <is>
+          <t>711??? ?</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>Odvětrání radonu z podloží — perforované DN50 trubky v štěrkovém loži + výdech nad střechu</t>
+          <t>Hydroizolační stěrka koupelen 3 ks — podlaha + sokl 200 mm + sprchový kout výška 2.0 m</t>
         </is>
       </c>
       <c r="F99" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G99" s="22" t="n">
-        <v>12</v>
+        <v>40.5</v>
       </c>
       <c r="H99" s="10" t="n"/>
       <c r="I99" s="10" t="n"/>
@@ -15467,7 +15431,7 @@
         </is>
       </c>
       <c r="K99" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L99" s="20" t="inlineStr">
         <is>
@@ -15476,12 +15440,12 @@
       </c>
       <c r="M99" s="8" t="inlineStr">
         <is>
-          <t>TZ statika §5.5 'ochrana proti radonu — modifikované asf. pásy + odvětrání'</t>
+          <t>DXF dum_DPZ MTEXT labels: 3× koupelna; TZ ARS — HI vana koupelny</t>
         </is>
       </c>
       <c r="N99" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#4</t>
         </is>
       </c>
       <c r="O99" s="26" t="inlineStr">
@@ -15502,22 +15466,22 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace HI</t>
+          <t>PSV-71 Izolace TI</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>HI koupelny 1.NP + 2.NP + 3.NP</t>
+          <t>Podlahový EPS 150</t>
         </is>
       </c>
       <c r="D100" s="27" t="inlineStr">
         <is>
-          <t>711??? ?</t>
+          <t>713121??? ?</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolační stěrka koupelen 3 ks — podlaha + sokl 200 mm + sprchový kout výška 2.0 m</t>
+          <t>Podlahový EPS 150 λ=0.035 tl. 120 mm — pod betonový potěr 1.NP a 3.NP</t>
         </is>
       </c>
       <c r="F100" s="20" t="inlineStr">
@@ -15526,17 +15490,17 @@
         </is>
       </c>
       <c r="G100" s="22" t="n">
-        <v>40.5</v>
+        <v>177.5</v>
       </c>
       <c r="H100" s="10" t="n"/>
       <c r="I100" s="10" t="n"/>
       <c r="J100" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>izolater_TI</t>
         </is>
       </c>
       <c r="K100" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L100" s="20" t="inlineStr">
         <is>
@@ -15545,7 +15509,7 @@
       </c>
       <c r="M100" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT labels: 3× koupelna; TZ ARS — HI vana koupelny</t>
+          <t>TZ ARS dům §4 — EPS 150 λ=0.035 tl. 120 mm</t>
         </is>
       </c>
       <c r="N100" s="20" t="inlineStr">
@@ -15576,7 +15540,7 @@
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>Podlahový EPS 150</t>
+          <t>Kročejová EPS nad ocelobeton</t>
         </is>
       </c>
       <c r="D101" s="27" t="inlineStr">
@@ -15586,7 +15550,7 @@
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>Podlahový EPS 150 λ=0.035 tl. 120 mm — pod betonový potěr 1.NP a 3.NP</t>
+          <t>Kročejová EPS 150 / 30 dB tl. 40 mm nad ocelobetonovým stropem 2.NP/3.NP</t>
         </is>
       </c>
       <c r="F101" s="20" t="inlineStr">
@@ -15595,7 +15559,7 @@
         </is>
       </c>
       <c r="G101" s="22" t="n">
-        <v>177.5</v>
+        <v>104.4</v>
       </c>
       <c r="H101" s="10" t="n"/>
       <c r="I101" s="10" t="n"/>
@@ -15605,7 +15569,7 @@
         </is>
       </c>
       <c r="K101" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L101" s="20" t="inlineStr">
         <is>
@@ -15614,12 +15578,12 @@
       </c>
       <c r="M101" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — EPS 150 λ=0.035 tl. 120 mm</t>
+          <t>TZ ARS dům §4 — kročejová EPS shora ocelobeton</t>
         </is>
       </c>
       <c r="N101" s="20" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O101" s="26" t="inlineStr">
@@ -15627,10 +15591,14 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P101" s="41" t="n"/>
+      <c r="P101" s="41" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
       <c r="Q101" s="41" t="inlineStr">
         <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+          <t>D2_KROCEJOVA_30_to_40_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -15640,41 +15608,41 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace TI</t>
+          <t>PSV-76 Klempíř</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>Kročejová EPS nad ocelobeton</t>
-        </is>
-      </c>
-      <c r="D102" s="27" t="inlineStr">
-        <is>
-          <t>713121??? ?</t>
+          <t>Oplechování krytiny</t>
+        </is>
+      </c>
+      <c r="D102" s="20" t="inlineStr">
+        <is>
+          <t>764312235</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>Kročejová EPS 150 / 30 dB tl. 40 mm nad ocelobetonovým stropem 2.NP/3.NP</t>
+          <t>Klempířské oplechování krytiny — úžlabí, hřeben, štítové lemy (Al / Pzn lakovaný 0.55 mm)</t>
         </is>
       </c>
       <c r="F102" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G102" s="22" t="n">
-        <v>104.4</v>
+        <v>69.5</v>
       </c>
       <c r="H102" s="10" t="n"/>
       <c r="I102" s="10" t="n"/>
       <c r="J102" s="8" t="inlineStr">
         <is>
-          <t>izolater_TI</t>
+          <t>klempir</t>
         </is>
       </c>
       <c r="K102" s="24" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="L102" s="20" t="inlineStr">
         <is>
@@ -15683,12 +15651,12 @@
       </c>
       <c r="M102" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kročejová EPS shora ocelobeton</t>
+          <t>DXF MA_klempíř (75.4 m) + SM__ klempířina (98.4 m) total = 173.8 m × 0.40 split heuristic — Path C Tier 3</t>
         </is>
       </c>
       <c r="N102" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O102" s="26" t="inlineStr">
@@ -15696,14 +15664,15 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P102" s="41" t="inlineStr">
-        <is>
-          <t>S09</t>
-        </is>
-      </c>
+      <c r="P102" s="41" t="n"/>
       <c r="Q102" s="41" t="inlineStr">
         <is>
-          <t>D2_KROCEJOVA_30_to_40_2026-06-01</t>
+          <t>URS_PHASE5B_FAMILY_VERIFIED_CHAPTER_MATCH</t>
+        </is>
+      </c>
+      <c r="R102" s="41" t="inlineStr">
+        <is>
+          <t>PSV-76 Klempíř items sum 159.9 m vs DXF MA_klempíř + SM__ klempířina total 173.8 m, Δ -8.0 % (-13.9 m). Within ±15 % tolerance per CEV Matrix D.4 verdict (gate-3). FLAG for Karel site walkthrough — possible missing klempíř segment (small). Source: outputs/cev_matrix_d_cross_doc_consistency.json D.4.</t>
         </is>
       </c>
     </row>
@@ -15718,17 +15687,17 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>Oplechování krytiny</t>
+          <t>Venkovní parapety oken</t>
         </is>
       </c>
       <c r="D103" s="20" t="inlineStr">
         <is>
-          <t>764312235</t>
+          <t>764218201</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>Klempířské oplechování krytiny — úžlabí, hřeben, štítové lemy (Al / Pzn lakovaný 0.55 mm)</t>
+          <t>Venkovní parapety oken — Pzn plech lakovaný 250 mm × tl. 0.55 mm × 16 ks oken</t>
         </is>
       </c>
       <c r="F103" s="20" t="inlineStr">
@@ -15737,7 +15706,7 @@
         </is>
       </c>
       <c r="G103" s="22" t="n">
-        <v>69.5</v>
+        <v>20.8</v>
       </c>
       <c r="H103" s="10" t="n"/>
       <c r="I103" s="10" t="n"/>
@@ -15747,7 +15716,7 @@
         </is>
       </c>
       <c r="K103" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L103" s="20" t="inlineStr">
         <is>
@@ -15756,12 +15725,12 @@
       </c>
       <c r="M103" s="8" t="inlineStr">
         <is>
-          <t>DXF MA_klempíř (75.4 m) + SM__ klempířina (98.4 m) total = 173.8 m × 0.40 split heuristic — Path C Tier 3</t>
+          <t>DXF okna 16 ks INSERT blocks + standard parapet width</t>
         </is>
       </c>
       <c r="N103" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O103" s="26" t="inlineStr">
@@ -15792,17 +15761,17 @@
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>Venkovní parapety oken</t>
+          <t>Dešťové svody + žlaby</t>
         </is>
       </c>
       <c r="D104" s="20" t="inlineStr">
         <is>
-          <t>764218201</t>
+          <t>764454802</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>Venkovní parapety oken — Pzn plech lakovaný 250 mm × tl. 0.55 mm × 16 ks oken</t>
+          <t>Dešťové svody Pzn 100 mm + žlaby — 4 svody × ~14 m + žlaby per obvod střechy</t>
         </is>
       </c>
       <c r="F104" s="20" t="inlineStr">
@@ -15811,7 +15780,7 @@
         </is>
       </c>
       <c r="G104" s="22" t="n">
-        <v>20.8</v>
+        <v>43.5</v>
       </c>
       <c r="H104" s="10" t="n"/>
       <c r="I104" s="10" t="n"/>
@@ -15821,7 +15790,7 @@
         </is>
       </c>
       <c r="K104" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L104" s="20" t="inlineStr">
         <is>
@@ -15830,7 +15799,7 @@
       </c>
       <c r="M104" s="8" t="inlineStr">
         <is>
-          <t>DXF okna 16 ks INSERT blocks + standard parapet width</t>
+          <t>DXF klempířina lengths split + TZ ARS dešťové svody</t>
         </is>
       </c>
       <c r="N104" s="20" t="inlineStr">
@@ -15866,17 +15835,17 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>Dešťové svody + žlaby</t>
+          <t>Vikýře + atika + závětrné lemy</t>
         </is>
       </c>
       <c r="D105" s="20" t="inlineStr">
         <is>
-          <t>764454802</t>
+          <t>764315235</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>Dešťové svody Pzn 100 mm + žlaby — 4 svody × ~14 m + žlaby per obvod střechy</t>
+          <t>Klempířské doplňky vikýřů + atika + závětrné lemy (4 vikýře komplexní detail)</t>
         </is>
       </c>
       <c r="F105" s="20" t="inlineStr">
@@ -15885,7 +15854,7 @@
         </is>
       </c>
       <c r="G105" s="22" t="n">
-        <v>43.5</v>
+        <v>26.1</v>
       </c>
       <c r="H105" s="10" t="n"/>
       <c r="I105" s="10" t="n"/>
@@ -15904,7 +15873,7 @@
       </c>
       <c r="M105" s="8" t="inlineStr">
         <is>
-          <t>DXF klempířina lengths split + TZ ARS dešťové svody</t>
+          <t>DXF klempířina geometry split + TZ ARS 4 vikýře</t>
         </is>
       </c>
       <c r="N105" s="20" t="inlineStr">
@@ -15935,50 +15904,50 @@
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Klempíř</t>
+          <t>PSV-76 Truhlář</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>Vikýře + atika + závětrné lemy</t>
+          <t>Dřevěné stupně schodišť</t>
         </is>
       </c>
       <c r="D106" s="20" t="inlineStr">
         <is>
-          <t>764315235</t>
+          <t>766811111</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>Klempířské doplňky vikýřů + atika + závětrné lemy (4 vikýře komplexní detail)</t>
+          <t>Dřevěné stupně ocelových schodišť (truhlářské, dub masiv tl. 40 mm)</t>
         </is>
       </c>
       <c r="F106" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G106" s="22" t="n">
-        <v>26.1</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G106" s="23" t="n">
+        <v>16</v>
       </c>
       <c r="H106" s="10" t="n"/>
       <c r="I106" s="10" t="n"/>
       <c r="J106" s="8" t="inlineStr">
         <is>
-          <t>klempir</t>
+          <t>truhlar</t>
         </is>
       </c>
       <c r="K106" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L106" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M106" s="8" t="inlineStr">
         <is>
-          <t>DXF klempířina geometry split + TZ ARS 4 vikýře</t>
+          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni truhlářské</t>
         </is>
       </c>
       <c r="N106" s="20" t="inlineStr">
@@ -15992,16 +15961,7 @@
         </is>
       </c>
       <c r="P106" s="41" t="n"/>
-      <c r="Q106" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED_CHAPTER_MATCH</t>
-        </is>
-      </c>
-      <c r="R106" s="41" t="inlineStr">
-        <is>
-          <t>PSV-76 Klempíř items sum 159.9 m vs DXF MA_klempíř + SM__ klempířina total 173.8 m, Δ -8.0 % (-13.9 m). Within ±15 % tolerance per CEV Matrix D.4 verdict (gate-3). FLAG for Karel site walkthrough — possible missing klempíř segment (small). Source: outputs/cev_matrix_d_cross_doc_consistency.json D.4.</t>
-        </is>
-      </c>
+      <c r="Q106" s="41" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="20" t="n">
@@ -16014,26 +15974,26 @@
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stupně schodišť</t>
-        </is>
-      </c>
-      <c r="D107" s="20" t="inlineStr">
-        <is>
-          <t>766811111</t>
+          <t>Terasa garapa za opěrnou stěnou — dřevěná pochozí vrstva</t>
+        </is>
+      </c>
+      <c r="D107" s="27" t="inlineStr">
+        <is>
+          <t>762??? ?</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stupně ocelových schodišť (truhlářské, dub masiv tl. 40 mm)</t>
+          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném roštu z hranolů 50 mm na rektifikovatelných terčích (terče + podkladní skladba viz HSV1.005)</t>
         </is>
       </c>
       <c r="F107" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G107" s="23" t="n">
-        <v>16</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G107" s="22" t="n">
+        <v>9.23</v>
       </c>
       <c r="H107" s="10" t="n"/>
       <c r="I107" s="10" t="n"/>
@@ -16043,16 +16003,16 @@
         </is>
       </c>
       <c r="K107" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L107" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_762_leaf_lookup_required</t>
         </is>
       </c>
       <c r="M107" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni truhlářské</t>
+          <t>TZ ARS dům §4 + DXF dum_situace PLOT_DREVENY_04 (terasa, ne 3.NP); ŘEZ C-C potvrzuje dřevěný rošt z hranolů (NE hliníkový) + dřevěnou pochozí vrstvu</t>
         </is>
       </c>
       <c r="N107" s="20" t="inlineStr">
@@ -16066,7 +16026,11 @@
         </is>
       </c>
       <c r="P107" s="41" t="n"/>
-      <c r="Q107" s="41" t="n"/>
+      <c r="Q107" s="41" t="inlineStr">
+        <is>
+          <t>REZ_CC_TERASA_FIX_2026-05-29; SITUACE_AREA_FIX_2026-05-29</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="20" t="n">
@@ -16074,55 +16038,55 @@
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Truhlář</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>Terasa garapa za opěrnou stěnou — dřevěná pochozí vrstva</t>
-        </is>
-      </c>
-      <c r="D108" s="27" t="inlineStr">
-        <is>
-          <t>762??? ?</t>
+          <t>Plastové okno trojsklo — 'okno 1.NP' (ulice)</t>
+        </is>
+      </c>
+      <c r="D108" s="20" t="inlineStr">
+        <is>
+          <t>766621011</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném roštu z hranolů 50 mm na rektifikovatelných terčích (terče + podkladní skladba viz HSV1.005)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP' velikost 1185×1600 mm × 2 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="F108" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G108" s="22" t="n">
-        <v>9.23</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G108" s="23" t="n">
+        <v>2</v>
       </c>
       <c r="H108" s="10" t="n"/>
       <c r="I108" s="10" t="n"/>
       <c r="J108" s="8" t="inlineStr">
         <is>
-          <t>truhlar</t>
+          <t>okennar</t>
         </is>
       </c>
       <c r="K108" s="24" t="n">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="L108" s="20" t="inlineStr">
         <is>
-          <t>family_762_leaf_lookup_required</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M108" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + DXF dum_situace PLOT_DREVENY_04 (terasa, ne 3.NP); ŘEZ C-C potvrzuje dřevěný rošt z hranolů (NE hliníkový) + dřevěnou pochozí vrstvu</t>
+          <t>DXF dum_DPZ INSERT block 'okno 1.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N108" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O108" s="26" t="inlineStr">
@@ -16131,11 +16095,7 @@
         </is>
       </c>
       <c r="P108" s="41" t="n"/>
-      <c r="Q108" s="41" t="inlineStr">
-        <is>
-          <t>REZ_CC_TERASA_FIX_2026-05-29; SITUACE_AREA_FIX_2026-05-29</t>
-        </is>
-      </c>
+      <c r="Q108" s="41" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="20" t="n">
@@ -16148,7 +16108,7 @@
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 1.NP' (ulice)</t>
+          <t>Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D109" s="20" t="inlineStr">
@@ -16158,7 +16118,7 @@
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP' velikost 1185×1600 mm × 2 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP vzadu' velikost 920×1600 mm × 3 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F109" s="20" t="inlineStr">
@@ -16167,7 +16127,7 @@
         </is>
       </c>
       <c r="G109" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H109" s="10" t="n"/>
       <c r="I109" s="10" t="n"/>
@@ -16181,12 +16141,12 @@
       </c>
       <c r="L109" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M109" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 1.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 1.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N109" s="20" t="inlineStr">
@@ -16213,7 +16173,7 @@
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada)</t>
+          <t>Plastové okno trojsklo — 'okno 2.NP' (ulice)</t>
         </is>
       </c>
       <c r="D110" s="20" t="inlineStr">
@@ -16223,7 +16183,7 @@
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP vzadu' velikost 920×1600 mm × 3 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 2.NP' velikost 1160×1480 mm × 4 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="F110" s="20" t="inlineStr">
@@ -16232,7 +16192,7 @@
         </is>
       </c>
       <c r="G110" s="23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H110" s="10" t="n"/>
       <c r="I110" s="10" t="n"/>
@@ -16251,7 +16211,7 @@
       </c>
       <c r="M110" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 1.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 2.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N110" s="20" t="inlineStr">
@@ -16278,7 +16238,7 @@
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 2.NP' (ulice)</t>
+          <t>Plastové okno trojsklo — 'okno 3.NP' (ulice)</t>
         </is>
       </c>
       <c r="D111" s="20" t="inlineStr">
@@ -16288,7 +16248,7 @@
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 2.NP' velikost 1160×1480 mm × 4 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP' velikost 1785×1241 mm × 3 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="F111" s="20" t="inlineStr">
@@ -16297,7 +16257,7 @@
         </is>
       </c>
       <c r="G111" s="23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H111" s="10" t="n"/>
       <c r="I111" s="10" t="n"/>
@@ -16316,7 +16276,7 @@
       </c>
       <c r="M111" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 2.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 3.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N111" s="20" t="inlineStr">
@@ -16343,7 +16303,7 @@
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 3.NP' (ulice)</t>
+          <t>Plastové okno trojsklo — 'okno 3.NP vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D112" s="20" t="inlineStr">
@@ -16353,7 +16313,7 @@
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP' velikost 1785×1241 mm × 3 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP vzadu' velikost 2075×1241 mm × 1 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F112" s="20" t="inlineStr">
@@ -16362,7 +16322,7 @@
         </is>
       </c>
       <c r="G112" s="23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H112" s="10" t="n"/>
       <c r="I112" s="10" t="n"/>
@@ -16381,7 +16341,7 @@
       </c>
       <c r="M112" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 3.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N112" s="20" t="inlineStr">
@@ -16408,7 +16368,7 @@
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 3.NP vzadu' (zahrada)</t>
+          <t>Plastové okno trojsklo — 'okno male 3.NP vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D113" s="20" t="inlineStr">
@@ -16418,7 +16378,7 @@
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP vzadu' velikost 2075×1241 mm × 1 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno male 3.NP vzadu' velikost 800×1241 mm × 1 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F113" s="20" t="inlineStr">
@@ -16446,7 +16406,7 @@
       </c>
       <c r="M113" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno male 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N113" s="20" t="inlineStr">
@@ -16473,7 +16433,7 @@
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno male 3.NP vzadu' (zahrada)</t>
+          <t>Plastové okno trojsklo — 'okno malé vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D114" s="20" t="inlineStr">
@@ -16483,7 +16443,7 @@
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno male 3.NP vzadu' velikost 800×1241 mm × 1 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno malé vzadu' velikost 700×800 mm × 2 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F114" s="20" t="inlineStr">
@@ -16492,7 +16452,7 @@
         </is>
       </c>
       <c r="G114" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H114" s="10" t="n"/>
       <c r="I114" s="10" t="n"/>
@@ -16511,7 +16471,7 @@
       </c>
       <c r="M114" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno male 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno malé vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N114" s="20" t="inlineStr">
@@ -16538,17 +16498,17 @@
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno malé vzadu' (zahrada)</t>
+          <t>Žaluzie kastlík purenit</t>
         </is>
       </c>
       <c r="D115" s="20" t="inlineStr">
         <is>
-          <t>766621011</t>
+          <t>766631211</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno malé vzadu' velikost 700×800 mm × 2 ks (fasáda zahrada)</t>
+          <t>Integrované stínící venkovní žaluzie v kastlíku pod omítkou s purenitovou izolací — uliční fasáda Fibichova (9 ks)</t>
         </is>
       </c>
       <c r="F115" s="20" t="inlineStr">
@@ -16557,17 +16517,17 @@
         </is>
       </c>
       <c r="G115" s="23" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H115" s="10" t="n"/>
       <c r="I115" s="10" t="n"/>
       <c r="J115" s="8" t="inlineStr">
         <is>
-          <t>okennar</t>
+          <t>okenni_zaluzie_kastlik_purenit</t>
         </is>
       </c>
       <c r="K115" s="24" t="n">
-        <v>0.99</v>
+        <v>0.95</v>
       </c>
       <c r="L115" s="20" t="inlineStr">
         <is>
@@ -16576,7 +16536,7 @@
       </c>
       <c r="M115" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno malé vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>TZ ARS dům §3.2 — 'do ulice Fibichova s integrovanými stínícími žaluziemi v kastlíku pod omítkou s purenitovou izolací'</t>
         </is>
       </c>
       <c r="N115" s="20" t="inlineStr">
@@ -16603,17 +16563,17 @@
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>Žaluzie kastlík purenit</t>
+          <t>Vstupní plastové dveře</t>
         </is>
       </c>
       <c r="D116" s="20" t="inlineStr">
         <is>
-          <t>766631211</t>
+          <t>766682111</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>Integrované stínící venkovní žaluzie v kastlíku pod omítkou s purenitovou izolací — uliční fasáda Fibichova (9 ks)</t>
+          <t>Plastové vstupní dveře (ulice + zahrada) — 2 ks</t>
         </is>
       </c>
       <c r="F116" s="20" t="inlineStr">
@@ -16622,17 +16582,17 @@
         </is>
       </c>
       <c r="G116" s="23" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H116" s="10" t="n"/>
       <c r="I116" s="10" t="n"/>
       <c r="J116" s="8" t="inlineStr">
         <is>
-          <t>okenni_zaluzie_kastlik_purenit</t>
+          <t>okennar</t>
         </is>
       </c>
       <c r="K116" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L116" s="20" t="inlineStr">
         <is>
@@ -16641,12 +16601,12 @@
       </c>
       <c r="M116" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — 'do ulice Fibichova s integrovanými stínícími žaluziemi v kastlíku pod omítkou s purenitovou izolací'</t>
+          <t>TZ ARS dům §4 — plastové vstupní dveře</t>
         </is>
       </c>
       <c r="N116" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O116" s="26" t="inlineStr">
@@ -16668,17 +16628,17 @@
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>Vstupní plastové dveře</t>
+          <t>Vnitřní dveře DTD laminované</t>
         </is>
       </c>
       <c r="D117" s="20" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>766660035</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>Plastové vstupní dveře (ulice + zahrada) — 2 ks</t>
+          <t>Vnitřní dveře DTD laminované s obložkovou zárubní — odhad 15 ks</t>
         </is>
       </c>
       <c r="F117" s="20" t="inlineStr">
@@ -16687,13 +16647,13 @@
         </is>
       </c>
       <c r="G117" s="23" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H117" s="10" t="n"/>
       <c r="I117" s="10" t="n"/>
       <c r="J117" s="8" t="inlineStr">
         <is>
-          <t>okennar</t>
+          <t>truhlar</t>
         </is>
       </c>
       <c r="K117" s="24" t="n">
@@ -16706,12 +16666,12 @@
       </c>
       <c r="M117" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — plastové vstupní dveře</t>
+          <t>TZ ARS dům §4 + DXF MTEXT room labels</t>
         </is>
       </c>
       <c r="N117" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O117" s="26" t="inlineStr">
@@ -16733,17 +16693,17 @@
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>Vnitřní dveře DTD laminované</t>
+          <t>Požárně odolné dveře EI 30 DP3</t>
         </is>
       </c>
       <c r="D118" s="20" t="inlineStr">
         <is>
-          <t>766660035</t>
+          <t>766694112</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>Vnitřní dveře DTD laminované s obložkovou zárubní — odhad 15 ks</t>
+          <t>Požárně odolné jednokřídlové dveře EI 30 DP3 na vrcholu schodiště mezi 1.PP a 1.NP — uzavírá otvor v REI 90 stropu klenby sklepa (per PBŘ TUSPO § 'Požární uzávěry otvorů v požárních stěnách a požárních stropech: podzemní 30 DP1')</t>
         </is>
       </c>
       <c r="F118" s="20" t="inlineStr">
@@ -16752,17 +16712,17 @@
         </is>
       </c>
       <c r="G118" s="23" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H118" s="10" t="n"/>
       <c r="I118" s="10" t="n"/>
       <c r="J118" s="8" t="inlineStr">
         <is>
-          <t>truhlar</t>
+          <t>specialista_RC3_dvere</t>
         </is>
       </c>
       <c r="K118" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L118" s="20" t="inlineStr">
         <is>
@@ -16771,12 +16731,12 @@
       </c>
       <c r="M118" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + DXF MTEXT room labels</t>
+          <t>PBŘ TUSPO § Požární uzávěry otvorů 'podzemní 30DP1'; DXF schodiště 1.PP→1.NP</t>
         </is>
       </c>
       <c r="N118" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O118" s="26" t="inlineStr">
@@ -16785,7 +16745,11 @@
         </is>
       </c>
       <c r="P118" s="41" t="n"/>
-      <c r="Q118" s="41" t="n"/>
+      <c r="Q118" s="41" t="inlineStr">
+        <is>
+          <t>GAP_008</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="20" t="n">
@@ -16798,17 +16762,17 @@
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>Požárně odolné dveře EI 30 DP3</t>
+          <t>Oplechování venkovních parapetů Pzn — 16 ks</t>
         </is>
       </c>
       <c r="D119" s="20" t="inlineStr">
         <is>
-          <t>766694112</t>
+          <t>764811112</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>Požárně odolné jednokřídlové dveře EI 30 DP3 na vrcholu schodiště mezi 1.PP a 1.NP — uzavírá otvor v REI 90 stropu klenby sklepa (per PBŘ TUSPO § 'Požární uzávěry otvorů v požárních stěnách a požárních stropech: podzemní 30 DP1')</t>
+          <t>Oplechování venkovních parapetů Pzn plech lakovaný 250 mm × tl. 0.55 mm, vč. okapnice + boční zakončení — 16 ks (per DXF INSERT okno × 16)</t>
         </is>
       </c>
       <c r="F119" s="20" t="inlineStr">
@@ -16817,17 +16781,17 @@
         </is>
       </c>
       <c r="G119" s="23" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H119" s="10" t="n"/>
       <c r="I119" s="10" t="n"/>
       <c r="J119" s="8" t="inlineStr">
         <is>
-          <t>specialista_RC3_dvere</t>
+          <t>klempir</t>
         </is>
       </c>
       <c r="K119" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L119" s="20" t="inlineStr">
         <is>
@@ -16836,7 +16800,7 @@
       </c>
       <c r="M119" s="8" t="inlineStr">
         <is>
-          <t>PBŘ TUSPO § Požární uzávěry otvorů 'podzemní 30DP1'; DXF schodiště 1.PP→1.NP</t>
+          <t>DXF blocks okno* 16 ks + DXF klempir_parapet 16 ks (Path C Tier 4 INSERT discovery)</t>
         </is>
       </c>
       <c r="N119" s="20" t="inlineStr">
@@ -16852,7 +16816,7 @@
       <c r="P119" s="41" t="n"/>
       <c r="Q119" s="41" t="inlineStr">
         <is>
-          <t>GAP_008</t>
+          <t>GAP_004</t>
         </is>
       </c>
     </row>
@@ -16862,55 +16826,55 @@
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>Oplechování venkovních parapetů Pzn — 16 ks</t>
+          <t>Ocelové schodiště UPE200 ze zahrady</t>
         </is>
       </c>
       <c r="D120" s="20" t="inlineStr">
         <is>
-          <t>764811112</t>
+          <t>767531111</t>
         </is>
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>Oplechování venkovních parapetů Pzn plech lakovaný 250 mm × tl. 0.55 mm, vč. okapnice + boční zakončení — 16 ks (per DXF INSERT okno × 16)</t>
+          <t>Ocelové schodiště ze zahrady na mezipodestu — UPE200 schodnice + dřevěné nášlapy, kotvené do koruny opěrné stěny a zdiva (TZ statika §4)</t>
         </is>
       </c>
       <c r="F120" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G120" s="23" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H120" s="10" t="n"/>
       <c r="I120" s="10" t="n"/>
       <c r="J120" s="8" t="inlineStr">
         <is>
-          <t>klempir</t>
+          <t>zamecnik_PSV</t>
         </is>
       </c>
       <c r="K120" s="24" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="L120" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M120" s="8" t="inlineStr">
         <is>
-          <t>DXF blocks okno* 16 ks + DXF klempir_parapet 16 ks (Path C Tier 4 INSERT discovery)</t>
+          <t>TZ statika dům §4 — schodiště UPE200 + UPE100 podružné prvky</t>
         </is>
       </c>
       <c r="N120" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O120" s="26" t="inlineStr">
@@ -16921,7 +16885,7 @@
       <c r="P120" s="41" t="n"/>
       <c r="Q120" s="41" t="inlineStr">
         <is>
-          <t>GAP_004</t>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
         </is>
       </c>
     </row>
@@ -16936,7 +16900,7 @@
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t>Ocelové schodiště UPE200 ze zahrady</t>
+          <t>Ocelové schodiště do spacího patra 3.NP</t>
         </is>
       </c>
       <c r="D121" s="20" t="inlineStr">
@@ -16946,7 +16910,7 @@
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>Ocelové schodiště ze zahrady na mezipodestu — UPE200 schodnice + dřevěné nášlapy, kotvené do koruny opěrné stěny a zdiva (TZ statika §4)</t>
+          <t>Interní ocelové schodiště do spacího patra v 3.NP s dřevěnými stupni (truhlářské)</t>
         </is>
       </c>
       <c r="F121" s="20" t="inlineStr">
@@ -16974,12 +16938,12 @@
       </c>
       <c r="M121" s="8" t="inlineStr">
         <is>
-          <t>TZ statika dům §4 — schodiště UPE200 + UPE100 podružné prvky</t>
+          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni</t>
         </is>
       </c>
       <c r="N121" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O121" s="26" t="inlineStr">
@@ -17005,26 +16969,26 @@
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>Ocelové schodiště do spacího patra 3.NP</t>
+          <t>Stříšky nad vstupy</t>
         </is>
       </c>
       <c r="D122" s="20" t="inlineStr">
         <is>
-          <t>767531111</t>
+          <t>767532111</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>Interní ocelové schodiště do spacího patra v 3.NP s dřevěnými stupni (truhlářské)</t>
+          <t>Stříšky nad vstupy z ocelové konstrukce + Cetris desky + falcovaná krytina — 2 ks (ulice + zahrada)</t>
         </is>
       </c>
       <c r="F122" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G122" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H122" s="10" t="n"/>
       <c r="I122" s="10" t="n"/>
@@ -17034,16 +16998,16 @@
         </is>
       </c>
       <c r="K122" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L122" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M122" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni</t>
+          <t>TZ ARS dům §4 — stříšky nad vstupy ocel+Cetris+plech</t>
         </is>
       </c>
       <c r="N122" s="20" t="inlineStr">
@@ -17057,11 +17021,7 @@
         </is>
       </c>
       <c r="P122" s="41" t="n"/>
-      <c r="Q122" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+      <c r="Q122" s="41" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="20" t="n">
@@ -17074,26 +17034,26 @@
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>Stříšky nad vstupy</t>
+          <t>Zábradlí z jeklů + nerez výplň</t>
         </is>
       </c>
       <c r="D123" s="20" t="inlineStr">
         <is>
-          <t>767532111</t>
+          <t>767163115</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>Stříšky nad vstupy z ocelové konstrukce + Cetris desky + falcovaná krytina — 2 ks (ulice + zahrada)</t>
+          <t>Ocelové zábradlí svařované z jeklů + nerez výplň pZn antracit — schodiště interier + venkovní terasa</t>
         </is>
       </c>
       <c r="F123" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G123" s="23" t="n">
-        <v>2</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G123" s="22" t="n">
+        <v>18</v>
       </c>
       <c r="H123" s="10" t="n"/>
       <c r="I123" s="10" t="n"/>
@@ -17112,7 +17072,7 @@
       </c>
       <c r="M123" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — stříšky nad vstupy ocel+Cetris+plech</t>
+          <t>TZ ARS dům §4 — zábradlí svařované z jeklů + nerez výplň</t>
         </is>
       </c>
       <c r="N123" s="20" t="inlineStr">
@@ -17134,55 +17094,55 @@
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>Zábradlí z jeklů + nerez výplň</t>
+          <t>Nášlap vinyl obytné místnosti</t>
         </is>
       </c>
       <c r="D124" s="20" t="inlineStr">
         <is>
-          <t>767163115</t>
+          <t>776511820</t>
         </is>
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>Ocelové zábradlí svařované z jeklů + nerez výplň pZn antracit — schodiště interier + venkovní terasa</t>
+          <t>Nášlapná vrstva vinyl tl. 4 mm na suchou skladbu — obytné místnosti (ložnice, obývák, kuchyně, chodby)</t>
         </is>
       </c>
       <c r="F124" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G124" s="22" t="n">
-        <v>18</v>
+        <v>171.5</v>
       </c>
       <c r="H124" s="10" t="n"/>
       <c r="I124" s="10" t="n"/>
       <c r="J124" s="8" t="inlineStr">
         <is>
-          <t>zamecnik_PSV</t>
+          <t>podlahar</t>
         </is>
       </c>
       <c r="K124" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L124" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M124" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — zábradlí svařované z jeklů + nerez výplň</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (kuchyně/obytná/chodba = vinyl) + TZ ARS §3.2.4 nášlapná vrstva</t>
         </is>
       </c>
       <c r="N124" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#4</t>
         </is>
       </c>
       <c r="O124" s="26" t="inlineStr">
@@ -17191,7 +17151,11 @@
         </is>
       </c>
       <c r="P124" s="41" t="n"/>
-      <c r="Q124" s="41" t="n"/>
+      <c r="Q124" s="41" t="inlineStr">
+        <is>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="20" t="n">
@@ -17204,17 +17168,17 @@
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t>Nášlap vinyl obytné místnosti</t>
+          <t>Nášlap keramická dlažba — mokré zóny</t>
         </is>
       </c>
       <c r="D125" s="20" t="inlineStr">
         <is>
-          <t>776511820</t>
+          <t>771274102</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva vinyl tl. 4 mm na suchou skladbu — obytné místnosti (ložnice, obývák, kuchyně, chodby)</t>
+          <t>Nášlapná vrstva keramická dlažba lepená — koupelny + WC + spíž + komora (NÁDRŽ NP)</t>
         </is>
       </c>
       <c r="F125" s="20" t="inlineStr">
@@ -17223,13 +17187,13 @@
         </is>
       </c>
       <c r="G125" s="22" t="n">
-        <v>171.5</v>
+        <v>13.5</v>
       </c>
       <c r="H125" s="10" t="n"/>
       <c r="I125" s="10" t="n"/>
       <c r="J125" s="8" t="inlineStr">
         <is>
-          <t>podlahar</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K125" s="24" t="n">
@@ -17237,12 +17201,12 @@
       </c>
       <c r="L125" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M125" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (kuchyně/obytná/chodba = vinyl) + TZ ARS §3.2.4 nášlapná vrstva</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (koupelna/WC/spíž = dlažba mokré) + TZ ARS skladba mokrá</t>
         </is>
       </c>
       <c r="N125" s="20" t="inlineStr">
@@ -17256,11 +17220,7 @@
         </is>
       </c>
       <c r="P125" s="41" t="n"/>
-      <c r="Q125" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+      <c r="Q125" s="41" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="20" t="n">
@@ -17273,7 +17233,7 @@
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>Nášlap keramická dlažba — mokré zóny</t>
+          <t>Nášlap keramická dlažba — 1.PP sklep</t>
         </is>
       </c>
       <c r="D126" s="20" t="inlineStr">
@@ -17283,7 +17243,7 @@
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva keramická dlažba lepená — koupelny + WC + spíž + komora (NÁDRŽ NP)</t>
+          <t>Nášlapná vrstva keramická dlažba — 1.PP technické místnosti (sušárna + sklepy + schodiště + chodba)</t>
         </is>
       </c>
       <c r="F126" s="20" t="inlineStr">
@@ -17292,7 +17252,7 @@
         </is>
       </c>
       <c r="G126" s="22" t="n">
-        <v>13.5</v>
+        <v>32.4</v>
       </c>
       <c r="H126" s="10" t="n"/>
       <c r="I126" s="10" t="n"/>
@@ -17311,7 +17271,7 @@
       </c>
       <c r="M126" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (koupelna/WC/spíž = dlažba mokré) + TZ ARS skladba mokrá</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — 1.PP all rooms = dlažba sklep zone</t>
         </is>
       </c>
       <c r="N126" s="20" t="inlineStr">
@@ -17338,17 +17298,17 @@
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t>Nášlap keramická dlažba — 1.PP sklep</t>
+          <t>Nášlap biodeska 3.NP spací patro</t>
         </is>
       </c>
       <c r="D127" s="20" t="inlineStr">
         <is>
-          <t>771274102</t>
+          <t>766411111</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva keramická dlažba — 1.PP technické místnosti (sušárna + sklepy + schodiště + chodba)</t>
+          <t>Nášlapná vrstva biodeska (smrk masiv) nebo OSB v 3.NP spací části nad krovem</t>
         </is>
       </c>
       <c r="F127" s="20" t="inlineStr">
@@ -17357,17 +17317,17 @@
         </is>
       </c>
       <c r="G127" s="22" t="n">
-        <v>32.4</v>
+        <v>25</v>
       </c>
       <c r="H127" s="10" t="n"/>
       <c r="I127" s="10" t="n"/>
       <c r="J127" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>biodeska_konstrukcni</t>
         </is>
       </c>
       <c r="K127" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L127" s="20" t="inlineStr">
         <is>
@@ -17376,12 +17336,12 @@
       </c>
       <c r="M127" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — 1.PP all rooms = dlažba sklep zone</t>
+          <t>TZ ARS dům §3.2.3 — biodeska patro pro přespání</t>
         </is>
       </c>
       <c r="N127" s="20" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O127" s="26" t="inlineStr">
@@ -17403,17 +17363,17 @@
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>Nášlap biodeska 3.NP spací patro</t>
+          <t>Betonový potěr s kari nad EPS</t>
         </is>
       </c>
       <c r="D128" s="20" t="inlineStr">
         <is>
-          <t>766411111</t>
+          <t>631321311</t>
         </is>
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva biodeska (smrk masiv) nebo OSB v 3.NP spací části nad krovem</t>
+          <t>Mokrá podlahová skladba — betonový potěr s kari síťkou 4/100/100 tl. 50 mm + samonivelační stěrka</t>
         </is>
       </c>
       <c r="F128" s="20" t="inlineStr">
@@ -17422,17 +17382,17 @@
         </is>
       </c>
       <c r="G128" s="22" t="n">
-        <v>25</v>
+        <v>126.4</v>
       </c>
       <c r="H128" s="10" t="n"/>
       <c r="I128" s="10" t="n"/>
       <c r="J128" s="8" t="inlineStr">
         <is>
-          <t>biodeska_konstrukcni</t>
+          <t>podlahar</t>
         </is>
       </c>
       <c r="K128" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L128" s="20" t="inlineStr">
         <is>
@@ -17441,12 +17401,12 @@
       </c>
       <c r="M128" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.3 — biodeska patro pro přespání</t>
+          <t>TZ ARS dům §3.2.4 + §3.2.x — 'kročejová izolace + betonový potěr s kari sítí'; DXF rooms areas</t>
         </is>
       </c>
       <c r="N128" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>#4</t>
         </is>
       </c>
       <c r="O128" s="26" t="inlineStr">
@@ -17468,26 +17428,26 @@
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t>Betonový potěr s kari nad EPS</t>
+          <t>Soklíky vinyl</t>
         </is>
       </c>
       <c r="D129" s="20" t="inlineStr">
         <is>
-          <t>631321311</t>
+          <t>776511831</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>Mokrá podlahová skladba — betonový potěr s kari síťkou 4/100/100 tl. 50 mm + samonivelační stěrka</t>
+          <t>Soklíky podlahové laminátové (dub) v obytných místnostech s vinyl podlahou</t>
         </is>
       </c>
       <c r="F129" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G129" s="22" t="n">
-        <v>126.4</v>
+        <v>72.03</v>
       </c>
       <c r="H129" s="10" t="n"/>
       <c r="I129" s="10" t="n"/>
@@ -17506,12 +17466,12 @@
       </c>
       <c r="M129" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.4 + §3.2.x — 'kročejová izolace + betonový potěr s kari sítí'; DXF rooms areas</t>
+          <t>DXF rooms vinyl + standard ratio per RD geometry</t>
         </is>
       </c>
       <c r="N129" s="20" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O129" s="26" t="inlineStr">
@@ -17533,17 +17493,17 @@
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>Soklíky vinyl</t>
+          <t>Soklíky keramické</t>
         </is>
       </c>
       <c r="D130" s="20" t="inlineStr">
         <is>
-          <t>776511831</t>
+          <t>771274107</t>
         </is>
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>Soklíky podlahové laminátové (dub) v obytných místnostech s vinyl podlahou</t>
+          <t>Soklíky keramické v místnostech s dlažbou (koupelny + WC + spíž + 1.PP)</t>
         </is>
       </c>
       <c r="F130" s="20" t="inlineStr">
@@ -17552,13 +17512,13 @@
         </is>
       </c>
       <c r="G130" s="22" t="n">
-        <v>72.03</v>
+        <v>19.28</v>
       </c>
       <c r="H130" s="10" t="n"/>
       <c r="I130" s="10" t="n"/>
       <c r="J130" s="8" t="inlineStr">
         <is>
-          <t>podlahar</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K130" s="24" t="n">
@@ -17571,7 +17531,7 @@
       </c>
       <c r="M130" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms vinyl + standard ratio per RD geometry</t>
+          <t>DXF rooms dlažba + standard ratio per RD geometry</t>
         </is>
       </c>
       <c r="N130" s="20" t="inlineStr">
@@ -17593,41 +17553,41 @@
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t>Soklíky keramické</t>
+          <t>Omítka jádrová + štuk 1.PP</t>
         </is>
       </c>
       <c r="D131" s="20" t="inlineStr">
         <is>
-          <t>771274107</t>
+          <t>612311311</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>Soklíky keramické v místnostech s dlažbou (koupelny + WC + spíž + 1.PP)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.PP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F131" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G131" s="22" t="n">
-        <v>19.28</v>
+        <v>78.2</v>
       </c>
       <c r="H131" s="10" t="n"/>
       <c r="I131" s="10" t="n"/>
       <c r="J131" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K131" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L131" s="20" t="inlineStr">
         <is>
@@ -17636,12 +17596,12 @@
       </c>
       <c r="M131" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms dlažba + standard ratio per RD geometry</t>
+          <t>DXF rooms 1.PP obvod + výška podlaží 2.1 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N131" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O131" s="26" t="inlineStr">
@@ -17663,7 +17623,7 @@
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 1.PP</t>
+          <t>Omítka jádrová + štuk 1.NP</t>
         </is>
       </c>
       <c r="D132" s="20" t="inlineStr">
@@ -17673,7 +17633,7 @@
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.PP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F132" s="20" t="inlineStr">
@@ -17682,7 +17642,7 @@
         </is>
       </c>
       <c r="G132" s="22" t="n">
-        <v>78.2</v>
+        <v>208.4</v>
       </c>
       <c r="H132" s="10" t="n"/>
       <c r="I132" s="10" t="n"/>
@@ -17701,7 +17661,7 @@
       </c>
       <c r="M132" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 1.PP obvod + výška podlaží 2.1 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 1.NP obvod + výška podlaží 2.795 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N132" s="20" t="inlineStr">
@@ -17728,7 +17688,7 @@
       </c>
       <c r="C133" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 1.NP</t>
+          <t>Omítka jádrová + štuk 2.NP</t>
         </is>
       </c>
       <c r="D133" s="20" t="inlineStr">
@@ -17738,7 +17698,7 @@
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.NP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 2.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F133" s="20" t="inlineStr">
@@ -17747,7 +17707,7 @@
         </is>
       </c>
       <c r="G133" s="22" t="n">
-        <v>208.4</v>
+        <v>201.6</v>
       </c>
       <c r="H133" s="10" t="n"/>
       <c r="I133" s="10" t="n"/>
@@ -17766,7 +17726,7 @@
       </c>
       <c r="M133" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 1.NP obvod + výška podlaží 2.795 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 2.NP obvod + výška podlaží 2.865 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N133" s="20" t="inlineStr">
@@ -17793,7 +17753,7 @@
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 2.NP</t>
+          <t>Omítka jádrová + štuk 3.NP</t>
         </is>
       </c>
       <c r="D134" s="20" t="inlineStr">
@@ -17803,7 +17763,7 @@
       </c>
       <c r="E134" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 2.NP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 3.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F134" s="20" t="inlineStr">
@@ -17812,7 +17772,7 @@
         </is>
       </c>
       <c r="G134" s="22" t="n">
-        <v>201.6</v>
+        <v>179.1</v>
       </c>
       <c r="H134" s="10" t="n"/>
       <c r="I134" s="10" t="n"/>
@@ -17831,7 +17791,7 @@
       </c>
       <c r="M134" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 2.NP obvod + výška podlaží 2.865 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 3.NP obvod + výška podlaží 2.63 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N134" s="20" t="inlineStr">
@@ -17858,17 +17818,17 @@
       </c>
       <c r="C135" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 3.NP</t>
+          <t>SDK podhled — tmelení + úprava 1.NP</t>
         </is>
       </c>
       <c r="D135" s="20" t="inlineStr">
         <is>
-          <t>612311311</t>
+          <t>612471141</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 3.NP (stávající vyspravené + nové zděné)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (1.NP)</t>
         </is>
       </c>
       <c r="F135" s="20" t="inlineStr">
@@ -17877,17 +17837,17 @@
         </is>
       </c>
       <c r="G135" s="22" t="n">
-        <v>179.1</v>
+        <v>59.5</v>
       </c>
       <c r="H135" s="10" t="n"/>
       <c r="I135" s="10" t="n"/>
       <c r="J135" s="8" t="inlineStr">
         <is>
-          <t>zednik</t>
+          <t>sadrokartonar</t>
         </is>
       </c>
       <c r="K135" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L135" s="20" t="inlineStr">
         <is>
@@ -17896,12 +17856,12 @@
       </c>
       <c r="M135" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 3.NP obvod + výška podlaží 2.63 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 1.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="N135" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O135" s="26" t="inlineStr">
@@ -17923,7 +17883,7 @@
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled — tmelení + úprava 1.NP</t>
+          <t>SDK podhled — tmelení + úprava 2.NP</t>
         </is>
       </c>
       <c r="D136" s="20" t="inlineStr">
@@ -17933,7 +17893,7 @@
       </c>
       <c r="E136" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (1.NP)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (2.NP)</t>
         </is>
       </c>
       <c r="F136" s="20" t="inlineStr">
@@ -17942,7 +17902,7 @@
         </is>
       </c>
       <c r="G136" s="22" t="n">
-        <v>59.5</v>
+        <v>61.1</v>
       </c>
       <c r="H136" s="10" t="n"/>
       <c r="I136" s="10" t="n"/>
@@ -17961,7 +17921,7 @@
       </c>
       <c r="M136" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 1.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 2.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="N136" s="20" t="inlineStr">
@@ -17988,7 +17948,7 @@
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled — tmelení + úprava 2.NP</t>
+          <t>SDK podhled — tmelení + úprava 3.NP</t>
         </is>
       </c>
       <c r="D137" s="20" t="inlineStr">
@@ -17998,7 +17958,7 @@
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (2.NP)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (3.NP)</t>
         </is>
       </c>
       <c r="F137" s="20" t="inlineStr">
@@ -18007,7 +17967,7 @@
         </is>
       </c>
       <c r="G137" s="22" t="n">
-        <v>61.1</v>
+        <v>64.5</v>
       </c>
       <c r="H137" s="10" t="n"/>
       <c r="I137" s="10" t="n"/>
@@ -18026,7 +17986,7 @@
       </c>
       <c r="M137" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 2.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 3.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="N137" s="20" t="inlineStr">
@@ -18053,17 +18013,17 @@
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled — tmelení + úprava 3.NP</t>
+          <t>Keramický obklad koupelna 1.05 (1.NP)</t>
         </is>
       </c>
       <c r="D138" s="20" t="inlineStr">
         <is>
-          <t>612471141</t>
+          <t>781447001</t>
         </is>
       </c>
       <c r="E138" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (3.NP)</t>
+          <t>Keramický obklad stěn koupelny 1.05 1.NP — výška obkladu 1.6 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="F138" s="20" t="inlineStr">
@@ -18072,17 +18032,17 @@
         </is>
       </c>
       <c r="G138" s="22" t="n">
-        <v>64.5</v>
+        <v>13.4</v>
       </c>
       <c r="H138" s="10" t="n"/>
       <c r="I138" s="10" t="n"/>
       <c r="J138" s="8" t="inlineStr">
         <is>
-          <t>sadrokartonar</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K138" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L138" s="20" t="inlineStr">
         <is>
@@ -18091,7 +18051,7 @@
       </c>
       <c r="M138" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 3.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF rooms PIP perimeter 1.05 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="N138" s="20" t="inlineStr">
@@ -18118,7 +18078,7 @@
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad koupelna 1.05 (1.NP)</t>
+          <t>Keramický obklad koupelna 2.03 (2.NP)</t>
         </is>
       </c>
       <c r="D139" s="20" t="inlineStr">
@@ -18128,7 +18088,7 @@
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 1.05 1.NP — výška obkladu 1.6 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad stěn koupelny 2.03 2.NP — výška obkladu 2.45 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="F139" s="20" t="inlineStr">
@@ -18137,7 +18097,7 @@
         </is>
       </c>
       <c r="G139" s="22" t="n">
-        <v>13.4</v>
+        <v>15.2</v>
       </c>
       <c r="H139" s="10" t="n"/>
       <c r="I139" s="10" t="n"/>
@@ -18156,7 +18116,7 @@
       </c>
       <c r="M139" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 1.05 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF rooms PIP perimeter 2.03 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="N139" s="20" t="inlineStr">
@@ -18183,7 +18143,7 @@
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad koupelna 2.03 (2.NP)</t>
+          <t>Keramický obklad koupelna 3.04 (3.NP)</t>
         </is>
       </c>
       <c r="D140" s="20" t="inlineStr">
@@ -18193,7 +18153,7 @@
       </c>
       <c r="E140" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 2.03 2.NP — výška obkladu 2.45 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad stěn koupelny 3.04 3.NP — výška obkladu 2.7 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="F140" s="20" t="inlineStr">
@@ -18202,7 +18162,7 @@
         </is>
       </c>
       <c r="G140" s="22" t="n">
-        <v>15.2</v>
+        <v>24.3</v>
       </c>
       <c r="H140" s="10" t="n"/>
       <c r="I140" s="10" t="n"/>
@@ -18221,7 +18181,7 @@
       </c>
       <c r="M140" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 2.03 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF rooms PIP perimeter 3.04 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="N140" s="20" t="inlineStr">
@@ -18248,7 +18208,7 @@
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad koupelna 3.04 (3.NP)</t>
+          <t>Obklad za kuchyňskou linkou</t>
         </is>
       </c>
       <c r="D141" s="20" t="inlineStr">
@@ -18258,7 +18218,7 @@
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 3.04 3.NP — výška obkladu 2.7 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad za kuchyňskou linkou nad pracovní deskou — 2 kuchyně × ~5 m² (1.06 byt rodičů + 3.05 byt 3.NP)</t>
         </is>
       </c>
       <c r="F141" s="20" t="inlineStr">
@@ -18267,7 +18227,7 @@
         </is>
       </c>
       <c r="G141" s="22" t="n">
-        <v>24.3</v>
+        <v>10</v>
       </c>
       <c r="H141" s="10" t="n"/>
       <c r="I141" s="10" t="n"/>
@@ -18277,7 +18237,7 @@
         </is>
       </c>
       <c r="K141" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L141" s="20" t="inlineStr">
         <is>
@@ -18286,7 +18246,7 @@
       </c>
       <c r="M141" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 3.04 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF dum_DPZ 2× kuchyně MTEXT + TZ ARS</t>
         </is>
       </c>
       <c r="N141" s="20" t="inlineStr">
@@ -18313,17 +18273,17 @@
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>Obklad za kuchyňskou linkou</t>
+          <t>Interiérová výmalba</t>
         </is>
       </c>
       <c r="D142" s="20" t="inlineStr">
         <is>
-          <t>781447001</t>
+          <t>784121011</t>
         </is>
       </c>
       <c r="E142" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad za kuchyňskou linkou nad pracovní deskou — 2 kuchyně × ~5 m² (1.06 byt rodičů + 3.05 byt 3.NP)</t>
+          <t>Interiérová výmalba akrylátová bílá 2× — všechny stěny + podhledy mimo obklad</t>
         </is>
       </c>
       <c r="F142" s="20" t="inlineStr">
@@ -18332,17 +18292,17 @@
         </is>
       </c>
       <c r="G142" s="22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H142" s="10" t="n"/>
       <c r="I142" s="10" t="n"/>
       <c r="J142" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>malir</t>
         </is>
       </c>
       <c r="K142" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L142" s="20" t="inlineStr">
         <is>
@@ -18351,7 +18311,7 @@
       </c>
       <c r="M142" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ 2× kuchyně MTEXT + TZ ARS</t>
+          <t>TZ ARS — interiérová výmalba (aggregate, no TZ per-room directive)</t>
         </is>
       </c>
       <c r="N142" s="20" t="inlineStr">
@@ -18365,7 +18325,11 @@
         </is>
       </c>
       <c r="P142" s="41" t="n"/>
-      <c r="Q142" s="41" t="n"/>
+      <c r="Q142" s="41" t="inlineStr">
+        <is>
+          <t>GAP_007_deprecated</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="20" t="n">
@@ -18378,7 +18342,7 @@
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba</t>
+          <t>Interiérová výmalba 1.NP</t>
         </is>
       </c>
       <c r="D143" s="20" t="inlineStr">
@@ -18388,7 +18352,7 @@
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba akrylátová bílá 2× — všechny stěny + podhledy mimo obklad</t>
+          <t>Interiérová výmalba 1.NP — stěny + SDK podhled − obklad koupelny 1.05 (1.6 m výška)</t>
         </is>
       </c>
       <c r="F143" s="20" t="inlineStr">
@@ -18397,7 +18361,7 @@
         </is>
       </c>
       <c r="G143" s="22" t="n">
-        <v>0</v>
+        <v>254.5</v>
       </c>
       <c r="H143" s="10" t="n"/>
       <c r="I143" s="10" t="n"/>
@@ -18407,7 +18371,7 @@
         </is>
       </c>
       <c r="K143" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L143" s="20" t="inlineStr">
         <is>
@@ -18416,7 +18380,7 @@
       </c>
       <c r="M143" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS — interiérová výmalba (aggregate, no TZ per-room directive)</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.002 + SDK podhled PSV78.005</t>
         </is>
       </c>
       <c r="N143" s="20" t="inlineStr">
@@ -18432,7 +18396,7 @@
       <c r="P143" s="41" t="n"/>
       <c r="Q143" s="41" t="inlineStr">
         <is>
-          <t>GAP_007_deprecated</t>
+          <t>GAP_007</t>
         </is>
       </c>
     </row>
@@ -18447,7 +18411,7 @@
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.NP</t>
+          <t>Interiérová výmalba 1.PP</t>
         </is>
       </c>
       <c r="D144" s="20" t="inlineStr">
@@ -18457,7 +18421,7 @@
       </c>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.NP — stěny + SDK podhled − obklad koupelny 1.05 (1.6 m výška)</t>
+          <t>Interiérová výmalba 1.PP — sklep stěny + klenba bílá vápenná 2×</t>
         </is>
       </c>
       <c r="F144" s="20" t="inlineStr">
@@ -18466,7 +18430,7 @@
         </is>
       </c>
       <c r="G144" s="22" t="n">
-        <v>254.5</v>
+        <v>78.2</v>
       </c>
       <c r="H144" s="10" t="n"/>
       <c r="I144" s="10" t="n"/>
@@ -18485,7 +18449,7 @@
       </c>
       <c r="M144" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.002 + SDK podhled PSV78.005</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.001 + SDK podhled PSV78.—</t>
         </is>
       </c>
       <c r="N144" s="20" t="inlineStr">
@@ -18516,7 +18480,7 @@
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.PP</t>
+          <t>Interiérová výmalba 2.NP</t>
         </is>
       </c>
       <c r="D145" s="20" t="inlineStr">
@@ -18526,7 +18490,7 @@
       </c>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.PP — sklep stěny + klenba bílá vápenná 2×</t>
+          <t>Interiérová výmalba 2.NP — stěny + SDK podhled − obklad koupelny 2.03 (2.45 m výška)</t>
         </is>
       </c>
       <c r="F145" s="20" t="inlineStr">
@@ -18535,7 +18499,7 @@
         </is>
       </c>
       <c r="G145" s="22" t="n">
-        <v>78.2</v>
+        <v>247.5</v>
       </c>
       <c r="H145" s="10" t="n"/>
       <c r="I145" s="10" t="n"/>
@@ -18554,7 +18518,7 @@
       </c>
       <c r="M145" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.001 + SDK podhled PSV78.—</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.003 + SDK podhled PSV78.006</t>
         </is>
       </c>
       <c r="N145" s="20" t="inlineStr">
@@ -18585,7 +18549,7 @@
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 2.NP</t>
+          <t>Interiérová výmalba 3.NP</t>
         </is>
       </c>
       <c r="D146" s="20" t="inlineStr">
@@ -18595,7 +18559,7 @@
       </c>
       <c r="E146" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 2.NP — stěny + SDK podhled − obklad koupelny 2.03 (2.45 m výška)</t>
+          <t>Interiérová výmalba 3.NP — stěny + SDK podhled − obklad koupelny 3.04 (2.7 m výška)</t>
         </is>
       </c>
       <c r="F146" s="20" t="inlineStr">
@@ -18604,7 +18568,7 @@
         </is>
       </c>
       <c r="G146" s="22" t="n">
-        <v>247.5</v>
+        <v>219.3</v>
       </c>
       <c r="H146" s="10" t="n"/>
       <c r="I146" s="10" t="n"/>
@@ -18623,7 +18587,7 @@
       </c>
       <c r="M146" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.003 + SDK podhled PSV78.006</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.004 + SDK podhled PSV78.007</t>
         </is>
       </c>
       <c r="N146" s="20" t="inlineStr">
@@ -18649,37 +18613,37 @@
       </c>
       <c r="B147" s="8" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-95 Detekce požární</t>
         </is>
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 3.NP</t>
+          <t>Autonomní hlásič kouře</t>
         </is>
       </c>
       <c r="D147" s="20" t="inlineStr">
         <is>
-          <t>784121011</t>
+          <t>375211101</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 3.NP — stěny + SDK podhled − obklad koupelny 3.04 (2.7 m výška)</t>
+          <t>Autonomní hlásič kouře dle ČSN EN 14604 — 4 ks v místnostech 1.01, 1.02, 2.04, 3.03 dle PBŘ</t>
         </is>
       </c>
       <c r="F147" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G147" s="22" t="n">
-        <v>219.3</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G147" s="23" t="n">
+        <v>4</v>
       </c>
       <c r="H147" s="10" t="n"/>
       <c r="I147" s="10" t="n"/>
       <c r="J147" s="8" t="inlineStr">
         <is>
-          <t>malir</t>
+          <t>elektroinstalater</t>
         </is>
       </c>
       <c r="K147" s="24" t="n">
@@ -18687,12 +18651,12 @@
       </c>
       <c r="L147" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M147" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.004 + SDK podhled PSV78.007</t>
+          <t>TZ PBŘ dům — ČSN EN 14604 autonomní hlásič kouře 4 ks</t>
         </is>
       </c>
       <c r="N147" s="20" t="inlineStr">
@@ -18708,7 +18672,7 @@
       <c r="P147" s="41" t="n"/>
       <c r="Q147" s="41" t="inlineStr">
         <is>
-          <t>GAP_007</t>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
         </is>
       </c>
     </row>
@@ -18723,17 +18687,17 @@
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>Autonomní hlásič kouře</t>
+          <t>Přenosný hasicí přístroj 34A</t>
         </is>
       </c>
       <c r="D148" s="20" t="inlineStr">
         <is>
-          <t>375211101</t>
+          <t>966067121</t>
         </is>
       </c>
       <c r="E148" s="8" t="inlineStr">
         <is>
-          <t>Autonomní hlásič kouře dle ČSN EN 14604 — 4 ks v místnostech 1.01, 1.02, 2.04, 3.03 dle PBŘ</t>
+          <t>Přenosný hasicí přístroj 34A dle PBŘ — min. 1 ks na společné chodbě</t>
         </is>
       </c>
       <c r="F148" s="20" t="inlineStr">
@@ -18742,13 +18706,13 @@
         </is>
       </c>
       <c r="G148" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H148" s="10" t="n"/>
       <c r="I148" s="10" t="n"/>
       <c r="J148" s="8" t="inlineStr">
         <is>
-          <t>elektroinstalater</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K148" s="24" t="n">
@@ -18756,12 +18720,12 @@
       </c>
       <c r="L148" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M148" s="8" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — ČSN EN 14604 autonomní hlásič kouře 4 ks</t>
+          <t>TZ PBŘ dům — PHP 34A 1 ks minimum</t>
         </is>
       </c>
       <c r="N148" s="20" t="inlineStr">
@@ -18775,11 +18739,7 @@
         </is>
       </c>
       <c r="P148" s="41" t="n"/>
-      <c r="Q148" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+      <c r="Q148" s="41" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="20" t="n">
@@ -18792,22 +18752,22 @@
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t>Přenosný hasicí přístroj 34A</t>
+          <t>Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
         </is>
       </c>
       <c r="D149" s="20" t="inlineStr">
         <is>
-          <t>966067121</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>Přenosný hasicí přístroj 34A dle PBŘ — min. 1 ks na společné chodbě</t>
+          <t>Předávací protokol krbu na tuhá paliva + kontrola bezpečných vzdáleností (800 mm směr sálání / 400 mm strany, nehořlavá zóna podlahy) dle PBŘ</t>
         </is>
       </c>
       <c r="F149" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>soubor</t>
         </is>
       </c>
       <c r="G149" s="23" t="n">
@@ -18817,11 +18777,11 @@
       <c r="I149" s="10" t="n"/>
       <c r="J149" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K149" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L149" s="20" t="inlineStr">
         <is>
@@ -18830,7 +18790,7 @@
       </c>
       <c r="M149" s="8" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — PHP 34A 1 ks minimum</t>
+          <t>PBŘ D.3</t>
         </is>
       </c>
       <c r="N149" s="20" t="inlineStr">
@@ -18843,8 +18803,12 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P149" s="41" t="n"/>
-      <c r="Q149" s="41" t="n"/>
+      <c r="P149" s="41" t="inlineStr"/>
+      <c r="Q149" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="20" t="n">
@@ -18852,27 +18816,27 @@
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
-          <t>PSV-95 Detekce požární</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+          <t>Demontáž stávající ELI</t>
         </is>
       </c>
       <c r="D150" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>210010011</t>
         </is>
       </c>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokol krbu na tuhá paliva + kontrola bezpečných vzdáleností (800 mm směr sálání / 400 mm strany, nehořlavá zóna podlahy) dle PBŘ</t>
+          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
         </is>
       </c>
       <c r="F150" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G150" s="23" t="n">
@@ -18882,11 +18846,11 @@
       <c r="I150" s="10" t="n"/>
       <c r="J150" s="8" t="inlineStr">
         <is>
-          <t>topenar</t>
+          <t>elektroinstalater</t>
         </is>
       </c>
       <c r="K150" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L150" s="20" t="inlineStr">
         <is>
@@ -18895,12 +18859,12 @@
       </c>
       <c r="M150" s="8" t="inlineStr">
         <is>
-          <t>PBŘ D.3</t>
+          <t>TZ ARS dům §4 — kompletně nová ELI</t>
         </is>
       </c>
       <c r="N150" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#7</t>
         </is>
       </c>
       <c r="O150" s="26" t="inlineStr">
@@ -18908,12 +18872,8 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P150" s="41" t="inlineStr"/>
-      <c r="Q150" s="41" t="inlineStr">
-        <is>
-          <t>DODATEK_PBR_GAPS_2026-06-01</t>
-        </is>
-      </c>
+      <c r="P150" s="41" t="n"/>
+      <c r="Q150" s="41" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="20" t="n">
@@ -18926,26 +18886,26 @@
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávající ELI</t>
+          <t>Pojistková skříň + 3× podružný rozvaděč</t>
         </is>
       </c>
       <c r="D151" s="20" t="inlineStr">
         <is>
-          <t>210010011</t>
+          <t>210110023</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
+          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
         </is>
       </c>
       <c r="F151" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G151" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H151" s="10" t="n"/>
       <c r="I151" s="10" t="n"/>
@@ -18964,7 +18924,7 @@
       </c>
       <c r="M151" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kompletně nová ELI</t>
+          <t>TZ ARS dům §4 — 'nová pojistková skříň s podružným měřením pro každé patro'</t>
         </is>
       </c>
       <c r="N151" s="20" t="inlineStr">
@@ -18991,26 +18951,26 @@
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>Pojistková skříň + 3× podružný rozvaděč</t>
+          <t>Rozvody silnoproud</t>
         </is>
       </c>
       <c r="D152" s="20" t="inlineStr">
         <is>
-          <t>210110023</t>
+          <t>210800012</t>
         </is>
       </c>
       <c r="E152" s="8" t="inlineStr">
         <is>
-          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
+          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
         </is>
       </c>
       <c r="F152" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G152" s="23" t="n">
-        <v>4</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G152" s="22" t="n">
+        <v>700</v>
       </c>
       <c r="H152" s="10" t="n"/>
       <c r="I152" s="10" t="n"/>
@@ -19020,7 +18980,7 @@
         </is>
       </c>
       <c r="K152" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L152" s="20" t="inlineStr">
         <is>
@@ -19029,7 +18989,7 @@
       </c>
       <c r="M152" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — 'nová pojistková skříň s podružným měřením pro každé patro'</t>
+          <t>TZ ARS + B4_productivity standard RD 3-byt. dispozice</t>
         </is>
       </c>
       <c r="N152" s="20" t="inlineStr">
@@ -19056,26 +19016,26 @@
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t>Rozvody silnoproud</t>
+          <t>Zásuvky a vypínače</t>
         </is>
       </c>
       <c r="D153" s="20" t="inlineStr">
         <is>
-          <t>210800012</t>
+          <t>210810050</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
+          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
         </is>
       </c>
       <c r="F153" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G153" s="22" t="n">
-        <v>700</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G153" s="23" t="n">
+        <v>70</v>
       </c>
       <c r="H153" s="10" t="n"/>
       <c r="I153" s="10" t="n"/>
@@ -19094,7 +19054,7 @@
       </c>
       <c r="M153" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD 3-byt. dispozice</t>
+          <t>TZ ARS + B4_productivity standard RD 220 m² 3-byt.</t>
         </is>
       </c>
       <c r="N153" s="20" t="inlineStr">
@@ -19121,17 +19081,17 @@
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>Zásuvky a vypínače</t>
+          <t>Svítidla</t>
         </is>
       </c>
       <c r="D154" s="20" t="inlineStr">
         <is>
-          <t>210810050</t>
+          <t>210820002</t>
         </is>
       </c>
       <c r="E154" s="8" t="inlineStr">
         <is>
-          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
+          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
         </is>
       </c>
       <c r="F154" s="20" t="inlineStr">
@@ -19140,7 +19100,7 @@
         </is>
       </c>
       <c r="G154" s="23" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="H154" s="10" t="n"/>
       <c r="I154" s="10" t="n"/>
@@ -19159,7 +19119,7 @@
       </c>
       <c r="M154" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD 220 m² 3-byt.</t>
+          <t>TZ ARS + B4_productivity standard RD</t>
         </is>
       </c>
       <c r="N154" s="20" t="inlineStr">
@@ -19186,26 +19146,26 @@
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t>Svítidla</t>
+          <t>Příprava FVE</t>
         </is>
       </c>
       <c r="D155" s="20" t="inlineStr">
         <is>
-          <t>210820002</t>
+          <t>210800099</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
+          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
         </is>
       </c>
       <c r="F155" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G155" s="23" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="H155" s="10" t="n"/>
       <c r="I155" s="10" t="n"/>
@@ -19215,7 +19175,7 @@
         </is>
       </c>
       <c r="K155" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L155" s="20" t="inlineStr">
         <is>
@@ -19224,7 +19184,7 @@
       </c>
       <c r="M155" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD</t>
+          <t>TZ ARS dům §4 — FVE příprava (bez panelů samotných)</t>
         </is>
       </c>
       <c r="N155" s="20" t="inlineStr">
@@ -19251,17 +19211,17 @@
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>Příprava FVE</t>
+          <t>Revize ELI při kolaudaci</t>
         </is>
       </c>
       <c r="D156" s="20" t="inlineStr">
         <is>
-          <t>210800099</t>
+          <t>996019011</t>
         </is>
       </c>
       <c r="E156" s="8" t="inlineStr">
         <is>
-          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
+          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
         </is>
       </c>
       <c r="F156" s="20" t="inlineStr">
@@ -19276,11 +19236,11 @@
       <c r="I156" s="10" t="n"/>
       <c r="J156" s="8" t="inlineStr">
         <is>
-          <t>elektroinstalater</t>
+          <t>revize_specialista</t>
         </is>
       </c>
       <c r="K156" s="24" t="n">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
       <c r="L156" s="20" t="inlineStr">
         <is>
@@ -19289,12 +19249,12 @@
       </c>
       <c r="M156" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — FVE příprava (bez panelů samotných)</t>
+          <t>Povinná revize ELI dle ČSN 33 2000-6 + kolaudace</t>
         </is>
       </c>
       <c r="N156" s="20" t="inlineStr">
         <is>
-          <t>#7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O156" s="26" t="inlineStr">
@@ -19311,22 +19271,22 @@
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t>Revize ELI při kolaudaci</t>
+          <t>Revize stávajících přípojek</t>
         </is>
       </c>
       <c r="D157" s="20" t="inlineStr">
         <is>
-          <t>996019011</t>
+          <t>722290515</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
+          <t>Revize stávajícího napojení vodovodu + kanalizace na pozemku — kontrola stavu, čištění, tlaková zkouška</t>
         </is>
       </c>
       <c r="F157" s="20" t="inlineStr">
@@ -19341,25 +19301,25 @@
       <c r="I157" s="10" t="n"/>
       <c r="J157" s="8" t="inlineStr">
         <is>
-          <t>revize_specialista</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K157" s="24" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="L157" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M157" s="8" t="inlineStr">
         <is>
-          <t>Povinná revize ELI dle ČSN 33 2000-6 + kolaudace</t>
+          <t>TZ ARS dům §4 — vodovod + kanalizace stávající, bez změny</t>
         </is>
       </c>
       <c r="N157" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O157" s="26" t="inlineStr">
@@ -19368,7 +19328,11 @@
         </is>
       </c>
       <c r="P157" s="41" t="n"/>
-      <c r="Q157" s="41" t="n"/>
+      <c r="Q157" s="41" t="inlineStr">
+        <is>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="20" t="n">
@@ -19381,26 +19345,26 @@
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajících přípojek</t>
+          <t>Nové rozvody vody do 3.NP</t>
         </is>
       </c>
       <c r="D158" s="20" t="inlineStr">
         <is>
-          <t>722290515</t>
+          <t>722172011</t>
         </is>
       </c>
       <c r="E158" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajícího napojení vodovodu + kanalizace na pozemku — kontrola stavu, čištění, tlaková zkouška</t>
+          <t>Nové rozvody studené + teplé vody do koupelen 1.NP + 2.NP + 3.NP a kuchyní (PEX/Cu, dimenze DN15-25)</t>
         </is>
       </c>
       <c r="F158" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G158" s="23" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G158" s="22" t="n">
+        <v>80</v>
       </c>
       <c r="H158" s="10" t="n"/>
       <c r="I158" s="10" t="n"/>
@@ -19410,7 +19374,7 @@
         </is>
       </c>
       <c r="K158" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L158" s="20" t="inlineStr">
         <is>
@@ -19419,7 +19383,7 @@
       </c>
       <c r="M158" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — vodovod + kanalizace stávající, bez změny</t>
+          <t>TZ ARS dům §4 — nové koupelny + kuchyně, vyjasnění #6 working assumption</t>
         </is>
       </c>
       <c r="N158" s="20" t="inlineStr">
@@ -19450,17 +19414,17 @@
       </c>
       <c r="C159" s="8" t="inlineStr">
         <is>
-          <t>Nové rozvody vody do 3.NP</t>
+          <t>Nové odpadní rozvody</t>
         </is>
       </c>
       <c r="D159" s="20" t="inlineStr">
         <is>
-          <t>722172011</t>
+          <t>721174021</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>Nové rozvody studené + teplé vody do koupelen 1.NP + 2.NP + 3.NP a kuchyní (PEX/Cu, dimenze DN15-25)</t>
+          <t>Nové odpadní rozvody PVC-HT DN40-DN110 ke koupelnám 1.NP, 2.NP, 3.NP a kuchyním + napojení na stávající</t>
         </is>
       </c>
       <c r="F159" s="20" t="inlineStr">
@@ -19469,7 +19433,7 @@
         </is>
       </c>
       <c r="G159" s="22" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H159" s="10" t="n"/>
       <c r="I159" s="10" t="n"/>
@@ -19483,12 +19447,12 @@
       </c>
       <c r="L159" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — nové koupelny + kuchyně, vyjasnění #6 working assumption</t>
+          <t>TZ ARS dům §4 — nové koupelny + kuchyně, odpad do stávající kanalizace</t>
         </is>
       </c>
       <c r="N159" s="20" t="inlineStr">
@@ -19502,11 +19466,7 @@
         </is>
       </c>
       <c r="P159" s="41" t="n"/>
-      <c r="Q159" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+      <c r="Q159" s="41" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="20" t="n">
@@ -19519,26 +19479,26 @@
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>Nové odpadní rozvody</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP)</t>
         </is>
       </c>
       <c r="D160" s="20" t="inlineStr">
         <is>
-          <t>721174021</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E160" s="8" t="inlineStr">
         <is>
-          <t>Nové odpadní rozvody PVC-HT DN40-DN110 ke koupelnám 1.NP, 2.NP, 3.NP a kuchyním + napojení na stávající</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
         </is>
       </c>
       <c r="F160" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>set</t>
         </is>
       </c>
       <c r="G160" s="22" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H160" s="10" t="n"/>
       <c r="I160" s="10" t="n"/>
@@ -19557,7 +19517,7 @@
       </c>
       <c r="M160" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — nové koupelny + kuchyně, odpad do stávající kanalizace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 1.05 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N160" s="20" t="inlineStr">
@@ -19571,7 +19531,11 @@
         </is>
       </c>
       <c r="P160" s="41" t="n"/>
-      <c r="Q160" s="41" t="n"/>
+      <c r="Q160" s="41" t="inlineStr">
+        <is>
+          <t>GAP_005_deprecated</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="20" t="n">
@@ -19584,26 +19548,26 @@
       </c>
       <c r="C161" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP)</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture A</t>
         </is>
       </c>
       <c r="D161" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>725211101</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
+          <t>Vana koupelnová obdélníková 170×70 cm — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F161" s="20" t="inlineStr">
         <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="G161" s="22" t="n">
-        <v>0</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G161" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H161" s="10" t="n"/>
       <c r="I161" s="10" t="n"/>
@@ -19613,7 +19577,7 @@
         </is>
       </c>
       <c r="K161" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L161" s="20" t="inlineStr">
         <is>
@@ -19622,12 +19586,12 @@
       </c>
       <c r="M161" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 1.05 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ MTEXT room 1.05 1.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N161" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O161" s="26" t="inlineStr">
@@ -19638,7 +19602,7 @@
       <c r="P161" s="41" t="n"/>
       <c r="Q161" s="41" t="inlineStr">
         <is>
-          <t>GAP_005_deprecated</t>
+          <t>GAP_005</t>
         </is>
       </c>
     </row>
@@ -19653,17 +19617,17 @@
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture B</t>
         </is>
       </c>
       <c r="D162" s="20" t="inlineStr">
         <is>
-          <t>725211101</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E162" s="8" t="inlineStr">
         <is>
-          <t>Vana koupelnová obdélníková 170×70 cm — koupelna 1.05 1.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F162" s="20" t="inlineStr">
@@ -19722,17 +19686,17 @@
       </c>
       <c r="C163" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture C</t>
         </is>
       </c>
       <c r="D163" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 1.05 1.NP</t>
+          <t>WC kombi keramické bílé — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F163" s="20" t="inlineStr">
@@ -19791,26 +19755,26 @@
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture C</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP)</t>
         </is>
       </c>
       <c r="D164" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E164" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 1.05 1.NP</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standard)</t>
         </is>
       </c>
       <c r="F164" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G164" s="23" t="n">
-        <v>1</v>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G164" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H164" s="10" t="n"/>
       <c r="I164" s="10" t="n"/>
@@ -19820,7 +19784,7 @@
         </is>
       </c>
       <c r="K164" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L164" s="20" t="inlineStr">
         <is>
@@ -19829,12 +19793,12 @@
       </c>
       <c r="M164" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 1.05 1.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 2.03 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N164" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O164" s="26" t="inlineStr">
@@ -19845,7 +19809,7 @@
       <c r="P164" s="41" t="n"/>
       <c r="Q164" s="41" t="inlineStr">
         <is>
-          <t>GAP_005</t>
+          <t>GAP_005_deprecated</t>
         </is>
       </c>
     </row>
@@ -19860,26 +19824,26 @@
       </c>
       <c r="C165" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP)</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture A</t>
         </is>
       </c>
       <c r="D165" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standard)</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F165" s="20" t="inlineStr">
         <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="G165" s="22" t="n">
-        <v>0</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G165" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H165" s="10" t="n"/>
       <c r="I165" s="10" t="n"/>
@@ -19889,7 +19853,7 @@
         </is>
       </c>
       <c r="K165" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L165" s="20" t="inlineStr">
         <is>
@@ -19898,12 +19862,12 @@
       </c>
       <c r="M165" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 2.03 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ MTEXT room 2.03 2.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N165" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O165" s="26" t="inlineStr">
@@ -19914,7 +19878,7 @@
       <c r="P165" s="41" t="n"/>
       <c r="Q165" s="41" t="inlineStr">
         <is>
-          <t>GAP_005_deprecated</t>
+          <t>GAP_005</t>
         </is>
       </c>
     </row>
@@ -19929,17 +19893,17 @@
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture B</t>
         </is>
       </c>
       <c r="D166" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725221201</t>
         </is>
       </c>
       <c r="E166" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 2.03 2.NP</t>
+          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F166" s="20" t="inlineStr">
@@ -19998,17 +19962,17 @@
       </c>
       <c r="C167" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture C</t>
         </is>
       </c>
       <c r="D167" s="20" t="inlineStr">
         <is>
-          <t>725221201</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
         <is>
-          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 2.03 2.NP</t>
+          <t>WC kombi keramické bílé — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F167" s="20" t="inlineStr">
@@ -20067,26 +20031,26 @@
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture C</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP)</t>
         </is>
       </c>
       <c r="D168" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E168" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 2.03 2.NP</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standard)</t>
         </is>
       </c>
       <c r="F168" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G168" s="23" t="n">
-        <v>1</v>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G168" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H168" s="10" t="n"/>
       <c r="I168" s="10" t="n"/>
@@ -20096,7 +20060,7 @@
         </is>
       </c>
       <c r="K168" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L168" s="20" t="inlineStr">
         <is>
@@ -20105,12 +20069,12 @@
       </c>
       <c r="M168" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 2.03 2.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 3.04 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N168" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O168" s="26" t="inlineStr">
@@ -20121,7 +20085,7 @@
       <c r="P168" s="41" t="n"/>
       <c r="Q168" s="41" t="inlineStr">
         <is>
-          <t>GAP_005</t>
+          <t>GAP_005_deprecated</t>
         </is>
       </c>
     </row>
@@ -20136,26 +20100,26 @@
       </c>
       <c r="C169" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP)</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture A</t>
         </is>
       </c>
       <c r="D169" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standard)</t>
+          <t>WC kombi keramické bílé — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F169" s="20" t="inlineStr">
         <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="G169" s="22" t="n">
-        <v>0</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G169" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H169" s="10" t="n"/>
       <c r="I169" s="10" t="n"/>
@@ -20165,7 +20129,7 @@
         </is>
       </c>
       <c r="K169" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L169" s="20" t="inlineStr">
         <is>
@@ -20174,12 +20138,12 @@
       </c>
       <c r="M169" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 3.04 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ MTEXT room 3.04 3.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N169" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O169" s="26" t="inlineStr">
@@ -20190,7 +20154,7 @@
       <c r="P169" s="41" t="n"/>
       <c r="Q169" s="41" t="inlineStr">
         <is>
-          <t>GAP_005_deprecated</t>
+          <t>GAP_005</t>
         </is>
       </c>
     </row>
@@ -20205,17 +20169,17 @@
       </c>
       <c r="C170" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture B</t>
         </is>
       </c>
       <c r="D170" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E170" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 3.04 3.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F170" s="20" t="inlineStr">
@@ -20274,17 +20238,17 @@
       </c>
       <c r="C171" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture C</t>
         </is>
       </c>
       <c r="D171" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725221201</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 3.04 3.NP</t>
+          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F171" s="20" t="inlineStr">
@@ -20343,17 +20307,17 @@
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture C</t>
+          <t>Kuchyňský dřez 2 ks (1.06 + 3.05)</t>
         </is>
       </c>
       <c r="D172" s="20" t="inlineStr">
         <is>
-          <t>725221201</t>
+          <t>725840111</t>
         </is>
       </c>
       <c r="E172" s="8" t="inlineStr">
         <is>
-          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 3.04 3.NP</t>
+          <t>Kuchyňský dřez nerez + montáž — 2 ks (kuchyně 1.06 byt rodičů + kuchyně 3.05 byt 3.NP)</t>
         </is>
       </c>
       <c r="F172" s="20" t="inlineStr">
@@ -20362,7 +20326,7 @@
         </is>
       </c>
       <c r="G172" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H172" s="10" t="n"/>
       <c r="I172" s="10" t="n"/>
@@ -20372,7 +20336,7 @@
         </is>
       </c>
       <c r="K172" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L172" s="20" t="inlineStr">
         <is>
@@ -20381,12 +20345,12 @@
       </c>
       <c r="M172" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 3.04 3.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF kuchyně MTEXT 2× + TZ ARS — dispozice byty</t>
         </is>
       </c>
       <c r="N172" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O172" s="26" t="inlineStr">
@@ -20395,11 +20359,7 @@
         </is>
       </c>
       <c r="P172" s="41" t="n"/>
-      <c r="Q172" s="41" t="inlineStr">
-        <is>
-          <t>GAP_005</t>
-        </is>
-      </c>
+      <c r="Q172" s="41" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="20" t="n">
@@ -20412,17 +20372,17 @@
       </c>
       <c r="C173" s="8" t="inlineStr">
         <is>
-          <t>Kuchyňský dřez 2 ks (1.06 + 3.05)</t>
+          <t>Vodovodní baterie + drobnosti</t>
         </is>
       </c>
       <c r="D173" s="20" t="inlineStr">
         <is>
-          <t>725840111</t>
+          <t>725822611</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
         <is>
-          <t>Kuchyňský dřez nerez + montáž — 2 ks (kuchyně 1.06 byt rodičů + kuchyně 3.05 byt 3.NP)</t>
+          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační materiály</t>
         </is>
       </c>
       <c r="F173" s="20" t="inlineStr">
@@ -20431,7 +20391,7 @@
         </is>
       </c>
       <c r="G173" s="23" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H173" s="10" t="n"/>
       <c r="I173" s="10" t="n"/>
@@ -20441,7 +20401,7 @@
         </is>
       </c>
       <c r="K173" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L173" s="20" t="inlineStr">
         <is>
@@ -20450,7 +20410,7 @@
       </c>
       <c r="M173" s="8" t="inlineStr">
         <is>
-          <t>DXF kuchyně MTEXT 2× + TZ ARS — dispozice byty</t>
+          <t>TZ ARS — kompletní baterie nové</t>
         </is>
       </c>
       <c r="N173" s="20" t="inlineStr">
@@ -20477,17 +20437,17 @@
       </c>
       <c r="C174" s="8" t="inlineStr">
         <is>
-          <t>Vodovodní baterie + drobnosti</t>
+          <t>Akumulační zásobník TUV v suterénu</t>
         </is>
       </c>
       <c r="D174" s="20" t="inlineStr">
         <is>
-          <t>725822611</t>
+          <t>732419411</t>
         </is>
       </c>
       <c r="E174" s="8" t="inlineStr">
         <is>
-          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační materiály</t>
+          <t>Akumulační zásobník TUV ~300 l v 1.PP napojený na topný systém (sporáková kamna + krb + elektrokotel) — nepřímotop</t>
         </is>
       </c>
       <c r="F174" s="20" t="inlineStr">
@@ -20496,17 +20456,17 @@
         </is>
       </c>
       <c r="G174" s="23" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H174" s="10" t="n"/>
       <c r="I174" s="10" t="n"/>
       <c r="J174" s="8" t="inlineStr">
         <is>
-          <t>vodar</t>
+          <t>instalater_TUV_akumulacni_zasobnik</t>
         </is>
       </c>
       <c r="K174" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L174" s="20" t="inlineStr">
         <is>
@@ -20515,7 +20475,7 @@
       </c>
       <c r="M174" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS — kompletní baterie nové</t>
+          <t>TZ ARS dům §4 — kombi akumulační zásobník napojený na multivariantní topný systém</t>
         </is>
       </c>
       <c r="N174" s="20" t="inlineStr">
@@ -20542,17 +20502,17 @@
       </c>
       <c r="C175" s="8" t="inlineStr">
         <is>
-          <t>Akumulační zásobník TUV v suterénu</t>
+          <t>Elektrický bojler 3.NP</t>
         </is>
       </c>
       <c r="D175" s="20" t="inlineStr">
         <is>
-          <t>732419411</t>
+          <t>732429211</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
         <is>
-          <t>Akumulační zásobník TUV ~300 l v 1.PP napojený na topný systém (sporáková kamna + krb + elektrokotel) — nepřímotop</t>
+          <t>Elektrický bojler ~80 l v koupelně 3.NP (nezávislý zdroj pro samostatný byt)</t>
         </is>
       </c>
       <c r="F175" s="20" t="inlineStr">
@@ -20567,7 +20527,7 @@
       <c r="I175" s="10" t="n"/>
       <c r="J175" s="8" t="inlineStr">
         <is>
-          <t>instalater_TUV_akumulacni_zasobnik</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K175" s="24" t="n">
@@ -20580,7 +20540,7 @@
       </c>
       <c r="M175" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kombi akumulační zásobník napojený na multivariantní topný systém</t>
+          <t>TZ ARS dům §4 — elektrický bojler v 3.NP koupelně, vyjasnění #6 odhad 80 l</t>
         </is>
       </c>
       <c r="N175" s="20" t="inlineStr">
@@ -20602,22 +20562,22 @@
       </c>
       <c r="B176" s="8" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>PSV-73 Vytápění</t>
         </is>
       </c>
       <c r="C176" s="8" t="inlineStr">
         <is>
-          <t>Elektrický bojler 3.NP</t>
+          <t>Sporáková kamna na tuhá paliva</t>
         </is>
       </c>
       <c r="D176" s="20" t="inlineStr">
         <is>
-          <t>732429211</t>
+          <t>733241011</t>
         </is>
       </c>
       <c r="E176" s="8" t="inlineStr">
         <is>
-          <t>Elektrický bojler ~80 l v koupelně 3.NP (nezávislý zdroj pro samostatný byt)</t>
+          <t>Sporáková kamna na tuhá paliva ~10 kW s akumulačním zásobníkem TUV — dodávka</t>
         </is>
       </c>
       <c r="F176" s="20" t="inlineStr">
@@ -20632,7 +20592,7 @@
       <c r="I176" s="10" t="n"/>
       <c r="J176" s="8" t="inlineStr">
         <is>
-          <t>vodar</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K176" s="24" t="n">
@@ -20645,7 +20605,7 @@
       </c>
       <c r="M176" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — elektrický bojler v 3.NP koupelně, vyjasnění #6 odhad 80 l</t>
+          <t>TZ ARS dům §4 — primární zdroj 1.NP/2.NP, ~10 kW odhad standard RD</t>
         </is>
       </c>
       <c r="N176" s="20" t="inlineStr">
@@ -20672,22 +20632,22 @@
       </c>
       <c r="C177" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna na tuhá paliva</t>
+          <t>Sporáková kamna — montáž</t>
         </is>
       </c>
       <c r="D177" s="20" t="inlineStr">
         <is>
-          <t>733241011</t>
+          <t>733281011</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna na tuhá paliva ~10 kW s akumulačním zásobníkem TUV — dodávka</t>
+          <t>Sporáková kamna — montáž vč. napojení na komín + akumulační zásobník (cca 8 Nh)</t>
         </is>
       </c>
       <c r="F177" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G177" s="23" t="n">
@@ -20701,7 +20661,7 @@
         </is>
       </c>
       <c r="K177" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L177" s="20" t="inlineStr">
         <is>
@@ -20710,12 +20670,12 @@
       </c>
       <c r="M177" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — primární zdroj 1.NP/2.NP, ~10 kW odhad standard RD</t>
+          <t>Standard montáž kamen s napojením na zásobník</t>
         </is>
       </c>
       <c r="N177" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O177" s="26" t="inlineStr">
@@ -20737,22 +20697,22 @@
       </c>
       <c r="C178" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna — montáž</t>
+          <t>Elektrokotel 3.NP</t>
         </is>
       </c>
       <c r="D178" s="20" t="inlineStr">
         <is>
-          <t>733281011</t>
+          <t>733131221</t>
         </is>
       </c>
       <c r="E178" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna — montáž vč. napojení na komín + akumulační zásobník (cca 8 Nh)</t>
+          <t>Elektrokotel ~8 kW pro 3.NP samostatný byt — dodávka + montáž + napojení</t>
         </is>
       </c>
       <c r="F178" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G178" s="23" t="n">
@@ -20766,7 +20726,7 @@
         </is>
       </c>
       <c r="K178" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L178" s="20" t="inlineStr">
         <is>
@@ -20775,12 +20735,12 @@
       </c>
       <c r="M178" s="8" t="inlineStr">
         <is>
-          <t>Standard montáž kamen s napojením na zásobník</t>
+          <t>TZ ARS dům §4 — 'Nově navržené 3.NP bude vytápěno elektrokotlem'; ~8 kW odhad</t>
         </is>
       </c>
       <c r="N178" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O178" s="26" t="inlineStr">
@@ -20802,17 +20762,17 @@
       </c>
       <c r="C179" s="8" t="inlineStr">
         <is>
-          <t>Elektrokotel 3.NP</t>
+          <t>Krb na tuhá paliva 3.NP</t>
         </is>
       </c>
       <c r="D179" s="20" t="inlineStr">
         <is>
-          <t>733131221</t>
+          <t>733241011</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
         <is>
-          <t>Elektrokotel ~8 kW pro 3.NP samostatný byt — dodávka + montáž + napojení</t>
+          <t>Krb na tuhá paliva v 3.NP ~6 kW — dodávka + montáž s napojením na samostatný komín</t>
         </is>
       </c>
       <c r="F179" s="20" t="inlineStr">
@@ -20840,7 +20800,7 @@
       </c>
       <c r="M179" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — 'Nově navržené 3.NP bude vytápěno elektrokotlem'; ~8 kW odhad</t>
+          <t>TZ ARS dům §4 — krb v 3.NP, ~6 kW odhad</t>
         </is>
       </c>
       <c r="N179" s="20" t="inlineStr">
@@ -20867,17 +20827,17 @@
       </c>
       <c r="C180" s="8" t="inlineStr">
         <is>
-          <t>Krb na tuhá paliva 3.NP</t>
+          <t>Multisplit TČ — venkovní jednotka</t>
         </is>
       </c>
       <c r="D180" s="20" t="inlineStr">
         <is>
-          <t>733241011</t>
+          <t>733425211</t>
         </is>
       </c>
       <c r="E180" s="8" t="inlineStr">
         <is>
-          <t>Krb na tuhá paliva v 3.NP ~6 kW — dodávka + montáž s napojením na samostatný komín</t>
+          <t>Multisplit tepelné čerpadlo vzduch-vzduch — 1× venkovní jednotka ~10 kW (silent mode hl. tlaku ≤49 dBA)</t>
         </is>
       </c>
       <c r="F180" s="20" t="inlineStr">
@@ -20892,7 +20852,7 @@
       <c r="I180" s="10" t="n"/>
       <c r="J180" s="8" t="inlineStr">
         <is>
-          <t>topenar</t>
+          <t>specialista_TC_multisplit</t>
         </is>
       </c>
       <c r="K180" s="24" t="n">
@@ -20905,7 +20865,7 @@
       </c>
       <c r="M180" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — krb v 3.NP, ~6 kW odhad</t>
+          <t>TZ ARS dům §4 — multisplit TČ s akustikou hl. tlaku ≤49 dBA, NV 272/2011</t>
         </is>
       </c>
       <c r="N180" s="20" t="inlineStr">
@@ -20932,17 +20892,17 @@
       </c>
       <c r="C181" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — venkovní jednotka</t>
+          <t>Multisplit TČ — vnitřní jednotky</t>
         </is>
       </c>
       <c r="D181" s="20" t="inlineStr">
         <is>
-          <t>733425211</t>
+          <t>733425221</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
         <is>
-          <t>Multisplit tepelné čerpadlo vzduch-vzduch — 1× venkovní jednotka ~10 kW (silent mode hl. tlaku ≤49 dBA)</t>
+          <t>Multisplit TČ — 5× vnitřní jednotka v obytných místnostech (1.NP, 2.NP, 3.NP — chlazení + vytápění)</t>
         </is>
       </c>
       <c r="F181" s="20" t="inlineStr">
@@ -20951,7 +20911,7 @@
         </is>
       </c>
       <c r="G181" s="23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H181" s="10" t="n"/>
       <c r="I181" s="10" t="n"/>
@@ -20961,7 +20921,7 @@
         </is>
       </c>
       <c r="K181" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L181" s="20" t="inlineStr">
         <is>
@@ -20970,7 +20930,7 @@
       </c>
       <c r="M181" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — multisplit TČ s akustikou hl. tlaku ≤49 dBA, NV 272/2011</t>
+          <t>TZ ARS dům §4 — vnitřní jednotky multisplit, vyjasnění #6 odhad 5 ks</t>
         </is>
       </c>
       <c r="N181" s="20" t="inlineStr">
@@ -20997,36 +20957,36 @@
       </c>
       <c r="C182" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — vnitřní jednotky</t>
+          <t>Revize komínu</t>
         </is>
       </c>
       <c r="D182" s="20" t="inlineStr">
         <is>
-          <t>733425221</t>
+          <t>734262122</t>
         </is>
       </c>
       <c r="E182" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — 5× vnitřní jednotka v obytných místnostech (1.NP, 2.NP, 3.NP — chlazení + vytápění)</t>
+          <t>Revize stávajícího komínu — kontrola, čištění, vystrojení vložkou nerez DN160 pro kamna + krb 3.NP</t>
         </is>
       </c>
       <c r="F182" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G182" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H182" s="10" t="n"/>
       <c r="I182" s="10" t="n"/>
       <c r="J182" s="8" t="inlineStr">
         <is>
-          <t>specialista_TC_multisplit</t>
+          <t>kominik</t>
         </is>
       </c>
       <c r="K182" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L182" s="20" t="inlineStr">
         <is>
@@ -21035,7 +20995,7 @@
       </c>
       <c r="M182" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — vnitřní jednotky multisplit, vyjasnění #6 odhad 5 ks</t>
+          <t>TZ ARS dům §4 — komín stávající, vystrojení vložkou pro kamna + krb</t>
         </is>
       </c>
       <c r="N182" s="20" t="inlineStr">
@@ -21062,36 +21022,36 @@
       </c>
       <c r="C183" s="8" t="inlineStr">
         <is>
-          <t>Revize komínu</t>
+          <t>Rozvody otopné soustavy</t>
         </is>
       </c>
       <c r="D183" s="20" t="inlineStr">
         <is>
-          <t>734262122</t>
+          <t>733111021</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajícího komínu — kontrola, čištění, vystrojení vložkou nerez DN160 pro kamna + krb 3.NP</t>
+          <t>Rozvody otopné soustavy Cu/PEX k vnitřním jednotkám TČ + radiátorům pro doplňkové (cca 100 bm odhad)</t>
         </is>
       </c>
       <c r="F183" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G183" s="23" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G183" s="22" t="n">
+        <v>100</v>
       </c>
       <c r="H183" s="10" t="n"/>
       <c r="I183" s="10" t="n"/>
       <c r="J183" s="8" t="inlineStr">
         <is>
-          <t>kominik</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K183" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L183" s="20" t="inlineStr">
         <is>
@@ -21100,7 +21060,7 @@
       </c>
       <c r="M183" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — komín stávající, vystrojení vložkou pro kamna + krb</t>
+          <t>TZ ARS dům §4 — rozvody otopné soustavy</t>
         </is>
       </c>
       <c r="N183" s="20" t="inlineStr">
@@ -21122,41 +21082,41 @@
       </c>
       <c r="B184" s="8" t="inlineStr">
         <is>
-          <t>PSV-73 Vytápění</t>
+          <t>VRN — BOZP</t>
         </is>
       </c>
       <c r="C184" s="8" t="inlineStr">
         <is>
-          <t>Rozvody otopné soustavy</t>
+          <t>Koordinace BOZP</t>
         </is>
       </c>
       <c r="D184" s="20" t="inlineStr">
         <is>
-          <t>733111021</t>
+          <t>030091000</t>
         </is>
       </c>
       <c r="E184" s="8" t="inlineStr">
         <is>
-          <t>Rozvody otopné soustavy Cu/PEX k vnitřním jednotkám TČ + radiátorům pro doplňkové (cca 100 bm odhad)</t>
+          <t>Koordinátor BOZP na staveništi dle zákona 309/2006 Sb. — pro stavbu s více než jedním zhotovitelem</t>
         </is>
       </c>
       <c r="F184" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G184" s="22" t="n">
-        <v>100</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G184" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H184" s="10" t="n"/>
       <c r="I184" s="10" t="n"/>
       <c r="J184" s="8" t="inlineStr">
         <is>
-          <t>topenar</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K184" s="24" t="n">
-        <v>0.75</v>
+        <v>0.99</v>
       </c>
       <c r="L184" s="20" t="inlineStr">
         <is>
@@ -21165,12 +21125,12 @@
       </c>
       <c r="M184" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — rozvody otopné soustavy</t>
+          <t>Zákon 309/2006 Sb. — povinný BOZP koordinátor pro vícezhotovitelskou stavbu</t>
         </is>
       </c>
       <c r="N184" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O184" s="26" t="inlineStr">
@@ -21187,22 +21147,22 @@
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
-          <t>VRN — BOZP</t>
+          <t>VRN — Dokumentace</t>
         </is>
       </c>
       <c r="C185" s="8" t="inlineStr">
         <is>
-          <t>Koordinace BOZP</t>
+          <t>Předávací protokoly + DSP</t>
         </is>
       </c>
       <c r="D185" s="20" t="inlineStr">
         <is>
-          <t>030091000</t>
+          <t>030151000</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
         <is>
-          <t>Koordinátor BOZP na staveništi dle zákona 309/2006 Sb. — pro stavbu s více než jedním zhotovitelem</t>
+          <t>Předávací protokoly + Dokumentace skutečného provedení (DSP) — sestavení, vázání, dodávka 2× tiskem + elektronická verze</t>
         </is>
       </c>
       <c r="F185" s="20" t="inlineStr">
@@ -21230,12 +21190,12 @@
       </c>
       <c r="M185" s="8" t="inlineStr">
         <is>
-          <t>Zákon 309/2006 Sb. — povinný BOZP koordinátor pro vícezhotovitelskou stavbu</t>
+          <t>Vyhláška 499/2006 Sb. + ČKAIT — DSP povinná pro kolaudaci</t>
         </is>
       </c>
       <c r="N185" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O185" s="26" t="inlineStr">
@@ -21252,41 +21212,41 @@
       </c>
       <c r="B186" s="8" t="inlineStr">
         <is>
-          <t>VRN — Dokumentace</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C186" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokoly + DSP</t>
+          <t>Kontejnery suti tříděné</t>
         </is>
       </c>
       <c r="D186" s="20" t="inlineStr">
         <is>
-          <t>030151000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="E186" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokoly + Dokumentace skutečného provedení (DSP) — sestavení, vázání, dodávka 2× tiskem + elektronická verze</t>
+          <t>Kontejnery na suť tříděnou velkoobjemové (beton/cihly, dřevo, kovy, EPS, sádra, směs) — pronájem + svozy</t>
         </is>
       </c>
       <c r="F186" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G186" s="23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H186" s="10" t="n"/>
       <c r="I186" s="10" t="n"/>
       <c r="J186" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K186" s="24" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="L186" s="20" t="inlineStr">
         <is>
@@ -21295,12 +21255,12 @@
       </c>
       <c r="M186" s="8" t="inlineStr">
         <is>
-          <t>Vyhláška 499/2006 Sb. + ČKAIT — DSP povinná pro kolaudaci</t>
+          <t>TZ B m.10.e: beton/cihly 46 t + dřevo 9 t + kovy 0.1 + EPS 0.1 + sádra 0.2 + směs 1.0</t>
         </is>
       </c>
       <c r="N186" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#9, #10</t>
         </is>
       </c>
       <c r="O186" s="26" t="inlineStr">
@@ -21322,36 +21282,36 @@
       </c>
       <c r="C187" s="8" t="inlineStr">
         <is>
-          <t>Kontejnery suti tříděné</t>
+          <t>Doprava materiálu</t>
         </is>
       </c>
       <c r="D187" s="20" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>031031000</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
         <is>
-          <t>Kontejnery na suť tříděnou velkoobjemové (beton/cihly, dřevo, kovy, EPS, sádra, směs) — pronájem + svozy</t>
+          <t>Doprava materiálu na stavbu (centrální koordinace) — paušál ~2-3 % z PN materiál</t>
         </is>
       </c>
       <c r="F187" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>paušál</t>
         </is>
       </c>
       <c r="G187" s="23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H187" s="10" t="n"/>
       <c r="I187" s="10" t="n"/>
       <c r="J187" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K187" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L187" s="20" t="inlineStr">
         <is>
@@ -21360,12 +21320,12 @@
       </c>
       <c r="M187" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e: beton/cihly 46 t + dřevo 9 t + kovy 0.1 + EPS 0.1 + sádra 0.2 + směs 1.0</t>
+          <t>B4_productivity — standard doprava RD městská zástavba</t>
         </is>
       </c>
       <c r="N187" s="20" t="inlineStr">
         <is>
-          <t>#9, #10</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O187" s="26" t="inlineStr">
@@ -21387,36 +21347,36 @@
       </c>
       <c r="C188" s="8" t="inlineStr">
         <is>
-          <t>Doprava materiálu</t>
+          <t>Likvidace odpadů 56.9 t</t>
         </is>
       </c>
       <c r="D188" s="20" t="inlineStr">
         <is>
-          <t>031031000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="E188" s="8" t="inlineStr">
         <is>
-          <t>Doprava materiálu na stavbu (centrální koordinace) — paušál ~2-3 % z PN materiál</t>
+          <t>Likvidace stavební suti dle vyhl. 8/2021 Sb. — skládkovné + recyklace + třídění (56.9 t celkem per TZ B m.10.e)</t>
         </is>
       </c>
       <c r="F188" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="G188" s="23" t="n">
-        <v>1</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G188" s="22" t="n">
+        <v>56.9</v>
       </c>
       <c r="H188" s="10" t="n"/>
       <c r="I188" s="10" t="n"/>
       <c r="J188" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K188" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L188" s="20" t="inlineStr">
         <is>
@@ -21425,12 +21385,12 @@
       </c>
       <c r="M188" s="8" t="inlineStr">
         <is>
-          <t>B4_productivity — standard doprava RD městská zástavba</t>
+          <t>TZ B m.10.e bilance odpadů celkem dům</t>
         </is>
       </c>
       <c r="N188" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>#9, #10</t>
         </is>
       </c>
       <c r="O188" s="26" t="inlineStr">
@@ -21447,41 +21407,41 @@
       </c>
       <c r="B189" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="C189" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadů 56.9 t</t>
+          <t>Geodetické zaměření před + po realizaci</t>
         </is>
       </c>
       <c r="D189" s="20" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>030141000</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
         <is>
-          <t>Likvidace stavební suti dle vyhl. 8/2021 Sb. — skládkovné + recyklace + třídění (56.9 t celkem per TZ B m.10.e)</t>
+          <t>Geodetické zaměření před realizací (verifikace polohopis + výškopis) + po dokončení (zaměření skutečného provedení pro kolaudaci)</t>
         </is>
       </c>
       <c r="F189" s="20" t="inlineStr">
         <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G189" s="22" t="n">
-        <v>56.9</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G189" s="23" t="n">
+        <v>2</v>
       </c>
       <c r="H189" s="10" t="n"/>
       <c r="I189" s="10" t="n"/>
       <c r="J189" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>geodet</t>
         </is>
       </c>
       <c r="K189" s="24" t="n">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
       <c r="L189" s="20" t="inlineStr">
         <is>
@@ -21490,12 +21450,12 @@
       </c>
       <c r="M189" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e bilance odpadů celkem dům</t>
+          <t>Standard — geodet před+po pro každou stavbu</t>
         </is>
       </c>
       <c r="N189" s="20" t="inlineStr">
         <is>
-          <t>#9, #10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O189" s="26" t="inlineStr">
@@ -21512,37 +21472,37 @@
       </c>
       <c r="B190" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Kolaudace</t>
         </is>
       </c>
       <c r="C190" s="8" t="inlineStr">
         <is>
-          <t>Geodetické zaměření před + po realizaci</t>
+          <t>Kolaudační řízení</t>
         </is>
       </c>
       <c r="D190" s="20" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>030171000</t>
         </is>
       </c>
       <c r="E190" s="8" t="inlineStr">
         <is>
-          <t>Geodetické zaměření před realizací (verifikace polohopis + výškopis) + po dokončení (zaměření skutečného provedení pro kolaudaci)</t>
+          <t>Kolaudační řízení — paušál (správní poplatky + součinnost) dle zákona 183/2006 Sb.</t>
         </is>
       </c>
       <c r="F190" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>paušál</t>
         </is>
       </c>
       <c r="G190" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H190" s="10" t="n"/>
       <c r="I190" s="10" t="n"/>
       <c r="J190" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K190" s="24" t="n">
@@ -21555,7 +21515,7 @@
       </c>
       <c r="M190" s="8" t="inlineStr">
         <is>
-          <t>Standard — geodet před+po pro každou stavbu</t>
+          <t>Zákon 183/2006 Sb. + vyhl. 499/2006 Sb.</t>
         </is>
       </c>
       <c r="N190" s="20" t="inlineStr">
@@ -21577,31 +21537,31 @@
       </c>
       <c r="B191" s="8" t="inlineStr">
         <is>
-          <t>VRN — Kolaudace</t>
+          <t>VRN — Lešení</t>
         </is>
       </c>
       <c r="C191" s="8" t="inlineStr">
         <is>
-          <t>Kolaudační řízení</t>
+          <t>Fasádní lešení (ETICS + krov + klempířina)</t>
         </is>
       </c>
       <c r="D191" s="20" t="inlineStr">
         <is>
-          <t>030171000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
         <is>
-          <t>Kolaudační řízení — paušál (správní poplatky + součinnost) dle zákona 183/2006 Sb.</t>
+          <t>Fasádní lešení trubkové/rámové vč. montáže + pronájmu + demontáže — pro provedení ETICS fasády, krovu a klempířiny po obvodu domu (výška 13 m)</t>
         </is>
       </c>
       <c r="F191" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="G191" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G191" s="22" t="n">
+        <v>503.1</v>
       </c>
       <c r="H191" s="10" t="n"/>
       <c r="I191" s="10" t="n"/>
@@ -21611,7 +21571,7 @@
         </is>
       </c>
       <c r="K191" s="24" t="n">
-        <v>0.99</v>
+        <v>0.8</v>
       </c>
       <c r="L191" s="20" t="inlineStr">
         <is>
@@ -21620,7 +21580,7 @@
       </c>
       <c r="M191" s="8" t="inlineStr">
         <is>
-          <t>Zákon 183/2006 Sb. + vyhl. 499/2006 Sb.</t>
+          <t>anchor checklist PM02 — technical necessity (ETICS 276.7 m² nelze provést bez lešení, 941xxx URS família) + DXF obvod 38.7 m + řez výška 13 m</t>
         </is>
       </c>
       <c r="N191" s="20" t="inlineStr">
@@ -21634,7 +21594,11 @@
         </is>
       </c>
       <c r="P191" s="41" t="n"/>
-      <c r="Q191" s="41" t="n"/>
+      <c r="Q191" s="41" t="inlineStr">
+        <is>
+          <t>ANCHOR_CHECKLIST_PM02</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="20" t="n">
@@ -21642,31 +21606,31 @@
       </c>
       <c r="B192" s="8" t="inlineStr">
         <is>
-          <t>VRN — Lešení</t>
+          <t>VRN — Pojištění + zábory</t>
         </is>
       </c>
       <c r="C192" s="8" t="inlineStr">
         <is>
-          <t>Fasádní lešení (ETICS + krov + klempířina)</t>
+          <t>Pojištění stavby (montážní + odpovědnostní)</t>
         </is>
       </c>
       <c r="D192" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>030081000</t>
         </is>
       </c>
       <c r="E192" s="8" t="inlineStr">
         <is>
-          <t>Fasádní lešení trubkové/rámové vč. montáže + pronájmu + demontáže — pro provedení ETICS fasády, krovu a klempířiny po obvodu domu (výška 13 m)</t>
+          <t>Montážní pojištění stavby (CAR) + pojištění odpovědnosti za škodu (zhotovitel) — paušál cca 0.3-0.5 % z PN</t>
         </is>
       </c>
       <c r="F192" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G192" s="22" t="n">
-        <v>503.1</v>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G192" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H192" s="10" t="n"/>
       <c r="I192" s="10" t="n"/>
@@ -21676,7 +21640,7 @@
         </is>
       </c>
       <c r="K192" s="24" t="n">
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="L192" s="20" t="inlineStr">
         <is>
@@ -21685,12 +21649,12 @@
       </c>
       <c r="M192" s="8" t="inlineStr">
         <is>
-          <t>anchor checklist PM02 — technical necessity (ETICS 276.7 m² nelze provést bez lešení, 941xxx URS família) + DXF obvod 38.7 m + řez výška 13 m</t>
+          <t>Standard zhotovitel — pojistná povinnost</t>
         </is>
       </c>
       <c r="N192" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O192" s="26" t="inlineStr">
@@ -21699,11 +21663,7 @@
         </is>
       </c>
       <c r="P192" s="41" t="n"/>
-      <c r="Q192" s="41" t="inlineStr">
-        <is>
-          <t>ANCHOR_CHECKLIST_PM02</t>
-        </is>
-      </c>
+      <c r="Q192" s="41" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="20" t="n">
@@ -21716,22 +21676,22 @@
       </c>
       <c r="C193" s="8" t="inlineStr">
         <is>
-          <t>Pojištění stavby (montážní + odpovědnostní)</t>
+          <t>Krátkodobé zábory ul. Fibichova</t>
         </is>
       </c>
       <c r="D193" s="20" t="inlineStr">
         <is>
-          <t>030081000</t>
+          <t>030083000</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
         <is>
-          <t>Montážní pojištění stavby (CAR) + pojištění odpovědnosti za škodu (zhotovitel) — paušál cca 0.3-0.5 % z PN</t>
+          <t>Krátkodobé zábory ulice Fibichova pro materiál a kontejnery (povolení MU Jáchymov + DI) — odhad 30 dnů kumulativně</t>
         </is>
       </c>
       <c r="F193" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G193" s="23" t="n">
@@ -21745,7 +21705,7 @@
         </is>
       </c>
       <c r="K193" s="24" t="n">
-        <v>0.99</v>
+        <v>0.75</v>
       </c>
       <c r="L193" s="20" t="inlineStr">
         <is>
@@ -21754,7 +21714,7 @@
       </c>
       <c r="M193" s="8" t="inlineStr">
         <is>
-          <t>Standard zhotovitel — pojistná povinnost</t>
+          <t>TZ B m.10 + situace — řadovka ul. Fibichova</t>
         </is>
       </c>
       <c r="N193" s="20" t="inlineStr">
@@ -21776,22 +21736,22 @@
       </c>
       <c r="B194" s="8" t="inlineStr">
         <is>
-          <t>VRN — Pojištění + zábory</t>
+          <t>VRN — Průzkumy</t>
         </is>
       </c>
       <c r="C194" s="8" t="inlineStr">
         <is>
-          <t>Krátkodobé zábory ul. Fibichova</t>
+          <t>Mykologický průzkum dřeva při bourání</t>
         </is>
       </c>
       <c r="D194" s="20" t="inlineStr">
         <is>
-          <t>030083000</t>
+          <t>030131000</t>
         </is>
       </c>
       <c r="E194" s="8" t="inlineStr">
         <is>
-          <t>Krátkodobé zábory ulice Fibichova pro materiál a kontejnery (povolení MU Jáchymov + DI) — odhad 30 dnů kumulativně</t>
+          <t>Mykologický průzkum + průzkum výskytu dřevokazného hmyzu stávajícího krovu a dřevěných trámů zhlaví — pro vyloučení narušení dřevěných konstrukcí; provádí autorizovaný mykolog při bourání</t>
         </is>
       </c>
       <c r="F194" s="20" t="inlineStr">
@@ -21806,11 +21766,11 @@
       <c r="I194" s="10" t="n"/>
       <c r="J194" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>mykolog</t>
         </is>
       </c>
       <c r="K194" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L194" s="20" t="inlineStr">
         <is>
@@ -21819,7 +21779,7 @@
       </c>
       <c r="M194" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10 + situace — řadovka ul. Fibichova</t>
+          <t>TZ ARS dům §3.2.3 + POZN.2.05 z půdorysů návrh + řez A-A návrh (explicit dřevokazný hmyz scope per drawing wording)</t>
         </is>
       </c>
       <c r="N194" s="20" t="inlineStr">
@@ -21833,7 +21793,11 @@
         </is>
       </c>
       <c r="P194" s="41" t="n"/>
-      <c r="Q194" s="41" t="n"/>
+      <c r="Q194" s="41" t="inlineStr">
+        <is>
+          <t>PER_DRAWING_ENRICHMENT_POZN_2_05</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="20" t="n">
@@ -21846,17 +21810,17 @@
       </c>
       <c r="C195" s="8" t="inlineStr">
         <is>
-          <t>Mykologický průzkum dřeva při bourání</t>
+          <t>Azbestový průzkum podrobný před demolicí</t>
         </is>
       </c>
       <c r="D195" s="20" t="inlineStr">
         <is>
-          <t>030131000</t>
+          <t>030133000</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
         <is>
-          <t>Mykologický průzkum + průzkum výskytu dřevokazného hmyzu stávajícího krovu a dřevěných trámů zhlaví — pro vyloučení narušení dřevěných konstrukcí; provádí autorizovaný mykolog při bourání</t>
+          <t>Azbestový průzkum podrobný před demolicí — laboratorní vzorky a posudek (B kap. m.7.a předběžně negativní, ale podrobný před bouráním povinný)</t>
         </is>
       </c>
       <c r="F195" s="20" t="inlineStr">
@@ -21871,7 +21835,7 @@
       <c r="I195" s="10" t="n"/>
       <c r="J195" s="8" t="inlineStr">
         <is>
-          <t>mykolog</t>
+          <t>azbestovy_specialista</t>
         </is>
       </c>
       <c r="K195" s="24" t="n">
@@ -21884,7 +21848,7 @@
       </c>
       <c r="M195" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.3 + POZN.2.05 z půdorysů návrh + řez A-A návrh (explicit dřevokazný hmyz scope per drawing wording)</t>
+          <t>TZ B m.7.a + ARS §3.2 — azbestový průzkum povinný před demolicí</t>
         </is>
       </c>
       <c r="N195" s="20" t="inlineStr">
@@ -21898,11 +21862,7 @@
         </is>
       </c>
       <c r="P195" s="41" t="n"/>
-      <c r="Q195" s="41" t="inlineStr">
-        <is>
-          <t>PER_DRAWING_ENRICHMENT_POZN_2_05</t>
-        </is>
-      </c>
+      <c r="Q195" s="41" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="20" t="n">
@@ -21910,41 +21870,41 @@
       </c>
       <c r="B196" s="8" t="inlineStr">
         <is>
-          <t>VRN — Průzkumy</t>
+          <t>VRN — Přesun hmot</t>
         </is>
       </c>
       <c r="C196" s="8" t="inlineStr">
         <is>
-          <t>Azbestový průzkum podrobný před demolicí</t>
+          <t>Přesun hmot pro budovu</t>
         </is>
       </c>
       <c r="D196" s="20" t="inlineStr">
         <is>
-          <t>030133000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E196" s="8" t="inlineStr">
         <is>
-          <t>Azbestový průzkum podrobný před demolicí — laboratorní vzorky a posudek (B kap. m.7.a předběžně negativní, ale podrobný před bouráním povinný)</t>
+          <t>Přesun hmot pro budovu — vnitrostaveništní vertikální + horizontální doprava materiálu a hmot (rekonstrukce vícepodlažní RD + nástavba 3.NP)</t>
         </is>
       </c>
       <c r="F196" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G196" s="23" t="n">
-        <v>1</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G196" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H196" s="10" t="n"/>
       <c r="I196" s="10" t="n"/>
       <c r="J196" s="8" t="inlineStr">
         <is>
-          <t>azbestovy_specialista</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K196" s="24" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="L196" s="20" t="inlineStr">
         <is>
@@ -21953,12 +21913,12 @@
       </c>
       <c r="M196" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.7.a + ARS §3.2 — azbestový průzkum povinný před demolicí</t>
+          <t>anchor checklist PM01 — technical necessity (povinná položka každého rozpočtu, 998xxx URS família)</t>
         </is>
       </c>
       <c r="N196" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O196" s="26" t="inlineStr">
@@ -21967,7 +21927,11 @@
         </is>
       </c>
       <c r="P196" s="41" t="n"/>
-      <c r="Q196" s="41" t="n"/>
+      <c r="Q196" s="41" t="inlineStr">
+        <is>
+          <t>ANCHOR_CHECKLIST_PM01</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="20" t="n">
@@ -21975,41 +21939,41 @@
       </c>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t>VRN — Přesun hmot</t>
+          <t>VRN — Revize</t>
         </is>
       </c>
       <c r="C197" s="8" t="inlineStr">
         <is>
-          <t>Přesun hmot pro budovu</t>
+          <t>Revize hydrantu vnějšího</t>
         </is>
       </c>
       <c r="D197" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>030161000</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
         <is>
-          <t>Přesun hmot pro budovu — vnitrostaveništní vertikální + horizontální doprava materiálu a hmot (rekonstrukce vícepodlažní RD + nástavba 3.NP)</t>
+          <t>Revize vnějšího hydrantu pro požární zabezpečení (DN min. 80, vzdálenost 100 m dle TZ PBŘ) — periodická kontrola</t>
         </is>
       </c>
       <c r="F197" s="20" t="inlineStr">
         <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G197" s="22" t="n">
-        <v>0</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G197" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H197" s="10" t="n"/>
       <c r="I197" s="10" t="n"/>
       <c r="J197" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>revize_specialista</t>
         </is>
       </c>
       <c r="K197" s="24" t="n">
-        <v>0.6</v>
+        <v>0.85</v>
       </c>
       <c r="L197" s="20" t="inlineStr">
         <is>
@@ -22018,7 +21982,7 @@
       </c>
       <c r="M197" s="8" t="inlineStr">
         <is>
-          <t>anchor checklist PM01 — technical necessity (povinná položka každého rozpočtu, 998xxx URS família)</t>
+          <t>TZ PBŘ dům — vnější odběrné místo požární vody, revize před kolaudací</t>
         </is>
       </c>
       <c r="N197" s="20" t="inlineStr">
@@ -22032,11 +21996,7 @@
         </is>
       </c>
       <c r="P197" s="41" t="n"/>
-      <c r="Q197" s="41" t="inlineStr">
-        <is>
-          <t>ANCHOR_CHECKLIST_PM01</t>
-        </is>
-      </c>
+      <c r="Q197" s="41" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="20" t="n">
@@ -22044,41 +22004,41 @@
       </c>
       <c r="B198" s="8" t="inlineStr">
         <is>
-          <t>VRN — Revize</t>
+          <t>VRN — Zařízení staveniště</t>
         </is>
       </c>
       <c r="C198" s="8" t="inlineStr">
         <is>
-          <t>Revize hydrantu vnějšího</t>
+          <t>Buňky kancelář + sociální</t>
         </is>
       </c>
       <c r="D198" s="20" t="inlineStr">
         <is>
-          <t>030161000</t>
+          <t>030011000</t>
         </is>
       </c>
       <c r="E198" s="8" t="inlineStr">
         <is>
-          <t>Revize vnějšího hydrantu pro požární zabezpečení (DN min. 80, vzdálenost 100 m dle TZ PBŘ) — periodická kontrola</t>
+          <t>Zařízení staveniště — buňka kancelář + sociální buňka (WC + šatna), pronájem ~8 měsíců</t>
         </is>
       </c>
       <c r="F198" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>kpl-měs</t>
         </is>
       </c>
       <c r="G198" s="23" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H198" s="10" t="n"/>
       <c r="I198" s="10" t="n"/>
       <c r="J198" s="8" t="inlineStr">
         <is>
-          <t>revize_specialista</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K198" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L198" s="20" t="inlineStr">
         <is>
@@ -22087,12 +22047,12 @@
       </c>
       <c r="M198" s="8" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — vnější odběrné místo požární vody, revize před kolaudací</t>
+          <t>TZ B m.1.m realizace 2026-2027 + standard staveniště RD městská zástavba</t>
         </is>
       </c>
       <c r="N198" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O198" s="26" t="inlineStr">
@@ -22114,22 +22074,22 @@
       </c>
       <c r="C199" s="8" t="inlineStr">
         <is>
-          <t>Buňky kancelář + sociální</t>
+          <t>Mobilní WC</t>
         </is>
       </c>
       <c r="D199" s="20" t="inlineStr">
         <is>
-          <t>030011000</t>
+          <t>030013000</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
         <is>
-          <t>Zařízení staveniště — buňka kancelář + sociální buňka (WC + šatna), pronájem ~8 měsíců</t>
+          <t>Mobilní chemické WC TOI TOI pro pracovníky — pronájem ~8 měsíců</t>
         </is>
       </c>
       <c r="F199" s="20" t="inlineStr">
         <is>
-          <t>kpl-měs</t>
+          <t>ks-měs</t>
         </is>
       </c>
       <c r="G199" s="23" t="n">
@@ -22152,7 +22112,7 @@
       </c>
       <c r="M199" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.1.m realizace 2026-2027 + standard staveniště RD městská zástavba</t>
+          <t>BOZP — mobilní WC povinné pro stavbu RD</t>
         </is>
       </c>
       <c r="N199" s="20" t="inlineStr">
@@ -22179,26 +22139,26 @@
       </c>
       <c r="C200" s="8" t="inlineStr">
         <is>
-          <t>Mobilní WC</t>
+          <t>El. odběr + vodovodní odběr stavby</t>
         </is>
       </c>
       <c r="D200" s="20" t="inlineStr">
         <is>
-          <t>030013000</t>
+          <t>031011000</t>
         </is>
       </c>
       <c r="E200" s="8" t="inlineStr">
         <is>
-          <t>Mobilní chemické WC TOI TOI pro pracovníky — pronájem ~8 měsíců</t>
+          <t>El. odběr stavby (zřízení staveništního rozvaděče + měřič) + vodovodní odběr (zřízení staveništní přípojky + vodoměr) — ~8 měsíců</t>
         </is>
       </c>
       <c r="F200" s="20" t="inlineStr">
         <is>
-          <t>ks-měs</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G200" s="23" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H200" s="10" t="n"/>
       <c r="I200" s="10" t="n"/>
@@ -22217,7 +22177,7 @@
       </c>
       <c r="M200" s="8" t="inlineStr">
         <is>
-          <t>BOZP — mobilní WC povinné pro stavbu RD</t>
+          <t>Standard staveniště — el. + voda zřízení a odběr po dobu stavby</t>
         </is>
       </c>
       <c r="N200" s="20" t="inlineStr">
@@ -22244,17 +22204,17 @@
       </c>
       <c r="C201" s="8" t="inlineStr">
         <is>
-          <t>El. odběr + vodovodní odběr stavby</t>
+          <t>Voda staveniště</t>
         </is>
       </c>
       <c r="D201" s="20" t="inlineStr">
         <is>
-          <t>031011000</t>
+          <t>012103101</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
         <is>
-          <t>El. odběr stavby (zřízení staveništního rozvaděče + měřič) + vodovodní odběr (zřízení staveništní přípojky + vodoměr) — ~8 měsíců</t>
+          <t>Voda staveniště — napojení na stávající vodovodní přípojku, dočasné rozvody na staveništi (mísení malt, čištění, soc. zázemí), paušál pro dobu výstavby ~18 měs.</t>
         </is>
       </c>
       <c r="F201" s="20" t="inlineStr">
@@ -22273,7 +22233,7 @@
         </is>
       </c>
       <c r="K201" s="24" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L201" s="20" t="inlineStr">
         <is>
@@ -22282,12 +22242,12 @@
       </c>
       <c r="M201" s="8" t="inlineStr">
         <is>
-          <t>Standard staveniště — el. + voda zřízení a odběr po dobu stavby</t>
+          <t>TZ B Souhrnná m.5 — 'Stávající vodovodní přípojka z veřejného vodovodu'</t>
         </is>
       </c>
       <c r="N201" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O201" s="26" t="inlineStr">
@@ -22296,7 +22256,11 @@
         </is>
       </c>
       <c r="P201" s="41" t="n"/>
-      <c r="Q201" s="41" t="n"/>
+      <c r="Q201" s="41" t="inlineStr">
+        <is>
+          <t>GAP_003</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="20" t="n">
@@ -22304,27 +22268,27 @@
       </c>
       <c r="B202" s="8" t="inlineStr">
         <is>
-          <t>VRN — Zařízení staveniště</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="C202" s="8" t="inlineStr">
         <is>
-          <t>Voda staveniště</t>
+          <t>Hlavní vypínač TOTAL STOP + požární značení</t>
         </is>
       </c>
       <c r="D202" s="20" t="inlineStr">
         <is>
-          <t>012103101</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E202" s="8" t="inlineStr">
         <is>
-          <t>Voda staveniště — napojení na stávající vodovodní přípojku, dočasné rozvody na staveništi (mísení malt, čištění, soc. zázemí), paušál pro dobu výstavby ~18 měs.</t>
+          <t>Hlavní vypínač elektrické energie TOTAL STOP + požární značení rozvodného zařízení a uzávěrů (voda/elektro)</t>
         </is>
       </c>
       <c r="F202" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>soubor</t>
         </is>
       </c>
       <c r="G202" s="23" t="n">
@@ -22334,11 +22298,11 @@
       <c r="I202" s="10" t="n"/>
       <c r="J202" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>elektrikar</t>
         </is>
       </c>
       <c r="K202" s="24" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="L202" s="20" t="inlineStr">
         <is>
@@ -22347,7 +22311,7 @@
       </c>
       <c r="M202" s="8" t="inlineStr">
         <is>
-          <t>TZ B Souhrnná m.5 — 'Stávající vodovodní přípojka z veřejného vodovodu'</t>
+          <t>PBŘ D.3 §16.05/16.06</t>
         </is>
       </c>
       <c r="N202" s="20" t="inlineStr">
@@ -22360,10 +22324,10 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P202" s="41" t="n"/>
+      <c r="P202" s="41" t="inlineStr"/>
       <c r="Q202" s="41" t="inlineStr">
         <is>
-          <t>GAP_003</t>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -22373,12 +22337,12 @@
       </c>
       <c r="B203" s="8" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>M-24 VZT</t>
         </is>
       </c>
       <c r="C203" s="8" t="inlineStr">
         <is>
-          <t>Hlavní vypínač TOTAL STOP + požární značení</t>
+          <t>Lokální odtah digestoří kuchyní</t>
         </is>
       </c>
       <c r="D203" s="20" t="inlineStr">
@@ -22388,26 +22352,26 @@
       </c>
       <c r="E203" s="8" t="inlineStr">
         <is>
-          <t>Hlavní vypínač elektrické energie TOTAL STOP + požární značení rozvodného zařízení a uzávěrů (voda/elektro)</t>
+          <t>Lokální odtah digestoří kuchyní (1.NP + 3.NP) — dodávka + montáž digestoře + prostup fasádou/střechou + zpětná klapka</t>
         </is>
       </c>
       <c r="F203" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G203" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H203" s="10" t="n"/>
       <c r="I203" s="10" t="n"/>
       <c r="J203" s="8" t="inlineStr">
         <is>
-          <t>elektrikar</t>
+          <t>vzduchotechnik</t>
         </is>
       </c>
       <c r="K203" s="24" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="L203" s="20" t="inlineStr">
         <is>
@@ -22416,7 +22380,7 @@
       </c>
       <c r="M203" s="8" t="inlineStr">
         <is>
-          <t>PBŘ D.3 §16.05/16.06</t>
+          <t>B zpráva — VZT: obytné místnosti větrání okny, kuchyně lokální odtah digestoří</t>
         </is>
       </c>
       <c r="N203" s="20" t="inlineStr">
@@ -22436,78 +22400,9 @@
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="20" t="n">
-        <v>203</v>
-      </c>
-      <c r="B204" s="8" t="inlineStr">
-        <is>
-          <t>M-24 VZT</t>
-        </is>
-      </c>
-      <c r="C204" s="8" t="inlineStr">
-        <is>
-          <t>Lokální odtah digestoří kuchyní</t>
-        </is>
-      </c>
-      <c r="D204" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E204" s="8" t="inlineStr">
-        <is>
-          <t>Lokální odtah digestoří kuchyní (1.NP + 3.NP) — dodávka + montáž digestoře + prostup fasádou/střechou + zpětná klapka</t>
-        </is>
-      </c>
-      <c r="F204" s="20" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G204" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H204" s="10" t="n"/>
-      <c r="I204" s="10" t="n"/>
-      <c r="J204" s="8" t="inlineStr">
-        <is>
-          <t>vzduchotechnik</t>
-        </is>
-      </c>
-      <c r="K204" s="24" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L204" s="20" t="inlineStr">
-        <is>
-          <t>needs_production_lookup</t>
-        </is>
-      </c>
-      <c r="M204" s="8" t="inlineStr">
-        <is>
-          <t>B zpráva — VZT: obytné místnosti větrání okny, kuchyně lokální odtah digestoří</t>
-        </is>
-      </c>
-      <c r="N204" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O204" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
-        </is>
-      </c>
-      <c r="P204" s="41" t="inlineStr"/>
-      <c r="Q204" s="41" t="inlineStr">
-        <is>
-          <t>DODATEK_PBR_GAPS_2026-06-01</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O204"/>
-  <conditionalFormatting sqref="K2:K204">
+  <autoFilter ref="A1:O203"/>
+  <conditionalFormatting sqref="K2:K203">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0" stopIfTrue="1">
       <formula>0.70</formula>
     </cfRule>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2_final.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2_final.xlsx
@@ -21,8 +21,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Var_A_Agregovany_Dum'!$A$1:$G$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Var_A_Agregovany_Sklad'!$A$1:$G$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$132</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$203</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$202</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Var_F_URS_Verification_Trail'!$A$1:$H$14</definedName>
   </definedNames>
@@ -1009,11 +1009,11 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>HSV položkově (118 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 131 řádků.</t>
+          <t>HSV položkově (117 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 130 řádků.</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D24" s="10" t="n"/>
       <c r="E24" s="10" t="n"/>
@@ -1027,11 +1027,11 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Plný detail (202 dum + 31 sklad = 233 položek). Cílový rozsah pro produkční pricing.</t>
+          <t>Plný detail (201 dum + 31 sklad = 232 položek). Cílový rozsah pro produkční pricing.</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D25" s="10" t="n"/>
       <c r="E25" s="10" t="n"/>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>233 (202 dum + 31 sklad)</t>
+          <t>232 (201 dum + 31 sklad)</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>HSV 118 | M 2 | PSV 56 | TZB 34 | VRN 23</t>
+          <t>HSV 117 | M 2 | PSV 56 | TZB 34 | VRN 23</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>0.99: 17 | 0.95: 32 | 0.90: 35 | 0.85: 41 | 0.80: 21 | 0.75: 71 | 0.70: 4 | 0.60: 3 | 0.50: 4 | 0.00: 5</t>
+          <t>0.99: 17 | 0.95: 32 | 0.90: 34 | 0.85: 41 | 0.80: 21 | 0.75: 71 | 0.70: 4 | 0.60: 3 | 0.50: 4 | 0.00: 5</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>8 WebSearch verified (3.4 %) ✓ | 5 wrong leaf flagged (2.1 %) ⚠ | 155 needs_production_lookup (66.5 %)</t>
+          <t>8 WebSearch verified (3.4 %) ✓ | 5 wrong leaf flagged (2.2 %) ⚠ | 155 needs_production_lookup (66.8 %)</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>30 items (viz Otazky_pro_Karla docx)</t>
+          <t>31 items (viz Otazky_pro_Karla docx)</t>
         </is>
       </c>
     </row>
@@ -1182,10 +1182,10 @@
       <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Rozpočet generován STAVAGENT pipelinem z DSP dokumentace s DPS-grade DXF metadaty.
-233 položek celkem (202 dum + 31 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
-Confidence distribution: 17×0.99 · 32×0.95 · 35×0.90 · 41×0.85 · 21×0.80 · 71×0.75 · 4×0.70 · 3×0.60 · 4×0.50 · 5×0.00.
+232 položek celkem (201 dum + 31 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
+Confidence distribution: 17×0.99 · 32×0.95 · 34×0.90 · 41×0.85 · 21×0.80 · 71×0.75 · 4×0.70 · 3×0.60 · 4×0.50 · 5×0.00.
 25 položek vzniklo per-room expansion ze 9 aggregate parents (každá expanded položka tagged _expansion_origin).
-10 položek recalculated s exact external perimeter 38.70 m (DXF km_R_návrh_tlustá 2 closed polygon) vs prior fallback 41.0 m.
+9 položek recalculated s exact external perimeter 38.70 m (DXF km_R_návrh_tlustá 2 closed polygon) vs prior fallback 41.0 m.
 Skladby vrstev (Sheet 8 Var_E) pochází POUZE z TZ explicit text + DXF cross-validation HATCH patterns. ŽÁDNÉ generic 'standardní RD' assumption — kde TZ silent, explicit fallback flag s ČSN default.
 ÚRS kódy navrženy heuristikou. Part 5b WebSearch verified 12 codes / 8 unique families (viz Sheet 9 Var_F_URS_Verification_Trail). Wrong-leaf pattern identifikován: heuristika odhadne 6-cifernou rodinu správně v ~75 % případů, ale 9-cifrový leaf je chybný v ~63 % (odlišný distance band / materiál / geometrie / lokace). Produkční URS_MATCHER service (Perplexity-driven online lookup) nutný pro finální ověření zbývajících položek před cenotvorbou. Jednotkové ceny ponecháno k vyplnění zhotovitelem.</t>
         </is>
@@ -1255,7 +1255,7 @@
     <row r="55">
       <c r="A55" s="45" t="inlineStr">
         <is>
-          <t>• Total items: 233 (202 dům + 31 sklad) — vč. CEV +3 (komín/zídky/drenáž), anchor-gap +2 (přesun hmot/lešení), terasa-area fix + venkovní schody na terénu. 70 items s realizuje_skladbu.</t>
+          <t>• Total items: 232 (201 dům + 31 sklad) — vč. CEV +3 (komín/zídky/drenáž), anchor-gap +2 (přesun hmot/lešení), terasa-area fix + venkovní schody na terénu. 69 items s realizuje_skladbu.</t>
         </is>
       </c>
     </row>
@@ -2670,11 +2670,11 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Příprava podkladu; ETICS EPS 70F grey 160 mm; ETICS sokl XPS; Špalety EPS; … (+5 dalších)</t>
+          <t>Příprava podkladu; ETICS EPS 70F grey 160 mm; Špalety EPS; Profilace fasády; … (+4 dalších)</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8" s="10" t="n"/>
       <c r="F8" s="10" t="n"/>
@@ -3207,7 +3207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J132"/>
+  <dimension ref="A1:J131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6970,16 +6970,16 @@
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>ETICS sokl XPS — ETICS sokl — XPS λ=0.034 tl. 120 mm + soklový profil + cihelný obklad spárovaný</t>
+          <t>Špalety EPS — Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
         </is>
       </c>
       <c r="E94" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="F94" s="22" t="n">
-        <v>13.5</v>
+        <v>82.2</v>
       </c>
       <c r="G94" s="10" t="n"/>
       <c r="H94" s="10" t="n"/>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="J94" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 622223111</t>
+          <t>URS-prop 622221221</t>
         </is>
       </c>
     </row>
@@ -7010,16 +7010,16 @@
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Špalety EPS — Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
+          <t>Profilace fasády — Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
         </is>
       </c>
       <c r="E95" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="F95" s="22" t="n">
-        <v>82.2</v>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="F95" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="G95" s="10" t="n"/>
       <c r="H95" s="10" t="n"/>
@@ -7050,16 +7050,16 @@
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Profilace fasády — Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
+          <t>Tenkovrstvá omítka pastovitá — Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
         </is>
       </c>
       <c r="E96" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="F96" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F96" s="22" t="n">
+        <v>276.7</v>
       </c>
       <c r="G96" s="10" t="n"/>
       <c r="H96" s="10" t="n"/>
@@ -7070,7 +7070,7 @@
       </c>
       <c r="J96" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 622221221</t>
+          <t>URS-prop 622521111</t>
         </is>
       </c>
     </row>
@@ -7085,32 +7085,32 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda ETICS</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>Tenkovrstvá omítka pastovitá — Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
+          <t>Demontáž oken — Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
         </is>
       </c>
       <c r="E97" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F97" s="22" t="n">
-        <v>290.2</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="F97" s="23" t="n">
+        <v>16</v>
       </c>
       <c r="G97" s="10" t="n"/>
       <c r="H97" s="10" t="n"/>
       <c r="I97" s="8" t="inlineStr">
         <is>
-          <t>fasadnik_etics</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="J97" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 622521111</t>
+          <t>URS-prop 978013181</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>Demontáž oken — Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
+          <t>Demontáž vstupních dveří venkovních — Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
         </is>
       </c>
       <c r="E98" s="20" t="inlineStr">
@@ -7139,7 +7139,7 @@
         </is>
       </c>
       <c r="F98" s="23" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G98" s="10" t="n"/>
       <c r="H98" s="10" t="n"/>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>Demontáž vstupních dveří venkovních — Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
+          <t>Demontáž vnitřních dveří vč. zárubní — Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
         </is>
       </c>
       <c r="E99" s="20" t="inlineStr">
@@ -7179,7 +7179,7 @@
         </is>
       </c>
       <c r="F99" s="23" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G99" s="10" t="n"/>
       <c r="H99" s="10" t="n"/>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="J99" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 978013181</t>
+          <t>URS-prop 968072456</t>
         </is>
       </c>
     </row>
@@ -7210,16 +7210,16 @@
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>Demontáž vnitřních dveří vč. zárubní — Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
+          <t>Bourání zdiva komínu — Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
         </is>
       </c>
       <c r="E100" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="F100" s="23" t="n">
-        <v>15</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F100" s="22" t="n">
+        <v>0.6</v>
       </c>
       <c r="G100" s="10" t="n"/>
       <c r="H100" s="10" t="n"/>
@@ -7230,7 +7230,7 @@
       </c>
       <c r="J100" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 968072456</t>
+          <t>URS-prop 962024141</t>
         </is>
       </c>
     </row>
@@ -7250,7 +7250,7 @@
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>Bourání zdiva komínu — Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
+          <t>Bourání venkovních konstrukcí — Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
         </is>
       </c>
       <c r="E101" s="20" t="inlineStr">
@@ -7259,7 +7259,7 @@
         </is>
       </c>
       <c r="F101" s="22" t="n">
-        <v>0.6</v>
+        <v>8</v>
       </c>
       <c r="G101" s="10" t="n"/>
       <c r="H101" s="10" t="n"/>
@@ -7270,7 +7270,7 @@
       </c>
       <c r="J101" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 962024141</t>
+          <t>URS-prop 961044111</t>
         </is>
       </c>
     </row>
@@ -7285,32 +7285,32 @@
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>Bourání venkovních konstrukcí — Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
+          <t>Drenáž za bílou vanou — Drenáž za opěrnou stěnou (bílou vanou) — drenážní trubka DN100 vlnitá perforovaná + štěrkový obsyp 16/32 + geotextilie + napojení do dešťové kanalizace, L po obvodu BV</t>
         </is>
       </c>
       <c r="E102" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F102" s="22" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G102" s="10" t="n"/>
       <c r="H102" s="10" t="n"/>
       <c r="I102" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="J102" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 961044111</t>
+          <t>URS-prop 877315111</t>
         </is>
       </c>
     </row>
@@ -7320,37 +7320,37 @@
       </c>
       <c r="B103" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>HSV-1 Zemní práce</t>
+          <t>HSV-5 Komunikace + schodiště</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>Drenáž za bílou vanou — Drenáž za opěrnou stěnou (bílou vanou) — drenážní trubka DN100 vlnitá perforovaná + štěrkový obsyp 16/32 + geotextilie + napojení do dešťové kanalizace, L po obvodu BV</t>
+          <t>Sklad mezipodesta schodiště prefa — Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
         </is>
       </c>
       <c r="E103" s="20" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F103" s="22" t="n">
-        <v>12</v>
+        <v>5.5</v>
       </c>
       <c r="G103" s="10" t="n"/>
       <c r="H103" s="10" t="n"/>
       <c r="I103" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>betonar</t>
         </is>
       </c>
       <c r="J103" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 877315111</t>
+          <t>URS-prop 121301101</t>
         </is>
       </c>
     </row>
@@ -7360,37 +7360,37 @@
       </c>
       <c r="B104" s="20" t="inlineStr">
         <is>
-          <t>260217_sklad</t>
+          <t>260219_dum</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + schodiště</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>Sklad mezipodesta schodiště prefa — Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
+          <t>Venkovní schody na terénu (zahrada za opěrnou stěnou) — Venkovní schody na terénu z betonových dílců do betonového lože — rameno 1: 8×175×280 mm + rameno 2: 5×175×280 mm (13 stupňů), zahrada za opěrnou stěnou</t>
         </is>
       </c>
       <c r="E104" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F104" s="22" t="n">
-        <v>5.5</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="F104" s="23" t="n">
+        <v>13</v>
       </c>
       <c r="G104" s="10" t="n"/>
       <c r="H104" s="10" t="n"/>
       <c r="I104" s="8" t="inlineStr">
         <is>
-          <t>betonar</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="J104" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 121301101</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -7405,12 +7405,12 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>HSV-1 Zemní práce</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>Venkovní schody na terénu (zahrada za opěrnou stěnou) — Venkovní schody na terénu z betonových dílců do betonového lože — rameno 1: 8×175×280 mm + rameno 2: 5×175×280 mm (13 stupňů), zahrada za opěrnou stěnou</t>
+          <t>Spojovací prostředky krovu — svorníky tesařských spojů — Montáž svorníků / šroubů tesařských spojů krovu délky přes 150 do 300 mm — spojení kleštin 2×60/180 mm s krokvemi (svorník cca 250 mm, M12), vč. tyče závitové + matic + podložek</t>
         </is>
       </c>
       <c r="E105" s="20" t="inlineStr">
@@ -7419,18 +7419,18 @@
         </is>
       </c>
       <c r="F105" s="23" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="G105" s="10" t="n"/>
       <c r="H105" s="10" t="n"/>
       <c r="I105" s="8" t="inlineStr">
         <is>
-          <t>zednik</t>
+          <t>tesar</t>
         </is>
       </c>
       <c r="J105" s="8" t="inlineStr">
         <is>
-          <t>URS-prop —</t>
+          <t>URS-prop 762085112</t>
         </is>
       </c>
     </row>
@@ -7445,32 +7445,32 @@
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Krov + střecha</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>Spojovací prostředky krovu — svorníky tesařských spojů — Montáž svorníků / šroubů tesařských spojů krovu délky přes 150 do 300 mm — spojení kleštin 2×60/180 mm s krokvemi (svorník cca 250 mm, M12), vč. tyče závitové + matic + podložek</t>
+          <t>Strop 1.NP/2.NP — kročejová izolace (S07) — Desky kročejové izolace (Isover T-P) tl. 30 mm — trámový strop 1.NP/2.NP</t>
         </is>
       </c>
       <c r="E106" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="F106" s="23" t="n">
-        <v>50</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F106" s="22" t="n">
+        <v>59.5</v>
       </c>
       <c r="G106" s="10" t="n"/>
       <c r="H106" s="10" t="n"/>
       <c r="I106" s="8" t="inlineStr">
         <is>
-          <t>tesar</t>
+          <t>izolater_TI</t>
         </is>
       </c>
       <c r="J106" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 762085112</t>
+          <t>URS-prop 713191</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>Strop 1.NP/2.NP — kročejová izolace (S07) — Desky kročejové izolace (Isover T-P) tl. 30 mm — trámový strop 1.NP/2.NP</t>
+          <t>Strop 1.NP/2.NP — separační geotextilie (S07) — Separační geotextilie pod suchý podsyp — trámový strop 1.NP/2.NP</t>
         </is>
       </c>
       <c r="E107" s="20" t="inlineStr">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="J107" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 713191</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>Strop 1.NP/2.NP — separační geotextilie (S07) — Separační geotextilie pod suchý podsyp — trámový strop 1.NP/2.NP</t>
+          <t>Strop 2.NP/3.NP — min. vata výplň mezi nosníky (S09) — Tepelná/akustická izolace minerální vata výplň mezi ocelové nosníky stropu 2.NP/3.NP, tl. 180/200 mm</t>
         </is>
       </c>
       <c r="E108" s="20" t="inlineStr">
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="F108" s="22" t="n">
-        <v>59.5</v>
+        <v>104.4</v>
       </c>
       <c r="G108" s="10" t="n"/>
       <c r="H108" s="10" t="n"/>
@@ -7550,7 +7550,7 @@
       </c>
       <c r="J108" s="8" t="inlineStr">
         <is>
-          <t>URS-prop —</t>
+          <t>URS-prop 713121</t>
         </is>
       </c>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>Strop 2.NP/3.NP — min. vata výplň mezi nosníky (S09) — Tepelná/akustická izolace minerální vata výplň mezi ocelové nosníky stropu 2.NP/3.NP, tl. 180/200 mm</t>
+          <t>Strop klemba mezi patry — Fermacell (S08) — Roznášecí sádrovláknité dílce Fermacell 2E22 tl. 25 mm — suchá skladba nad cihelnou klembou S08</t>
         </is>
       </c>
       <c r="E109" s="20" t="inlineStr">
@@ -7578,19 +7578,17 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="F109" s="22" t="n">
-        <v>104.4</v>
-      </c>
+      <c r="F109" s="22" t="n"/>
       <c r="G109" s="10" t="n"/>
       <c r="H109" s="10" t="n"/>
       <c r="I109" s="8" t="inlineStr">
         <is>
-          <t>izolater_TI</t>
+          <t>suchá_vystavba</t>
         </is>
       </c>
       <c r="J109" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 713121</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7608,7 @@
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>Strop klemba mezi patry — Fermacell (S08) — Roznášecí sádrovláknité dílce Fermacell 2E22 tl. 25 mm — suchá skladba nad cihelnou klembou S08</t>
+          <t>Strop klemba mezi patry — kročejová izolace (S08) — Desky kročejové izolace (Isover T-P) tl. 30 mm — suchá skladba nad klembou S08</t>
         </is>
       </c>
       <c r="E110" s="20" t="inlineStr">
@@ -7623,12 +7621,12 @@
       <c r="H110" s="10" t="n"/>
       <c r="I110" s="8" t="inlineStr">
         <is>
-          <t>suchá_vystavba</t>
+          <t>izolater_TI</t>
         </is>
       </c>
       <c r="J110" s="8" t="inlineStr">
         <is>
-          <t>URS-prop —</t>
+          <t>URS-prop 713191</t>
         </is>
       </c>
     </row>
@@ -7648,7 +7646,7 @@
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>Strop klemba mezi patry — kročejová izolace (S08) — Desky kročejové izolace (Isover T-P) tl. 30 mm — suchá skladba nad klembou S08</t>
+          <t>Strop klemba mezi patry — suchý podsyp + dřevěný rošt (S08) — Vyrovnávací suchý podsyp keramzit/liapor + dřevěný rošt tl. 50 mm — nad klembou S08</t>
         </is>
       </c>
       <c r="E111" s="20" t="inlineStr">
@@ -7661,12 +7659,12 @@
       <c r="H111" s="10" t="n"/>
       <c r="I111" s="8" t="inlineStr">
         <is>
-          <t>izolater_TI</t>
+          <t>suchá_vystavba</t>
         </is>
       </c>
       <c r="J111" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 713191</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7684,7 @@
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>Strop klemba mezi patry — suchý podsyp + dřevěný rošt (S08) — Vyrovnávací suchý podsyp keramzit/liapor + dřevěný rošt tl. 50 mm — nad klembou S08</t>
+          <t>Strop klemba mezi patry — separační vrstva (S08) — Separační vrstva pod suchý podsyp — nad cihelnou klembou S08</t>
         </is>
       </c>
       <c r="E112" s="20" t="inlineStr">
@@ -7719,12 +7717,12 @@
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-7 Fasáda + zateplení</t>
         </is>
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>Strop klemba mezi patry — separační vrstva (S08) — Separační vrstva pod suchý podsyp — nad cihelnou klembou S08</t>
+          <t>Sokl suterénu — sanační zateplení (S03) — Sanační zateplení soklu — sanační izolační deska Styrcon 200 + lepící tmel (Lepstyr plus) + armovací vrstva s tkaninou + penetrace</t>
         </is>
       </c>
       <c r="E113" s="20" t="inlineStr">
@@ -7732,12 +7730,14 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="F113" s="22" t="n"/>
+      <c r="F113" s="22" t="n">
+        <v>23</v>
+      </c>
       <c r="G113" s="10" t="n"/>
       <c r="H113" s="10" t="n"/>
       <c r="I113" s="8" t="inlineStr">
         <is>
-          <t>suchá_vystavba</t>
+          <t>fasader</t>
         </is>
       </c>
       <c r="J113" s="8" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>Sokl suterénu — sanační zateplení (S03) — Sanační zateplení soklu — sanační izolační deska Styrcon 200 + lepící tmel (Lepstyr plus) + armovací vrstva s tkaninou + penetrace</t>
+          <t>Sokl pod terénem — drenážní nopová folie (S03a) — Drenážní vrstva — nopová folie tl. 20 mm na suterénní stěnu pod úrovní terénu</t>
         </is>
       </c>
       <c r="E114" s="20" t="inlineStr">
@@ -7777,7 +7777,7 @@
       <c r="H114" s="10" t="n"/>
       <c r="I114" s="8" t="inlineStr">
         <is>
-          <t>fasader</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="J114" s="8" t="inlineStr">
@@ -7802,7 +7802,7 @@
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>Sokl pod terénem — drenážní nopová folie (S03a) — Drenážní vrstva — nopová folie tl. 20 mm na suterénní stěnu pod úrovní terénu</t>
+          <t>Sokl nad terénem — provětraný obklad (S03b) — Provětrávaná mezera s kotevním roštem 40 mm + keramický obklad 20 mm — sokl nad úrovní terénu</t>
         </is>
       </c>
       <c r="E115" s="20" t="inlineStr">
@@ -7817,7 +7817,7 @@
       <c r="H115" s="10" t="n"/>
       <c r="I115" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="J115" s="8" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda + zateplení</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>Sokl nad terénem — provětraný obklad (S03b) — Provětrávaná mezera s kotevním roštem 40 mm + keramický obklad 20 mm — sokl nad úrovní terénu</t>
+          <t>Střecha — pojistná HI folie pod Al krytinu (S10) — Pojistná hydroizolační folie pod hliníkovou falcovanou krytinu (nad celoplošným bedněním)</t>
         </is>
       </c>
       <c r="E116" s="20" t="inlineStr">
@@ -7851,13 +7851,13 @@
         </is>
       </c>
       <c r="F116" s="22" t="n">
-        <v>23</v>
+        <v>140.94</v>
       </c>
       <c r="G116" s="10" t="n"/>
       <c r="H116" s="10" t="n"/>
       <c r="I116" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>pokryvac</t>
         </is>
       </c>
       <c r="J116" s="8" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Krov + střecha</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>Střecha — pojistná HI folie pod Al krytinu (S10) — Pojistná hydroizolační folie pod hliníkovou falcovanou krytinu (nad celoplošným bedněním)</t>
+          <t>Demontáž vnějšího keram. obkladu suterénu (S03 stávající) — Demontáž stávajícího vnějšího keramického obkladu suterénní stěny (sokl) tl. 20 mm</t>
         </is>
       </c>
       <c r="E117" s="20" t="inlineStr">
@@ -7891,13 +7891,13 @@
         </is>
       </c>
       <c r="F117" s="22" t="n">
-        <v>140.94</v>
+        <v>23</v>
       </c>
       <c r="G117" s="10" t="n"/>
       <c r="H117" s="10" t="n"/>
       <c r="I117" s="8" t="inlineStr">
         <is>
-          <t>pokryvac</t>
+          <t>bourac</t>
         </is>
       </c>
       <c r="J117" s="8" t="inlineStr">
@@ -7912,17 +7912,17 @@
       </c>
       <c r="B118" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-5 Komunikace + vjezd</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>Demontáž vnějšího keram. obkladu suterénu (S03 stávající) — Demontáž stávajícího vnějšího keramického obkladu suterénní stěny (sokl) tl. 20 mm</t>
+          <t>Vjezd Dvořákova — napojení na komunikaci — Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťové vody na pozemek (ne na komunikaci)</t>
         </is>
       </c>
       <c r="E118" s="20" t="inlineStr">
@@ -7930,14 +7930,12 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="F118" s="22" t="n">
-        <v>23</v>
-      </c>
+      <c r="F118" s="22" t="n"/>
       <c r="G118" s="10" t="n"/>
       <c r="H118" s="10" t="n"/>
       <c r="I118" s="8" t="inlineStr">
         <is>
-          <t>bourac</t>
+          <t>komunikace</t>
         </is>
       </c>
       <c r="J118" s="8" t="inlineStr">
@@ -7955,32 +7953,34 @@
           <t>260217_sklad</t>
         </is>
       </c>
-      <c r="C119" s="8" t="inlineStr">
-        <is>
-          <t>HSV-5 Komunikace + vjezd</t>
+      <c r="C119" s="21" t="inlineStr">
+        <is>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr">
         <is>
-          <t>Vjezd Dvořákova — napojení na komunikaci — Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťové vody na pozemek (ne na komunikaci)</t>
+          <t>[agregát] 2 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána</t>
         </is>
       </c>
       <c r="E119" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F119" s="22" t="n"/>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F119" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="G119" s="10" t="n"/>
       <c r="H119" s="10" t="n"/>
       <c r="I119" s="8" t="inlineStr">
         <is>
-          <t>komunikace</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J119" s="8" t="inlineStr">
         <is>
-          <t>URS-prop —</t>
+          <t>agregát</t>
         </is>
       </c>
     </row>
@@ -7995,12 +7995,12 @@
       </c>
       <c r="C120" s="21" t="inlineStr">
         <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 2 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána</t>
+          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
         </is>
       </c>
       <c r="E120" s="20" t="inlineStr">
@@ -8035,12 +8035,12 @@
       </c>
       <c r="C121" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
+          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E121" s="20" t="inlineStr">
@@ -8070,17 +8070,17 @@
       </c>
       <c r="B122" s="20" t="inlineStr">
         <is>
-          <t>260217_sklad</t>
+          <t>260219_dum</t>
         </is>
       </c>
       <c r="C122" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>M-21 — Elektroinstalace silnoproudá</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
+          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E122" s="20" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="C123" s="21" t="inlineStr">
         <is>
-          <t>M-21 — Elektroinstalace silnoproudá</t>
+          <t>M-24</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
+          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
         </is>
       </c>
       <c r="E123" s="20" t="inlineStr">
@@ -8155,12 +8155,12 @@
       </c>
       <c r="C124" s="21" t="inlineStr">
         <is>
-          <t>M-24</t>
+          <t>PSV-71 — Izolace HI + TI</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
+          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E124" s="20" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="C125" s="21" t="inlineStr">
         <is>
-          <t>PSV-71 — Izolace HI + TI</t>
+          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
         </is>
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
+          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
         </is>
       </c>
       <c r="E125" s="20" t="inlineStr">
@@ -8235,12 +8235,12 @@
       </c>
       <c r="C126" s="21" t="inlineStr">
         <is>
-          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
+          <t>PSV-73 — Vytápění + komín</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
+          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E126" s="20" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="C127" s="21" t="inlineStr">
         <is>
-          <t>PSV-73 — Vytápění + komín</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
+          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
         </is>
       </c>
       <c r="E127" s="20" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="C128" s="21" t="inlineStr">
         <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
+          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
         </is>
       </c>
       <c r="E128" s="20" t="inlineStr">
@@ -8355,12 +8355,12 @@
       </c>
       <c r="C129" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>PSV-78 — Povrchové úpravy</t>
         </is>
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
+          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
         </is>
       </c>
       <c r="E129" s="20" t="inlineStr">
@@ -8395,12 +8395,12 @@
       </c>
       <c r="C130" s="21" t="inlineStr">
         <is>
-          <t>PSV-78 — Povrchové úpravy</t>
+          <t>PSV-95 — Detekce požární</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
+          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
         </is>
       </c>
       <c r="E130" s="20" t="inlineStr">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="C131" s="21" t="inlineStr">
         <is>
-          <t>PSV-95 — Detekce požární</t>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
         </is>
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
         </is>
       </c>
       <c r="E131" s="20" t="inlineStr">
@@ -8464,48 +8464,8 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="20" t="n">
-        <v>131</v>
-      </c>
-      <c r="B132" s="20" t="inlineStr">
-        <is>
-          <t>260219_dum</t>
-        </is>
-      </c>
-      <c r="C132" s="21" t="inlineStr">
-        <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
-        </is>
-      </c>
-      <c r="D132" s="8" t="inlineStr">
-        <is>
-          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
-        </is>
-      </c>
-      <c r="E132" s="20" t="inlineStr">
-        <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F132" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G132" s="10" t="n"/>
-      <c r="H132" s="10" t="n"/>
-      <c r="I132" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J132" s="8" t="inlineStr">
-        <is>
-          <t>agregát</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J132"/>
+  <autoFilter ref="A1:J131"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8516,7 +8476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R203"/>
+  <dimension ref="A1:R202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -14662,7 +14622,7 @@
       </c>
       <c r="N88" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#35</t>
         </is>
       </c>
       <c r="O88" s="26" t="inlineStr">
@@ -14808,7 +14768,7 @@
       </c>
       <c r="N90" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#35</t>
         </is>
       </c>
       <c r="O90" s="26" t="inlineStr">
@@ -14980,26 +14940,26 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>ETICS sokl XPS</t>
+          <t>Špalety EPS</t>
         </is>
       </c>
       <c r="D93" s="20" t="inlineStr">
         <is>
-          <t>622223111</t>
+          <t>622221221</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>ETICS sokl — XPS λ=0.034 tl. 120 mm + soklový profil + cihelný obklad spárovaný</t>
+          <t>Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
         </is>
       </c>
       <c r="F93" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G93" s="22" t="n">
-        <v>13.5</v>
+        <v>82.2</v>
       </c>
       <c r="H93" s="10" t="n"/>
       <c r="I93" s="10" t="n"/>
@@ -15009,21 +14969,21 @@
         </is>
       </c>
       <c r="K93" s="24" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
       <c r="L93" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M93" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — sokl XPS + cihelný obklad + DXF perimeter</t>
+          <t>DXF okna per typ bbox + TZ ARS §3.2 EPS přesah na špaletách 35-40 mm</t>
         </is>
       </c>
       <c r="N93" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O93" s="26" t="inlineStr">
@@ -15033,14 +14993,10 @@
       </c>
       <c r="P93" s="41" t="inlineStr">
         <is>
-          <t>S01</t>
-        </is>
-      </c>
-      <c r="Q93" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+          <t>S01, S12a</t>
+        </is>
+      </c>
+      <c r="Q93" s="41" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="20" t="n">
@@ -15053,7 +15009,7 @@
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>Špalety EPS</t>
+          <t>Profilace fasády</t>
         </is>
       </c>
       <c r="D94" s="20" t="inlineStr">
@@ -15063,16 +15019,16 @@
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
+          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
         </is>
       </c>
       <c r="F94" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G94" s="22" t="n">
-        <v>82.2</v>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="G94" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H94" s="10" t="n"/>
       <c r="I94" s="10" t="n"/>
@@ -15091,12 +15047,12 @@
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>DXF okna per typ bbox + TZ ARS §3.2 EPS přesah na špaletách 35-40 mm</t>
+          <t>TZ ARS dům §3.2 — profilace různými tl. EPS</t>
         </is>
       </c>
       <c r="N94" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O94" s="26" t="inlineStr">
@@ -15122,26 +15078,26 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>Profilace fasády</t>
+          <t>Tenkovrstvá omítka pastovitá</t>
         </is>
       </c>
       <c r="D95" s="20" t="inlineStr">
         <is>
-          <t>622221221</t>
+          <t>622521111</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
+          <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
         </is>
       </c>
       <c r="F95" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="G95" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G95" s="22" t="n">
+        <v>276.7</v>
       </c>
       <c r="H95" s="10" t="n"/>
       <c r="I95" s="10" t="n"/>
@@ -15151,16 +15107,16 @@
         </is>
       </c>
       <c r="K95" s="24" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
       <c r="L95" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M95" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — profilace různými tl. EPS</t>
+          <t>TZ ARS dům §3.2 — pastovitá probarvená lomená bílá + DXF perimeter</t>
         </is>
       </c>
       <c r="N95" s="20" t="inlineStr">
@@ -15175,10 +15131,14 @@
       </c>
       <c r="P95" s="41" t="inlineStr">
         <is>
-          <t>S01, S12a</t>
-        </is>
-      </c>
-      <c r="Q95" s="41" t="n"/>
+          <t>S01, S12a, S12b</t>
+        </is>
+      </c>
+      <c r="Q95" s="41" t="inlineStr">
+        <is>
+          <t>SOKL_RECONCILE_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="20" t="n">
@@ -15186,22 +15146,22 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda ETICS</t>
+          <t>PSV-71 Izolace HI</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>Tenkovrstvá omítka pastovitá</t>
+          <t>HI pod ŽB deskou 1.NP</t>
         </is>
       </c>
       <c r="D96" s="20" t="inlineStr">
         <is>
-          <t>622521111</t>
+          <t>712311101</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
+          <t>Hydroizolace pod ŽB deskou 1.NP — modifikované asfaltové pásy SBS 2× (zároveň protiradonová bariéra)</t>
         </is>
       </c>
       <c r="F96" s="20" t="inlineStr">
@@ -15210,17 +15170,17 @@
         </is>
       </c>
       <c r="G96" s="22" t="n">
-        <v>290.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="H96" s="10" t="n"/>
       <c r="I96" s="10" t="n"/>
       <c r="J96" s="8" t="inlineStr">
         <is>
-          <t>fasadnik_etics</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K96" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L96" s="20" t="inlineStr">
         <is>
@@ -15229,12 +15189,12 @@
       </c>
       <c r="M96" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — pastovitá probarvená lomená bílá + DXF perimeter</t>
+          <t>TZ ARS dům §4 + statika §5.5 — asfaltové pásy mod. proti radonu</t>
         </is>
       </c>
       <c r="N96" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O96" s="26" t="inlineStr">
@@ -15242,14 +15202,10 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P96" s="41" t="inlineStr">
-        <is>
-          <t>S01, S12a, S12b</t>
-        </is>
-      </c>
+      <c r="P96" s="41" t="n"/>
       <c r="Q96" s="41" t="inlineStr">
         <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+          <t>URS_PHASE5B_FAMILY_VERIFIED; URS_PHASE5B_FAMILY_VERIFIED</t>
         </is>
       </c>
     </row>
@@ -15264,26 +15220,26 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>HI pod ŽB deskou 1.NP</t>
+          <t>Odvětrání radonu z podloží</t>
         </is>
       </c>
       <c r="D97" s="20" t="inlineStr">
         <is>
-          <t>712311101</t>
+          <t>712381111</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolace pod ŽB deskou 1.NP — modifikované asfaltové pásy SBS 2× (zároveň protiradonová bariéra)</t>
+          <t>Odvětrání radonu z podloží — perforované DN50 trubky v štěrkovém loži + výdech nad střechu</t>
         </is>
       </c>
       <c r="F97" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G97" s="22" t="n">
-        <v>80.40000000000001</v>
+        <v>12</v>
       </c>
       <c r="H97" s="10" t="n"/>
       <c r="I97" s="10" t="n"/>
@@ -15302,12 +15258,12 @@
       </c>
       <c r="M97" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + statika §5.5 — asfaltové pásy mod. proti radonu</t>
+          <t>TZ statika §5.5 'ochrana proti radonu — modifikované asf. pásy + odvětrání'</t>
         </is>
       </c>
       <c r="N97" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O97" s="26" t="inlineStr">
@@ -15318,7 +15274,7 @@
       <c r="P97" s="41" t="n"/>
       <c r="Q97" s="41" t="inlineStr">
         <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED; URS_PHASE5B_FAMILY_VERIFIED</t>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
         </is>
       </c>
     </row>
@@ -15333,26 +15289,26 @@
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>Odvětrání radonu z podloží</t>
-        </is>
-      </c>
-      <c r="D98" s="20" t="inlineStr">
-        <is>
-          <t>712381111</t>
+          <t>HI koupelny 1.NP + 2.NP + 3.NP</t>
+        </is>
+      </c>
+      <c r="D98" s="27" t="inlineStr">
+        <is>
+          <t>711??? ?</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>Odvětrání radonu z podloží — perforované DN50 trubky v štěrkovém loži + výdech nad střechu</t>
+          <t>Hydroizolační stěrka koupelen 3 ks — podlaha + sokl 200 mm + sprchový kout výška 2.0 m</t>
         </is>
       </c>
       <c r="F98" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G98" s="22" t="n">
-        <v>12</v>
+        <v>40.5</v>
       </c>
       <c r="H98" s="10" t="n"/>
       <c r="I98" s="10" t="n"/>
@@ -15362,7 +15318,7 @@
         </is>
       </c>
       <c r="K98" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L98" s="20" t="inlineStr">
         <is>
@@ -15371,12 +15327,12 @@
       </c>
       <c r="M98" s="8" t="inlineStr">
         <is>
-          <t>TZ statika §5.5 'ochrana proti radonu — modifikované asf. pásy + odvětrání'</t>
+          <t>DXF dum_DPZ MTEXT labels: 3× koupelna; TZ ARS — HI vana koupelny</t>
         </is>
       </c>
       <c r="N98" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#4</t>
         </is>
       </c>
       <c r="O98" s="26" t="inlineStr">
@@ -15397,22 +15353,22 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace HI</t>
+          <t>PSV-71 Izolace TI</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>HI koupelny 1.NP + 2.NP + 3.NP</t>
+          <t>Podlahový EPS 150</t>
         </is>
       </c>
       <c r="D99" s="27" t="inlineStr">
         <is>
-          <t>711??? ?</t>
+          <t>713121??? ?</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolační stěrka koupelen 3 ks — podlaha + sokl 200 mm + sprchový kout výška 2.0 m</t>
+          <t>Podlahový EPS 150 λ=0.035 tl. 120 mm — pod betonový potěr 1.NP a 3.NP</t>
         </is>
       </c>
       <c r="F99" s="20" t="inlineStr">
@@ -15421,17 +15377,17 @@
         </is>
       </c>
       <c r="G99" s="22" t="n">
-        <v>40.5</v>
+        <v>177.5</v>
       </c>
       <c r="H99" s="10" t="n"/>
       <c r="I99" s="10" t="n"/>
       <c r="J99" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>izolater_TI</t>
         </is>
       </c>
       <c r="K99" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L99" s="20" t="inlineStr">
         <is>
@@ -15440,7 +15396,7 @@
       </c>
       <c r="M99" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT labels: 3× koupelna; TZ ARS — HI vana koupelny</t>
+          <t>TZ ARS dům §4 — EPS 150 λ=0.035 tl. 120 mm</t>
         </is>
       </c>
       <c r="N99" s="20" t="inlineStr">
@@ -15471,7 +15427,7 @@
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>Podlahový EPS 150</t>
+          <t>Kročejová EPS nad ocelobeton</t>
         </is>
       </c>
       <c r="D100" s="27" t="inlineStr">
@@ -15481,7 +15437,7 @@
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>Podlahový EPS 150 λ=0.035 tl. 120 mm — pod betonový potěr 1.NP a 3.NP</t>
+          <t>Kročejová EPS 150 / 30 dB tl. 40 mm nad ocelobetonovým stropem 2.NP/3.NP</t>
         </is>
       </c>
       <c r="F100" s="20" t="inlineStr">
@@ -15490,7 +15446,7 @@
         </is>
       </c>
       <c r="G100" s="22" t="n">
-        <v>177.5</v>
+        <v>104.4</v>
       </c>
       <c r="H100" s="10" t="n"/>
       <c r="I100" s="10" t="n"/>
@@ -15500,7 +15456,7 @@
         </is>
       </c>
       <c r="K100" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L100" s="20" t="inlineStr">
         <is>
@@ -15509,12 +15465,12 @@
       </c>
       <c r="M100" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — EPS 150 λ=0.035 tl. 120 mm</t>
+          <t>TZ ARS dům §4 — kročejová EPS shora ocelobeton</t>
         </is>
       </c>
       <c r="N100" s="20" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O100" s="26" t="inlineStr">
@@ -15522,10 +15478,14 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P100" s="41" t="n"/>
+      <c r="P100" s="41" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
       <c r="Q100" s="41" t="inlineStr">
         <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+          <t>D2_KROCEJOVA_30_to_40_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -15535,41 +15495,41 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace TI</t>
+          <t>PSV-76 Klempíř</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>Kročejová EPS nad ocelobeton</t>
-        </is>
-      </c>
-      <c r="D101" s="27" t="inlineStr">
-        <is>
-          <t>713121??? ?</t>
+          <t>Oplechování krytiny</t>
+        </is>
+      </c>
+      <c r="D101" s="20" t="inlineStr">
+        <is>
+          <t>764312235</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>Kročejová EPS 150 / 30 dB tl. 40 mm nad ocelobetonovým stropem 2.NP/3.NP</t>
+          <t>Klempířské oplechování krytiny — úžlabí, hřeben, štítové lemy (Al / Pzn lakovaný 0.55 mm)</t>
         </is>
       </c>
       <c r="F101" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G101" s="22" t="n">
-        <v>104.4</v>
+        <v>69.5</v>
       </c>
       <c r="H101" s="10" t="n"/>
       <c r="I101" s="10" t="n"/>
       <c r="J101" s="8" t="inlineStr">
         <is>
-          <t>izolater_TI</t>
+          <t>klempir</t>
         </is>
       </c>
       <c r="K101" s="24" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="L101" s="20" t="inlineStr">
         <is>
@@ -15578,12 +15538,12 @@
       </c>
       <c r="M101" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kročejová EPS shora ocelobeton</t>
+          <t>DXF MA_klempíř (75.4 m) + SM__ klempířina (98.4 m) total = 173.8 m × 0.40 split heuristic — Path C Tier 3</t>
         </is>
       </c>
       <c r="N101" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O101" s="26" t="inlineStr">
@@ -15591,14 +15551,15 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P101" s="41" t="inlineStr">
-        <is>
-          <t>S09</t>
-        </is>
-      </c>
+      <c r="P101" s="41" t="n"/>
       <c r="Q101" s="41" t="inlineStr">
         <is>
-          <t>D2_KROCEJOVA_30_to_40_2026-06-01</t>
+          <t>URS_PHASE5B_FAMILY_VERIFIED_CHAPTER_MATCH</t>
+        </is>
+      </c>
+      <c r="R101" s="41" t="inlineStr">
+        <is>
+          <t>PSV-76 Klempíř items sum 159.9 m vs DXF MA_klempíř + SM__ klempířina total 173.8 m, Δ -8.0 % (-13.9 m). Within ±15 % tolerance per CEV Matrix D.4 verdict (gate-3). FLAG for Karel site walkthrough — possible missing klempíř segment (small). Source: outputs/cev_matrix_d_cross_doc_consistency.json D.4.</t>
         </is>
       </c>
     </row>
@@ -15613,17 +15574,17 @@
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>Oplechování krytiny</t>
+          <t>Venkovní parapety oken</t>
         </is>
       </c>
       <c r="D102" s="20" t="inlineStr">
         <is>
-          <t>764312235</t>
+          <t>764218201</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>Klempířské oplechování krytiny — úžlabí, hřeben, štítové lemy (Al / Pzn lakovaný 0.55 mm)</t>
+          <t>Venkovní parapety oken — Pzn plech lakovaný 250 mm × tl. 0.55 mm × 16 ks oken</t>
         </is>
       </c>
       <c r="F102" s="20" t="inlineStr">
@@ -15632,7 +15593,7 @@
         </is>
       </c>
       <c r="G102" s="22" t="n">
-        <v>69.5</v>
+        <v>20.8</v>
       </c>
       <c r="H102" s="10" t="n"/>
       <c r="I102" s="10" t="n"/>
@@ -15642,7 +15603,7 @@
         </is>
       </c>
       <c r="K102" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L102" s="20" t="inlineStr">
         <is>
@@ -15651,12 +15612,12 @@
       </c>
       <c r="M102" s="8" t="inlineStr">
         <is>
-          <t>DXF MA_klempíř (75.4 m) + SM__ klempířina (98.4 m) total = 173.8 m × 0.40 split heuristic — Path C Tier 3</t>
+          <t>DXF okna 16 ks INSERT blocks + standard parapet width</t>
         </is>
       </c>
       <c r="N102" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O102" s="26" t="inlineStr">
@@ -15687,17 +15648,17 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>Venkovní parapety oken</t>
+          <t>Dešťové svody + žlaby</t>
         </is>
       </c>
       <c r="D103" s="20" t="inlineStr">
         <is>
-          <t>764218201</t>
+          <t>764454802</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>Venkovní parapety oken — Pzn plech lakovaný 250 mm × tl. 0.55 mm × 16 ks oken</t>
+          <t>Dešťové svody Pzn 100 mm + žlaby — 4 svody × ~14 m + žlaby per obvod střechy</t>
         </is>
       </c>
       <c r="F103" s="20" t="inlineStr">
@@ -15706,7 +15667,7 @@
         </is>
       </c>
       <c r="G103" s="22" t="n">
-        <v>20.8</v>
+        <v>43.5</v>
       </c>
       <c r="H103" s="10" t="n"/>
       <c r="I103" s="10" t="n"/>
@@ -15716,7 +15677,7 @@
         </is>
       </c>
       <c r="K103" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L103" s="20" t="inlineStr">
         <is>
@@ -15725,7 +15686,7 @@
       </c>
       <c r="M103" s="8" t="inlineStr">
         <is>
-          <t>DXF okna 16 ks INSERT blocks + standard parapet width</t>
+          <t>DXF klempířina lengths split + TZ ARS dešťové svody</t>
         </is>
       </c>
       <c r="N103" s="20" t="inlineStr">
@@ -15761,17 +15722,17 @@
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>Dešťové svody + žlaby</t>
+          <t>Vikýře + atika + závětrné lemy</t>
         </is>
       </c>
       <c r="D104" s="20" t="inlineStr">
         <is>
-          <t>764454802</t>
+          <t>764315235</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>Dešťové svody Pzn 100 mm + žlaby — 4 svody × ~14 m + žlaby per obvod střechy</t>
+          <t>Klempířské doplňky vikýřů + atika + závětrné lemy (4 vikýře komplexní detail)</t>
         </is>
       </c>
       <c r="F104" s="20" t="inlineStr">
@@ -15780,7 +15741,7 @@
         </is>
       </c>
       <c r="G104" s="22" t="n">
-        <v>43.5</v>
+        <v>26.1</v>
       </c>
       <c r="H104" s="10" t="n"/>
       <c r="I104" s="10" t="n"/>
@@ -15799,7 +15760,7 @@
       </c>
       <c r="M104" s="8" t="inlineStr">
         <is>
-          <t>DXF klempířina lengths split + TZ ARS dešťové svody</t>
+          <t>DXF klempířina geometry split + TZ ARS 4 vikýře</t>
         </is>
       </c>
       <c r="N104" s="20" t="inlineStr">
@@ -15830,50 +15791,50 @@
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Klempíř</t>
+          <t>PSV-76 Truhlář</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>Vikýře + atika + závětrné lemy</t>
+          <t>Dřevěné stupně schodišť</t>
         </is>
       </c>
       <c r="D105" s="20" t="inlineStr">
         <is>
-          <t>764315235</t>
+          <t>766811111</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>Klempířské doplňky vikýřů + atika + závětrné lemy (4 vikýře komplexní detail)</t>
+          <t>Dřevěné stupně ocelových schodišť (truhlářské, dub masiv tl. 40 mm)</t>
         </is>
       </c>
       <c r="F105" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G105" s="22" t="n">
-        <v>26.1</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G105" s="23" t="n">
+        <v>16</v>
       </c>
       <c r="H105" s="10" t="n"/>
       <c r="I105" s="10" t="n"/>
       <c r="J105" s="8" t="inlineStr">
         <is>
-          <t>klempir</t>
+          <t>truhlar</t>
         </is>
       </c>
       <c r="K105" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L105" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M105" s="8" t="inlineStr">
         <is>
-          <t>DXF klempířina geometry split + TZ ARS 4 vikýře</t>
+          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni truhlářské</t>
         </is>
       </c>
       <c r="N105" s="20" t="inlineStr">
@@ -15887,16 +15848,7 @@
         </is>
       </c>
       <c r="P105" s="41" t="n"/>
-      <c r="Q105" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED_CHAPTER_MATCH</t>
-        </is>
-      </c>
-      <c r="R105" s="41" t="inlineStr">
-        <is>
-          <t>PSV-76 Klempíř items sum 159.9 m vs DXF MA_klempíř + SM__ klempířina total 173.8 m, Δ -8.0 % (-13.9 m). Within ±15 % tolerance per CEV Matrix D.4 verdict (gate-3). FLAG for Karel site walkthrough — possible missing klempíř segment (small). Source: outputs/cev_matrix_d_cross_doc_consistency.json D.4.</t>
-        </is>
-      </c>
+      <c r="Q105" s="41" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="20" t="n">
@@ -15909,26 +15861,26 @@
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stupně schodišť</t>
-        </is>
-      </c>
-      <c r="D106" s="20" t="inlineStr">
-        <is>
-          <t>766811111</t>
+          <t>Terasa garapa za opěrnou stěnou — dřevěná pochozí vrstva</t>
+        </is>
+      </c>
+      <c r="D106" s="27" t="inlineStr">
+        <is>
+          <t>762??? ?</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stupně ocelových schodišť (truhlářské, dub masiv tl. 40 mm)</t>
+          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném roštu z hranolů 50 mm na rektifikovatelných terčích (terče + podkladní skladba viz HSV1.005)</t>
         </is>
       </c>
       <c r="F106" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G106" s="23" t="n">
-        <v>16</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G106" s="22" t="n">
+        <v>9.23</v>
       </c>
       <c r="H106" s="10" t="n"/>
       <c r="I106" s="10" t="n"/>
@@ -15938,16 +15890,16 @@
         </is>
       </c>
       <c r="K106" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L106" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_762_leaf_lookup_required</t>
         </is>
       </c>
       <c r="M106" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni truhlářské</t>
+          <t>TZ ARS dům §4 + DXF dum_situace PLOT_DREVENY_04 (terasa, ne 3.NP); ŘEZ C-C potvrzuje dřevěný rošt z hranolů (NE hliníkový) + dřevěnou pochozí vrstvu</t>
         </is>
       </c>
       <c r="N106" s="20" t="inlineStr">
@@ -15961,7 +15913,11 @@
         </is>
       </c>
       <c r="P106" s="41" t="n"/>
-      <c r="Q106" s="41" t="n"/>
+      <c r="Q106" s="41" t="inlineStr">
+        <is>
+          <t>REZ_CC_TERASA_FIX_2026-05-29; SITUACE_AREA_FIX_2026-05-29</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="20" t="n">
@@ -15969,55 +15925,55 @@
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Truhlář</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>Terasa garapa za opěrnou stěnou — dřevěná pochozí vrstva</t>
-        </is>
-      </c>
-      <c r="D107" s="27" t="inlineStr">
-        <is>
-          <t>762??? ?</t>
+          <t>Plastové okno trojsklo — 'okno 1.NP' (ulice)</t>
+        </is>
+      </c>
+      <c r="D107" s="20" t="inlineStr">
+        <is>
+          <t>766621011</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném roštu z hranolů 50 mm na rektifikovatelných terčích (terče + podkladní skladba viz HSV1.005)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP' velikost 1185×1600 mm × 2 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="F107" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G107" s="22" t="n">
-        <v>9.23</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G107" s="23" t="n">
+        <v>2</v>
       </c>
       <c r="H107" s="10" t="n"/>
       <c r="I107" s="10" t="n"/>
       <c r="J107" s="8" t="inlineStr">
         <is>
-          <t>truhlar</t>
+          <t>okennar</t>
         </is>
       </c>
       <c r="K107" s="24" t="n">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="L107" s="20" t="inlineStr">
         <is>
-          <t>family_762_leaf_lookup_required</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M107" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + DXF dum_situace PLOT_DREVENY_04 (terasa, ne 3.NP); ŘEZ C-C potvrzuje dřevěný rošt z hranolů (NE hliníkový) + dřevěnou pochozí vrstvu</t>
+          <t>DXF dum_DPZ INSERT block 'okno 1.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N107" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O107" s="26" t="inlineStr">
@@ -16026,11 +15982,7 @@
         </is>
       </c>
       <c r="P107" s="41" t="n"/>
-      <c r="Q107" s="41" t="inlineStr">
-        <is>
-          <t>REZ_CC_TERASA_FIX_2026-05-29; SITUACE_AREA_FIX_2026-05-29</t>
-        </is>
-      </c>
+      <c r="Q107" s="41" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="20" t="n">
@@ -16043,7 +15995,7 @@
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 1.NP' (ulice)</t>
+          <t>Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D108" s="20" t="inlineStr">
@@ -16053,7 +16005,7 @@
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP' velikost 1185×1600 mm × 2 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP vzadu' velikost 920×1600 mm × 3 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F108" s="20" t="inlineStr">
@@ -16062,7 +16014,7 @@
         </is>
       </c>
       <c r="G108" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H108" s="10" t="n"/>
       <c r="I108" s="10" t="n"/>
@@ -16076,12 +16028,12 @@
       </c>
       <c r="L108" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M108" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 1.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 1.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N108" s="20" t="inlineStr">
@@ -16108,7 +16060,7 @@
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada)</t>
+          <t>Plastové okno trojsklo — 'okno 2.NP' (ulice)</t>
         </is>
       </c>
       <c r="D109" s="20" t="inlineStr">
@@ -16118,7 +16070,7 @@
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP vzadu' velikost 920×1600 mm × 3 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 2.NP' velikost 1160×1480 mm × 4 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="F109" s="20" t="inlineStr">
@@ -16127,7 +16079,7 @@
         </is>
       </c>
       <c r="G109" s="23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H109" s="10" t="n"/>
       <c r="I109" s="10" t="n"/>
@@ -16146,7 +16098,7 @@
       </c>
       <c r="M109" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 1.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 2.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N109" s="20" t="inlineStr">
@@ -16173,7 +16125,7 @@
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 2.NP' (ulice)</t>
+          <t>Plastové okno trojsklo — 'okno 3.NP' (ulice)</t>
         </is>
       </c>
       <c r="D110" s="20" t="inlineStr">
@@ -16183,7 +16135,7 @@
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 2.NP' velikost 1160×1480 mm × 4 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP' velikost 1785×1241 mm × 3 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="F110" s="20" t="inlineStr">
@@ -16192,7 +16144,7 @@
         </is>
       </c>
       <c r="G110" s="23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H110" s="10" t="n"/>
       <c r="I110" s="10" t="n"/>
@@ -16211,7 +16163,7 @@
       </c>
       <c r="M110" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 2.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 3.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N110" s="20" t="inlineStr">
@@ -16238,7 +16190,7 @@
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 3.NP' (ulice)</t>
+          <t>Plastové okno trojsklo — 'okno 3.NP vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D111" s="20" t="inlineStr">
@@ -16248,7 +16200,7 @@
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP' velikost 1785×1241 mm × 3 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP vzadu' velikost 2075×1241 mm × 1 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F111" s="20" t="inlineStr">
@@ -16257,7 +16209,7 @@
         </is>
       </c>
       <c r="G111" s="23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H111" s="10" t="n"/>
       <c r="I111" s="10" t="n"/>
@@ -16276,7 +16228,7 @@
       </c>
       <c r="M111" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 3.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N111" s="20" t="inlineStr">
@@ -16303,7 +16255,7 @@
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 3.NP vzadu' (zahrada)</t>
+          <t>Plastové okno trojsklo — 'okno male 3.NP vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D112" s="20" t="inlineStr">
@@ -16313,7 +16265,7 @@
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP vzadu' velikost 2075×1241 mm × 1 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno male 3.NP vzadu' velikost 800×1241 mm × 1 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F112" s="20" t="inlineStr">
@@ -16341,7 +16293,7 @@
       </c>
       <c r="M112" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno male 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N112" s="20" t="inlineStr">
@@ -16368,7 +16320,7 @@
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno male 3.NP vzadu' (zahrada)</t>
+          <t>Plastové okno trojsklo — 'okno malé vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D113" s="20" t="inlineStr">
@@ -16378,7 +16330,7 @@
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno male 3.NP vzadu' velikost 800×1241 mm × 1 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno malé vzadu' velikost 700×800 mm × 2 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F113" s="20" t="inlineStr">
@@ -16387,7 +16339,7 @@
         </is>
       </c>
       <c r="G113" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H113" s="10" t="n"/>
       <c r="I113" s="10" t="n"/>
@@ -16406,7 +16358,7 @@
       </c>
       <c r="M113" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno male 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno malé vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N113" s="20" t="inlineStr">
@@ -16433,17 +16385,17 @@
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno malé vzadu' (zahrada)</t>
+          <t>Žaluzie kastlík purenit</t>
         </is>
       </c>
       <c r="D114" s="20" t="inlineStr">
         <is>
-          <t>766621011</t>
+          <t>766631211</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno malé vzadu' velikost 700×800 mm × 2 ks (fasáda zahrada)</t>
+          <t>Integrované stínící venkovní žaluzie v kastlíku pod omítkou s purenitovou izolací — uliční fasáda Fibichova (9 ks)</t>
         </is>
       </c>
       <c r="F114" s="20" t="inlineStr">
@@ -16452,17 +16404,17 @@
         </is>
       </c>
       <c r="G114" s="23" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H114" s="10" t="n"/>
       <c r="I114" s="10" t="n"/>
       <c r="J114" s="8" t="inlineStr">
         <is>
-          <t>okennar</t>
+          <t>okenni_zaluzie_kastlik_purenit</t>
         </is>
       </c>
       <c r="K114" s="24" t="n">
-        <v>0.99</v>
+        <v>0.95</v>
       </c>
       <c r="L114" s="20" t="inlineStr">
         <is>
@@ -16471,7 +16423,7 @@
       </c>
       <c r="M114" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno malé vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>TZ ARS dům §3.2 — 'do ulice Fibichova s integrovanými stínícími žaluziemi v kastlíku pod omítkou s purenitovou izolací'</t>
         </is>
       </c>
       <c r="N114" s="20" t="inlineStr">
@@ -16498,17 +16450,17 @@
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>Žaluzie kastlík purenit</t>
+          <t>Vstupní plastové dveře</t>
         </is>
       </c>
       <c r="D115" s="20" t="inlineStr">
         <is>
-          <t>766631211</t>
+          <t>766682111</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>Integrované stínící venkovní žaluzie v kastlíku pod omítkou s purenitovou izolací — uliční fasáda Fibichova (9 ks)</t>
+          <t>Plastové vstupní dveře (ulice + zahrada) — 2 ks</t>
         </is>
       </c>
       <c r="F115" s="20" t="inlineStr">
@@ -16517,17 +16469,17 @@
         </is>
       </c>
       <c r="G115" s="23" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H115" s="10" t="n"/>
       <c r="I115" s="10" t="n"/>
       <c r="J115" s="8" t="inlineStr">
         <is>
-          <t>okenni_zaluzie_kastlik_purenit</t>
+          <t>okennar</t>
         </is>
       </c>
       <c r="K115" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L115" s="20" t="inlineStr">
         <is>
@@ -16536,12 +16488,12 @@
       </c>
       <c r="M115" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — 'do ulice Fibichova s integrovanými stínícími žaluziemi v kastlíku pod omítkou s purenitovou izolací'</t>
+          <t>TZ ARS dům §4 — plastové vstupní dveře</t>
         </is>
       </c>
       <c r="N115" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O115" s="26" t="inlineStr">
@@ -16563,17 +16515,17 @@
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>Vstupní plastové dveře</t>
+          <t>Vnitřní dveře DTD laminované</t>
         </is>
       </c>
       <c r="D116" s="20" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>766660035</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>Plastové vstupní dveře (ulice + zahrada) — 2 ks</t>
+          <t>Vnitřní dveře DTD laminované s obložkovou zárubní — odhad 15 ks</t>
         </is>
       </c>
       <c r="F116" s="20" t="inlineStr">
@@ -16582,13 +16534,13 @@
         </is>
       </c>
       <c r="G116" s="23" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H116" s="10" t="n"/>
       <c r="I116" s="10" t="n"/>
       <c r="J116" s="8" t="inlineStr">
         <is>
-          <t>okennar</t>
+          <t>truhlar</t>
         </is>
       </c>
       <c r="K116" s="24" t="n">
@@ -16601,12 +16553,12 @@
       </c>
       <c r="M116" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — plastové vstupní dveře</t>
+          <t>TZ ARS dům §4 + DXF MTEXT room labels</t>
         </is>
       </c>
       <c r="N116" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O116" s="26" t="inlineStr">
@@ -16628,17 +16580,17 @@
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>Vnitřní dveře DTD laminované</t>
+          <t>Požárně odolné dveře EI 30 DP3</t>
         </is>
       </c>
       <c r="D117" s="20" t="inlineStr">
         <is>
-          <t>766660035</t>
+          <t>766694112</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>Vnitřní dveře DTD laminované s obložkovou zárubní — odhad 15 ks</t>
+          <t>Požárně odolné jednokřídlové dveře EI 30 DP3 na vrcholu schodiště mezi 1.PP a 1.NP — uzavírá otvor v REI 90 stropu klenby sklepa (per PBŘ TUSPO § 'Požární uzávěry otvorů v požárních stěnách a požárních stropech: podzemní 30 DP1')</t>
         </is>
       </c>
       <c r="F117" s="20" t="inlineStr">
@@ -16647,17 +16599,17 @@
         </is>
       </c>
       <c r="G117" s="23" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H117" s="10" t="n"/>
       <c r="I117" s="10" t="n"/>
       <c r="J117" s="8" t="inlineStr">
         <is>
-          <t>truhlar</t>
+          <t>specialista_RC3_dvere</t>
         </is>
       </c>
       <c r="K117" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L117" s="20" t="inlineStr">
         <is>
@@ -16666,12 +16618,12 @@
       </c>
       <c r="M117" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + DXF MTEXT room labels</t>
+          <t>PBŘ TUSPO § Požární uzávěry otvorů 'podzemní 30DP1'; DXF schodiště 1.PP→1.NP</t>
         </is>
       </c>
       <c r="N117" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O117" s="26" t="inlineStr">
@@ -16680,7 +16632,11 @@
         </is>
       </c>
       <c r="P117" s="41" t="n"/>
-      <c r="Q117" s="41" t="n"/>
+      <c r="Q117" s="41" t="inlineStr">
+        <is>
+          <t>GAP_008</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="20" t="n">
@@ -16693,17 +16649,17 @@
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>Požárně odolné dveře EI 30 DP3</t>
+          <t>Oplechování venkovních parapetů Pzn — 16 ks</t>
         </is>
       </c>
       <c r="D118" s="20" t="inlineStr">
         <is>
-          <t>766694112</t>
+          <t>764811112</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>Požárně odolné jednokřídlové dveře EI 30 DP3 na vrcholu schodiště mezi 1.PP a 1.NP — uzavírá otvor v REI 90 stropu klenby sklepa (per PBŘ TUSPO § 'Požární uzávěry otvorů v požárních stěnách a požárních stropech: podzemní 30 DP1')</t>
+          <t>Oplechování venkovních parapetů Pzn plech lakovaný 250 mm × tl. 0.55 mm, vč. okapnice + boční zakončení — 16 ks (per DXF INSERT okno × 16)</t>
         </is>
       </c>
       <c r="F118" s="20" t="inlineStr">
@@ -16712,17 +16668,17 @@
         </is>
       </c>
       <c r="G118" s="23" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H118" s="10" t="n"/>
       <c r="I118" s="10" t="n"/>
       <c r="J118" s="8" t="inlineStr">
         <is>
-          <t>specialista_RC3_dvere</t>
+          <t>klempir</t>
         </is>
       </c>
       <c r="K118" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L118" s="20" t="inlineStr">
         <is>
@@ -16731,7 +16687,7 @@
       </c>
       <c r="M118" s="8" t="inlineStr">
         <is>
-          <t>PBŘ TUSPO § Požární uzávěry otvorů 'podzemní 30DP1'; DXF schodiště 1.PP→1.NP</t>
+          <t>DXF blocks okno* 16 ks + DXF klempir_parapet 16 ks (Path C Tier 4 INSERT discovery)</t>
         </is>
       </c>
       <c r="N118" s="20" t="inlineStr">
@@ -16747,7 +16703,7 @@
       <c r="P118" s="41" t="n"/>
       <c r="Q118" s="41" t="inlineStr">
         <is>
-          <t>GAP_008</t>
+          <t>GAP_004</t>
         </is>
       </c>
     </row>
@@ -16757,55 +16713,55 @@
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>Oplechování venkovních parapetů Pzn — 16 ks</t>
+          <t>Ocelové schodiště UPE200 ze zahrady</t>
         </is>
       </c>
       <c r="D119" s="20" t="inlineStr">
         <is>
-          <t>764811112</t>
+          <t>767531111</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>Oplechování venkovních parapetů Pzn plech lakovaný 250 mm × tl. 0.55 mm, vč. okapnice + boční zakončení — 16 ks (per DXF INSERT okno × 16)</t>
+          <t>Ocelové schodiště ze zahrady na mezipodestu — UPE200 schodnice + dřevěné nášlapy, kotvené do koruny opěrné stěny a zdiva (TZ statika §4)</t>
         </is>
       </c>
       <c r="F119" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G119" s="23" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H119" s="10" t="n"/>
       <c r="I119" s="10" t="n"/>
       <c r="J119" s="8" t="inlineStr">
         <is>
-          <t>klempir</t>
+          <t>zamecnik_PSV</t>
         </is>
       </c>
       <c r="K119" s="24" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="L119" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M119" s="8" t="inlineStr">
         <is>
-          <t>DXF blocks okno* 16 ks + DXF klempir_parapet 16 ks (Path C Tier 4 INSERT discovery)</t>
+          <t>TZ statika dům §4 — schodiště UPE200 + UPE100 podružné prvky</t>
         </is>
       </c>
       <c r="N119" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O119" s="26" t="inlineStr">
@@ -16816,7 +16772,7 @@
       <c r="P119" s="41" t="n"/>
       <c r="Q119" s="41" t="inlineStr">
         <is>
-          <t>GAP_004</t>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
         </is>
       </c>
     </row>
@@ -16831,7 +16787,7 @@
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>Ocelové schodiště UPE200 ze zahrady</t>
+          <t>Ocelové schodiště do spacího patra 3.NP</t>
         </is>
       </c>
       <c r="D120" s="20" t="inlineStr">
@@ -16841,7 +16797,7 @@
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>Ocelové schodiště ze zahrady na mezipodestu — UPE200 schodnice + dřevěné nášlapy, kotvené do koruny opěrné stěny a zdiva (TZ statika §4)</t>
+          <t>Interní ocelové schodiště do spacího patra v 3.NP s dřevěnými stupni (truhlářské)</t>
         </is>
       </c>
       <c r="F120" s="20" t="inlineStr">
@@ -16869,12 +16825,12 @@
       </c>
       <c r="M120" s="8" t="inlineStr">
         <is>
-          <t>TZ statika dům §4 — schodiště UPE200 + UPE100 podružné prvky</t>
+          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni</t>
         </is>
       </c>
       <c r="N120" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O120" s="26" t="inlineStr">
@@ -16900,26 +16856,26 @@
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t>Ocelové schodiště do spacího patra 3.NP</t>
+          <t>Stříšky nad vstupy</t>
         </is>
       </c>
       <c r="D121" s="20" t="inlineStr">
         <is>
-          <t>767531111</t>
+          <t>767532111</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>Interní ocelové schodiště do spacího patra v 3.NP s dřevěnými stupni (truhlářské)</t>
+          <t>Stříšky nad vstupy z ocelové konstrukce + Cetris desky + falcovaná krytina — 2 ks (ulice + zahrada)</t>
         </is>
       </c>
       <c r="F121" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G121" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H121" s="10" t="n"/>
       <c r="I121" s="10" t="n"/>
@@ -16929,16 +16885,16 @@
         </is>
       </c>
       <c r="K121" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L121" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M121" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni</t>
+          <t>TZ ARS dům §4 — stříšky nad vstupy ocel+Cetris+plech</t>
         </is>
       </c>
       <c r="N121" s="20" t="inlineStr">
@@ -16952,11 +16908,7 @@
         </is>
       </c>
       <c r="P121" s="41" t="n"/>
-      <c r="Q121" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+      <c r="Q121" s="41" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="20" t="n">
@@ -16969,26 +16921,26 @@
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>Stříšky nad vstupy</t>
+          <t>Zábradlí z jeklů + nerez výplň</t>
         </is>
       </c>
       <c r="D122" s="20" t="inlineStr">
         <is>
-          <t>767532111</t>
+          <t>767163115</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>Stříšky nad vstupy z ocelové konstrukce + Cetris desky + falcovaná krytina — 2 ks (ulice + zahrada)</t>
+          <t>Ocelové zábradlí svařované z jeklů + nerez výplň pZn antracit — schodiště interier + venkovní terasa</t>
         </is>
       </c>
       <c r="F122" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G122" s="23" t="n">
-        <v>2</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G122" s="22" t="n">
+        <v>18</v>
       </c>
       <c r="H122" s="10" t="n"/>
       <c r="I122" s="10" t="n"/>
@@ -17007,7 +16959,7 @@
       </c>
       <c r="M122" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — stříšky nad vstupy ocel+Cetris+plech</t>
+          <t>TZ ARS dům §4 — zábradlí svařované z jeklů + nerez výplň</t>
         </is>
       </c>
       <c r="N122" s="20" t="inlineStr">
@@ -17029,55 +16981,55 @@
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>Zábradlí z jeklů + nerez výplň</t>
+          <t>Nášlap vinyl obytné místnosti</t>
         </is>
       </c>
       <c r="D123" s="20" t="inlineStr">
         <is>
-          <t>767163115</t>
+          <t>776511820</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>Ocelové zábradlí svařované z jeklů + nerez výplň pZn antracit — schodiště interier + venkovní terasa</t>
+          <t>Nášlapná vrstva vinyl tl. 4 mm na suchou skladbu — obytné místnosti (ložnice, obývák, kuchyně, chodby)</t>
         </is>
       </c>
       <c r="F123" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G123" s="22" t="n">
-        <v>18</v>
+        <v>171.5</v>
       </c>
       <c r="H123" s="10" t="n"/>
       <c r="I123" s="10" t="n"/>
       <c r="J123" s="8" t="inlineStr">
         <is>
-          <t>zamecnik_PSV</t>
+          <t>podlahar</t>
         </is>
       </c>
       <c r="K123" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L123" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M123" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — zábradlí svařované z jeklů + nerez výplň</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (kuchyně/obytná/chodba = vinyl) + TZ ARS §3.2.4 nášlapná vrstva</t>
         </is>
       </c>
       <c r="N123" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#4</t>
         </is>
       </c>
       <c r="O123" s="26" t="inlineStr">
@@ -17086,7 +17038,11 @@
         </is>
       </c>
       <c r="P123" s="41" t="n"/>
-      <c r="Q123" s="41" t="n"/>
+      <c r="Q123" s="41" t="inlineStr">
+        <is>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="20" t="n">
@@ -17099,17 +17055,17 @@
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>Nášlap vinyl obytné místnosti</t>
+          <t>Nášlap keramická dlažba — mokré zóny</t>
         </is>
       </c>
       <c r="D124" s="20" t="inlineStr">
         <is>
-          <t>776511820</t>
+          <t>771274102</t>
         </is>
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva vinyl tl. 4 mm na suchou skladbu — obytné místnosti (ložnice, obývák, kuchyně, chodby)</t>
+          <t>Nášlapná vrstva keramická dlažba lepená — koupelny + WC + spíž + komora (NÁDRŽ NP)</t>
         </is>
       </c>
       <c r="F124" s="20" t="inlineStr">
@@ -17118,13 +17074,13 @@
         </is>
       </c>
       <c r="G124" s="22" t="n">
-        <v>171.5</v>
+        <v>13.5</v>
       </c>
       <c r="H124" s="10" t="n"/>
       <c r="I124" s="10" t="n"/>
       <c r="J124" s="8" t="inlineStr">
         <is>
-          <t>podlahar</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K124" s="24" t="n">
@@ -17132,12 +17088,12 @@
       </c>
       <c r="L124" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M124" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (kuchyně/obytná/chodba = vinyl) + TZ ARS §3.2.4 nášlapná vrstva</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (koupelna/WC/spíž = dlažba mokré) + TZ ARS skladba mokrá</t>
         </is>
       </c>
       <c r="N124" s="20" t="inlineStr">
@@ -17151,11 +17107,7 @@
         </is>
       </c>
       <c r="P124" s="41" t="n"/>
-      <c r="Q124" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+      <c r="Q124" s="41" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="20" t="n">
@@ -17168,7 +17120,7 @@
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t>Nášlap keramická dlažba — mokré zóny</t>
+          <t>Nášlap keramická dlažba — 1.PP sklep</t>
         </is>
       </c>
       <c r="D125" s="20" t="inlineStr">
@@ -17178,7 +17130,7 @@
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva keramická dlažba lepená — koupelny + WC + spíž + komora (NÁDRŽ NP)</t>
+          <t>Nášlapná vrstva keramická dlažba — 1.PP technické místnosti (sušárna + sklepy + schodiště + chodba)</t>
         </is>
       </c>
       <c r="F125" s="20" t="inlineStr">
@@ -17187,7 +17139,7 @@
         </is>
       </c>
       <c r="G125" s="22" t="n">
-        <v>13.5</v>
+        <v>32.4</v>
       </c>
       <c r="H125" s="10" t="n"/>
       <c r="I125" s="10" t="n"/>
@@ -17206,7 +17158,7 @@
       </c>
       <c r="M125" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (koupelna/WC/spíž = dlažba mokré) + TZ ARS skladba mokrá</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — 1.PP all rooms = dlažba sklep zone</t>
         </is>
       </c>
       <c r="N125" s="20" t="inlineStr">
@@ -17233,17 +17185,17 @@
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>Nášlap keramická dlažba — 1.PP sklep</t>
+          <t>Nášlap biodeska 3.NP spací patro</t>
         </is>
       </c>
       <c r="D126" s="20" t="inlineStr">
         <is>
-          <t>771274102</t>
+          <t>766411111</t>
         </is>
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva keramická dlažba — 1.PP technické místnosti (sušárna + sklepy + schodiště + chodba)</t>
+          <t>Nášlapná vrstva biodeska (smrk masiv) nebo OSB v 3.NP spací části nad krovem</t>
         </is>
       </c>
       <c r="F126" s="20" t="inlineStr">
@@ -17252,17 +17204,17 @@
         </is>
       </c>
       <c r="G126" s="22" t="n">
-        <v>32.4</v>
+        <v>25</v>
       </c>
       <c r="H126" s="10" t="n"/>
       <c r="I126" s="10" t="n"/>
       <c r="J126" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>biodeska_konstrukcni</t>
         </is>
       </c>
       <c r="K126" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L126" s="20" t="inlineStr">
         <is>
@@ -17271,12 +17223,12 @@
       </c>
       <c r="M126" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — 1.PP all rooms = dlažba sklep zone</t>
+          <t>TZ ARS dům §3.2.3 — biodeska patro pro přespání</t>
         </is>
       </c>
       <c r="N126" s="20" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O126" s="26" t="inlineStr">
@@ -17298,17 +17250,17 @@
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t>Nášlap biodeska 3.NP spací patro</t>
+          <t>Betonový potěr s kari nad EPS</t>
         </is>
       </c>
       <c r="D127" s="20" t="inlineStr">
         <is>
-          <t>766411111</t>
+          <t>631321311</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva biodeska (smrk masiv) nebo OSB v 3.NP spací části nad krovem</t>
+          <t>Mokrá podlahová skladba — betonový potěr s kari síťkou 4/100/100 tl. 50 mm + samonivelační stěrka</t>
         </is>
       </c>
       <c r="F127" s="20" t="inlineStr">
@@ -17317,17 +17269,17 @@
         </is>
       </c>
       <c r="G127" s="22" t="n">
-        <v>25</v>
+        <v>126.4</v>
       </c>
       <c r="H127" s="10" t="n"/>
       <c r="I127" s="10" t="n"/>
       <c r="J127" s="8" t="inlineStr">
         <is>
-          <t>biodeska_konstrukcni</t>
+          <t>podlahar</t>
         </is>
       </c>
       <c r="K127" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L127" s="20" t="inlineStr">
         <is>
@@ -17336,12 +17288,12 @@
       </c>
       <c r="M127" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.3 — biodeska patro pro přespání</t>
+          <t>TZ ARS dům §3.2.4 + §3.2.x — 'kročejová izolace + betonový potěr s kari sítí'; DXF rooms areas</t>
         </is>
       </c>
       <c r="N127" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>#4</t>
         </is>
       </c>
       <c r="O127" s="26" t="inlineStr">
@@ -17363,26 +17315,26 @@
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>Betonový potěr s kari nad EPS</t>
+          <t>Soklíky vinyl</t>
         </is>
       </c>
       <c r="D128" s="20" t="inlineStr">
         <is>
-          <t>631321311</t>
+          <t>776511831</t>
         </is>
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>Mokrá podlahová skladba — betonový potěr s kari síťkou 4/100/100 tl. 50 mm + samonivelační stěrka</t>
+          <t>Soklíky podlahové laminátové (dub) v obytných místnostech s vinyl podlahou</t>
         </is>
       </c>
       <c r="F128" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G128" s="22" t="n">
-        <v>126.4</v>
+        <v>72.03</v>
       </c>
       <c r="H128" s="10" t="n"/>
       <c r="I128" s="10" t="n"/>
@@ -17401,12 +17353,12 @@
       </c>
       <c r="M128" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.4 + §3.2.x — 'kročejová izolace + betonový potěr s kari sítí'; DXF rooms areas</t>
+          <t>DXF rooms vinyl + standard ratio per RD geometry</t>
         </is>
       </c>
       <c r="N128" s="20" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O128" s="26" t="inlineStr">
@@ -17428,17 +17380,17 @@
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t>Soklíky vinyl</t>
+          <t>Soklíky keramické</t>
         </is>
       </c>
       <c r="D129" s="20" t="inlineStr">
         <is>
-          <t>776511831</t>
+          <t>771274107</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>Soklíky podlahové laminátové (dub) v obytných místnostech s vinyl podlahou</t>
+          <t>Soklíky keramické v místnostech s dlažbou (koupelny + WC + spíž + 1.PP)</t>
         </is>
       </c>
       <c r="F129" s="20" t="inlineStr">
@@ -17447,13 +17399,13 @@
         </is>
       </c>
       <c r="G129" s="22" t="n">
-        <v>72.03</v>
+        <v>19.28</v>
       </c>
       <c r="H129" s="10" t="n"/>
       <c r="I129" s="10" t="n"/>
       <c r="J129" s="8" t="inlineStr">
         <is>
-          <t>podlahar</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K129" s="24" t="n">
@@ -17466,7 +17418,7 @@
       </c>
       <c r="M129" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms vinyl + standard ratio per RD geometry</t>
+          <t>DXF rooms dlažba + standard ratio per RD geometry</t>
         </is>
       </c>
       <c r="N129" s="20" t="inlineStr">
@@ -17488,41 +17440,41 @@
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>Soklíky keramické</t>
+          <t>Omítka jádrová + štuk 1.PP</t>
         </is>
       </c>
       <c r="D130" s="20" t="inlineStr">
         <is>
-          <t>771274107</t>
+          <t>612311311</t>
         </is>
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>Soklíky keramické v místnostech s dlažbou (koupelny + WC + spíž + 1.PP)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.PP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F130" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G130" s="22" t="n">
-        <v>19.28</v>
+        <v>78.2</v>
       </c>
       <c r="H130" s="10" t="n"/>
       <c r="I130" s="10" t="n"/>
       <c r="J130" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K130" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L130" s="20" t="inlineStr">
         <is>
@@ -17531,12 +17483,12 @@
       </c>
       <c r="M130" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms dlažba + standard ratio per RD geometry</t>
+          <t>DXF rooms 1.PP obvod + výška podlaží 2.1 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N130" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O130" s="26" t="inlineStr">
@@ -17558,7 +17510,7 @@
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 1.PP</t>
+          <t>Omítka jádrová + štuk 1.NP</t>
         </is>
       </c>
       <c r="D131" s="20" t="inlineStr">
@@ -17568,7 +17520,7 @@
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.PP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F131" s="20" t="inlineStr">
@@ -17577,7 +17529,7 @@
         </is>
       </c>
       <c r="G131" s="22" t="n">
-        <v>78.2</v>
+        <v>208.4</v>
       </c>
       <c r="H131" s="10" t="n"/>
       <c r="I131" s="10" t="n"/>
@@ -17596,7 +17548,7 @@
       </c>
       <c r="M131" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 1.PP obvod + výška podlaží 2.1 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 1.NP obvod + výška podlaží 2.795 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N131" s="20" t="inlineStr">
@@ -17623,7 +17575,7 @@
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 1.NP</t>
+          <t>Omítka jádrová + štuk 2.NP</t>
         </is>
       </c>
       <c r="D132" s="20" t="inlineStr">
@@ -17633,7 +17585,7 @@
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.NP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 2.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F132" s="20" t="inlineStr">
@@ -17642,7 +17594,7 @@
         </is>
       </c>
       <c r="G132" s="22" t="n">
-        <v>208.4</v>
+        <v>201.6</v>
       </c>
       <c r="H132" s="10" t="n"/>
       <c r="I132" s="10" t="n"/>
@@ -17661,7 +17613,7 @@
       </c>
       <c r="M132" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 1.NP obvod + výška podlaží 2.795 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 2.NP obvod + výška podlaží 2.865 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N132" s="20" t="inlineStr">
@@ -17688,7 +17640,7 @@
       </c>
       <c r="C133" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 2.NP</t>
+          <t>Omítka jádrová + štuk 3.NP</t>
         </is>
       </c>
       <c r="D133" s="20" t="inlineStr">
@@ -17698,7 +17650,7 @@
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 2.NP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 3.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F133" s="20" t="inlineStr">
@@ -17707,7 +17659,7 @@
         </is>
       </c>
       <c r="G133" s="22" t="n">
-        <v>201.6</v>
+        <v>179.1</v>
       </c>
       <c r="H133" s="10" t="n"/>
       <c r="I133" s="10" t="n"/>
@@ -17726,7 +17678,7 @@
       </c>
       <c r="M133" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 2.NP obvod + výška podlaží 2.865 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 3.NP obvod + výška podlaží 2.63 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N133" s="20" t="inlineStr">
@@ -17753,17 +17705,17 @@
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 3.NP</t>
+          <t>SDK podhled — tmelení + úprava 1.NP</t>
         </is>
       </c>
       <c r="D134" s="20" t="inlineStr">
         <is>
-          <t>612311311</t>
+          <t>612471141</t>
         </is>
       </c>
       <c r="E134" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 3.NP (stávající vyspravené + nové zděné)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (1.NP)</t>
         </is>
       </c>
       <c r="F134" s="20" t="inlineStr">
@@ -17772,17 +17724,17 @@
         </is>
       </c>
       <c r="G134" s="22" t="n">
-        <v>179.1</v>
+        <v>59.5</v>
       </c>
       <c r="H134" s="10" t="n"/>
       <c r="I134" s="10" t="n"/>
       <c r="J134" s="8" t="inlineStr">
         <is>
-          <t>zednik</t>
+          <t>sadrokartonar</t>
         </is>
       </c>
       <c r="K134" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L134" s="20" t="inlineStr">
         <is>
@@ -17791,12 +17743,12 @@
       </c>
       <c r="M134" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 3.NP obvod + výška podlaží 2.63 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 1.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="N134" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O134" s="26" t="inlineStr">
@@ -17818,7 +17770,7 @@
       </c>
       <c r="C135" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled — tmelení + úprava 1.NP</t>
+          <t>SDK podhled — tmelení + úprava 2.NP</t>
         </is>
       </c>
       <c r="D135" s="20" t="inlineStr">
@@ -17828,7 +17780,7 @@
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (1.NP)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (2.NP)</t>
         </is>
       </c>
       <c r="F135" s="20" t="inlineStr">
@@ -17837,7 +17789,7 @@
         </is>
       </c>
       <c r="G135" s="22" t="n">
-        <v>59.5</v>
+        <v>61.1</v>
       </c>
       <c r="H135" s="10" t="n"/>
       <c r="I135" s="10" t="n"/>
@@ -17856,7 +17808,7 @@
       </c>
       <c r="M135" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 1.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 2.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="N135" s="20" t="inlineStr">
@@ -17883,7 +17835,7 @@
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled — tmelení + úprava 2.NP</t>
+          <t>SDK podhled — tmelení + úprava 3.NP</t>
         </is>
       </c>
       <c r="D136" s="20" t="inlineStr">
@@ -17893,7 +17845,7 @@
       </c>
       <c r="E136" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (2.NP)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (3.NP)</t>
         </is>
       </c>
       <c r="F136" s="20" t="inlineStr">
@@ -17902,7 +17854,7 @@
         </is>
       </c>
       <c r="G136" s="22" t="n">
-        <v>61.1</v>
+        <v>64.5</v>
       </c>
       <c r="H136" s="10" t="n"/>
       <c r="I136" s="10" t="n"/>
@@ -17921,7 +17873,7 @@
       </c>
       <c r="M136" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 2.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 3.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="N136" s="20" t="inlineStr">
@@ -17948,17 +17900,17 @@
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled — tmelení + úprava 3.NP</t>
+          <t>Keramický obklad koupelna 1.05 (1.NP)</t>
         </is>
       </c>
       <c r="D137" s="20" t="inlineStr">
         <is>
-          <t>612471141</t>
+          <t>781447001</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (3.NP)</t>
+          <t>Keramický obklad stěn koupelny 1.05 1.NP — výška obkladu 1.6 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="F137" s="20" t="inlineStr">
@@ -17967,17 +17919,17 @@
         </is>
       </c>
       <c r="G137" s="22" t="n">
-        <v>64.5</v>
+        <v>13.4</v>
       </c>
       <c r="H137" s="10" t="n"/>
       <c r="I137" s="10" t="n"/>
       <c r="J137" s="8" t="inlineStr">
         <is>
-          <t>sadrokartonar</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K137" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L137" s="20" t="inlineStr">
         <is>
@@ -17986,7 +17938,7 @@
       </c>
       <c r="M137" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 3.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF rooms PIP perimeter 1.05 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="N137" s="20" t="inlineStr">
@@ -18013,7 +17965,7 @@
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad koupelna 1.05 (1.NP)</t>
+          <t>Keramický obklad koupelna 2.03 (2.NP)</t>
         </is>
       </c>
       <c r="D138" s="20" t="inlineStr">
@@ -18023,7 +17975,7 @@
       </c>
       <c r="E138" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 1.05 1.NP — výška obkladu 1.6 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad stěn koupelny 2.03 2.NP — výška obkladu 2.45 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="F138" s="20" t="inlineStr">
@@ -18032,7 +17984,7 @@
         </is>
       </c>
       <c r="G138" s="22" t="n">
-        <v>13.4</v>
+        <v>15.2</v>
       </c>
       <c r="H138" s="10" t="n"/>
       <c r="I138" s="10" t="n"/>
@@ -18051,7 +18003,7 @@
       </c>
       <c r="M138" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 1.05 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF rooms PIP perimeter 2.03 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="N138" s="20" t="inlineStr">
@@ -18078,7 +18030,7 @@
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad koupelna 2.03 (2.NP)</t>
+          <t>Keramický obklad koupelna 3.04 (3.NP)</t>
         </is>
       </c>
       <c r="D139" s="20" t="inlineStr">
@@ -18088,7 +18040,7 @@
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 2.03 2.NP — výška obkladu 2.45 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad stěn koupelny 3.04 3.NP — výška obkladu 2.7 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="F139" s="20" t="inlineStr">
@@ -18097,7 +18049,7 @@
         </is>
       </c>
       <c r="G139" s="22" t="n">
-        <v>15.2</v>
+        <v>24.3</v>
       </c>
       <c r="H139" s="10" t="n"/>
       <c r="I139" s="10" t="n"/>
@@ -18116,7 +18068,7 @@
       </c>
       <c r="M139" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 2.03 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF rooms PIP perimeter 3.04 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="N139" s="20" t="inlineStr">
@@ -18143,7 +18095,7 @@
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad koupelna 3.04 (3.NP)</t>
+          <t>Obklad za kuchyňskou linkou</t>
         </is>
       </c>
       <c r="D140" s="20" t="inlineStr">
@@ -18153,7 +18105,7 @@
       </c>
       <c r="E140" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 3.04 3.NP — výška obkladu 2.7 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad za kuchyňskou linkou nad pracovní deskou — 2 kuchyně × ~5 m² (1.06 byt rodičů + 3.05 byt 3.NP)</t>
         </is>
       </c>
       <c r="F140" s="20" t="inlineStr">
@@ -18162,7 +18114,7 @@
         </is>
       </c>
       <c r="G140" s="22" t="n">
-        <v>24.3</v>
+        <v>10</v>
       </c>
       <c r="H140" s="10" t="n"/>
       <c r="I140" s="10" t="n"/>
@@ -18172,7 +18124,7 @@
         </is>
       </c>
       <c r="K140" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L140" s="20" t="inlineStr">
         <is>
@@ -18181,7 +18133,7 @@
       </c>
       <c r="M140" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 3.04 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF dum_DPZ 2× kuchyně MTEXT + TZ ARS</t>
         </is>
       </c>
       <c r="N140" s="20" t="inlineStr">
@@ -18208,17 +18160,17 @@
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t>Obklad za kuchyňskou linkou</t>
+          <t>Interiérová výmalba</t>
         </is>
       </c>
       <c r="D141" s="20" t="inlineStr">
         <is>
-          <t>781447001</t>
+          <t>784121011</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad za kuchyňskou linkou nad pracovní deskou — 2 kuchyně × ~5 m² (1.06 byt rodičů + 3.05 byt 3.NP)</t>
+          <t>Interiérová výmalba akrylátová bílá 2× — všechny stěny + podhledy mimo obklad</t>
         </is>
       </c>
       <c r="F141" s="20" t="inlineStr">
@@ -18227,17 +18179,17 @@
         </is>
       </c>
       <c r="G141" s="22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H141" s="10" t="n"/>
       <c r="I141" s="10" t="n"/>
       <c r="J141" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>malir</t>
         </is>
       </c>
       <c r="K141" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L141" s="20" t="inlineStr">
         <is>
@@ -18246,7 +18198,7 @@
       </c>
       <c r="M141" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ 2× kuchyně MTEXT + TZ ARS</t>
+          <t>TZ ARS — interiérová výmalba (aggregate, no TZ per-room directive)</t>
         </is>
       </c>
       <c r="N141" s="20" t="inlineStr">
@@ -18260,7 +18212,11 @@
         </is>
       </c>
       <c r="P141" s="41" t="n"/>
-      <c r="Q141" s="41" t="n"/>
+      <c r="Q141" s="41" t="inlineStr">
+        <is>
+          <t>GAP_007_deprecated</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="20" t="n">
@@ -18273,7 +18229,7 @@
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba</t>
+          <t>Interiérová výmalba 1.NP</t>
         </is>
       </c>
       <c r="D142" s="20" t="inlineStr">
@@ -18283,7 +18239,7 @@
       </c>
       <c r="E142" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba akrylátová bílá 2× — všechny stěny + podhledy mimo obklad</t>
+          <t>Interiérová výmalba 1.NP — stěny + SDK podhled − obklad koupelny 1.05 (1.6 m výška)</t>
         </is>
       </c>
       <c r="F142" s="20" t="inlineStr">
@@ -18292,7 +18248,7 @@
         </is>
       </c>
       <c r="G142" s="22" t="n">
-        <v>0</v>
+        <v>254.5</v>
       </c>
       <c r="H142" s="10" t="n"/>
       <c r="I142" s="10" t="n"/>
@@ -18302,7 +18258,7 @@
         </is>
       </c>
       <c r="K142" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L142" s="20" t="inlineStr">
         <is>
@@ -18311,7 +18267,7 @@
       </c>
       <c r="M142" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS — interiérová výmalba (aggregate, no TZ per-room directive)</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.002 + SDK podhled PSV78.005</t>
         </is>
       </c>
       <c r="N142" s="20" t="inlineStr">
@@ -18327,7 +18283,7 @@
       <c r="P142" s="41" t="n"/>
       <c r="Q142" s="41" t="inlineStr">
         <is>
-          <t>GAP_007_deprecated</t>
+          <t>GAP_007</t>
         </is>
       </c>
     </row>
@@ -18342,7 +18298,7 @@
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.NP</t>
+          <t>Interiérová výmalba 1.PP</t>
         </is>
       </c>
       <c r="D143" s="20" t="inlineStr">
@@ -18352,7 +18308,7 @@
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.NP — stěny + SDK podhled − obklad koupelny 1.05 (1.6 m výška)</t>
+          <t>Interiérová výmalba 1.PP — sklep stěny + klenba bílá vápenná 2×</t>
         </is>
       </c>
       <c r="F143" s="20" t="inlineStr">
@@ -18361,7 +18317,7 @@
         </is>
       </c>
       <c r="G143" s="22" t="n">
-        <v>254.5</v>
+        <v>78.2</v>
       </c>
       <c r="H143" s="10" t="n"/>
       <c r="I143" s="10" t="n"/>
@@ -18380,7 +18336,7 @@
       </c>
       <c r="M143" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.002 + SDK podhled PSV78.005</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.001 + SDK podhled PSV78.—</t>
         </is>
       </c>
       <c r="N143" s="20" t="inlineStr">
@@ -18411,7 +18367,7 @@
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.PP</t>
+          <t>Interiérová výmalba 2.NP</t>
         </is>
       </c>
       <c r="D144" s="20" t="inlineStr">
@@ -18421,7 +18377,7 @@
       </c>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.PP — sklep stěny + klenba bílá vápenná 2×</t>
+          <t>Interiérová výmalba 2.NP — stěny + SDK podhled − obklad koupelny 2.03 (2.45 m výška)</t>
         </is>
       </c>
       <c r="F144" s="20" t="inlineStr">
@@ -18430,7 +18386,7 @@
         </is>
       </c>
       <c r="G144" s="22" t="n">
-        <v>78.2</v>
+        <v>247.5</v>
       </c>
       <c r="H144" s="10" t="n"/>
       <c r="I144" s="10" t="n"/>
@@ -18449,7 +18405,7 @@
       </c>
       <c r="M144" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.001 + SDK podhled PSV78.—</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.003 + SDK podhled PSV78.006</t>
         </is>
       </c>
       <c r="N144" s="20" t="inlineStr">
@@ -18480,7 +18436,7 @@
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 2.NP</t>
+          <t>Interiérová výmalba 3.NP</t>
         </is>
       </c>
       <c r="D145" s="20" t="inlineStr">
@@ -18490,7 +18446,7 @@
       </c>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 2.NP — stěny + SDK podhled − obklad koupelny 2.03 (2.45 m výška)</t>
+          <t>Interiérová výmalba 3.NP — stěny + SDK podhled − obklad koupelny 3.04 (2.7 m výška)</t>
         </is>
       </c>
       <c r="F145" s="20" t="inlineStr">
@@ -18499,7 +18455,7 @@
         </is>
       </c>
       <c r="G145" s="22" t="n">
-        <v>247.5</v>
+        <v>219.3</v>
       </c>
       <c r="H145" s="10" t="n"/>
       <c r="I145" s="10" t="n"/>
@@ -18518,7 +18474,7 @@
       </c>
       <c r="M145" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.003 + SDK podhled PSV78.006</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.004 + SDK podhled PSV78.007</t>
         </is>
       </c>
       <c r="N145" s="20" t="inlineStr">
@@ -18544,37 +18500,37 @@
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-95 Detekce požární</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 3.NP</t>
+          <t>Autonomní hlásič kouře</t>
         </is>
       </c>
       <c r="D146" s="20" t="inlineStr">
         <is>
-          <t>784121011</t>
+          <t>375211101</t>
         </is>
       </c>
       <c r="E146" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 3.NP — stěny + SDK podhled − obklad koupelny 3.04 (2.7 m výška)</t>
+          <t>Autonomní hlásič kouře dle ČSN EN 14604 — 4 ks v místnostech 1.01, 1.02, 2.04, 3.03 dle PBŘ</t>
         </is>
       </c>
       <c r="F146" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G146" s="22" t="n">
-        <v>219.3</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G146" s="23" t="n">
+        <v>4</v>
       </c>
       <c r="H146" s="10" t="n"/>
       <c r="I146" s="10" t="n"/>
       <c r="J146" s="8" t="inlineStr">
         <is>
-          <t>malir</t>
+          <t>elektroinstalater</t>
         </is>
       </c>
       <c r="K146" s="24" t="n">
@@ -18582,12 +18538,12 @@
       </c>
       <c r="L146" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M146" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.004 + SDK podhled PSV78.007</t>
+          <t>TZ PBŘ dům — ČSN EN 14604 autonomní hlásič kouře 4 ks</t>
         </is>
       </c>
       <c r="N146" s="20" t="inlineStr">
@@ -18603,7 +18559,7 @@
       <c r="P146" s="41" t="n"/>
       <c r="Q146" s="41" t="inlineStr">
         <is>
-          <t>GAP_007</t>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
         </is>
       </c>
     </row>
@@ -18618,17 +18574,17 @@
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t>Autonomní hlásič kouře</t>
+          <t>Přenosný hasicí přístroj 34A</t>
         </is>
       </c>
       <c r="D147" s="20" t="inlineStr">
         <is>
-          <t>375211101</t>
+          <t>966067121</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>Autonomní hlásič kouře dle ČSN EN 14604 — 4 ks v místnostech 1.01, 1.02, 2.04, 3.03 dle PBŘ</t>
+          <t>Přenosný hasicí přístroj 34A dle PBŘ — min. 1 ks na společné chodbě</t>
         </is>
       </c>
       <c r="F147" s="20" t="inlineStr">
@@ -18637,13 +18593,13 @@
         </is>
       </c>
       <c r="G147" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H147" s="10" t="n"/>
       <c r="I147" s="10" t="n"/>
       <c r="J147" s="8" t="inlineStr">
         <is>
-          <t>elektroinstalater</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K147" s="24" t="n">
@@ -18651,12 +18607,12 @@
       </c>
       <c r="L147" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M147" s="8" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — ČSN EN 14604 autonomní hlásič kouře 4 ks</t>
+          <t>TZ PBŘ dům — PHP 34A 1 ks minimum</t>
         </is>
       </c>
       <c r="N147" s="20" t="inlineStr">
@@ -18670,11 +18626,7 @@
         </is>
       </c>
       <c r="P147" s="41" t="n"/>
-      <c r="Q147" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+      <c r="Q147" s="41" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="20" t="n">
@@ -18687,22 +18639,22 @@
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>Přenosný hasicí přístroj 34A</t>
+          <t>Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
         </is>
       </c>
       <c r="D148" s="20" t="inlineStr">
         <is>
-          <t>966067121</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E148" s="8" t="inlineStr">
         <is>
-          <t>Přenosný hasicí přístroj 34A dle PBŘ — min. 1 ks na společné chodbě</t>
+          <t>Předávací protokol krbu na tuhá paliva + kontrola bezpečných vzdáleností (800 mm směr sálání / 400 mm strany, nehořlavá zóna podlahy) dle PBŘ</t>
         </is>
       </c>
       <c r="F148" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>soubor</t>
         </is>
       </c>
       <c r="G148" s="23" t="n">
@@ -18712,11 +18664,11 @@
       <c r="I148" s="10" t="n"/>
       <c r="J148" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K148" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L148" s="20" t="inlineStr">
         <is>
@@ -18725,7 +18677,7 @@
       </c>
       <c r="M148" s="8" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — PHP 34A 1 ks minimum</t>
+          <t>PBŘ D.3</t>
         </is>
       </c>
       <c r="N148" s="20" t="inlineStr">
@@ -18738,8 +18690,12 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P148" s="41" t="n"/>
-      <c r="Q148" s="41" t="n"/>
+      <c r="P148" s="41" t="inlineStr"/>
+      <c r="Q148" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="20" t="n">
@@ -18747,27 +18703,27 @@
       </c>
       <c r="B149" s="8" t="inlineStr">
         <is>
-          <t>PSV-95 Detekce požární</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+          <t>Demontáž stávající ELI</t>
         </is>
       </c>
       <c r="D149" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>210010011</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokol krbu na tuhá paliva + kontrola bezpečných vzdáleností (800 mm směr sálání / 400 mm strany, nehořlavá zóna podlahy) dle PBŘ</t>
+          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
         </is>
       </c>
       <c r="F149" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G149" s="23" t="n">
@@ -18777,11 +18733,11 @@
       <c r="I149" s="10" t="n"/>
       <c r="J149" s="8" t="inlineStr">
         <is>
-          <t>topenar</t>
+          <t>elektroinstalater</t>
         </is>
       </c>
       <c r="K149" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L149" s="20" t="inlineStr">
         <is>
@@ -18790,12 +18746,12 @@
       </c>
       <c r="M149" s="8" t="inlineStr">
         <is>
-          <t>PBŘ D.3</t>
+          <t>TZ ARS dům §4 — kompletně nová ELI</t>
         </is>
       </c>
       <c r="N149" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#7</t>
         </is>
       </c>
       <c r="O149" s="26" t="inlineStr">
@@ -18803,12 +18759,8 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P149" s="41" t="inlineStr"/>
-      <c r="Q149" s="41" t="inlineStr">
-        <is>
-          <t>DODATEK_PBR_GAPS_2026-06-01</t>
-        </is>
-      </c>
+      <c r="P149" s="41" t="n"/>
+      <c r="Q149" s="41" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="20" t="n">
@@ -18821,26 +18773,26 @@
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávající ELI</t>
+          <t>Pojistková skříň + 3× podružný rozvaděč</t>
         </is>
       </c>
       <c r="D150" s="20" t="inlineStr">
         <is>
-          <t>210010011</t>
+          <t>210110023</t>
         </is>
       </c>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
+          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
         </is>
       </c>
       <c r="F150" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G150" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H150" s="10" t="n"/>
       <c r="I150" s="10" t="n"/>
@@ -18859,7 +18811,7 @@
       </c>
       <c r="M150" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kompletně nová ELI</t>
+          <t>TZ ARS dům §4 — 'nová pojistková skříň s podružným měřením pro každé patro'</t>
         </is>
       </c>
       <c r="N150" s="20" t="inlineStr">
@@ -18886,26 +18838,26 @@
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t>Pojistková skříň + 3× podružný rozvaděč</t>
+          <t>Rozvody silnoproud</t>
         </is>
       </c>
       <c r="D151" s="20" t="inlineStr">
         <is>
-          <t>210110023</t>
+          <t>210800012</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
+          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
         </is>
       </c>
       <c r="F151" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G151" s="23" t="n">
-        <v>4</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G151" s="22" t="n">
+        <v>700</v>
       </c>
       <c r="H151" s="10" t="n"/>
       <c r="I151" s="10" t="n"/>
@@ -18915,7 +18867,7 @@
         </is>
       </c>
       <c r="K151" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L151" s="20" t="inlineStr">
         <is>
@@ -18924,7 +18876,7 @@
       </c>
       <c r="M151" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — 'nová pojistková skříň s podružným měřením pro každé patro'</t>
+          <t>TZ ARS + B4_productivity standard RD 3-byt. dispozice</t>
         </is>
       </c>
       <c r="N151" s="20" t="inlineStr">
@@ -18951,26 +18903,26 @@
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>Rozvody silnoproud</t>
+          <t>Zásuvky a vypínače</t>
         </is>
       </c>
       <c r="D152" s="20" t="inlineStr">
         <is>
-          <t>210800012</t>
+          <t>210810050</t>
         </is>
       </c>
       <c r="E152" s="8" t="inlineStr">
         <is>
-          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
+          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
         </is>
       </c>
       <c r="F152" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G152" s="22" t="n">
-        <v>700</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G152" s="23" t="n">
+        <v>70</v>
       </c>
       <c r="H152" s="10" t="n"/>
       <c r="I152" s="10" t="n"/>
@@ -18989,7 +18941,7 @@
       </c>
       <c r="M152" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD 3-byt. dispozice</t>
+          <t>TZ ARS + B4_productivity standard RD 220 m² 3-byt.</t>
         </is>
       </c>
       <c r="N152" s="20" t="inlineStr">
@@ -19016,17 +18968,17 @@
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t>Zásuvky a vypínače</t>
+          <t>Svítidla</t>
         </is>
       </c>
       <c r="D153" s="20" t="inlineStr">
         <is>
-          <t>210810050</t>
+          <t>210820002</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
+          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
         </is>
       </c>
       <c r="F153" s="20" t="inlineStr">
@@ -19035,7 +18987,7 @@
         </is>
       </c>
       <c r="G153" s="23" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="H153" s="10" t="n"/>
       <c r="I153" s="10" t="n"/>
@@ -19054,7 +19006,7 @@
       </c>
       <c r="M153" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD 220 m² 3-byt.</t>
+          <t>TZ ARS + B4_productivity standard RD</t>
         </is>
       </c>
       <c r="N153" s="20" t="inlineStr">
@@ -19081,26 +19033,26 @@
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>Svítidla</t>
+          <t>Příprava FVE</t>
         </is>
       </c>
       <c r="D154" s="20" t="inlineStr">
         <is>
-          <t>210820002</t>
+          <t>210800099</t>
         </is>
       </c>
       <c r="E154" s="8" t="inlineStr">
         <is>
-          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
+          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
         </is>
       </c>
       <c r="F154" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G154" s="23" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="H154" s="10" t="n"/>
       <c r="I154" s="10" t="n"/>
@@ -19110,7 +19062,7 @@
         </is>
       </c>
       <c r="K154" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L154" s="20" t="inlineStr">
         <is>
@@ -19119,7 +19071,7 @@
       </c>
       <c r="M154" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD</t>
+          <t>TZ ARS dům §4 — FVE příprava (bez panelů samotných)</t>
         </is>
       </c>
       <c r="N154" s="20" t="inlineStr">
@@ -19146,17 +19098,17 @@
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t>Příprava FVE</t>
+          <t>Revize ELI při kolaudaci</t>
         </is>
       </c>
       <c r="D155" s="20" t="inlineStr">
         <is>
-          <t>210800099</t>
+          <t>996019011</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
+          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
         </is>
       </c>
       <c r="F155" s="20" t="inlineStr">
@@ -19171,11 +19123,11 @@
       <c r="I155" s="10" t="n"/>
       <c r="J155" s="8" t="inlineStr">
         <is>
-          <t>elektroinstalater</t>
+          <t>revize_specialista</t>
         </is>
       </c>
       <c r="K155" s="24" t="n">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
       <c r="L155" s="20" t="inlineStr">
         <is>
@@ -19184,12 +19136,12 @@
       </c>
       <c r="M155" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — FVE příprava (bez panelů samotných)</t>
+          <t>Povinná revize ELI dle ČSN 33 2000-6 + kolaudace</t>
         </is>
       </c>
       <c r="N155" s="20" t="inlineStr">
         <is>
-          <t>#7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O155" s="26" t="inlineStr">
@@ -19206,22 +19158,22 @@
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>Revize ELI při kolaudaci</t>
+          <t>Revize stávajících přípojek</t>
         </is>
       </c>
       <c r="D156" s="20" t="inlineStr">
         <is>
-          <t>996019011</t>
+          <t>722290515</t>
         </is>
       </c>
       <c r="E156" s="8" t="inlineStr">
         <is>
-          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
+          <t>Revize stávajícího napojení vodovodu + kanalizace na pozemku — kontrola stavu, čištění, tlaková zkouška</t>
         </is>
       </c>
       <c r="F156" s="20" t="inlineStr">
@@ -19236,25 +19188,25 @@
       <c r="I156" s="10" t="n"/>
       <c r="J156" s="8" t="inlineStr">
         <is>
-          <t>revize_specialista</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K156" s="24" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="L156" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M156" s="8" t="inlineStr">
         <is>
-          <t>Povinná revize ELI dle ČSN 33 2000-6 + kolaudace</t>
+          <t>TZ ARS dům §4 — vodovod + kanalizace stávající, bez změny</t>
         </is>
       </c>
       <c r="N156" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O156" s="26" t="inlineStr">
@@ -19263,7 +19215,11 @@
         </is>
       </c>
       <c r="P156" s="41" t="n"/>
-      <c r="Q156" s="41" t="n"/>
+      <c r="Q156" s="41" t="inlineStr">
+        <is>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="20" t="n">
@@ -19276,26 +19232,26 @@
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajících přípojek</t>
+          <t>Nové rozvody vody do 3.NP</t>
         </is>
       </c>
       <c r="D157" s="20" t="inlineStr">
         <is>
-          <t>722290515</t>
+          <t>722172011</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajícího napojení vodovodu + kanalizace na pozemku — kontrola stavu, čištění, tlaková zkouška</t>
+          <t>Nové rozvody studené + teplé vody do koupelen 1.NP + 2.NP + 3.NP a kuchyní (PEX/Cu, dimenze DN15-25)</t>
         </is>
       </c>
       <c r="F157" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G157" s="23" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G157" s="22" t="n">
+        <v>80</v>
       </c>
       <c r="H157" s="10" t="n"/>
       <c r="I157" s="10" t="n"/>
@@ -19305,7 +19261,7 @@
         </is>
       </c>
       <c r="K157" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L157" s="20" t="inlineStr">
         <is>
@@ -19314,7 +19270,7 @@
       </c>
       <c r="M157" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — vodovod + kanalizace stávající, bez změny</t>
+          <t>TZ ARS dům §4 — nové koupelny + kuchyně, vyjasnění #6 working assumption</t>
         </is>
       </c>
       <c r="N157" s="20" t="inlineStr">
@@ -19345,17 +19301,17 @@
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>Nové rozvody vody do 3.NP</t>
+          <t>Nové odpadní rozvody</t>
         </is>
       </c>
       <c r="D158" s="20" t="inlineStr">
         <is>
-          <t>722172011</t>
+          <t>721174021</t>
         </is>
       </c>
       <c r="E158" s="8" t="inlineStr">
         <is>
-          <t>Nové rozvody studené + teplé vody do koupelen 1.NP + 2.NP + 3.NP a kuchyní (PEX/Cu, dimenze DN15-25)</t>
+          <t>Nové odpadní rozvody PVC-HT DN40-DN110 ke koupelnám 1.NP, 2.NP, 3.NP a kuchyním + napojení na stávající</t>
         </is>
       </c>
       <c r="F158" s="20" t="inlineStr">
@@ -19364,7 +19320,7 @@
         </is>
       </c>
       <c r="G158" s="22" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H158" s="10" t="n"/>
       <c r="I158" s="10" t="n"/>
@@ -19378,12 +19334,12 @@
       </c>
       <c r="L158" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M158" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — nové koupelny + kuchyně, vyjasnění #6 working assumption</t>
+          <t>TZ ARS dům §4 — nové koupelny + kuchyně, odpad do stávající kanalizace</t>
         </is>
       </c>
       <c r="N158" s="20" t="inlineStr">
@@ -19397,11 +19353,7 @@
         </is>
       </c>
       <c r="P158" s="41" t="n"/>
-      <c r="Q158" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+      <c r="Q158" s="41" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="20" t="n">
@@ -19414,26 +19366,26 @@
       </c>
       <c r="C159" s="8" t="inlineStr">
         <is>
-          <t>Nové odpadní rozvody</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP)</t>
         </is>
       </c>
       <c r="D159" s="20" t="inlineStr">
         <is>
-          <t>721174021</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>Nové odpadní rozvody PVC-HT DN40-DN110 ke koupelnám 1.NP, 2.NP, 3.NP a kuchyním + napojení na stávající</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
         </is>
       </c>
       <c r="F159" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>set</t>
         </is>
       </c>
       <c r="G159" s="22" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H159" s="10" t="n"/>
       <c r="I159" s="10" t="n"/>
@@ -19452,7 +19404,7 @@
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — nové koupelny + kuchyně, odpad do stávající kanalizace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 1.05 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N159" s="20" t="inlineStr">
@@ -19466,7 +19418,11 @@
         </is>
       </c>
       <c r="P159" s="41" t="n"/>
-      <c r="Q159" s="41" t="n"/>
+      <c r="Q159" s="41" t="inlineStr">
+        <is>
+          <t>GAP_005_deprecated</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="20" t="n">
@@ -19479,26 +19435,26 @@
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP)</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture A</t>
         </is>
       </c>
       <c r="D160" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>725211101</t>
         </is>
       </c>
       <c r="E160" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
+          <t>Vana koupelnová obdélníková 170×70 cm — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F160" s="20" t="inlineStr">
         <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="G160" s="22" t="n">
-        <v>0</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G160" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H160" s="10" t="n"/>
       <c r="I160" s="10" t="n"/>
@@ -19508,7 +19464,7 @@
         </is>
       </c>
       <c r="K160" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L160" s="20" t="inlineStr">
         <is>
@@ -19517,12 +19473,12 @@
       </c>
       <c r="M160" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 1.05 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ MTEXT room 1.05 1.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N160" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O160" s="26" t="inlineStr">
@@ -19533,7 +19489,7 @@
       <c r="P160" s="41" t="n"/>
       <c r="Q160" s="41" t="inlineStr">
         <is>
-          <t>GAP_005_deprecated</t>
+          <t>GAP_005</t>
         </is>
       </c>
     </row>
@@ -19548,17 +19504,17 @@
       </c>
       <c r="C161" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture B</t>
         </is>
       </c>
       <c r="D161" s="20" t="inlineStr">
         <is>
-          <t>725211101</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t>Vana koupelnová obdélníková 170×70 cm — koupelna 1.05 1.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F161" s="20" t="inlineStr">
@@ -19617,17 +19573,17 @@
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture C</t>
         </is>
       </c>
       <c r="D162" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E162" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 1.05 1.NP</t>
+          <t>WC kombi keramické bílé — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F162" s="20" t="inlineStr">
@@ -19686,26 +19642,26 @@
       </c>
       <c r="C163" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture C</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP)</t>
         </is>
       </c>
       <c r="D163" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 1.05 1.NP</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standard)</t>
         </is>
       </c>
       <c r="F163" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G163" s="23" t="n">
-        <v>1</v>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G163" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H163" s="10" t="n"/>
       <c r="I163" s="10" t="n"/>
@@ -19715,7 +19671,7 @@
         </is>
       </c>
       <c r="K163" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L163" s="20" t="inlineStr">
         <is>
@@ -19724,12 +19680,12 @@
       </c>
       <c r="M163" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 1.05 1.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 2.03 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N163" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O163" s="26" t="inlineStr">
@@ -19740,7 +19696,7 @@
       <c r="P163" s="41" t="n"/>
       <c r="Q163" s="41" t="inlineStr">
         <is>
-          <t>GAP_005</t>
+          <t>GAP_005_deprecated</t>
         </is>
       </c>
     </row>
@@ -19755,26 +19711,26 @@
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP)</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture A</t>
         </is>
       </c>
       <c r="D164" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E164" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standard)</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F164" s="20" t="inlineStr">
         <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="G164" s="22" t="n">
-        <v>0</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G164" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H164" s="10" t="n"/>
       <c r="I164" s="10" t="n"/>
@@ -19784,7 +19740,7 @@
         </is>
       </c>
       <c r="K164" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L164" s="20" t="inlineStr">
         <is>
@@ -19793,12 +19749,12 @@
       </c>
       <c r="M164" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 2.03 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ MTEXT room 2.03 2.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N164" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O164" s="26" t="inlineStr">
@@ -19809,7 +19765,7 @@
       <c r="P164" s="41" t="n"/>
       <c r="Q164" s="41" t="inlineStr">
         <is>
-          <t>GAP_005_deprecated</t>
+          <t>GAP_005</t>
         </is>
       </c>
     </row>
@@ -19824,17 +19780,17 @@
       </c>
       <c r="C165" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture B</t>
         </is>
       </c>
       <c r="D165" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725221201</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 2.03 2.NP</t>
+          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F165" s="20" t="inlineStr">
@@ -19893,17 +19849,17 @@
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture C</t>
         </is>
       </c>
       <c r="D166" s="20" t="inlineStr">
         <is>
-          <t>725221201</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E166" s="8" t="inlineStr">
         <is>
-          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 2.03 2.NP</t>
+          <t>WC kombi keramické bílé — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F166" s="20" t="inlineStr">
@@ -19962,26 +19918,26 @@
       </c>
       <c r="C167" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture C</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP)</t>
         </is>
       </c>
       <c r="D167" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 2.03 2.NP</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standard)</t>
         </is>
       </c>
       <c r="F167" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G167" s="23" t="n">
-        <v>1</v>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G167" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H167" s="10" t="n"/>
       <c r="I167" s="10" t="n"/>
@@ -19991,7 +19947,7 @@
         </is>
       </c>
       <c r="K167" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L167" s="20" t="inlineStr">
         <is>
@@ -20000,12 +19956,12 @@
       </c>
       <c r="M167" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 2.03 2.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 3.04 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N167" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O167" s="26" t="inlineStr">
@@ -20016,7 +19972,7 @@
       <c r="P167" s="41" t="n"/>
       <c r="Q167" s="41" t="inlineStr">
         <is>
-          <t>GAP_005</t>
+          <t>GAP_005_deprecated</t>
         </is>
       </c>
     </row>
@@ -20031,26 +19987,26 @@
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP)</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture A</t>
         </is>
       </c>
       <c r="D168" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E168" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standard)</t>
+          <t>WC kombi keramické bílé — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F168" s="20" t="inlineStr">
         <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="G168" s="22" t="n">
-        <v>0</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G168" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H168" s="10" t="n"/>
       <c r="I168" s="10" t="n"/>
@@ -20060,7 +20016,7 @@
         </is>
       </c>
       <c r="K168" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L168" s="20" t="inlineStr">
         <is>
@@ -20069,12 +20025,12 @@
       </c>
       <c r="M168" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 3.04 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ MTEXT room 3.04 3.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N168" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O168" s="26" t="inlineStr">
@@ -20085,7 +20041,7 @@
       <c r="P168" s="41" t="n"/>
       <c r="Q168" s="41" t="inlineStr">
         <is>
-          <t>GAP_005_deprecated</t>
+          <t>GAP_005</t>
         </is>
       </c>
     </row>
@@ -20100,17 +20056,17 @@
       </c>
       <c r="C169" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture B</t>
         </is>
       </c>
       <c r="D169" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 3.04 3.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F169" s="20" t="inlineStr">
@@ -20169,17 +20125,17 @@
       </c>
       <c r="C170" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture C</t>
         </is>
       </c>
       <c r="D170" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725221201</t>
         </is>
       </c>
       <c r="E170" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 3.04 3.NP</t>
+          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F170" s="20" t="inlineStr">
@@ -20238,17 +20194,17 @@
       </c>
       <c r="C171" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture C</t>
+          <t>Kuchyňský dřez 2 ks (1.06 + 3.05)</t>
         </is>
       </c>
       <c r="D171" s="20" t="inlineStr">
         <is>
-          <t>725221201</t>
+          <t>725840111</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
         <is>
-          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 3.04 3.NP</t>
+          <t>Kuchyňský dřez nerez + montáž — 2 ks (kuchyně 1.06 byt rodičů + kuchyně 3.05 byt 3.NP)</t>
         </is>
       </c>
       <c r="F171" s="20" t="inlineStr">
@@ -20257,7 +20213,7 @@
         </is>
       </c>
       <c r="G171" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H171" s="10" t="n"/>
       <c r="I171" s="10" t="n"/>
@@ -20267,7 +20223,7 @@
         </is>
       </c>
       <c r="K171" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L171" s="20" t="inlineStr">
         <is>
@@ -20276,12 +20232,12 @@
       </c>
       <c r="M171" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 3.04 3.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF kuchyně MTEXT 2× + TZ ARS — dispozice byty</t>
         </is>
       </c>
       <c r="N171" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O171" s="26" t="inlineStr">
@@ -20290,11 +20246,7 @@
         </is>
       </c>
       <c r="P171" s="41" t="n"/>
-      <c r="Q171" s="41" t="inlineStr">
-        <is>
-          <t>GAP_005</t>
-        </is>
-      </c>
+      <c r="Q171" s="41" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="20" t="n">
@@ -20307,17 +20259,17 @@
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t>Kuchyňský dřez 2 ks (1.06 + 3.05)</t>
+          <t>Vodovodní baterie + drobnosti</t>
         </is>
       </c>
       <c r="D172" s="20" t="inlineStr">
         <is>
-          <t>725840111</t>
+          <t>725822611</t>
         </is>
       </c>
       <c r="E172" s="8" t="inlineStr">
         <is>
-          <t>Kuchyňský dřez nerez + montáž — 2 ks (kuchyně 1.06 byt rodičů + kuchyně 3.05 byt 3.NP)</t>
+          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační materiály</t>
         </is>
       </c>
       <c r="F172" s="20" t="inlineStr">
@@ -20326,7 +20278,7 @@
         </is>
       </c>
       <c r="G172" s="23" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H172" s="10" t="n"/>
       <c r="I172" s="10" t="n"/>
@@ -20336,7 +20288,7 @@
         </is>
       </c>
       <c r="K172" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L172" s="20" t="inlineStr">
         <is>
@@ -20345,7 +20297,7 @@
       </c>
       <c r="M172" s="8" t="inlineStr">
         <is>
-          <t>DXF kuchyně MTEXT 2× + TZ ARS — dispozice byty</t>
+          <t>TZ ARS — kompletní baterie nové</t>
         </is>
       </c>
       <c r="N172" s="20" t="inlineStr">
@@ -20372,17 +20324,17 @@
       </c>
       <c r="C173" s="8" t="inlineStr">
         <is>
-          <t>Vodovodní baterie + drobnosti</t>
+          <t>Akumulační zásobník TUV v suterénu</t>
         </is>
       </c>
       <c r="D173" s="20" t="inlineStr">
         <is>
-          <t>725822611</t>
+          <t>732419411</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
         <is>
-          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační materiály</t>
+          <t>Akumulační zásobník TUV ~300 l v 1.PP napojený na topný systém (sporáková kamna + krb + elektrokotel) — nepřímotop</t>
         </is>
       </c>
       <c r="F173" s="20" t="inlineStr">
@@ -20391,17 +20343,17 @@
         </is>
       </c>
       <c r="G173" s="23" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H173" s="10" t="n"/>
       <c r="I173" s="10" t="n"/>
       <c r="J173" s="8" t="inlineStr">
         <is>
-          <t>vodar</t>
+          <t>instalater_TUV_akumulacni_zasobnik</t>
         </is>
       </c>
       <c r="K173" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L173" s="20" t="inlineStr">
         <is>
@@ -20410,7 +20362,7 @@
       </c>
       <c r="M173" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS — kompletní baterie nové</t>
+          <t>TZ ARS dům §4 — kombi akumulační zásobník napojený na multivariantní topný systém</t>
         </is>
       </c>
       <c r="N173" s="20" t="inlineStr">
@@ -20437,17 +20389,17 @@
       </c>
       <c r="C174" s="8" t="inlineStr">
         <is>
-          <t>Akumulační zásobník TUV v suterénu</t>
+          <t>Elektrický bojler 3.NP</t>
         </is>
       </c>
       <c r="D174" s="20" t="inlineStr">
         <is>
-          <t>732419411</t>
+          <t>732429211</t>
         </is>
       </c>
       <c r="E174" s="8" t="inlineStr">
         <is>
-          <t>Akumulační zásobník TUV ~300 l v 1.PP napojený na topný systém (sporáková kamna + krb + elektrokotel) — nepřímotop</t>
+          <t>Elektrický bojler ~80 l v koupelně 3.NP (nezávislý zdroj pro samostatný byt)</t>
         </is>
       </c>
       <c r="F174" s="20" t="inlineStr">
@@ -20462,7 +20414,7 @@
       <c r="I174" s="10" t="n"/>
       <c r="J174" s="8" t="inlineStr">
         <is>
-          <t>instalater_TUV_akumulacni_zasobnik</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K174" s="24" t="n">
@@ -20475,7 +20427,7 @@
       </c>
       <c r="M174" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kombi akumulační zásobník napojený na multivariantní topný systém</t>
+          <t>TZ ARS dům §4 — elektrický bojler v 3.NP koupelně, vyjasnění #6 odhad 80 l</t>
         </is>
       </c>
       <c r="N174" s="20" t="inlineStr">
@@ -20497,22 +20449,22 @@
       </c>
       <c r="B175" s="8" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>PSV-73 Vytápění</t>
         </is>
       </c>
       <c r="C175" s="8" t="inlineStr">
         <is>
-          <t>Elektrický bojler 3.NP</t>
+          <t>Sporáková kamna na tuhá paliva</t>
         </is>
       </c>
       <c r="D175" s="20" t="inlineStr">
         <is>
-          <t>732429211</t>
+          <t>733241011</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
         <is>
-          <t>Elektrický bojler ~80 l v koupelně 3.NP (nezávislý zdroj pro samostatný byt)</t>
+          <t>Sporáková kamna na tuhá paliva ~10 kW s akumulačním zásobníkem TUV — dodávka</t>
         </is>
       </c>
       <c r="F175" s="20" t="inlineStr">
@@ -20527,7 +20479,7 @@
       <c r="I175" s="10" t="n"/>
       <c r="J175" s="8" t="inlineStr">
         <is>
-          <t>vodar</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K175" s="24" t="n">
@@ -20540,7 +20492,7 @@
       </c>
       <c r="M175" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — elektrický bojler v 3.NP koupelně, vyjasnění #6 odhad 80 l</t>
+          <t>TZ ARS dům §4 — primární zdroj 1.NP/2.NP, ~10 kW odhad standard RD</t>
         </is>
       </c>
       <c r="N175" s="20" t="inlineStr">
@@ -20567,22 +20519,22 @@
       </c>
       <c r="C176" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna na tuhá paliva</t>
+          <t>Sporáková kamna — montáž</t>
         </is>
       </c>
       <c r="D176" s="20" t="inlineStr">
         <is>
-          <t>733241011</t>
+          <t>733281011</t>
         </is>
       </c>
       <c r="E176" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna na tuhá paliva ~10 kW s akumulačním zásobníkem TUV — dodávka</t>
+          <t>Sporáková kamna — montáž vč. napojení na komín + akumulační zásobník (cca 8 Nh)</t>
         </is>
       </c>
       <c r="F176" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G176" s="23" t="n">
@@ -20596,7 +20548,7 @@
         </is>
       </c>
       <c r="K176" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L176" s="20" t="inlineStr">
         <is>
@@ -20605,12 +20557,12 @@
       </c>
       <c r="M176" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — primární zdroj 1.NP/2.NP, ~10 kW odhad standard RD</t>
+          <t>Standard montáž kamen s napojením na zásobník</t>
         </is>
       </c>
       <c r="N176" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O176" s="26" t="inlineStr">
@@ -20632,22 +20584,22 @@
       </c>
       <c r="C177" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna — montáž</t>
+          <t>Elektrokotel 3.NP</t>
         </is>
       </c>
       <c r="D177" s="20" t="inlineStr">
         <is>
-          <t>733281011</t>
+          <t>733131221</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna — montáž vč. napojení na komín + akumulační zásobník (cca 8 Nh)</t>
+          <t>Elektrokotel ~8 kW pro 3.NP samostatný byt — dodávka + montáž + napojení</t>
         </is>
       </c>
       <c r="F177" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G177" s="23" t="n">
@@ -20661,7 +20613,7 @@
         </is>
       </c>
       <c r="K177" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L177" s="20" t="inlineStr">
         <is>
@@ -20670,12 +20622,12 @@
       </c>
       <c r="M177" s="8" t="inlineStr">
         <is>
-          <t>Standard montáž kamen s napojením na zásobník</t>
+          <t>TZ ARS dům §4 — 'Nově navržené 3.NP bude vytápěno elektrokotlem'; ~8 kW odhad</t>
         </is>
       </c>
       <c r="N177" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O177" s="26" t="inlineStr">
@@ -20697,17 +20649,17 @@
       </c>
       <c r="C178" s="8" t="inlineStr">
         <is>
-          <t>Elektrokotel 3.NP</t>
+          <t>Krb na tuhá paliva 3.NP</t>
         </is>
       </c>
       <c r="D178" s="20" t="inlineStr">
         <is>
-          <t>733131221</t>
+          <t>733241011</t>
         </is>
       </c>
       <c r="E178" s="8" t="inlineStr">
         <is>
-          <t>Elektrokotel ~8 kW pro 3.NP samostatný byt — dodávka + montáž + napojení</t>
+          <t>Krb na tuhá paliva v 3.NP ~6 kW — dodávka + montáž s napojením na samostatný komín</t>
         </is>
       </c>
       <c r="F178" s="20" t="inlineStr">
@@ -20735,7 +20687,7 @@
       </c>
       <c r="M178" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — 'Nově navržené 3.NP bude vytápěno elektrokotlem'; ~8 kW odhad</t>
+          <t>TZ ARS dům §4 — krb v 3.NP, ~6 kW odhad</t>
         </is>
       </c>
       <c r="N178" s="20" t="inlineStr">
@@ -20762,17 +20714,17 @@
       </c>
       <c r="C179" s="8" t="inlineStr">
         <is>
-          <t>Krb na tuhá paliva 3.NP</t>
+          <t>Multisplit TČ — venkovní jednotka</t>
         </is>
       </c>
       <c r="D179" s="20" t="inlineStr">
         <is>
-          <t>733241011</t>
+          <t>733425211</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
         <is>
-          <t>Krb na tuhá paliva v 3.NP ~6 kW — dodávka + montáž s napojením na samostatný komín</t>
+          <t>Multisplit tepelné čerpadlo vzduch-vzduch — 1× venkovní jednotka ~10 kW (silent mode hl. tlaku ≤49 dBA)</t>
         </is>
       </c>
       <c r="F179" s="20" t="inlineStr">
@@ -20787,7 +20739,7 @@
       <c r="I179" s="10" t="n"/>
       <c r="J179" s="8" t="inlineStr">
         <is>
-          <t>topenar</t>
+          <t>specialista_TC_multisplit</t>
         </is>
       </c>
       <c r="K179" s="24" t="n">
@@ -20800,7 +20752,7 @@
       </c>
       <c r="M179" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — krb v 3.NP, ~6 kW odhad</t>
+          <t>TZ ARS dům §4 — multisplit TČ s akustikou hl. tlaku ≤49 dBA, NV 272/2011</t>
         </is>
       </c>
       <c r="N179" s="20" t="inlineStr">
@@ -20827,17 +20779,17 @@
       </c>
       <c r="C180" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — venkovní jednotka</t>
+          <t>Multisplit TČ — vnitřní jednotky</t>
         </is>
       </c>
       <c r="D180" s="20" t="inlineStr">
         <is>
-          <t>733425211</t>
+          <t>733425221</t>
         </is>
       </c>
       <c r="E180" s="8" t="inlineStr">
         <is>
-          <t>Multisplit tepelné čerpadlo vzduch-vzduch — 1× venkovní jednotka ~10 kW (silent mode hl. tlaku ≤49 dBA)</t>
+          <t>Multisplit TČ — 5× vnitřní jednotka v obytných místnostech (1.NP, 2.NP, 3.NP — chlazení + vytápění)</t>
         </is>
       </c>
       <c r="F180" s="20" t="inlineStr">
@@ -20846,7 +20798,7 @@
         </is>
       </c>
       <c r="G180" s="23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H180" s="10" t="n"/>
       <c r="I180" s="10" t="n"/>
@@ -20856,7 +20808,7 @@
         </is>
       </c>
       <c r="K180" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L180" s="20" t="inlineStr">
         <is>
@@ -20865,7 +20817,7 @@
       </c>
       <c r="M180" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — multisplit TČ s akustikou hl. tlaku ≤49 dBA, NV 272/2011</t>
+          <t>TZ ARS dům §4 — vnitřní jednotky multisplit, vyjasnění #6 odhad 5 ks</t>
         </is>
       </c>
       <c r="N180" s="20" t="inlineStr">
@@ -20892,36 +20844,36 @@
       </c>
       <c r="C181" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — vnitřní jednotky</t>
+          <t>Revize komínu</t>
         </is>
       </c>
       <c r="D181" s="20" t="inlineStr">
         <is>
-          <t>733425221</t>
+          <t>734262122</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — 5× vnitřní jednotka v obytných místnostech (1.NP, 2.NP, 3.NP — chlazení + vytápění)</t>
+          <t>Revize stávajícího komínu — kontrola, čištění, vystrojení vložkou nerez DN160 pro kamna + krb 3.NP</t>
         </is>
       </c>
       <c r="F181" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G181" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H181" s="10" t="n"/>
       <c r="I181" s="10" t="n"/>
       <c r="J181" s="8" t="inlineStr">
         <is>
-          <t>specialista_TC_multisplit</t>
+          <t>kominik</t>
         </is>
       </c>
       <c r="K181" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L181" s="20" t="inlineStr">
         <is>
@@ -20930,7 +20882,7 @@
       </c>
       <c r="M181" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — vnitřní jednotky multisplit, vyjasnění #6 odhad 5 ks</t>
+          <t>TZ ARS dům §4 — komín stávající, vystrojení vložkou pro kamna + krb</t>
         </is>
       </c>
       <c r="N181" s="20" t="inlineStr">
@@ -20957,36 +20909,36 @@
       </c>
       <c r="C182" s="8" t="inlineStr">
         <is>
-          <t>Revize komínu</t>
+          <t>Rozvody otopné soustavy</t>
         </is>
       </c>
       <c r="D182" s="20" t="inlineStr">
         <is>
-          <t>734262122</t>
+          <t>733111021</t>
         </is>
       </c>
       <c r="E182" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajícího komínu — kontrola, čištění, vystrojení vložkou nerez DN160 pro kamna + krb 3.NP</t>
+          <t>Rozvody otopné soustavy Cu/PEX k vnitřním jednotkám TČ + radiátorům pro doplňkové (cca 100 bm odhad)</t>
         </is>
       </c>
       <c r="F182" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G182" s="23" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G182" s="22" t="n">
+        <v>100</v>
       </c>
       <c r="H182" s="10" t="n"/>
       <c r="I182" s="10" t="n"/>
       <c r="J182" s="8" t="inlineStr">
         <is>
-          <t>kominik</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K182" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L182" s="20" t="inlineStr">
         <is>
@@ -20995,7 +20947,7 @@
       </c>
       <c r="M182" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — komín stávající, vystrojení vložkou pro kamna + krb</t>
+          <t>TZ ARS dům §4 — rozvody otopné soustavy</t>
         </is>
       </c>
       <c r="N182" s="20" t="inlineStr">
@@ -21017,41 +20969,41 @@
       </c>
       <c r="B183" s="8" t="inlineStr">
         <is>
-          <t>PSV-73 Vytápění</t>
+          <t>VRN — BOZP</t>
         </is>
       </c>
       <c r="C183" s="8" t="inlineStr">
         <is>
-          <t>Rozvody otopné soustavy</t>
+          <t>Koordinace BOZP</t>
         </is>
       </c>
       <c r="D183" s="20" t="inlineStr">
         <is>
-          <t>733111021</t>
+          <t>030091000</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
         <is>
-          <t>Rozvody otopné soustavy Cu/PEX k vnitřním jednotkám TČ + radiátorům pro doplňkové (cca 100 bm odhad)</t>
+          <t>Koordinátor BOZP na staveništi dle zákona 309/2006 Sb. — pro stavbu s více než jedním zhotovitelem</t>
         </is>
       </c>
       <c r="F183" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G183" s="22" t="n">
-        <v>100</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G183" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H183" s="10" t="n"/>
       <c r="I183" s="10" t="n"/>
       <c r="J183" s="8" t="inlineStr">
         <is>
-          <t>topenar</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K183" s="24" t="n">
-        <v>0.75</v>
+        <v>0.99</v>
       </c>
       <c r="L183" s="20" t="inlineStr">
         <is>
@@ -21060,12 +21012,12 @@
       </c>
       <c r="M183" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — rozvody otopné soustavy</t>
+          <t>Zákon 309/2006 Sb. — povinný BOZP koordinátor pro vícezhotovitelskou stavbu</t>
         </is>
       </c>
       <c r="N183" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O183" s="26" t="inlineStr">
@@ -21082,22 +21034,22 @@
       </c>
       <c r="B184" s="8" t="inlineStr">
         <is>
-          <t>VRN — BOZP</t>
+          <t>VRN — Dokumentace</t>
         </is>
       </c>
       <c r="C184" s="8" t="inlineStr">
         <is>
-          <t>Koordinace BOZP</t>
+          <t>Předávací protokoly + DSP</t>
         </is>
       </c>
       <c r="D184" s="20" t="inlineStr">
         <is>
-          <t>030091000</t>
+          <t>030151000</t>
         </is>
       </c>
       <c r="E184" s="8" t="inlineStr">
         <is>
-          <t>Koordinátor BOZP na staveništi dle zákona 309/2006 Sb. — pro stavbu s více než jedním zhotovitelem</t>
+          <t>Předávací protokoly + Dokumentace skutečného provedení (DSP) — sestavení, vázání, dodávka 2× tiskem + elektronická verze</t>
         </is>
       </c>
       <c r="F184" s="20" t="inlineStr">
@@ -21125,12 +21077,12 @@
       </c>
       <c r="M184" s="8" t="inlineStr">
         <is>
-          <t>Zákon 309/2006 Sb. — povinný BOZP koordinátor pro vícezhotovitelskou stavbu</t>
+          <t>Vyhláška 499/2006 Sb. + ČKAIT — DSP povinná pro kolaudaci</t>
         </is>
       </c>
       <c r="N184" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O184" s="26" t="inlineStr">
@@ -21147,41 +21099,41 @@
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
-          <t>VRN — Dokumentace</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C185" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokoly + DSP</t>
+          <t>Kontejnery suti tříděné</t>
         </is>
       </c>
       <c r="D185" s="20" t="inlineStr">
         <is>
-          <t>030151000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokoly + Dokumentace skutečného provedení (DSP) — sestavení, vázání, dodávka 2× tiskem + elektronická verze</t>
+          <t>Kontejnery na suť tříděnou velkoobjemové (beton/cihly, dřevo, kovy, EPS, sádra, směs) — pronájem + svozy</t>
         </is>
       </c>
       <c r="F185" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G185" s="23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H185" s="10" t="n"/>
       <c r="I185" s="10" t="n"/>
       <c r="J185" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K185" s="24" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="L185" s="20" t="inlineStr">
         <is>
@@ -21190,12 +21142,12 @@
       </c>
       <c r="M185" s="8" t="inlineStr">
         <is>
-          <t>Vyhláška 499/2006 Sb. + ČKAIT — DSP povinná pro kolaudaci</t>
+          <t>TZ B m.10.e: beton/cihly 46 t + dřevo 9 t + kovy 0.1 + EPS 0.1 + sádra 0.2 + směs 1.0</t>
         </is>
       </c>
       <c r="N185" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#9, #10</t>
         </is>
       </c>
       <c r="O185" s="26" t="inlineStr">
@@ -21217,36 +21169,36 @@
       </c>
       <c r="C186" s="8" t="inlineStr">
         <is>
-          <t>Kontejnery suti tříděné</t>
+          <t>Doprava materiálu</t>
         </is>
       </c>
       <c r="D186" s="20" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>031031000</t>
         </is>
       </c>
       <c r="E186" s="8" t="inlineStr">
         <is>
-          <t>Kontejnery na suť tříděnou velkoobjemové (beton/cihly, dřevo, kovy, EPS, sádra, směs) — pronájem + svozy</t>
+          <t>Doprava materiálu na stavbu (centrální koordinace) — paušál ~2-3 % z PN materiál</t>
         </is>
       </c>
       <c r="F186" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>paušál</t>
         </is>
       </c>
       <c r="G186" s="23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H186" s="10" t="n"/>
       <c r="I186" s="10" t="n"/>
       <c r="J186" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K186" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L186" s="20" t="inlineStr">
         <is>
@@ -21255,12 +21207,12 @@
       </c>
       <c r="M186" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e: beton/cihly 46 t + dřevo 9 t + kovy 0.1 + EPS 0.1 + sádra 0.2 + směs 1.0</t>
+          <t>B4_productivity — standard doprava RD městská zástavba</t>
         </is>
       </c>
       <c r="N186" s="20" t="inlineStr">
         <is>
-          <t>#9, #10</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O186" s="26" t="inlineStr">
@@ -21282,36 +21234,36 @@
       </c>
       <c r="C187" s="8" t="inlineStr">
         <is>
-          <t>Doprava materiálu</t>
+          <t>Likvidace odpadů 56.9 t</t>
         </is>
       </c>
       <c r="D187" s="20" t="inlineStr">
         <is>
-          <t>031031000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
         <is>
-          <t>Doprava materiálu na stavbu (centrální koordinace) — paušál ~2-3 % z PN materiál</t>
+          <t>Likvidace stavební suti dle vyhl. 8/2021 Sb. — skládkovné + recyklace + třídění (56.9 t celkem per TZ B m.10.e)</t>
         </is>
       </c>
       <c r="F187" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="G187" s="23" t="n">
-        <v>1</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G187" s="22" t="n">
+        <v>56.9</v>
       </c>
       <c r="H187" s="10" t="n"/>
       <c r="I187" s="10" t="n"/>
       <c r="J187" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K187" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L187" s="20" t="inlineStr">
         <is>
@@ -21320,12 +21272,12 @@
       </c>
       <c r="M187" s="8" t="inlineStr">
         <is>
-          <t>B4_productivity — standard doprava RD městská zástavba</t>
+          <t>TZ B m.10.e bilance odpadů celkem dům</t>
         </is>
       </c>
       <c r="N187" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>#9, #10</t>
         </is>
       </c>
       <c r="O187" s="26" t="inlineStr">
@@ -21342,41 +21294,41 @@
       </c>
       <c r="B188" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="C188" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadů 56.9 t</t>
+          <t>Geodetické zaměření před + po realizaci</t>
         </is>
       </c>
       <c r="D188" s="20" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>030141000</t>
         </is>
       </c>
       <c r="E188" s="8" t="inlineStr">
         <is>
-          <t>Likvidace stavební suti dle vyhl. 8/2021 Sb. — skládkovné + recyklace + třídění (56.9 t celkem per TZ B m.10.e)</t>
+          <t>Geodetické zaměření před realizací (verifikace polohopis + výškopis) + po dokončení (zaměření skutečného provedení pro kolaudaci)</t>
         </is>
       </c>
       <c r="F188" s="20" t="inlineStr">
         <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G188" s="22" t="n">
-        <v>56.9</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G188" s="23" t="n">
+        <v>2</v>
       </c>
       <c r="H188" s="10" t="n"/>
       <c r="I188" s="10" t="n"/>
       <c r="J188" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>geodet</t>
         </is>
       </c>
       <c r="K188" s="24" t="n">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
       <c r="L188" s="20" t="inlineStr">
         <is>
@@ -21385,12 +21337,12 @@
       </c>
       <c r="M188" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e bilance odpadů celkem dům</t>
+          <t>Standard — geodet před+po pro každou stavbu</t>
         </is>
       </c>
       <c r="N188" s="20" t="inlineStr">
         <is>
-          <t>#9, #10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O188" s="26" t="inlineStr">
@@ -21407,37 +21359,37 @@
       </c>
       <c r="B189" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Kolaudace</t>
         </is>
       </c>
       <c r="C189" s="8" t="inlineStr">
         <is>
-          <t>Geodetické zaměření před + po realizaci</t>
+          <t>Kolaudační řízení</t>
         </is>
       </c>
       <c r="D189" s="20" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>030171000</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
         <is>
-          <t>Geodetické zaměření před realizací (verifikace polohopis + výškopis) + po dokončení (zaměření skutečného provedení pro kolaudaci)</t>
+          <t>Kolaudační řízení — paušál (správní poplatky + součinnost) dle zákona 183/2006 Sb.</t>
         </is>
       </c>
       <c r="F189" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>paušál</t>
         </is>
       </c>
       <c r="G189" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H189" s="10" t="n"/>
       <c r="I189" s="10" t="n"/>
       <c r="J189" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K189" s="24" t="n">
@@ -21450,7 +21402,7 @@
       </c>
       <c r="M189" s="8" t="inlineStr">
         <is>
-          <t>Standard — geodet před+po pro každou stavbu</t>
+          <t>Zákon 183/2006 Sb. + vyhl. 499/2006 Sb.</t>
         </is>
       </c>
       <c r="N189" s="20" t="inlineStr">
@@ -21472,31 +21424,31 @@
       </c>
       <c r="B190" s="8" t="inlineStr">
         <is>
-          <t>VRN — Kolaudace</t>
+          <t>VRN — Lešení</t>
         </is>
       </c>
       <c r="C190" s="8" t="inlineStr">
         <is>
-          <t>Kolaudační řízení</t>
+          <t>Fasádní lešení (ETICS + krov + klempířina)</t>
         </is>
       </c>
       <c r="D190" s="20" t="inlineStr">
         <is>
-          <t>030171000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E190" s="8" t="inlineStr">
         <is>
-          <t>Kolaudační řízení — paušál (správní poplatky + součinnost) dle zákona 183/2006 Sb.</t>
+          <t>Fasádní lešení trubkové/rámové vč. montáže + pronájmu + demontáže — pro provedení ETICS fasády, krovu a klempířiny po obvodu domu (výška 13 m)</t>
         </is>
       </c>
       <c r="F190" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="G190" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G190" s="22" t="n">
+        <v>503.1</v>
       </c>
       <c r="H190" s="10" t="n"/>
       <c r="I190" s="10" t="n"/>
@@ -21506,7 +21458,7 @@
         </is>
       </c>
       <c r="K190" s="24" t="n">
-        <v>0.99</v>
+        <v>0.8</v>
       </c>
       <c r="L190" s="20" t="inlineStr">
         <is>
@@ -21515,7 +21467,7 @@
       </c>
       <c r="M190" s="8" t="inlineStr">
         <is>
-          <t>Zákon 183/2006 Sb. + vyhl. 499/2006 Sb.</t>
+          <t>anchor checklist PM02 — technical necessity (ETICS 276.7 m² nelze provést bez lešení, 941xxx URS família) + DXF obvod 38.7 m + řez výška 13 m</t>
         </is>
       </c>
       <c r="N190" s="20" t="inlineStr">
@@ -21529,7 +21481,11 @@
         </is>
       </c>
       <c r="P190" s="41" t="n"/>
-      <c r="Q190" s="41" t="n"/>
+      <c r="Q190" s="41" t="inlineStr">
+        <is>
+          <t>ANCHOR_CHECKLIST_PM02</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="20" t="n">
@@ -21537,31 +21493,31 @@
       </c>
       <c r="B191" s="8" t="inlineStr">
         <is>
-          <t>VRN — Lešení</t>
+          <t>VRN — Pojištění + zábory</t>
         </is>
       </c>
       <c r="C191" s="8" t="inlineStr">
         <is>
-          <t>Fasádní lešení (ETICS + krov + klempířina)</t>
+          <t>Pojištění stavby (montážní + odpovědnostní)</t>
         </is>
       </c>
       <c r="D191" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>030081000</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
         <is>
-          <t>Fasádní lešení trubkové/rámové vč. montáže + pronájmu + demontáže — pro provedení ETICS fasády, krovu a klempířiny po obvodu domu (výška 13 m)</t>
+          <t>Montážní pojištění stavby (CAR) + pojištění odpovědnosti za škodu (zhotovitel) — paušál cca 0.3-0.5 % z PN</t>
         </is>
       </c>
       <c r="F191" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G191" s="22" t="n">
-        <v>503.1</v>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G191" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H191" s="10" t="n"/>
       <c r="I191" s="10" t="n"/>
@@ -21571,7 +21527,7 @@
         </is>
       </c>
       <c r="K191" s="24" t="n">
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="L191" s="20" t="inlineStr">
         <is>
@@ -21580,12 +21536,12 @@
       </c>
       <c r="M191" s="8" t="inlineStr">
         <is>
-          <t>anchor checklist PM02 — technical necessity (ETICS 276.7 m² nelze provést bez lešení, 941xxx URS família) + DXF obvod 38.7 m + řez výška 13 m</t>
+          <t>Standard zhotovitel — pojistná povinnost</t>
         </is>
       </c>
       <c r="N191" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O191" s="26" t="inlineStr">
@@ -21594,11 +21550,7 @@
         </is>
       </c>
       <c r="P191" s="41" t="n"/>
-      <c r="Q191" s="41" t="inlineStr">
-        <is>
-          <t>ANCHOR_CHECKLIST_PM02</t>
-        </is>
-      </c>
+      <c r="Q191" s="41" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="20" t="n">
@@ -21611,22 +21563,22 @@
       </c>
       <c r="C192" s="8" t="inlineStr">
         <is>
-          <t>Pojištění stavby (montážní + odpovědnostní)</t>
+          <t>Krátkodobé zábory ul. Fibichova</t>
         </is>
       </c>
       <c r="D192" s="20" t="inlineStr">
         <is>
-          <t>030081000</t>
+          <t>030083000</t>
         </is>
       </c>
       <c r="E192" s="8" t="inlineStr">
         <is>
-          <t>Montážní pojištění stavby (CAR) + pojištění odpovědnosti za škodu (zhotovitel) — paušál cca 0.3-0.5 % z PN</t>
+          <t>Krátkodobé zábory ulice Fibichova pro materiál a kontejnery (povolení MU Jáchymov + DI) — odhad 30 dnů kumulativně</t>
         </is>
       </c>
       <c r="F192" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G192" s="23" t="n">
@@ -21640,7 +21592,7 @@
         </is>
       </c>
       <c r="K192" s="24" t="n">
-        <v>0.99</v>
+        <v>0.75</v>
       </c>
       <c r="L192" s="20" t="inlineStr">
         <is>
@@ -21649,7 +21601,7 @@
       </c>
       <c r="M192" s="8" t="inlineStr">
         <is>
-          <t>Standard zhotovitel — pojistná povinnost</t>
+          <t>TZ B m.10 + situace — řadovka ul. Fibichova</t>
         </is>
       </c>
       <c r="N192" s="20" t="inlineStr">
@@ -21671,22 +21623,22 @@
       </c>
       <c r="B193" s="8" t="inlineStr">
         <is>
-          <t>VRN — Pojištění + zábory</t>
+          <t>VRN — Průzkumy</t>
         </is>
       </c>
       <c r="C193" s="8" t="inlineStr">
         <is>
-          <t>Krátkodobé zábory ul. Fibichova</t>
+          <t>Mykologický průzkum dřeva při bourání</t>
         </is>
       </c>
       <c r="D193" s="20" t="inlineStr">
         <is>
-          <t>030083000</t>
+          <t>030131000</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
         <is>
-          <t>Krátkodobé zábory ulice Fibichova pro materiál a kontejnery (povolení MU Jáchymov + DI) — odhad 30 dnů kumulativně</t>
+          <t>Mykologický průzkum + průzkum výskytu dřevokazného hmyzu stávajícího krovu a dřevěných trámů zhlaví — pro vyloučení narušení dřevěných konstrukcí; provádí autorizovaný mykolog při bourání</t>
         </is>
       </c>
       <c r="F193" s="20" t="inlineStr">
@@ -21701,11 +21653,11 @@
       <c r="I193" s="10" t="n"/>
       <c r="J193" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>mykolog</t>
         </is>
       </c>
       <c r="K193" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L193" s="20" t="inlineStr">
         <is>
@@ -21714,7 +21666,7 @@
       </c>
       <c r="M193" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10 + situace — řadovka ul. Fibichova</t>
+          <t>TZ ARS dům §3.2.3 + POZN.2.05 z půdorysů návrh + řez A-A návrh (explicit dřevokazný hmyz scope per drawing wording)</t>
         </is>
       </c>
       <c r="N193" s="20" t="inlineStr">
@@ -21728,7 +21680,11 @@
         </is>
       </c>
       <c r="P193" s="41" t="n"/>
-      <c r="Q193" s="41" t="n"/>
+      <c r="Q193" s="41" t="inlineStr">
+        <is>
+          <t>PER_DRAWING_ENRICHMENT_POZN_2_05</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="20" t="n">
@@ -21741,17 +21697,17 @@
       </c>
       <c r="C194" s="8" t="inlineStr">
         <is>
-          <t>Mykologický průzkum dřeva při bourání</t>
+          <t>Azbestový průzkum podrobný před demolicí</t>
         </is>
       </c>
       <c r="D194" s="20" t="inlineStr">
         <is>
-          <t>030131000</t>
+          <t>030133000</t>
         </is>
       </c>
       <c r="E194" s="8" t="inlineStr">
         <is>
-          <t>Mykologický průzkum + průzkum výskytu dřevokazného hmyzu stávajícího krovu a dřevěných trámů zhlaví — pro vyloučení narušení dřevěných konstrukcí; provádí autorizovaný mykolog při bourání</t>
+          <t>Azbestový průzkum podrobný před demolicí — laboratorní vzorky a posudek (B kap. m.7.a předběžně negativní, ale podrobný před bouráním povinný)</t>
         </is>
       </c>
       <c r="F194" s="20" t="inlineStr">
@@ -21766,7 +21722,7 @@
       <c r="I194" s="10" t="n"/>
       <c r="J194" s="8" t="inlineStr">
         <is>
-          <t>mykolog</t>
+          <t>azbestovy_specialista</t>
         </is>
       </c>
       <c r="K194" s="24" t="n">
@@ -21779,7 +21735,7 @@
       </c>
       <c r="M194" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.3 + POZN.2.05 z půdorysů návrh + řez A-A návrh (explicit dřevokazný hmyz scope per drawing wording)</t>
+          <t>TZ B m.7.a + ARS §3.2 — azbestový průzkum povinný před demolicí</t>
         </is>
       </c>
       <c r="N194" s="20" t="inlineStr">
@@ -21793,11 +21749,7 @@
         </is>
       </c>
       <c r="P194" s="41" t="n"/>
-      <c r="Q194" s="41" t="inlineStr">
-        <is>
-          <t>PER_DRAWING_ENRICHMENT_POZN_2_05</t>
-        </is>
-      </c>
+      <c r="Q194" s="41" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="20" t="n">
@@ -21805,41 +21757,41 @@
       </c>
       <c r="B195" s="8" t="inlineStr">
         <is>
-          <t>VRN — Průzkumy</t>
+          <t>VRN — Přesun hmot</t>
         </is>
       </c>
       <c r="C195" s="8" t="inlineStr">
         <is>
-          <t>Azbestový průzkum podrobný před demolicí</t>
+          <t>Přesun hmot pro budovu</t>
         </is>
       </c>
       <c r="D195" s="20" t="inlineStr">
         <is>
-          <t>030133000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
         <is>
-          <t>Azbestový průzkum podrobný před demolicí — laboratorní vzorky a posudek (B kap. m.7.a předběžně negativní, ale podrobný před bouráním povinný)</t>
+          <t>Přesun hmot pro budovu — vnitrostaveništní vertikální + horizontální doprava materiálu a hmot (rekonstrukce vícepodlažní RD + nástavba 3.NP)</t>
         </is>
       </c>
       <c r="F195" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G195" s="23" t="n">
-        <v>1</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G195" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H195" s="10" t="n"/>
       <c r="I195" s="10" t="n"/>
       <c r="J195" s="8" t="inlineStr">
         <is>
-          <t>azbestovy_specialista</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K195" s="24" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="L195" s="20" t="inlineStr">
         <is>
@@ -21848,12 +21800,12 @@
       </c>
       <c r="M195" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.7.a + ARS §3.2 — azbestový průzkum povinný před demolicí</t>
+          <t>anchor checklist PM01 — technical necessity (povinná položka každého rozpočtu, 998xxx URS família)</t>
         </is>
       </c>
       <c r="N195" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O195" s="26" t="inlineStr">
@@ -21862,7 +21814,11 @@
         </is>
       </c>
       <c r="P195" s="41" t="n"/>
-      <c r="Q195" s="41" t="n"/>
+      <c r="Q195" s="41" t="inlineStr">
+        <is>
+          <t>ANCHOR_CHECKLIST_PM01</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="20" t="n">
@@ -21870,41 +21826,41 @@
       </c>
       <c r="B196" s="8" t="inlineStr">
         <is>
-          <t>VRN — Přesun hmot</t>
+          <t>VRN — Revize</t>
         </is>
       </c>
       <c r="C196" s="8" t="inlineStr">
         <is>
-          <t>Přesun hmot pro budovu</t>
+          <t>Revize hydrantu vnějšího</t>
         </is>
       </c>
       <c r="D196" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>030161000</t>
         </is>
       </c>
       <c r="E196" s="8" t="inlineStr">
         <is>
-          <t>Přesun hmot pro budovu — vnitrostaveništní vertikální + horizontální doprava materiálu a hmot (rekonstrukce vícepodlažní RD + nástavba 3.NP)</t>
+          <t>Revize vnějšího hydrantu pro požární zabezpečení (DN min. 80, vzdálenost 100 m dle TZ PBŘ) — periodická kontrola</t>
         </is>
       </c>
       <c r="F196" s="20" t="inlineStr">
         <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G196" s="22" t="n">
-        <v>0</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G196" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H196" s="10" t="n"/>
       <c r="I196" s="10" t="n"/>
       <c r="J196" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>revize_specialista</t>
         </is>
       </c>
       <c r="K196" s="24" t="n">
-        <v>0.6</v>
+        <v>0.85</v>
       </c>
       <c r="L196" s="20" t="inlineStr">
         <is>
@@ -21913,7 +21869,7 @@
       </c>
       <c r="M196" s="8" t="inlineStr">
         <is>
-          <t>anchor checklist PM01 — technical necessity (povinná položka každého rozpočtu, 998xxx URS família)</t>
+          <t>TZ PBŘ dům — vnější odběrné místo požární vody, revize před kolaudací</t>
         </is>
       </c>
       <c r="N196" s="20" t="inlineStr">
@@ -21927,11 +21883,7 @@
         </is>
       </c>
       <c r="P196" s="41" t="n"/>
-      <c r="Q196" s="41" t="inlineStr">
-        <is>
-          <t>ANCHOR_CHECKLIST_PM01</t>
-        </is>
-      </c>
+      <c r="Q196" s="41" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="20" t="n">
@@ -21939,41 +21891,41 @@
       </c>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t>VRN — Revize</t>
+          <t>VRN — Zařízení staveniště</t>
         </is>
       </c>
       <c r="C197" s="8" t="inlineStr">
         <is>
-          <t>Revize hydrantu vnějšího</t>
+          <t>Buňky kancelář + sociální</t>
         </is>
       </c>
       <c r="D197" s="20" t="inlineStr">
         <is>
-          <t>030161000</t>
+          <t>030011000</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
         <is>
-          <t>Revize vnějšího hydrantu pro požární zabezpečení (DN min. 80, vzdálenost 100 m dle TZ PBŘ) — periodická kontrola</t>
+          <t>Zařízení staveniště — buňka kancelář + sociální buňka (WC + šatna), pronájem ~8 měsíců</t>
         </is>
       </c>
       <c r="F197" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>kpl-měs</t>
         </is>
       </c>
       <c r="G197" s="23" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H197" s="10" t="n"/>
       <c r="I197" s="10" t="n"/>
       <c r="J197" s="8" t="inlineStr">
         <is>
-          <t>revize_specialista</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K197" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L197" s="20" t="inlineStr">
         <is>
@@ -21982,12 +21934,12 @@
       </c>
       <c r="M197" s="8" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — vnější odběrné místo požární vody, revize před kolaudací</t>
+          <t>TZ B m.1.m realizace 2026-2027 + standard staveniště RD městská zástavba</t>
         </is>
       </c>
       <c r="N197" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O197" s="26" t="inlineStr">
@@ -22009,22 +21961,22 @@
       </c>
       <c r="C198" s="8" t="inlineStr">
         <is>
-          <t>Buňky kancelář + sociální</t>
+          <t>Mobilní WC</t>
         </is>
       </c>
       <c r="D198" s="20" t="inlineStr">
         <is>
-          <t>030011000</t>
+          <t>030013000</t>
         </is>
       </c>
       <c r="E198" s="8" t="inlineStr">
         <is>
-          <t>Zařízení staveniště — buňka kancelář + sociální buňka (WC + šatna), pronájem ~8 měsíců</t>
+          <t>Mobilní chemické WC TOI TOI pro pracovníky — pronájem ~8 měsíců</t>
         </is>
       </c>
       <c r="F198" s="20" t="inlineStr">
         <is>
-          <t>kpl-měs</t>
+          <t>ks-měs</t>
         </is>
       </c>
       <c r="G198" s="23" t="n">
@@ -22047,7 +21999,7 @@
       </c>
       <c r="M198" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.1.m realizace 2026-2027 + standard staveniště RD městská zástavba</t>
+          <t>BOZP — mobilní WC povinné pro stavbu RD</t>
         </is>
       </c>
       <c r="N198" s="20" t="inlineStr">
@@ -22074,26 +22026,26 @@
       </c>
       <c r="C199" s="8" t="inlineStr">
         <is>
-          <t>Mobilní WC</t>
+          <t>El. odběr + vodovodní odběr stavby</t>
         </is>
       </c>
       <c r="D199" s="20" t="inlineStr">
         <is>
-          <t>030013000</t>
+          <t>031011000</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
         <is>
-          <t>Mobilní chemické WC TOI TOI pro pracovníky — pronájem ~8 měsíců</t>
+          <t>El. odběr stavby (zřízení staveništního rozvaděče + měřič) + vodovodní odběr (zřízení staveništní přípojky + vodoměr) — ~8 měsíců</t>
         </is>
       </c>
       <c r="F199" s="20" t="inlineStr">
         <is>
-          <t>ks-měs</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G199" s="23" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H199" s="10" t="n"/>
       <c r="I199" s="10" t="n"/>
@@ -22112,7 +22064,7 @@
       </c>
       <c r="M199" s="8" t="inlineStr">
         <is>
-          <t>BOZP — mobilní WC povinné pro stavbu RD</t>
+          <t>Standard staveniště — el. + voda zřízení a odběr po dobu stavby</t>
         </is>
       </c>
       <c r="N199" s="20" t="inlineStr">
@@ -22139,17 +22091,17 @@
       </c>
       <c r="C200" s="8" t="inlineStr">
         <is>
-          <t>El. odběr + vodovodní odběr stavby</t>
+          <t>Voda staveniště</t>
         </is>
       </c>
       <c r="D200" s="20" t="inlineStr">
         <is>
-          <t>031011000</t>
+          <t>012103101</t>
         </is>
       </c>
       <c r="E200" s="8" t="inlineStr">
         <is>
-          <t>El. odběr stavby (zřízení staveništního rozvaděče + měřič) + vodovodní odběr (zřízení staveništní přípojky + vodoměr) — ~8 měsíců</t>
+          <t>Voda staveniště — napojení na stávající vodovodní přípojku, dočasné rozvody na staveništi (mísení malt, čištění, soc. zázemí), paušál pro dobu výstavby ~18 měs.</t>
         </is>
       </c>
       <c r="F200" s="20" t="inlineStr">
@@ -22168,7 +22120,7 @@
         </is>
       </c>
       <c r="K200" s="24" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L200" s="20" t="inlineStr">
         <is>
@@ -22177,12 +22129,12 @@
       </c>
       <c r="M200" s="8" t="inlineStr">
         <is>
-          <t>Standard staveniště — el. + voda zřízení a odběr po dobu stavby</t>
+          <t>TZ B Souhrnná m.5 — 'Stávající vodovodní přípojka z veřejného vodovodu'</t>
         </is>
       </c>
       <c r="N200" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O200" s="26" t="inlineStr">
@@ -22191,7 +22143,11 @@
         </is>
       </c>
       <c r="P200" s="41" t="n"/>
-      <c r="Q200" s="41" t="n"/>
+      <c r="Q200" s="41" t="inlineStr">
+        <is>
+          <t>GAP_003</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="20" t="n">
@@ -22199,27 +22155,27 @@
       </c>
       <c r="B201" s="8" t="inlineStr">
         <is>
-          <t>VRN — Zařízení staveniště</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="C201" s="8" t="inlineStr">
         <is>
-          <t>Voda staveniště</t>
+          <t>Hlavní vypínač TOTAL STOP + požární značení</t>
         </is>
       </c>
       <c r="D201" s="20" t="inlineStr">
         <is>
-          <t>012103101</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
         <is>
-          <t>Voda staveniště — napojení na stávající vodovodní přípojku, dočasné rozvody na staveništi (mísení malt, čištění, soc. zázemí), paušál pro dobu výstavby ~18 měs.</t>
+          <t>Hlavní vypínač elektrické energie TOTAL STOP + požární značení rozvodného zařízení a uzávěrů (voda/elektro)</t>
         </is>
       </c>
       <c r="F201" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>soubor</t>
         </is>
       </c>
       <c r="G201" s="23" t="n">
@@ -22229,11 +22185,11 @@
       <c r="I201" s="10" t="n"/>
       <c r="J201" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>elektrikar</t>
         </is>
       </c>
       <c r="K201" s="24" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="L201" s="20" t="inlineStr">
         <is>
@@ -22242,7 +22198,7 @@
       </c>
       <c r="M201" s="8" t="inlineStr">
         <is>
-          <t>TZ B Souhrnná m.5 — 'Stávající vodovodní přípojka z veřejného vodovodu'</t>
+          <t>PBŘ D.3 §16.05/16.06</t>
         </is>
       </c>
       <c r="N201" s="20" t="inlineStr">
@@ -22255,10 +22211,10 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P201" s="41" t="n"/>
+      <c r="P201" s="41" t="inlineStr"/>
       <c r="Q201" s="41" t="inlineStr">
         <is>
-          <t>GAP_003</t>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -22268,12 +22224,12 @@
       </c>
       <c r="B202" s="8" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>M-24 VZT</t>
         </is>
       </c>
       <c r="C202" s="8" t="inlineStr">
         <is>
-          <t>Hlavní vypínač TOTAL STOP + požární značení</t>
+          <t>Lokální odtah digestoří kuchyní</t>
         </is>
       </c>
       <c r="D202" s="20" t="inlineStr">
@@ -22283,26 +22239,26 @@
       </c>
       <c r="E202" s="8" t="inlineStr">
         <is>
-          <t>Hlavní vypínač elektrické energie TOTAL STOP + požární značení rozvodného zařízení a uzávěrů (voda/elektro)</t>
+          <t>Lokální odtah digestoří kuchyní (1.NP + 3.NP) — dodávka + montáž digestoře + prostup fasádou/střechou + zpětná klapka</t>
         </is>
       </c>
       <c r="F202" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G202" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H202" s="10" t="n"/>
       <c r="I202" s="10" t="n"/>
       <c r="J202" s="8" t="inlineStr">
         <is>
-          <t>elektrikar</t>
+          <t>vzduchotechnik</t>
         </is>
       </c>
       <c r="K202" s="24" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="L202" s="20" t="inlineStr">
         <is>
@@ -22311,7 +22267,7 @@
       </c>
       <c r="M202" s="8" t="inlineStr">
         <is>
-          <t>PBŘ D.3 §16.05/16.06</t>
+          <t>B zpráva — VZT: obytné místnosti větrání okny, kuchyně lokální odtah digestoří</t>
         </is>
       </c>
       <c r="N202" s="20" t="inlineStr">
@@ -22331,78 +22287,9 @@
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="20" t="n">
-        <v>202</v>
-      </c>
-      <c r="B203" s="8" t="inlineStr">
-        <is>
-          <t>M-24 VZT</t>
-        </is>
-      </c>
-      <c r="C203" s="8" t="inlineStr">
-        <is>
-          <t>Lokální odtah digestoří kuchyní</t>
-        </is>
-      </c>
-      <c r="D203" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E203" s="8" t="inlineStr">
-        <is>
-          <t>Lokální odtah digestoří kuchyní (1.NP + 3.NP) — dodávka + montáž digestoře + prostup fasádou/střechou + zpětná klapka</t>
-        </is>
-      </c>
-      <c r="F203" s="20" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G203" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H203" s="10" t="n"/>
-      <c r="I203" s="10" t="n"/>
-      <c r="J203" s="8" t="inlineStr">
-        <is>
-          <t>vzduchotechnik</t>
-        </is>
-      </c>
-      <c r="K203" s="24" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L203" s="20" t="inlineStr">
-        <is>
-          <t>needs_production_lookup</t>
-        </is>
-      </c>
-      <c r="M203" s="8" t="inlineStr">
-        <is>
-          <t>B zpráva — VZT: obytné místnosti větrání okny, kuchyně lokální odtah digestoří</t>
-        </is>
-      </c>
-      <c r="N203" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O203" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
-        </is>
-      </c>
-      <c r="P203" s="41" t="inlineStr"/>
-      <c r="Q203" s="41" t="inlineStr">
-        <is>
-          <t>DODATEK_PBR_GAPS_2026-06-01</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O203"/>
-  <conditionalFormatting sqref="K2:K203">
+  <autoFilter ref="A1:O202"/>
+  <conditionalFormatting sqref="K2:K202">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0" stopIfTrue="1">
       <formula>0.70</formula>
     </cfRule>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2_final.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2_final.xlsx
@@ -21,9 +21,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Var_A_Agregovany_Dum'!$A$1:$G$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Var_A_Agregovany_Sklad'!$A$1:$G$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$133</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$202</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Var_F_URS_Verification_Trail'!$A$1:$H$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1009,11 +1009,11 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>HSV položkově (117 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 130 řádků.</t>
+          <t>HSV položkově (119 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 132 řádků.</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D24" s="10" t="n"/>
       <c r="E24" s="10" t="n"/>
@@ -1027,11 +1027,11 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Plný detail (201 dum + 31 sklad = 232 položek). Cílový rozsah pro produkční pricing.</t>
+          <t>Plný detail (201 dum + 33 sklad = 234 položek). Cílový rozsah pro produkční pricing.</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D25" s="10" t="n"/>
       <c r="E25" s="10" t="n"/>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>232 (201 dum + 31 sklad)</t>
+          <t>234 (201 dum + 33 sklad)</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>HSV 117 | M 2 | PSV 56 | TZB 34 | VRN 23</t>
+          <t>HSV 119 | M 2 | PSV 56 | TZB 34 | VRN 23</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>0.99: 17 | 0.95: 32 | 0.90: 34 | 0.85: 41 | 0.80: 21 | 0.75: 71 | 0.70: 4 | 0.60: 3 | 0.50: 4 | 0.00: 5</t>
+          <t>0.99: 17 | 0.95: 32 | 0.90: 34 | 0.85: 41 | 0.80: 21 | 0.75: 71 | 0.70: 4 | 0.60: 3 | 0.50: 6 | 0.00: 5</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>8 WebSearch verified (3.4 %) ✓ | 5 wrong leaf flagged (2.2 %) ⚠ | 155 needs_production_lookup (66.8 %)</t>
+          <t>8 WebSearch verified (3.4 %) ✓ | 5 wrong leaf flagged (2.1 %) ⚠ | 157 needs_production_lookup (67.1 %)</t>
         </is>
       </c>
     </row>
@@ -1182,8 +1182,8 @@
       <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Rozpočet generován STAVAGENT pipelinem z DSP dokumentace s DPS-grade DXF metadaty.
-232 položek celkem (201 dum + 31 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
-Confidence distribution: 17×0.99 · 32×0.95 · 34×0.90 · 41×0.85 · 21×0.80 · 71×0.75 · 4×0.70 · 3×0.60 · 4×0.50 · 5×0.00.
+234 položek celkem (201 dum + 33 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
+Confidence distribution: 17×0.99 · 32×0.95 · 34×0.90 · 41×0.85 · 21×0.80 · 71×0.75 · 4×0.70 · 3×0.60 · 6×0.50 · 5×0.00.
 25 položek vzniklo per-room expansion ze 9 aggregate parents (každá expanded položka tagged _expansion_origin).
 9 položek recalculated s exact external perimeter 38.70 m (DXF km_R_návrh_tlustá 2 closed polygon) vs prior fallback 41.0 m.
 Skladby vrstev (Sheet 8 Var_E) pochází POUZE z TZ explicit text + DXF cross-validation HATCH patterns. ŽÁDNÉ generic 'standardní RD' assumption — kde TZ silent, explicit fallback flag s ČSN default.
@@ -1255,7 +1255,7 @@
     <row r="55">
       <c r="A55" s="45" t="inlineStr">
         <is>
-          <t>• Total items: 232 (201 dům + 31 sklad) — vč. CEV +3 (komín/zídky/drenáž), anchor-gap +2 (přesun hmot/lešení), terasa-area fix + venkovní schody na terénu. 69 items s realizuje_skladbu.</t>
+          <t>• Total items: 234 (201 dům + 33 sklad) — vč. CEV +3 (komín/zídky/drenáž), anchor-gap +2 (přesun hmot/lešení), terasa-area fix + venkovní schody na terénu. 71 items s realizuje_skladbu.</t>
         </is>
       </c>
     </row>
@@ -3056,11 +3056,11 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>H-BLOK opěrná stěna; Tvarovky ZB obvod skladu; Výztuž ZB tvarovek</t>
+          <t>H-BLOK opěrná stěna; Tvarovky ZB obvod skladu; Výztuž ZB tvarovek; Hydroizolace + protiradon stěn pod terénem (S03a+S04); … (+1 dalších)</t>
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E4" s="10" t="n"/>
       <c r="F4" s="10" t="n"/>
@@ -3207,7 +3207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J131"/>
+  <dimension ref="A1:J133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="F14" s="22" t="n">
-        <v>3.2</v>
+        <v>2.64</v>
       </c>
       <c r="G14" s="10" t="n"/>
       <c r="H14" s="10" t="n"/>
@@ -4539,7 +4539,7 @@
         </is>
       </c>
       <c r="F33" s="22" t="n">
-        <v>2.12</v>
+        <v>1.76</v>
       </c>
       <c r="G33" s="10" t="n"/>
       <c r="H33" s="10" t="n"/>
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="F59" s="22" t="n">
-        <v>33.9</v>
+        <v>36.74</v>
       </c>
       <c r="G59" s="10" t="n"/>
       <c r="H59" s="10" t="n"/>
@@ -7731,7 +7731,7 @@
         </is>
       </c>
       <c r="F113" s="22" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G113" s="10" t="n"/>
       <c r="H113" s="10" t="n"/>
@@ -7771,7 +7771,7 @@
         </is>
       </c>
       <c r="F114" s="22" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G114" s="10" t="n"/>
       <c r="H114" s="10" t="n"/>
@@ -7811,7 +7811,7 @@
         </is>
       </c>
       <c r="F115" s="22" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G115" s="10" t="n"/>
       <c r="H115" s="10" t="n"/>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="F117" s="22" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G117" s="10" t="n"/>
       <c r="H117" s="10" t="n"/>
@@ -7953,34 +7953,34 @@
           <t>260217_sklad</t>
         </is>
       </c>
-      <c r="C119" s="21" t="inlineStr">
-        <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+      <c r="C119" s="8" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 2 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána</t>
+          <t>Hydroizolace + protiradon stěn pod terénem (S03a+S04) — Hydroizolace + protiradonová ochrana obvodových stěn (S03a) + opěrné stěny (S04) pod úrovní terénu — asfaltová penetrace + 2× HI a protiradonový pás z modif. asfaltu 2×4 mm</t>
         </is>
       </c>
       <c r="E119" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F119" s="9" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F119" s="22" t="n">
+        <v>33</v>
       </c>
       <c r="G119" s="10" t="n"/>
       <c r="H119" s="10" t="n"/>
       <c r="I119" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="J119" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -7993,34 +7993,34 @@
           <t>260217_sklad</t>
         </is>
       </c>
-      <c r="C120" s="21" t="inlineStr">
-        <is>
-          <t>PSV-77 — Podlahy</t>
+      <c r="C120" s="8" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
+          <t>Drenáž nopová folie stěn pod terénem (S03a+S04) — Drenážní vrstva — nopová folie tl. 20 mm na obvodové stěny (S03a) + opěrnou stěnu (S04) pod úrovní terénu</t>
         </is>
       </c>
       <c r="E120" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F120" s="9" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F120" s="22" t="n">
+        <v>33</v>
       </c>
       <c r="G120" s="10" t="n"/>
       <c r="H120" s="10" t="n"/>
       <c r="I120" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="J120" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="C121" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
+          <t>[agregát] 2 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána</t>
         </is>
       </c>
       <c r="E121" s="20" t="inlineStr">
@@ -8070,17 +8070,17 @@
       </c>
       <c r="B122" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C122" s="21" t="inlineStr">
         <is>
-          <t>M-21 — Elektroinstalace silnoproudá</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
+          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
         </is>
       </c>
       <c r="E122" s="20" t="inlineStr">
@@ -8110,17 +8110,17 @@
       </c>
       <c r="B123" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C123" s="21" t="inlineStr">
         <is>
-          <t>M-24</t>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
+          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E123" s="20" t="inlineStr">
@@ -8155,12 +8155,12 @@
       </c>
       <c r="C124" s="21" t="inlineStr">
         <is>
-          <t>PSV-71 — Izolace HI + TI</t>
+          <t>M-21 — Elektroinstalace silnoproudá</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
+          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E124" s="20" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="C125" s="21" t="inlineStr">
         <is>
-          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
+          <t>M-24</t>
         </is>
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
+          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
         </is>
       </c>
       <c r="E125" s="20" t="inlineStr">
@@ -8235,12 +8235,12 @@
       </c>
       <c r="C126" s="21" t="inlineStr">
         <is>
-          <t>PSV-73 — Vytápění + komín</t>
+          <t>PSV-71 — Izolace HI + TI</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
+          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E126" s="20" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="C127" s="21" t="inlineStr">
         <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
         </is>
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
+          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
         </is>
       </c>
       <c r="E127" s="20" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="C128" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>PSV-73 — Vytápění + komín</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
+          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E128" s="20" t="inlineStr">
@@ -8355,12 +8355,12 @@
       </c>
       <c r="C129" s="21" t="inlineStr">
         <is>
-          <t>PSV-78 — Povrchové úpravy</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
+          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
         </is>
       </c>
       <c r="E129" s="20" t="inlineStr">
@@ -8395,12 +8395,12 @@
       </c>
       <c r="C130" s="21" t="inlineStr">
         <is>
-          <t>PSV-95 — Detekce požární</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
         </is>
       </c>
       <c r="E130" s="20" t="inlineStr">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="C131" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>PSV-78 — Povrchové úpravy</t>
         </is>
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
+          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
         </is>
       </c>
       <c r="E131" s="20" t="inlineStr">
@@ -8464,8 +8464,88 @@
         </is>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" s="20" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C132" s="21" t="inlineStr">
+        <is>
+          <t>PSV-95 — Detekce požární</t>
+        </is>
+      </c>
+      <c r="D132" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+        </is>
+      </c>
+      <c r="E132" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F132" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" s="10" t="n"/>
+      <c r="H132" s="10" t="n"/>
+      <c r="I132" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J132" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="20" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C133" s="21" t="inlineStr">
+        <is>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
+        </is>
+      </c>
+      <c r="D133" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
+        </is>
+      </c>
+      <c r="E133" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F133" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" s="10" t="n"/>
+      <c r="H133" s="10" t="n"/>
+      <c r="I133" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J133" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J131"/>
+  <autoFilter ref="A1:J133"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14525,7 +14605,7 @@
         </is>
       </c>
       <c r="G87" s="22" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H87" s="10" t="n"/>
       <c r="I87" s="10" t="n"/>
@@ -14564,7 +14644,7 @@
       </c>
       <c r="Q87" s="41" t="inlineStr">
         <is>
-          <t>SKLADBY_GAPS_2026-06-01</t>
+          <t>W2_SOKL_23to16_RADOVKA_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -14598,7 +14678,7 @@
         </is>
       </c>
       <c r="G88" s="22" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H88" s="10" t="n"/>
       <c r="I88" s="10" t="n"/>
@@ -14637,7 +14717,7 @@
       </c>
       <c r="Q88" s="41" t="inlineStr">
         <is>
-          <t>SKLADBY_GAPS_2026-06-01</t>
+          <t>W2_SOKL_23to16_RADOVKA_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -14671,7 +14751,7 @@
         </is>
       </c>
       <c r="G89" s="22" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H89" s="10" t="n"/>
       <c r="I89" s="10" t="n"/>
@@ -14710,7 +14790,7 @@
       </c>
       <c r="Q89" s="41" t="inlineStr">
         <is>
-          <t>SKLADBY_GAPS_2026-06-01</t>
+          <t>W2_SOKL_23to16_RADOVKA_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -14744,7 +14824,7 @@
         </is>
       </c>
       <c r="G90" s="22" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H90" s="10" t="n"/>
       <c r="I90" s="10" t="n"/>
@@ -14783,7 +14863,7 @@
       </c>
       <c r="Q90" s="41" t="inlineStr">
         <is>
-          <t>SKLADBY_GAPS_2026-06-01</t>
+          <t>W2_SOKL_23to16_RADOVKA_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -22307,12 +22387,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R32"/>
+  <dimension ref="A1:R34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
@@ -22716,7 +22796,7 @@
         </is>
       </c>
       <c r="G6" s="22" t="n">
-        <v>3.2</v>
+        <v>2.64</v>
       </c>
       <c r="H6" s="10" t="n"/>
       <c r="I6" s="10" t="n"/>
@@ -22753,7 +22833,11 @@
           <t>S01_sklad</t>
         </is>
       </c>
-      <c r="Q6" s="41" t="n"/>
+      <c r="Q6" s="41" t="inlineStr">
+        <is>
+          <t>W1_PODLAHA_17.6_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="n">
@@ -23117,7 +23201,7 @@
         </is>
       </c>
       <c r="G12" s="22" t="n">
-        <v>2.12</v>
+        <v>1.76</v>
       </c>
       <c r="H12" s="10" t="n"/>
       <c r="I12" s="10" t="n"/>
@@ -23156,7 +23240,7 @@
       </c>
       <c r="Q12" s="41" t="inlineStr">
         <is>
-          <t>URS_PHASE5B_CROSS_DISCIPLINE_OK</t>
+          <t>W1_PODLAHA_17.6_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -23446,41 +23530,41 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stropnice skladu</t>
+          <t>Hydroizolace + protiradon stěn pod terénem (S03a+S04)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
         <is>
-          <t>762341110</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
+          <t>Hydroizolace + protiradonová ochrana obvodových stěn (S03a) + opěrné stěny (S04) pod úrovní terénu — asfaltová penetrace + 2× HI a protiradonový pás z modif. asfaltu 2×4 mm</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G17" s="22" t="n">
-        <v>33.9</v>
+        <v>33</v>
       </c>
       <c r="H17" s="10" t="n"/>
       <c r="I17" s="10" t="n"/>
       <c r="J17" s="8" t="inlineStr">
         <is>
-          <t>krov_tesarsky_kompletni</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K17" s="24" t="n">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="L17" s="20" t="inlineStr">
         <is>
@@ -23489,7 +23573,7 @@
       </c>
       <c r="M17" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + DXF DIMENSION</t>
+          <t>skladba S03a+S04 řez D.1.1.03/04 + legenda materiálu</t>
         </is>
       </c>
       <c r="N17" s="20" t="inlineStr">
@@ -23504,10 +23588,14 @@
       </c>
       <c r="P17" s="41" t="inlineStr">
         <is>
-          <t>S02_sklad</t>
-        </is>
-      </c>
-      <c r="Q17" s="41" t="n"/>
+          <t>S03a, S04</t>
+        </is>
+      </c>
+      <c r="Q17" s="41" t="inlineStr">
+        <is>
+          <t>SKLAD_WALL_HI_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n">
@@ -23515,22 +23603,22 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Prkenný záklop stropu skladu</t>
+          <t>Drenáž nopová folie stěn pod terénem (S03a+S04)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>762331110</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
+          <t>Drenážní vrstva — nopová folie tl. 20 mm na obvodové stěny (S03a) + opěrnou stěnu (S04) pod úrovní terénu</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -23539,17 +23627,17 @@
         </is>
       </c>
       <c r="G18" s="22" t="n">
-        <v>21.209</v>
+        <v>33</v>
       </c>
       <c r="H18" s="10" t="n"/>
       <c r="I18" s="10" t="n"/>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>krov_tesarsky_kompletni</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K18" s="24" t="n">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="L18" s="20" t="inlineStr">
         <is>
@@ -23558,7 +23646,7 @@
       </c>
       <c r="M18" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + DXF</t>
+          <t>skladba S03a+S04 řez D.1.1.03/04</t>
         </is>
       </c>
       <c r="N18" s="20" t="inlineStr">
@@ -23573,10 +23661,14 @@
       </c>
       <c r="P18" s="41" t="inlineStr">
         <is>
-          <t>S02_sklad</t>
-        </is>
-      </c>
-      <c r="Q18" s="41" t="n"/>
+          <t>S03a, S04</t>
+        </is>
+      </c>
+      <c r="Q18" s="41" t="inlineStr">
+        <is>
+          <t>SKLAD_WALL_HI_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="n">
@@ -23589,32 +23681,32 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolační střešní souvrství skladu</t>
+          <t>Dřevěné stropnice skladu</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
         <is>
-          <t>712331101</t>
+          <t>762341110</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
+          <t>Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G19" s="22" t="n">
-        <v>22.26945</v>
+        <v>36.74</v>
       </c>
       <c r="H19" s="10" t="n"/>
       <c r="I19" s="10" t="n"/>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>krov_tesarsky_kompletni</t>
         </is>
       </c>
       <c r="K19" s="24" t="n">
@@ -23627,7 +23719,7 @@
       </c>
       <c r="M19" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 — HI souvrství</t>
+          <t>TZ statika sklad §4 + DXF DIMENSION</t>
         </is>
       </c>
       <c r="N19" s="20" t="inlineStr">
@@ -23645,7 +23737,11 @@
           <t>S02_sklad</t>
         </is>
       </c>
-      <c r="Q19" s="41" t="n"/>
+      <c r="Q19" s="41" t="inlineStr">
+        <is>
+          <t>DS3_STROPNICE_11_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="n">
@@ -23658,36 +23754,36 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>IPE180 parking — sekundární</t>
+          <t>Prkenný záklop stropu skladu</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>411321414</t>
+          <t>762331110</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 7 m × 7 ks</t>
+          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G20" s="22" t="n">
-        <v>921</v>
+        <v>21.209</v>
       </c>
       <c r="H20" s="10" t="n"/>
       <c r="I20" s="10" t="n"/>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>ocel_zamecnik_konstrukce</t>
+          <t>krov_tesarsky_kompletni</t>
         </is>
       </c>
       <c r="K20" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L20" s="20" t="inlineStr">
         <is>
@@ -23696,12 +23792,12 @@
       </c>
       <c r="M20" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §1.4 + DXF LWPOLYLINE 7000 mm + rozteč 1000 mm</t>
+          <t>TZ statika sklad §4 + DXF</t>
         </is>
       </c>
       <c r="N20" s="20" t="inlineStr">
         <is>
-          <t>#18</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O20" s="26" t="inlineStr">
@@ -23727,17 +23823,17 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Pojezdové ocelové pororošty</t>
+          <t>Hydroizolační střešní souvrství skladu</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>411321515</t>
+          <t>712331101</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
+          <t>Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -23746,26 +23842,26 @@
         </is>
       </c>
       <c r="G21" s="22" t="n">
-        <v>44.6</v>
+        <v>22.26945</v>
       </c>
       <c r="H21" s="10" t="n"/>
       <c r="I21" s="10" t="n"/>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>ocel_zamecnik_konstrukce</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K21" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L21" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
+          <t>TZ statika sklad §4 — HI souvrství</t>
         </is>
       </c>
       <c r="N21" s="20" t="inlineStr">
@@ -23783,11 +23879,7 @@
           <t>S02_sklad</t>
         </is>
       </c>
-      <c r="Q21" s="41" t="inlineStr">
-        <is>
-          <t>PHASE_3_5_SKLAD_QTY_DXF_VERIFY; URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+      <c r="Q21" s="41" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="20" t="n">
@@ -23800,17 +23892,17 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Žárový zinek IPE + pororošty</t>
+          <t>IPE180 parking — sekundární</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>783201001</t>
+          <t>411321414</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
+          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 7 m × 7 ks</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -23819,7 +23911,7 @@
         </is>
       </c>
       <c r="G22" s="22" t="n">
-        <v>1551</v>
+        <v>921</v>
       </c>
       <c r="H22" s="10" t="n"/>
       <c r="I22" s="10" t="n"/>
@@ -23829,7 +23921,7 @@
         </is>
       </c>
       <c r="K22" s="24" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L22" s="20" t="inlineStr">
         <is>
@@ -23838,12 +23930,12 @@
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §1.4 + ČSN EN ISO 12944 — žárový zinek pro pojezdové ocel</t>
+          <t>TZ statika sklad §1.4 + DXF LWPOLYLINE 7000 mm + rozteč 1000 mm</t>
         </is>
       </c>
       <c r="N22" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#18</t>
         </is>
       </c>
       <c r="O22" s="26" t="inlineStr">
@@ -23864,22 +23956,22 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + schodiště</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Sklad mezipodesta schodiště prefa</t>
+          <t>Pojezdové ocelové pororošty</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>121301101</t>
+          <t>411321515</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
+          <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -23888,26 +23980,26 @@
         </is>
       </c>
       <c r="G23" s="22" t="n">
-        <v>5.5</v>
+        <v>44.6</v>
       </c>
       <c r="H23" s="10" t="n"/>
       <c r="I23" s="10" t="n"/>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>betonar</t>
+          <t>ocel_zamecnik_konstrukce</t>
         </is>
       </c>
       <c r="K23" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L23" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M23" s="8" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností room 1.02 + DXF dimension 9×179.5×250 mm + Phase 3.5 sklad S-code mapping (S05 sklad schodiště skladba)</t>
+          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
         </is>
       </c>
       <c r="N23" s="20" t="inlineStr">
@@ -23922,12 +24014,12 @@
       </c>
       <c r="P23" s="41" t="inlineStr">
         <is>
-          <t>S05_sklad</t>
+          <t>S02_sklad</t>
         </is>
       </c>
       <c r="Q23" s="41" t="inlineStr">
         <is>
-          <t>PHASE_3_5_SKLAD_MEZIPODESTA_GAP</t>
+          <t>PHASE_3_5_SKLAD_QTY_DXF_VERIFY; URS_PHASE5B_FAMILY_VERIFIED</t>
         </is>
       </c>
     </row>
@@ -23937,39 +24029,41 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + vjezd</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Vjezd Dvořákova — napojení na komunikaci</t>
+          <t>Žárový zinek IPE + pororošty</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>783201001</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťové vody na pozemek (ne na komunikaci)</t>
+          <t>Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G24" s="22" t="n"/>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="n">
+        <v>1551</v>
+      </c>
       <c r="H24" s="10" t="n"/>
       <c r="I24" s="10" t="n"/>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>komunikace</t>
+          <t>ocel_zamecnik_konstrukce</t>
         </is>
       </c>
       <c r="K24" s="24" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L24" s="20" t="inlineStr">
         <is>
@@ -23978,7 +24072,7 @@
       </c>
       <c r="M24" s="8" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01) / DI PČR požadavek</t>
+          <t>TZ statika sklad §1.4 + ČSN EN ISO 12944 — žárový zinek pro pojezdové ocel</t>
         </is>
       </c>
       <c r="N24" s="20" t="inlineStr">
@@ -23991,12 +24085,12 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P24" s="41" t="inlineStr"/>
-      <c r="Q24" s="41" t="inlineStr">
-        <is>
-          <t>DODATEK_PBR_GAPS_2026-06-01</t>
-        </is>
-      </c>
+      <c r="P24" s="41" t="inlineStr">
+        <is>
+          <t>S02_sklad</t>
+        </is>
+      </c>
+      <c r="Q24" s="41" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="20" t="n">
@@ -24004,41 +24098,41 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>HSV-5 Komunikace + schodiště</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 sklad</t>
+          <t>Sklad mezipodesta schodiště prefa</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>121301101</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
+          <t>Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G25" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="n">
+        <v>5.5</v>
       </c>
       <c r="H25" s="10" t="n"/>
       <c r="I25" s="10" t="n"/>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>specialista_RC3_dvere</t>
+          <t>betonar</t>
         </is>
       </c>
       <c r="K25" s="24" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="L25" s="20" t="inlineStr">
         <is>
@@ -24047,7 +24141,7 @@
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §1.4 — RC3 bezpečnostní dveře v ocelové zárubni</t>
+          <t>DXF sklad_DPZ km_tabulka místností room 1.02 + DXF dimension 9×179.5×250 mm + Phase 3.5 sklad S-code mapping (S05 sklad schodiště skladba)</t>
         </is>
       </c>
       <c r="N25" s="20" t="inlineStr">
@@ -24060,8 +24154,16 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P25" s="41" t="n"/>
-      <c r="Q25" s="41" t="n"/>
+      <c r="P25" s="41" t="inlineStr">
+        <is>
+          <t>S05_sklad</t>
+        </is>
+      </c>
+      <c r="Q25" s="41" t="inlineStr">
+        <is>
+          <t>PHASE_3_5_SKLAD_MEZIPODESTA_GAP</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="20" t="n">
@@ -24069,12 +24171,12 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>HSV-5 Komunikace + vjezd</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Vjezdová brána</t>
+          <t>Vjezd Dvořákova — napojení na komunikaci</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -24084,26 +24186,24 @@
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>Vjezdová brána na pozemku investora (ocelová) — dodávka + montáž</t>
+          <t>Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťové vody na pozemek (ne na komunikaci)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G26" s="23" t="n">
-        <v>1</v>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="n"/>
       <c r="H26" s="10" t="n"/>
       <c r="I26" s="10" t="n"/>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>zamecnik</t>
+          <t>komunikace</t>
         </is>
       </c>
       <c r="K26" s="24" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L26" s="20" t="inlineStr">
         <is>
@@ -24112,7 +24212,7 @@
       </c>
       <c r="M26" s="8" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01)</t>
+          <t>Dodatek PD č.1 (E.01) / DI PČR požadavek</t>
         </is>
       </c>
       <c r="N26" s="20" t="inlineStr">
@@ -24138,50 +24238,50 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Betonová dlažba sklad</t>
-        </is>
-      </c>
-      <c r="D27" s="27" t="inlineStr">
-        <is>
-          <t>596??? ?</t>
+          <t>Bezpečnostní dveře RC3 sklad</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>766682111</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Betonová dlažba do pískového lože — povrch podlahy skladu (~21 m²)</t>
+          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G27" s="22" t="n">
-        <v>17.6</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G27" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H27" s="10" t="n"/>
       <c r="I27" s="10" t="n"/>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>podlahar</t>
+          <t>specialista_RC3_dvere</t>
         </is>
       </c>
       <c r="K27" s="24" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="L27" s="20" t="inlineStr">
         <is>
-          <t>wrong_leaf_disambiguation_needed</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M27" s="8" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
+          <t>TZ statika sklad §1.4 — RC3 bezpečnostní dveře v ocelové zárubni</t>
         </is>
       </c>
       <c r="N27" s="20" t="inlineStr">
@@ -24189,21 +24289,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O27" s="28" t="inlineStr">
-        <is>
-          <t>LEAF CHYBNÝ — viz alternatives</t>
-        </is>
-      </c>
-      <c r="P27" s="41" t="inlineStr">
-        <is>
-          <t>S01_sklad</t>
-        </is>
-      </c>
-      <c r="Q27" s="41" t="inlineStr">
-        <is>
-          <t>PHASE_3_5_SKLAD_QTY_DXF_VERIFY</t>
-        </is>
-      </c>
+      <c r="O27" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P27" s="41" t="n"/>
+      <c r="Q27" s="41" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="20" t="n">
@@ -24211,27 +24303,27 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Doprava prefa H-BLOK auto s hyd. rukou</t>
+          <t>Vjezdová brána</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>031032000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
+          <t>Vjezdová brána na pozemku investora (ocelová) — dodávka + montáž</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G28" s="23" t="n">
@@ -24241,11 +24333,11 @@
       <c r="I28" s="10" t="n"/>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t>prefa_bloky_specialista</t>
+          <t>zamecnik</t>
         </is>
       </c>
       <c r="K28" s="24" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="L28" s="20" t="inlineStr">
         <is>
@@ -24254,7 +24346,7 @@
       </c>
       <c r="M28" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + ARS — auto s hyd. rukou pro osazení H-BLOK</t>
+          <t>Dodatek PD č.1 (E.01)</t>
         </is>
       </c>
       <c r="N28" s="20" t="inlineStr">
@@ -24267,8 +24359,12 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P28" s="41" t="n"/>
-      <c r="Q28" s="41" t="n"/>
+      <c r="P28" s="41" t="inlineStr"/>
+      <c r="Q28" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="20" t="n">
@@ -24276,50 +24372,50 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadu sklad</t>
-        </is>
-      </c>
-      <c r="D29" s="20" t="inlineStr">
-        <is>
-          <t>997013211</t>
+          <t>Betonová dlažba sklad</t>
+        </is>
+      </c>
+      <c r="D29" s="27" t="inlineStr">
+        <is>
+          <t>596??? ?</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
+          <t>Betonová dlažba do pískového lože — povrch podlahy skladu (~21 m²)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G29" s="22" t="n">
-        <v>8</v>
+        <v>17.6</v>
       </c>
       <c r="H29" s="10" t="n"/>
       <c r="I29" s="10" t="n"/>
       <c r="J29" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>podlahar</t>
         </is>
       </c>
       <c r="K29" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L29" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>wrong_leaf_disambiguation_needed</t>
         </is>
       </c>
       <c r="M29" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS sklad §3 — kamenné zídky + schodiště odstraneny</t>
+          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
         </is>
       </c>
       <c r="N29" s="20" t="inlineStr">
@@ -24327,13 +24423,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O29" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
-        </is>
-      </c>
-      <c r="P29" s="41" t="n"/>
-      <c r="Q29" s="41" t="n"/>
+      <c r="O29" s="28" t="inlineStr">
+        <is>
+          <t>LEAF CHYBNÝ — viz alternatives</t>
+        </is>
+      </c>
+      <c r="P29" s="41" t="inlineStr">
+        <is>
+          <t>S01_sklad</t>
+        </is>
+      </c>
+      <c r="Q29" s="41" t="inlineStr">
+        <is>
+          <t>PHASE_3_5_SKLAD_QTY_DXF_VERIFY</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="20" t="n">
@@ -24341,22 +24445,22 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Geodetické vytýčení sklad</t>
+          <t>Doprava prefa H-BLOK auto s hyd. rukou</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>031032000</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
+          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -24371,11 +24475,11 @@
       <c r="I30" s="10" t="n"/>
       <c r="J30" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>prefa_bloky_specialista</t>
         </is>
       </c>
       <c r="K30" s="24" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="L30" s="20" t="inlineStr">
         <is>
@@ -24384,7 +24488,7 @@
       </c>
       <c r="M30" s="8" t="inlineStr">
         <is>
-          <t>Standard — geodet vytýčení pro každý nový objekt</t>
+          <t>TZ statika sklad §4 + ARS — auto s hyd. rukou pro osazení H-BLOK</t>
         </is>
       </c>
       <c r="N30" s="20" t="inlineStr">
@@ -24406,41 +24510,41 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet / PČR</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Rozhledové trojúhelníky — vytyčení + kontrola</t>
+          <t>Likvidace odpadu sklad</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40 km/h, Dz=25 m) dle požadavku DI PČR</t>
+          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="G31" s="23" t="n">
-        <v>1</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G31" s="22" t="n">
+        <v>8</v>
       </c>
       <c r="H31" s="10" t="n"/>
       <c r="I31" s="10" t="n"/>
       <c r="J31" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K31" s="24" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="L31" s="20" t="inlineStr">
         <is>
@@ -24449,7 +24553,7 @@
       </c>
       <c r="M31" s="8" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01) / DI PČR</t>
+          <t>TZ ARS sklad §3 — kamenné zídky + schodiště odstraneny</t>
         </is>
       </c>
       <c r="N31" s="20" t="inlineStr">
@@ -24462,12 +24566,8 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P31" s="41" t="inlineStr"/>
-      <c r="Q31" s="41" t="inlineStr">
-        <is>
-          <t>DODATEK_PBR_GAPS_2026-06-01</t>
-        </is>
-      </c>
+      <c r="P31" s="41" t="n"/>
+      <c r="Q31" s="41" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="20" t="n">
@@ -24475,27 +24575,27 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN dům</t>
+          <t>Geodetické vytýčení sklad</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
         <is>
-          <t>030001000</t>
+          <t>030141000</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G32" s="23" t="n">
@@ -24505,11 +24605,11 @@
       <c r="I32" s="10" t="n"/>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>geodet</t>
         </is>
       </c>
       <c r="K32" s="24" t="n">
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="L32" s="20" t="inlineStr">
         <is>
@@ -24518,7 +24618,7 @@
       </c>
       <c r="M32" s="8" t="inlineStr">
         <is>
-          <t>Standard zhotovitel — alokace VRN pro paralelně realizovaný sklad</t>
+          <t>Standard — geodet vytýčení pro každý nový objekt</t>
         </is>
       </c>
       <c r="N32" s="20" t="inlineStr">
@@ -24534,9 +24634,143 @@
       <c r="P32" s="41" t="n"/>
       <c r="Q32" s="41" t="n"/>
     </row>
+    <row r="33">
+      <c r="A33" s="20" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Geodet / PČR</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Rozhledové trojúhelníky — vytyčení + kontrola</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40 km/h, Dz=25 m) dle požadavku DI PČR</t>
+        </is>
+      </c>
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="G33" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="10" t="n"/>
+      <c r="I33" s="10" t="n"/>
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>geodet</t>
+        </is>
+      </c>
+      <c r="K33" s="24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L33" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M33" s="8" t="inlineStr">
+        <is>
+          <t>Dodatek PD č.1 (E.01) / DI PČR</t>
+        </is>
+      </c>
+      <c r="N33" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O33" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P33" s="41" t="inlineStr"/>
+      <c r="Q33" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="20" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Společné</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN dům</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>030001000</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G34" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="10" t="n"/>
+      <c r="I34" s="10" t="n"/>
+      <c r="J34" s="8" t="inlineStr">
+        <is>
+          <t>VRN_management</t>
+        </is>
+      </c>
+      <c r="K34" s="24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L34" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M34" s="8" t="inlineStr">
+        <is>
+          <t>Standard zhotovitel — alokace VRN pro paralelně realizovaný sklad</t>
+        </is>
+      </c>
+      <c r="N34" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O34" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P34" s="41" t="n"/>
+      <c r="Q34" s="41" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O32"/>
-  <conditionalFormatting sqref="K2:K32">
+  <autoFilter ref="A1:O34"/>
+  <conditionalFormatting sqref="K2:K34">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0" stopIfTrue="1">
       <formula>0.70</formula>
     </cfRule>
@@ -26551,7 +26785,7 @@
       </c>
       <c r="E30" s="44" t="inlineStr">
         <is>
-          <t>obvod skladu pod terénem — items: HSV2.001, HSV3.002, HSV3.003</t>
+          <t>obvod skladu pod terénem — items: HSV2.001, HSV3.002, HSV3.003, HSV3.004, HSV3.005</t>
         </is>
       </c>
       <c r="F30" s="44" t="inlineStr">
@@ -26633,12 +26867,12 @@
       </c>
       <c r="E32" s="44" t="inlineStr">
         <is>
-          <t>zadní opěrná stěna prefa Herkul — items: HSV3.001</t>
+          <t>zadní opěrná stěna prefa Herkul — items: HSV3.001, HSV3.004, HSV3.005</t>
         </is>
       </c>
       <c r="F32" s="44" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33.00 m²</t>
         </is>
       </c>
       <c r="G32" s="44" t="inlineStr">

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2_final.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2_final.xlsx
@@ -23588,7 +23588,7 @@
       </c>
       <c r="P17" s="41" t="inlineStr">
         <is>
-          <t>S03a, S04</t>
+          <t>S03a_sklad, S04_sklad</t>
         </is>
       </c>
       <c r="Q17" s="41" t="inlineStr">
@@ -23661,7 +23661,7 @@
       </c>
       <c r="P18" s="41" t="inlineStr">
         <is>
-          <t>S03a, S04</t>
+          <t>S03a_sklad, S04_sklad</t>
         </is>
       </c>
       <c r="Q18" s="41" t="inlineStr">

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2_final.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2_final.xlsx
@@ -23362,7 +23362,7 @@
       </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + ARS — Herkul H-BLOK, montáž auto s hyd. rukou</t>
+          <t>TZ statika sklad §[19] tech. list H-BLOK Standard Herkul a.s. (Obrnice) + řez A-A výška 3000</t>
         </is>
       </c>
       <c r="N14" s="20" t="inlineStr">
@@ -23380,7 +23380,11 @@
           <t>S04_sklad</t>
         </is>
       </c>
-      <c r="Q14" s="41" t="n"/>
+      <c r="Q14" s="41" t="inlineStr">
+        <is>
+          <t>PREFA_HEIGHT3.0_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="n">

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2_final.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2_final.xlsx
@@ -1095,7 +1095,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>0.99: 17 | 0.95: 32 | 0.90: 34 | 0.85: 41 | 0.80: 21 | 0.75: 71 | 0.70: 4 | 0.60: 3 | 0.50: 6 | 0.00: 5</t>
+          <t>0.99: 17 | 0.95: 32 | 0.90: 34 | 0.85: 41 | 0.82: 1 | 0.80: 21 | 0.75: 70 | 0.70: 4 | 0.60: 3 | 0.50: 6 | 0.00: 5</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
         <is>
           <t>Rozpočet generován STAVAGENT pipelinem z DSP dokumentace s DPS-grade DXF metadaty.
 234 položek celkem (201 dum + 33 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
-Confidence distribution: 17×0.99 · 32×0.95 · 34×0.90 · 41×0.85 · 21×0.80 · 71×0.75 · 4×0.70 · 3×0.60 · 6×0.50 · 5×0.00.
+Confidence distribution: 17×0.99 · 32×0.95 · 34×0.90 · 41×0.85 · 1×0.82 · 21×0.80 · 70×0.75 · 4×0.70 · 3×0.60 · 6×0.50 · 5×0.00.
 25 položek vzniklo per-room expansion ze 9 aggregate parents (každá expanded položka tagged _expansion_origin).
 9 položek recalculated s exact external perimeter 38.70 m (DXF km_R_návrh_tlustá 2 closed polygon) vs prior fallback 41.0 m.
 Skladby vrstev (Sheet 8 Var_E) pochází POUZE z TZ explicit text + DXF cross-validation HATCH patterns. ŽÁDNÉ generic 'standardní RD' assumption — kde TZ silent, explicit fallback flag s ČSN default.
@@ -4899,7 +4899,7 @@
         </is>
       </c>
       <c r="F42" s="23" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="G42" s="10" t="n"/>
       <c r="H42" s="10" t="n"/>
@@ -23343,7 +23343,7 @@
         </is>
       </c>
       <c r="G14" s="23" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="H14" s="10" t="n"/>
       <c r="I14" s="10" t="n"/>
@@ -23353,7 +23353,7 @@
         </is>
       </c>
       <c r="K14" s="24" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="L14" s="20" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
       </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §[19] tech. list H-BLOK Standard Herkul a.s. (Obrnice) + řez A-A výška 3000</t>
+          <t>TZ statika sklad §[19] + web: H-BLOK Standard Herkul (Obrnice) líc 1800×600 mm = 1.08 m²/blok; ověřit definitiv z tech. listu dodavatele</t>
         </is>
       </c>
       <c r="N14" s="20" t="inlineStr">
@@ -23382,7 +23382,7 @@
       </c>
       <c r="Q14" s="41" t="inlineStr">
         <is>
-          <t>PREFA_HEIGHT3.0_2026-06-01</t>
+          <t>HBLOK_ROZMERY_2026-06-01</t>
         </is>
       </c>
     </row>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2_final.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2_final.xlsx
@@ -23362,7 +23362,7 @@
       </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §[19] + web: H-BLOK Standard Herkul (Obrnice) líc 1800×600 mm = 1.08 m²/blok; ověřit definitiv z tech. listu dodavatele</t>
+          <t>TZ statika sklad §[19] H-BLOK Standard Herkul (Obrnice). Rozměr bloku NEověřen z tech. listu — odhad 1800×600 mm z web-analogie (BB6 stejný gabarit). Plocha líce 19.05 m² je measured (řez A-A); count 18 ks je estimate závislý na rozměru bloku.</t>
         </is>
       </c>
       <c r="N14" s="20" t="inlineStr">
@@ -23382,7 +23382,7 @@
       </c>
       <c r="Q14" s="41" t="inlineStr">
         <is>
-          <t>HBLOK_ROZMERY_2026-06-01</t>
+          <t>HBLOK_ROZMERY_ESTIMATE_2026-06-01</t>
         </is>
       </c>
     </row>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2_final.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2_final.xlsx
@@ -1095,7 +1095,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>0.99: 17 | 0.95: 32 | 0.90: 34 | 0.85: 41 | 0.80: 21 | 0.75: 71 | 0.70: 4 | 0.60: 3 | 0.50: 6 | 0.00: 5</t>
+          <t>0.99: 17 | 0.95: 32 | 0.90: 34 | 0.85: 41 | 0.82: 1 | 0.80: 21 | 0.75: 70 | 0.70: 4 | 0.60: 3 | 0.50: 6 | 0.00: 5</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
         <is>
           <t>Rozpočet generován STAVAGENT pipelinem z DSP dokumentace s DPS-grade DXF metadaty.
 234 položek celkem (201 dum + 33 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
-Confidence distribution: 17×0.99 · 32×0.95 · 34×0.90 · 41×0.85 · 21×0.80 · 71×0.75 · 4×0.70 · 3×0.60 · 6×0.50 · 5×0.00.
+Confidence distribution: 17×0.99 · 32×0.95 · 34×0.90 · 41×0.85 · 1×0.82 · 21×0.80 · 70×0.75 · 4×0.70 · 3×0.60 · 6×0.50 · 5×0.00.
 25 položek vzniklo per-room expansion ze 9 aggregate parents (každá expanded položka tagged _expansion_origin).
 9 položek recalculated s exact external perimeter 38.70 m (DXF km_R_návrh_tlustá 2 closed polygon) vs prior fallback 41.0 m.
 Skladby vrstev (Sheet 8 Var_E) pochází POUZE z TZ explicit text + DXF cross-validation HATCH patterns. ŽÁDNÉ generic 'standardní RD' assumption — kde TZ silent, explicit fallback flag s ČSN default.
@@ -4899,7 +4899,7 @@
         </is>
       </c>
       <c r="F42" s="23" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="G42" s="10" t="n"/>
       <c r="H42" s="10" t="n"/>
@@ -23343,7 +23343,7 @@
         </is>
       </c>
       <c r="G14" s="23" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="H14" s="10" t="n"/>
       <c r="I14" s="10" t="n"/>
@@ -23353,7 +23353,7 @@
         </is>
       </c>
       <c r="K14" s="24" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="L14" s="20" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
       </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §[19] tech. list H-BLOK Standard Herkul a.s. (Obrnice) + řez A-A výška 3000</t>
+          <t>TZ statika sklad §[19] H-BLOK Standard Herkul (Obrnice). Rozměr bloku NEověřen z tech. listu — odhad 1800×600 mm z web-analogie (BB6 stejný gabarit). Plocha líce 19.05 m² je measured (řez A-A); count 18 ks je estimate závislý na rozměru bloku.</t>
         </is>
       </c>
       <c r="N14" s="20" t="inlineStr">
@@ -23382,7 +23382,7 @@
       </c>
       <c r="Q14" s="41" t="inlineStr">
         <is>
-          <t>PREFA_HEIGHT3.0_2026-06-01</t>
+          <t>HBLOK_ROZMERY_ESTIMATE_2026-06-01</t>
         </is>
       </c>
     </row>
